--- a/Daily Excel/Online Practice Excel.xlsx
+++ b/Daily Excel/Online Practice Excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d58d4d655bee1e81/Desktop/Github/Daily_practice/Daily Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="137" documentId="11_F25DC773A252ABDACC1048BD89DC52D45ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A4577899-D48A-43D9-BA44-7128DFB3DB1D}"/>
+  <xr:revisionPtr revIDLastSave="147" documentId="11_F25DC773A252ABDACC1048BD89DC52D45ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0E23443A-AE84-4B33-A2AA-165C664DDBAA}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="453">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="506">
   <si>
     <t>Double-click on cell A1 in the spreadsheet editor. Replace the placeholder text with:</t>
   </si>
@@ -1515,6 +1515,171 @@
   <si>
     <t>SKU result:</t>
   </si>
+  <si>
+    <t>XLOOKUP with default</t>
+  </si>
+  <si>
+    <t>Unit cost</t>
+  </si>
+  <si>
+    <t>Restock SKU</t>
+  </si>
+  <si>
+    <t>NW-1001</t>
+  </si>
+  <si>
+    <t>Box Cutter</t>
+  </si>
+  <si>
+    <t>Tools</t>
+  </si>
+  <si>
+    <t>NW-1002</t>
+  </si>
+  <si>
+    <t>Packing Tape (48mm)</t>
+  </si>
+  <si>
+    <t>Packaging</t>
+  </si>
+  <si>
+    <t>NW-1008</t>
+  </si>
+  <si>
+    <t>NW-1003</t>
+  </si>
+  <si>
+    <t>Bubble Wrap Roll</t>
+  </si>
+  <si>
+    <t>NW-1004</t>
+  </si>
+  <si>
+    <t>Pallet Wrap</t>
+  </si>
+  <si>
+    <t>NW-1012</t>
+  </si>
+  <si>
+    <t>NW-1005</t>
+  </si>
+  <si>
+    <t>Safety Gloves (L)</t>
+  </si>
+  <si>
+    <t>Safety</t>
+  </si>
+  <si>
+    <t>NW-1006</t>
+  </si>
+  <si>
+    <t>Label Printer Paper</t>
+  </si>
+  <si>
+    <t>NW-9999</t>
+  </si>
+  <si>
+    <t>NW-1007</t>
+  </si>
+  <si>
+    <t>Warehouse Marking Tape</t>
+  </si>
+  <si>
+    <t>You have an item master list in columns A:D (SKU, Product, Category, Unit cost). On the right, there’s a restock list of SKUs in F2:F8.
+In cell G2, use XLOOKUP to return the Product name for the SKU in F2.
+If the SKU isn’t in the item master list, return Discontinued (not an error).
+Fill the formula down through G8.
+Tip: Lock the lookup ranges (with $) so the formula copies down cleanly.</t>
+  </si>
+  <si>
+    <t>In inventory datasets, you’ll often get a list of SKUs that includes old or discontinued items. Instead of returning an error, you can make your lookup return a clean default value.
+XLOOKUP can return a fallback result using its optional if_not_found argument:
+=XLOOKUP(lookup_value, lookup_array, return_array, "if_not_found")</t>
+  </si>
+  <si>
+    <t>XLOOKUP with wildcard search</t>
+  </si>
+  <si>
+    <t>In inventory work, product names are not always entered consistently. Sometimes you only know part of a product name, but you still need to find the matching item quickly.</t>
+  </si>
+  <si>
+    <t>The full XLOOKUP syntax is:</t>
+  </si>
+  <si>
+    <t>=XLOOKUP(lookup_value, lookup_array, return_array, [if_not_found], [match_mode])</t>
+  </si>
+  <si>
+    <t>Unit price</t>
+  </si>
+  <si>
+    <t>PK-101</t>
+  </si>
+  <si>
+    <t>Pallet Wrap Film</t>
+  </si>
+  <si>
+    <t>CL-204</t>
+  </si>
+  <si>
+    <t>Industrial Cleaner Pro</t>
+  </si>
+  <si>
+    <t>Cleaning supplies</t>
+  </si>
+  <si>
+    <t>LB-220</t>
+  </si>
+  <si>
+    <t>Storage Bin Label Set</t>
+  </si>
+  <si>
+    <t>Storage</t>
+  </si>
+  <si>
+    <t>CL-318</t>
+  </si>
+  <si>
+    <t>Heavy-Duty Cleaner Spray</t>
+  </si>
+  <si>
+    <t>SF-402</t>
+  </si>
+  <si>
+    <t>Safety Floor Sign</t>
+  </si>
+  <si>
+    <t>CL-509</t>
+  </si>
+  <si>
+    <t>Citrus Surface Cleaner</t>
+  </si>
+  <si>
+    <t>TB-615</t>
+  </si>
+  <si>
+    <t>Tool Cart Liner</t>
+  </si>
+  <si>
+    <t>Maintenance</t>
+  </si>
+  <si>
+    <t>CW-730</t>
+  </si>
+  <si>
+    <t>Cleaning Wipes Bulk Pack</t>
+  </si>
+  <si>
+    <t>Search term</t>
+  </si>
+  <si>
+    <t>Surface</t>
+  </si>
+  <si>
+    <t>Matching product</t>
+  </si>
+  <si>
+    <t>XLOOKUP can handle wildcard searches when you set the match_mode argument to 2. The asterisk (*) wildcard means "any sequence of characters", so a partial term can match a longer product name that contains that text.</t>
+  </si>
 </sst>
 </file>
 
@@ -1523,7 +1688,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;₹&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1552,21 +1717,8 @@
       <family val="2"/>
       <scheme val="major"/>
     </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1639,6 +1791,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF7ED"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1652,7 +1810,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -1760,10 +1918,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2046,7 +2207,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W427"/>
+  <dimension ref="A1:W464"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="149.88671875" style="1" bestFit="1" customWidth="1"/>
@@ -5829,77 +5990,77 @@
         <v>440</v>
       </c>
     </row>
-    <row r="418" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A418" s="38" t="s">
+    <row r="418" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A418" s="7" t="s">
         <v>202</v>
       </c>
-      <c r="B418" s="38" t="s">
+      <c r="B418" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="C418" s="38" t="s">
+      <c r="C418" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="D418" s="38" t="s">
+      <c r="D418" s="7" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="419" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A419" s="37" t="s">
+    <row r="419" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A419" s="4" t="s">
         <v>442</v>
       </c>
-      <c r="B419" s="37" t="s">
+      <c r="B419" s="4" t="s">
         <v>443</v>
       </c>
-      <c r="C419" s="37" t="s">
+      <c r="C419" s="4" t="s">
         <v>444</v>
       </c>
-      <c r="D419" s="37">
+      <c r="D419" s="4">
         <v>12</v>
       </c>
     </row>
-    <row r="420" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A420" s="37" t="s">
+    <row r="420" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A420" s="4" t="s">
         <v>445</v>
       </c>
-      <c r="B420" s="37" t="s">
+      <c r="B420" s="4" t="s">
         <v>446</v>
       </c>
-      <c r="C420" s="37" t="s">
+      <c r="C420" s="4" t="s">
         <v>447</v>
       </c>
-      <c r="D420" s="37">
+      <c r="D420" s="4">
         <v>18</v>
       </c>
     </row>
-    <row r="421" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A421" s="37" t="s">
+    <row r="421" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A421" s="4" t="s">
         <v>448</v>
       </c>
-      <c r="B421" s="37" t="s">
+      <c r="B421" s="4" t="s">
         <v>449</v>
       </c>
-      <c r="C421" s="37" t="s">
+      <c r="C421" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="D421" s="37">
+      <c r="D421" s="4">
         <v>24</v>
       </c>
     </row>
-    <row r="422" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A422" s="37" t="s">
+    <row r="422" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A422" s="4" t="s">
         <v>450</v>
       </c>
-      <c r="B422" s="37" t="s">
+      <c r="B422" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="C422" s="37" t="s">
+      <c r="C422" s="4" t="s">
         <v>447</v>
       </c>
-      <c r="D422" s="37">
+      <c r="D422" s="4">
         <v>35</v>
       </c>
     </row>
-    <row r="424" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B424" s="1" t="s">
         <v>451</v>
       </c>
@@ -5907,7 +6068,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="425" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B425" s="1" t="s">
         <v>452</v>
       </c>
@@ -5916,10 +6077,408 @@
         <v>SK-200</v>
       </c>
     </row>
-    <row r="427" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C427" s="1" t="str">
         <f ca="1">_xlfn.FORMULATEXT(C425)</f>
         <v>=XLOOKUP(C424,B419:B422,A419:A422,"Not Found")</v>
+      </c>
+    </row>
+    <row r="429" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A429" s="29" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="430" spans="1:7" ht="69" x14ac:dyDescent="0.3">
+      <c r="A430" s="38" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="431" spans="1:7" ht="82.8" x14ac:dyDescent="0.3">
+      <c r="A431" s="38" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="432" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A432" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="B432" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C432" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D432" s="7" t="s">
+        <v>454</v>
+      </c>
+      <c r="E432" s="4"/>
+      <c r="F432" s="7" t="s">
+        <v>455</v>
+      </c>
+      <c r="G432" s="7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="433" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A433" s="4" t="s">
+        <v>456</v>
+      </c>
+      <c r="B433" s="4" t="s">
+        <v>457</v>
+      </c>
+      <c r="C433" s="4" t="s">
+        <v>458</v>
+      </c>
+      <c r="D433" s="4">
+        <v>6.25</v>
+      </c>
+      <c r="E433" s="4"/>
+      <c r="F433" s="37" t="s">
+        <v>456</v>
+      </c>
+      <c r="G433" s="5" t="str">
+        <f>_xlfn.XLOOKUP(F433,$A$433:$A$439,$B$433:$B$439,"Discontinued")</f>
+        <v>Box Cutter</v>
+      </c>
+    </row>
+    <row r="434" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A434" s="4" t="s">
+        <v>459</v>
+      </c>
+      <c r="B434" s="4" t="s">
+        <v>460</v>
+      </c>
+      <c r="C434" s="4" t="s">
+        <v>461</v>
+      </c>
+      <c r="D434" s="4">
+        <v>3.4</v>
+      </c>
+      <c r="E434" s="4"/>
+      <c r="F434" s="37" t="s">
+        <v>462</v>
+      </c>
+      <c r="G434" s="5" t="str">
+        <f>_xlfn.XLOOKUP(F434,$A$433:$A$439,$B$433:$B$439,"Discontinued")</f>
+        <v>Discontinued</v>
+      </c>
+    </row>
+    <row r="435" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A435" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="B435" s="4" t="s">
+        <v>464</v>
+      </c>
+      <c r="C435" s="4" t="s">
+        <v>461</v>
+      </c>
+      <c r="D435" s="4">
+        <v>19.989999999999998</v>
+      </c>
+      <c r="E435" s="4"/>
+      <c r="F435" s="37" t="s">
+        <v>463</v>
+      </c>
+      <c r="G435" s="5" t="str">
+        <f>_xlfn.XLOOKUP(F435,$A$433:$A$439,$B$433:$B$439,"Discontinued")</f>
+        <v>Bubble Wrap Roll</v>
+      </c>
+    </row>
+    <row r="436" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A436" s="4" t="s">
+        <v>465</v>
+      </c>
+      <c r="B436" s="4" t="s">
+        <v>466</v>
+      </c>
+      <c r="C436" s="4" t="s">
+        <v>461</v>
+      </c>
+      <c r="D436" s="4">
+        <v>14.5</v>
+      </c>
+      <c r="E436" s="4"/>
+      <c r="F436" s="37" t="s">
+        <v>467</v>
+      </c>
+      <c r="G436" s="5" t="str">
+        <f>_xlfn.XLOOKUP(F436,$A$433:$A$439,$B$433:$B$439,"Discontinued")</f>
+        <v>Discontinued</v>
+      </c>
+    </row>
+    <row r="437" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A437" s="4" t="s">
+        <v>468</v>
+      </c>
+      <c r="B437" s="4" t="s">
+        <v>469</v>
+      </c>
+      <c r="C437" s="4" t="s">
+        <v>470</v>
+      </c>
+      <c r="D437" s="4">
+        <v>8.75</v>
+      </c>
+      <c r="E437" s="4"/>
+      <c r="F437" s="37" t="s">
+        <v>468</v>
+      </c>
+      <c r="G437" s="5" t="str">
+        <f>_xlfn.XLOOKUP(F437,$A$433:$A$439,$B$433:$B$439,"Discontinued")</f>
+        <v>Safety Gloves (L)</v>
+      </c>
+    </row>
+    <row r="438" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A438" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="B438" s="4" t="s">
+        <v>472</v>
+      </c>
+      <c r="C438" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="D438" s="4">
+        <v>27.5</v>
+      </c>
+      <c r="E438" s="4"/>
+      <c r="F438" s="37" t="s">
+        <v>473</v>
+      </c>
+      <c r="G438" s="5" t="str">
+        <f>_xlfn.XLOOKUP(F438,$A$433:$A$439,$B$433:$B$439,"Discontinued")</f>
+        <v>Discontinued</v>
+      </c>
+    </row>
+    <row r="439" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A439" s="4" t="s">
+        <v>474</v>
+      </c>
+      <c r="B439" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="C439" s="4" t="s">
+        <v>470</v>
+      </c>
+      <c r="D439" s="4">
+        <v>12</v>
+      </c>
+      <c r="E439" s="4"/>
+      <c r="F439" s="37" t="s">
+        <v>474</v>
+      </c>
+      <c r="G439" s="5" t="str">
+        <f>_xlfn.XLOOKUP(F439,$A$433:$A$439,$B$433:$B$439,"Discontinued")</f>
+        <v>Warehouse Marking Tape</v>
+      </c>
+    </row>
+    <row r="441" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A441" s="29" t="s">
+        <v>478</v>
+      </c>
+      <c r="G441" s="1" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(G433)</f>
+        <v>=XLOOKUP(F433,$A$433:$A$439,$B$433:$B$439,"Discontinued")</v>
+      </c>
+    </row>
+    <row r="442" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A442" s="4" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="443" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A443" s="16"/>
+    </row>
+    <row r="444" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A444" s="4" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="445" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A445" s="16"/>
+    </row>
+    <row r="446" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A446" s="4" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="447" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A447" s="16"/>
+    </row>
+    <row r="448" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A448" s="4" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="450" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A450" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="B450" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="C450" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="D450" s="10" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="451" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A451" s="4" t="s">
+        <v>483</v>
+      </c>
+      <c r="B451" s="4" t="s">
+        <v>484</v>
+      </c>
+      <c r="C451" s="4" t="s">
+        <v>461</v>
+      </c>
+      <c r="D451" s="4">
+        <v>22.4</v>
+      </c>
+    </row>
+    <row r="452" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A452" s="4" t="s">
+        <v>485</v>
+      </c>
+      <c r="B452" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="C452" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="D452" s="4">
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="453" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A453" s="4" t="s">
+        <v>488</v>
+      </c>
+      <c r="B453" s="4" t="s">
+        <v>489</v>
+      </c>
+      <c r="C453" s="4" t="s">
+        <v>490</v>
+      </c>
+      <c r="D453" s="4">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="454" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A454" s="4" t="s">
+        <v>491</v>
+      </c>
+      <c r="B454" s="4" t="s">
+        <v>492</v>
+      </c>
+      <c r="C454" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="D454" s="4">
+        <v>9.75</v>
+      </c>
+    </row>
+    <row r="455" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A455" s="4" t="s">
+        <v>493</v>
+      </c>
+      <c r="B455" s="4" t="s">
+        <v>494</v>
+      </c>
+      <c r="C455" s="4" t="s">
+        <v>470</v>
+      </c>
+      <c r="D455" s="4">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="456" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A456" s="4" t="s">
+        <v>495</v>
+      </c>
+      <c r="B456" s="4" t="s">
+        <v>496</v>
+      </c>
+      <c r="C456" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="D456" s="4">
+        <v>12.6</v>
+      </c>
+    </row>
+    <row r="457" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A457" s="4" t="s">
+        <v>497</v>
+      </c>
+      <c r="B457" s="4" t="s">
+        <v>498</v>
+      </c>
+      <c r="C457" s="4" t="s">
+        <v>499</v>
+      </c>
+      <c r="D457" s="4">
+        <v>14.25</v>
+      </c>
+    </row>
+    <row r="458" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A458" s="4" t="s">
+        <v>500</v>
+      </c>
+      <c r="B458" s="4" t="s">
+        <v>501</v>
+      </c>
+      <c r="C458" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="D458" s="4">
+        <v>24.9</v>
+      </c>
+    </row>
+    <row r="459" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A459" s="4"/>
+      <c r="B459" s="4"/>
+      <c r="C459" s="4"/>
+      <c r="D459" s="4"/>
+    </row>
+    <row r="460" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A460" s="14" t="s">
+        <v>502</v>
+      </c>
+      <c r="B460" s="39" t="s">
+        <v>503</v>
+      </c>
+      <c r="C460" s="4"/>
+      <c r="D460" s="4"/>
+    </row>
+    <row r="461" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A461" s="14" t="s">
+        <v>504</v>
+      </c>
+      <c r="B461" s="5" t="str">
+        <f>_xlfn.XLOOKUP("*"&amp;B460&amp;"*",B451:B458,B451:B458,,2)</f>
+        <v>Citrus Surface Cleaner</v>
+      </c>
+      <c r="C461" s="4"/>
+      <c r="D461" s="4"/>
+    </row>
+    <row r="462" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A462" s="14" t="s">
+        <v>482</v>
+      </c>
+      <c r="B462" s="5">
+        <f>_xlfn.XLOOKUP("*"&amp;B460&amp;"*",B451:B458,D451:D458,,2)</f>
+        <v>12.6</v>
+      </c>
+      <c r="C462" s="4"/>
+      <c r="D462" s="4"/>
+    </row>
+    <row r="464" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B464" s="1" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(B461)</f>
+        <v>=XLOOKUP("*"&amp;B460&amp;"*",B451:B458,B451:B458,,2)</v>
       </c>
     </row>
   </sheetData>

--- a/Daily Excel/Online Practice Excel.xlsx
+++ b/Daily Excel/Online Practice Excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d58d4d655bee1e81/Desktop/Github/Daily_practice/Daily Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="187" documentId="11_F25DC773A252ABDACC1048BD89DC52D45ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A7C11D8A-F5B6-4C34-A4B4-B0708F5E3960}"/>
+  <xr:revisionPtr revIDLastSave="188" documentId="11_F25DC773A252ABDACC1048BD89DC52D45ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{28382681-0350-4684-8354-561904C401B9}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="696" uniqueCount="548">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="772" uniqueCount="610">
   <si>
     <t>Double-click on cell A1 in the spreadsheet editor. Replace the placeholder text with:</t>
   </si>
@@ -1814,6 +1814,195 @@
     <t>Fill in the missing manager names for the three pay change requests:
 Enter an INDEX-MATCH formula in C12 that looks up the manager for the employee in B12.
 Copy the formula down through C14.</t>
+  </si>
+  <si>
+    <t>INDEX-MATCH left lookup</t>
+  </si>
+  <si>
+    <t>It's a common sight: exports where the columns aren’t in the order you wish they were. For example, email appears to the left of customer ID, so a basic VLOOKUP can’t return it.</t>
+  </si>
+  <si>
+    <t>INDEX + MATCH solves this cleanly:</t>
+  </si>
+  <si>
+    <t>Fill the missing emails for the campaign tasks:</t>
+  </si>
+  <si>
+    <t>Use exact match in MATCH, and lock the directory ranges so your formula copies correctly.</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Segment</t>
+  </si>
+  <si>
+    <t>alex.garcia@northwind.com</t>
+  </si>
+  <si>
+    <t>C-1042</t>
+  </si>
+  <si>
+    <t>Alex Garcia</t>
+  </si>
+  <si>
+    <t>SMB</t>
+  </si>
+  <si>
+    <t>bianca.chen@northwind.com</t>
+  </si>
+  <si>
+    <t>C-1047</t>
+  </si>
+  <si>
+    <t>Bianca Chen</t>
+  </si>
+  <si>
+    <t>diego.souza@northwind.com</t>
+  </si>
+  <si>
+    <t>C-1050</t>
+  </si>
+  <si>
+    <t>Diego Souza</t>
+  </si>
+  <si>
+    <t>Mid-market</t>
+  </si>
+  <si>
+    <t>emma.johansson@northwind.com</t>
+  </si>
+  <si>
+    <t>C-1055</t>
+  </si>
+  <si>
+    <t>Emma Johansson</t>
+  </si>
+  <si>
+    <t>Enterprise</t>
+  </si>
+  <si>
+    <t>farah.khan@northwind.com</t>
+  </si>
+  <si>
+    <t>C-1059</t>
+  </si>
+  <si>
+    <t>Farah Khan</t>
+  </si>
+  <si>
+    <t>henry.patel@northwind.com</t>
+  </si>
+  <si>
+    <t>C-1061</t>
+  </si>
+  <si>
+    <t>Henry Patel</t>
+  </si>
+  <si>
+    <t>ingrid.larsen@northwind.com</t>
+  </si>
+  <si>
+    <t>C-1068</t>
+  </si>
+  <si>
+    <t>Ingrid Larsen</t>
+  </si>
+  <si>
+    <t>jordan.reed@northwind.com</t>
+  </si>
+  <si>
+    <t>C-1072</t>
+  </si>
+  <si>
+    <t>Jordan Reed</t>
+  </si>
+  <si>
+    <t>Campaign task</t>
+  </si>
+  <si>
+    <t>Email (fill)</t>
+  </si>
+  <si>
+    <t>Note</t>
+  </si>
+  <si>
+    <t>Renewal reminder</t>
+  </si>
+  <si>
+    <t>Email needed for send list</t>
+  </si>
+  <si>
+    <t>Upsell outreach</t>
+  </si>
+  <si>
+    <t>Confirm contact before sending</t>
+  </si>
+  <si>
+    <t>Onboarding check-in</t>
+  </si>
+  <si>
+    <t>Customer asked for follow-up</t>
+  </si>
+  <si>
+    <t>MATCH finds the row number where a customer ID appears</t>
+  </si>
+  <si>
+    <t>INDEX returns the email from that same row</t>
+  </si>
+  <si>
+    <t>You have a customer directory in A1:D9, where Email is in column A and Customer ID is in column B.</t>
+  </si>
+  <si>
+    <t>1. In C12, write an INDEX-MATCH formula that returns the email for the customer ID in B12.</t>
+  </si>
+  <si>
+    <t>2. Copy the formula down through C14.</t>
+  </si>
+  <si>
+    <t>INDEX-MATCH with MATCH in both directions</t>
+  </si>
+  <si>
+    <t>Shipping teams often keep delivery prices in a matrix, with one category listed by row and another by column. A two-way lookup pulls the value where those two labels intersect, which makes this pattern useful for rate cards, schedules, and pricing tables.
+In this exercise, you'll use INDEX with two MATCH functions to return the correct shipping rate. One MATCH should find the row for the selected zone, and the other should find the column for the selected weight bracket.
+A common pattern looks like this:
+=INDEX(data_range, MATCH(row_value, row_labels, 0), MATCH(column_value, column_labels, 0))</t>
+  </si>
+  <si>
+    <t>0-5 kg</t>
+  </si>
+  <si>
+    <t>5-10 kg</t>
+  </si>
+  <si>
+    <t>10-20 kg</t>
+  </si>
+  <si>
+    <t>20+ kg</t>
+  </si>
+  <si>
+    <t>Local</t>
+  </si>
+  <si>
+    <t>Regional</t>
+  </si>
+  <si>
+    <t>National</t>
+  </si>
+  <si>
+    <t>International</t>
+  </si>
+  <si>
+    <t>Express</t>
+  </si>
+  <si>
+    <t>Lookup zone</t>
+  </si>
+  <si>
+    <t>Lookup weight</t>
+  </si>
+  <si>
+    <t>Shipping rate</t>
   </si>
 </sst>
 </file>
@@ -1853,7 +2042,7 @@
       <scheme val="major"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1950,6 +2139,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8F1FF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1963,7 +2158,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -2074,12 +2269,6 @@
     <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -2087,6 +2276,18 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2369,12 +2570,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W504"/>
+  <dimension ref="A1:W552"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="149.88671875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="30.109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="38.21875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="43.33203125" style="1" customWidth="1"/>
     <col min="4" max="4" width="27.33203125" style="1" customWidth="1"/>
     <col min="5" max="5" width="26" style="1" customWidth="1"/>
     <col min="6" max="6" width="24.44140625" style="1" customWidth="1"/>
@@ -4630,13 +4831,13 @@
         <f>_xlfn.XLOOKUP(B235,A227:A233,C227:C233,0)</f>
         <v>Office equipment</v>
       </c>
-      <c r="C236" s="38" t="str">
+      <c r="C236" s="41" t="str">
         <f ca="1">_xlfn.FORMULATEXT(B236)</f>
         <v>=XLOOKUP(B235,A227:A233,C227:C233,0)</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C237" s="38"/>
+      <c r="C237" s="41"/>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A238" s="29" t="s">
@@ -4801,11 +5002,11 @@
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B256" s="39" t="str">
+      <c r="B256" s="42" t="str">
         <f ca="1">_xlfn.FORMULATEXT(C251)</f>
         <v>=XLOOKUP(A251,A$242:A$248,$C$242:$C$248,0)</v>
       </c>
-      <c r="C256" s="39"/>
+      <c r="C256" s="42"/>
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A258" s="29" t="s">
@@ -5696,7 +5897,7 @@
       <c r="A359" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="C359" s="38" t="str">
+      <c r="C359" s="41" t="str">
         <f ca="1">_xlfn.FORMULATEXT(C358)</f>
         <v>=HLOOKUP(B358,A355:E356,2,0)</v>
       </c>
@@ -5704,7 +5905,7 @@
       <c r="E359" s="4"/>
     </row>
     <row r="360" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="C360" s="38"/>
+      <c r="C360" s="41"/>
     </row>
     <row r="362" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A362" s="29" t="s">
@@ -6778,7 +6979,7 @@
       <c r="A475" s="4" t="s">
         <v>516</v>
       </c>
-      <c r="B475" s="40" t="s">
+      <c r="B475" s="38" t="s">
         <v>517</v>
       </c>
       <c r="C475" s="4"/>
@@ -6789,37 +6990,37 @@
       <c r="H475" s="4"/>
     </row>
     <row r="476" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A476" s="41" t="s">
+      <c r="A476" s="39" t="s">
         <v>518</v>
       </c>
       <c r="B476" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(B475,A471:C473,2,0),"Not Found")</f>
         <v>Not Found</v>
       </c>
-      <c r="C476" s="38" t="str">
+      <c r="C476" s="41" t="str">
         <f ca="1">_xlfn.FORMULATEXT(B476)</f>
         <v>=IFNA(VLOOKUP(B475,A471:C473,2,0),"Not Found")</v>
       </c>
-      <c r="D476" s="38"/>
-      <c r="E476" s="38"/>
+      <c r="D476" s="41"/>
+      <c r="E476" s="41"/>
       <c r="F476" s="4"/>
       <c r="G476" s="4"/>
       <c r="H476" s="4"/>
     </row>
     <row r="477" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A477" s="41" t="s">
+      <c r="A477" s="39" t="s">
         <v>519</v>
       </c>
       <c r="B477" s="5" t="str">
         <f>_xlfn.XLOOKUP(B475,A471:A473,B471:B473,"Not Found")</f>
         <v>Not Found</v>
       </c>
-      <c r="C477" s="38" t="str">
+      <c r="C477" s="41" t="str">
         <f ca="1">_xlfn.FORMULATEXT(B477)</f>
         <v>=XLOOKUP(B475,A471:A473,B471:B473,"Not Found")</v>
       </c>
-      <c r="D477" s="38"/>
-      <c r="E477" s="38"/>
+      <c r="D477" s="41"/>
+      <c r="E477" s="41"/>
       <c r="F477" s="4"/>
       <c r="G477" s="4"/>
       <c r="H477" s="4"/>
@@ -7054,7 +7255,7 @@
       <c r="E493" s="4"/>
     </row>
     <row r="494" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A494" s="42" t="s">
+      <c r="A494" s="40" t="s">
         <v>539</v>
       </c>
       <c r="B494" s="4"/>
@@ -7063,13 +7264,13 @@
       <c r="E494" s="4"/>
     </row>
     <row r="495" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A495" s="42" t="s">
+      <c r="A495" s="40" t="s">
         <v>113</v>
       </c>
-      <c r="B495" s="42" t="s">
+      <c r="B495" s="40" t="s">
         <v>540</v>
       </c>
-      <c r="C495" s="42" t="s">
+      <c r="C495" s="40" t="s">
         <v>541</v>
       </c>
       <c r="D495" s="4"/>
@@ -7079,7 +7280,7 @@
       <c r="A496" s="4" t="s">
         <v>530</v>
       </c>
-      <c r="B496" s="42" t="str">
+      <c r="B496" s="40" t="str">
         <f>INDEX(A485:A492,MATCH(A496,B485:B492,0))</f>
         <v>Thomas Nguyen</v>
       </c>
@@ -7093,7 +7294,7 @@
       <c r="A497" s="4" t="s">
         <v>535</v>
       </c>
-      <c r="B497" s="42" t="str">
+      <c r="B497" s="40" t="str">
         <f>INDEX(A485:A492,MATCH(A497,B485:B492,0))</f>
         <v>David Brown</v>
       </c>
@@ -7107,7 +7308,7 @@
       <c r="A498" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="B498" s="42" t="str">
+      <c r="B498" s="40" t="str">
         <f>INDEX(A485:A492,MATCH(A498,B485:B492,0))</f>
         <v>Maria Gomez</v>
       </c>
@@ -7126,11 +7327,11 @@
     </row>
     <row r="500" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A500" s="4"/>
-      <c r="B500" s="38" t="str">
+      <c r="B500" s="41" t="str">
         <f ca="1">_xlfn.FORMULATEXT(B496)</f>
         <v>=INDEX(A485:A492,MATCH(A496,B485:B492,0))</v>
       </c>
-      <c r="C500" s="38"/>
+      <c r="C500" s="41"/>
       <c r="D500" s="4"/>
       <c r="E500" s="4"/>
     </row>
@@ -7142,14 +7343,18 @@
       <c r="E501" s="4"/>
     </row>
     <row r="502" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A502" s="4"/>
+      <c r="A502" s="29" t="s">
+        <v>548</v>
+      </c>
       <c r="B502" s="4"/>
       <c r="C502" s="4"/>
       <c r="D502" s="4"/>
       <c r="E502" s="4"/>
     </row>
     <row r="503" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A503" s="4"/>
+      <c r="A503" s="4" t="s">
+        <v>549</v>
+      </c>
       <c r="B503" s="4"/>
       <c r="C503" s="4"/>
       <c r="D503" s="4"/>
@@ -7162,8 +7367,427 @@
       <c r="D504" s="4"/>
       <c r="E504" s="4"/>
     </row>
+    <row r="505" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A505" s="4" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="506" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A506" s="4"/>
+    </row>
+    <row r="507" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A507" s="4" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="508" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A508" s="4" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="509" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A509" s="4"/>
+    </row>
+    <row r="510" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A510" s="4" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="511" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A511" s="4"/>
+    </row>
+    <row r="512" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A512" s="4" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="513" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A513" s="4"/>
+    </row>
+    <row r="514" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A514" s="4" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="515" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A515" s="4" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="516" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A516" s="4"/>
+    </row>
+    <row r="517" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A517" s="4" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="519" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A519" s="7" t="s">
+        <v>553</v>
+      </c>
+      <c r="B519" s="7" t="s">
+        <v>403</v>
+      </c>
+      <c r="C519" s="7" t="s">
+        <v>404</v>
+      </c>
+      <c r="D519" s="7" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="520" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A520" s="4" t="s">
+        <v>555</v>
+      </c>
+      <c r="B520" s="4" t="s">
+        <v>556</v>
+      </c>
+      <c r="C520" s="4" t="s">
+        <v>557</v>
+      </c>
+      <c r="D520" s="4" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="521" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A521" s="4" t="s">
+        <v>559</v>
+      </c>
+      <c r="B521" s="4" t="s">
+        <v>560</v>
+      </c>
+      <c r="C521" s="4" t="s">
+        <v>561</v>
+      </c>
+      <c r="D521" s="4" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="522" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A522" s="4" t="s">
+        <v>562</v>
+      </c>
+      <c r="B522" s="4" t="s">
+        <v>563</v>
+      </c>
+      <c r="C522" s="4" t="s">
+        <v>564</v>
+      </c>
+      <c r="D522" s="4" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="523" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A523" s="4" t="s">
+        <v>566</v>
+      </c>
+      <c r="B523" s="4" t="s">
+        <v>567</v>
+      </c>
+      <c r="C523" s="4" t="s">
+        <v>568</v>
+      </c>
+      <c r="D523" s="4" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="524" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A524" s="4" t="s">
+        <v>570</v>
+      </c>
+      <c r="B524" s="4" t="s">
+        <v>571</v>
+      </c>
+      <c r="C524" s="4" t="s">
+        <v>572</v>
+      </c>
+      <c r="D524" s="4" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="525" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A525" s="4" t="s">
+        <v>573</v>
+      </c>
+      <c r="B525" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="C525" s="4" t="s">
+        <v>575</v>
+      </c>
+      <c r="D525" s="4" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="526" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A526" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="B526" s="4" t="s">
+        <v>577</v>
+      </c>
+      <c r="C526" s="4" t="s">
+        <v>578</v>
+      </c>
+      <c r="D526" s="4" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="527" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A527" s="4" t="s">
+        <v>579</v>
+      </c>
+      <c r="B527" s="4" t="s">
+        <v>580</v>
+      </c>
+      <c r="C527" s="4" t="s">
+        <v>581</v>
+      </c>
+      <c r="D527" s="4" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="528" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A528" s="4"/>
+      <c r="B528" s="4"/>
+      <c r="C528" s="4"/>
+      <c r="D528" s="4"/>
+    </row>
+    <row r="529" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A529" s="43" t="s">
+        <v>582</v>
+      </c>
+      <c r="B529" s="43" t="s">
+        <v>403</v>
+      </c>
+      <c r="C529" s="43" t="s">
+        <v>583</v>
+      </c>
+      <c r="D529" s="43" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="530" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A530" s="4" t="s">
+        <v>585</v>
+      </c>
+      <c r="B530" s="4" t="s">
+        <v>577</v>
+      </c>
+      <c r="C530" s="5" t="str">
+        <f>INDEX(A520:A527,MATCH(B530,B520:B527,0))</f>
+        <v>ingrid.larsen@northwind.com</v>
+      </c>
+      <c r="D530" s="4" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="531" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A531" s="4" t="s">
+        <v>587</v>
+      </c>
+      <c r="B531" s="4" t="s">
+        <v>560</v>
+      </c>
+      <c r="C531" s="5" t="str">
+        <f t="shared" ref="C531:C532" si="19">INDEX(A521:A528,MATCH(B531,B521:B528,0))</f>
+        <v>bianca.chen@northwind.com</v>
+      </c>
+      <c r="D531" s="4" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="532" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A532" s="4" t="s">
+        <v>589</v>
+      </c>
+      <c r="B532" s="4" t="s">
+        <v>563</v>
+      </c>
+      <c r="C532" s="5" t="str">
+        <f t="shared" si="19"/>
+        <v>diego.souza@northwind.com</v>
+      </c>
+      <c r="D532" s="4" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="533" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="534" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="C534" s="4" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(C530)</f>
+        <v>=INDEX(A520:A527,MATCH(B530,B520:B527,0))</v>
+      </c>
+    </row>
+    <row r="536" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A536" s="29" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="537" spans="1:5" ht="124.2" x14ac:dyDescent="0.3">
+      <c r="A537" s="2" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="539" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A539" s="7" t="s">
+        <v>383</v>
+      </c>
+      <c r="B539" s="7" t="s">
+        <v>598</v>
+      </c>
+      <c r="C539" s="7" t="s">
+        <v>599</v>
+      </c>
+      <c r="D539" s="7" t="s">
+        <v>600</v>
+      </c>
+      <c r="E539" s="7" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="540" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A540" s="4" t="s">
+        <v>602</v>
+      </c>
+      <c r="B540" s="4">
+        <v>5</v>
+      </c>
+      <c r="C540" s="4">
+        <v>7</v>
+      </c>
+      <c r="D540" s="4">
+        <v>10</v>
+      </c>
+      <c r="E540" s="4">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="541" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A541" s="4" t="s">
+        <v>603</v>
+      </c>
+      <c r="B541" s="4">
+        <v>9</v>
+      </c>
+      <c r="C541" s="4">
+        <v>12</v>
+      </c>
+      <c r="D541" s="4">
+        <v>16</v>
+      </c>
+      <c r="E541" s="4">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="542" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A542" s="4" t="s">
+        <v>604</v>
+      </c>
+      <c r="B542" s="4">
+        <v>14</v>
+      </c>
+      <c r="C542" s="4">
+        <v>19</v>
+      </c>
+      <c r="D542" s="4">
+        <v>28</v>
+      </c>
+      <c r="E542" s="4">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="543" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A543" s="4" t="s">
+        <v>605</v>
+      </c>
+      <c r="B543" s="4">
+        <v>24</v>
+      </c>
+      <c r="C543" s="4">
+        <v>33</v>
+      </c>
+      <c r="D543" s="4">
+        <v>48</v>
+      </c>
+      <c r="E543" s="4">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="544" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A544" s="4" t="s">
+        <v>606</v>
+      </c>
+      <c r="B544" s="4">
+        <v>30</v>
+      </c>
+      <c r="C544" s="4">
+        <v>42</v>
+      </c>
+      <c r="D544" s="4">
+        <v>60</v>
+      </c>
+      <c r="E544" s="4">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="545" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A545" s="4"/>
+      <c r="B545" s="4"/>
+      <c r="C545" s="4"/>
+      <c r="D545" s="4"/>
+      <c r="E545" s="4"/>
+    </row>
+    <row r="546" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A546" s="4" t="s">
+        <v>607</v>
+      </c>
+      <c r="B546" s="4" t="s">
+        <v>604</v>
+      </c>
+      <c r="C546" s="4"/>
+      <c r="D546" s="4"/>
+      <c r="E546" s="4"/>
+    </row>
+    <row r="547" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A547" s="4" t="s">
+        <v>608</v>
+      </c>
+      <c r="B547" s="4" t="s">
+        <v>600</v>
+      </c>
+      <c r="C547" s="4"/>
+      <c r="D547" s="4"/>
+      <c r="E547" s="4"/>
+    </row>
+    <row r="548" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A548" s="4" t="s">
+        <v>609</v>
+      </c>
+      <c r="B548" s="5">
+        <f>INDEX(B540:E544,MATCH(B546,A540:A544),MATCH(B547,B539:E539,0))</f>
+        <v>28</v>
+      </c>
+      <c r="C548" s="4"/>
+      <c r="D548" s="4"/>
+      <c r="E548" s="4"/>
+    </row>
+    <row r="550" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B550" s="44" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(B548)</f>
+        <v>=INDEX(B540:E544,MATCH(B546,A540:A544),MATCH(B547,B539:E539,0))</v>
+      </c>
+    </row>
+    <row r="551" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B551" s="44"/>
+    </row>
+    <row r="552" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B552" s="44"/>
+    </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
+    <mergeCell ref="B550:B552"/>
     <mergeCell ref="B500:C500"/>
     <mergeCell ref="C236:C237"/>
     <mergeCell ref="B256:C256"/>

--- a/Daily Excel/Online Practice Excel.xlsx
+++ b/Daily Excel/Online Practice Excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d58d4d655bee1e81/Desktop/Github/Daily_practice/Daily Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="188" documentId="11_F25DC773A252ABDACC1048BD89DC52D45ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{28382681-0350-4684-8354-561904C401B9}"/>
+  <xr:revisionPtr revIDLastSave="208" documentId="11_F25DC773A252ABDACC1048BD89DC52D45ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C186A09D-528D-4353-A5B2-ED0FD621E2BC}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="772" uniqueCount="610">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="651">
   <si>
     <t>Double-click on cell A1 in the spreadsheet editor. Replace the placeholder text with:</t>
   </si>
@@ -2004,6 +2004,144 @@
   <si>
     <t>Shipping rate</t>
   </si>
+  <si>
+    <t>XLOOKUP multiple criteria</t>
+  </si>
+  <si>
+    <t>In real-world scenarios, you often need to look up data based on multiple criteria. While XLOOKUP is typically used for single-criterion lookups, you can nest XLOOKUP functions to handle two-dimensional lookups.
+The key insight is that XLOOKUP's return_array parameter can itself be an XLOOKUP result. This creates a powerful two-way lookup:
+=XLOOKUP(row_lookup, row_range, XLOOKUP(col_lookup, col_headers, data_range))
+The inner XLOOKUP finds the correct column, returning an entire column of data. The outer XLOOKUP then finds the correct row within that column.</t>
+  </si>
+  <si>
+    <t>Your task
+You have a pricing table with products in column A and quarterly prices in columns B through E. The goal is to build a dynamic lookup that returns the price for any product in any quarter.
+In cell H2, enter the product name "Widget D".
+In cell H3, enter the quarter "Q3".
+In cell H5, write a nested XLOOKUP formula that:
+Uses the product in H2 to find the correct row
+Uses the quarter in H3 to find the correct column
+Returns the price at the intersection</t>
+  </si>
+  <si>
+    <t>Find price for:</t>
+  </si>
+  <si>
+    <t>Widget A</t>
+  </si>
+  <si>
+    <t>Widget B</t>
+  </si>
+  <si>
+    <t>Quarter:</t>
+  </si>
+  <si>
+    <t>Widget C</t>
+  </si>
+  <si>
+    <t>Widget D</t>
+  </si>
+  <si>
+    <t>Price:</t>
+  </si>
+  <si>
+    <t>Widget E</t>
+  </si>
+  <si>
+    <t>Widget F</t>
+  </si>
+  <si>
+    <t>Widget G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Product: </t>
+  </si>
+  <si>
+    <t>Return multiple columns</t>
+  </si>
+  <si>
+    <t>In analytical datasets, you rarely look up a single field. More often you need to pull a small “record” (multiple columns) for an ID, and you want it to stay maintainable as the dataset grows.
+Your sheet contains a customer table in A9:E15. The lookup key is Customer ID (column A). The fields you need to return are Name, Email, Phone (columns B–D).</t>
+  </si>
+  <si>
+    <t>Write a single formula in C5 that:
+Uses the Customer ID in B3 as the lookup value
+Returns Name, Email, and Phone as a horizontal array that spills across C5:E5
+Pulls the values from the customer table (do not hardcode any customer details)
+Your solution should keep working if the value in B3 changes to any other valid ID in the table.</t>
+  </si>
+  <si>
+    <t>Customer Lookup</t>
+  </si>
+  <si>
+    <t>Look up a customer ID and return Name, Email, and Phone in one spilled row.</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Phone</t>
+  </si>
+  <si>
+    <t>Keira Lewis</t>
+  </si>
+  <si>
+    <t>keira.lewis@northwind.com</t>
+  </si>
+  <si>
+    <t>(555) 010-1188</t>
+  </si>
+  <si>
+    <t>Customer Table</t>
+  </si>
+  <si>
+    <t>ava.patel@northwind.com</t>
+  </si>
+  <si>
+    <t>(555) 010-0421</t>
+  </si>
+  <si>
+    <t>Standard</t>
+  </si>
+  <si>
+    <t>noah.kim@northwind.com</t>
+  </si>
+  <si>
+    <t>(555) 010-0673</t>
+  </si>
+  <si>
+    <t>Sofia Martinez</t>
+  </si>
+  <si>
+    <t>sofia.martinez@northwind.com</t>
+  </si>
+  <si>
+    <t>(555) 010-0905</t>
+  </si>
+  <si>
+    <t>Premium</t>
+  </si>
+  <si>
+    <t>liam.chen@northwind.com</t>
+  </si>
+  <si>
+    <t>(555) 010-1430</t>
+  </si>
+  <si>
+    <t>Maya Singh</t>
+  </si>
+  <si>
+    <t>maya.singh@northwind.com</t>
+  </si>
+  <si>
+    <t>(555) 010-1762</t>
+  </si>
+  <si>
+    <t>ethan.brooks@northwind.com</t>
+  </si>
+  <si>
+    <t>(555) 010-2014</t>
+  </si>
 </sst>
 </file>
 
@@ -2012,7 +2150,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;₹&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2041,8 +2179,16 @@
       <family val="2"/>
       <scheme val="major"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri Light"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
   </fonts>
-  <fills count="18">
+  <fills count="19">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2145,6 +2291,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -2158,7 +2310,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -2281,14 +2433,29 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2570,7 +2737,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W552"/>
+  <dimension ref="A1:W603"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="149.88671875" style="1" bestFit="1" customWidth="1"/>
@@ -4831,13 +4998,13 @@
         <f>_xlfn.XLOOKUP(B235,A227:A233,C227:C233,0)</f>
         <v>Office equipment</v>
       </c>
-      <c r="C236" s="41" t="str">
+      <c r="C236" s="44" t="str">
         <f ca="1">_xlfn.FORMULATEXT(B236)</f>
         <v>=XLOOKUP(B235,A227:A233,C227:C233,0)</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C237" s="41"/>
+      <c r="C237" s="44"/>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A238" s="29" t="s">
@@ -5002,11 +5169,11 @@
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B256" s="42" t="str">
+      <c r="B256" s="45" t="str">
         <f ca="1">_xlfn.FORMULATEXT(C251)</f>
         <v>=XLOOKUP(A251,A$242:A$248,$C$242:$C$248,0)</v>
       </c>
-      <c r="C256" s="42"/>
+      <c r="C256" s="45"/>
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A258" s="29" t="s">
@@ -5897,7 +6064,7 @@
       <c r="A359" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="C359" s="41" t="str">
+      <c r="C359" s="44" t="str">
         <f ca="1">_xlfn.FORMULATEXT(C358)</f>
         <v>=HLOOKUP(B358,A355:E356,2,0)</v>
       </c>
@@ -5905,7 +6072,7 @@
       <c r="E359" s="4"/>
     </row>
     <row r="360" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="C360" s="41"/>
+      <c r="C360" s="44"/>
     </row>
     <row r="362" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A362" s="29" t="s">
@@ -6997,12 +7164,12 @@
         <f>_xlfn.IFNA(VLOOKUP(B475,A471:C473,2,0),"Not Found")</f>
         <v>Not Found</v>
       </c>
-      <c r="C476" s="41" t="str">
+      <c r="C476" s="44" t="str">
         <f ca="1">_xlfn.FORMULATEXT(B476)</f>
         <v>=IFNA(VLOOKUP(B475,A471:C473,2,0),"Not Found")</v>
       </c>
-      <c r="D476" s="41"/>
-      <c r="E476" s="41"/>
+      <c r="D476" s="44"/>
+      <c r="E476" s="44"/>
       <c r="F476" s="4"/>
       <c r="G476" s="4"/>
       <c r="H476" s="4"/>
@@ -7015,12 +7182,12 @@
         <f>_xlfn.XLOOKUP(B475,A471:A473,B471:B473,"Not Found")</f>
         <v>Not Found</v>
       </c>
-      <c r="C477" s="41" t="str">
+      <c r="C477" s="44" t="str">
         <f ca="1">_xlfn.FORMULATEXT(B477)</f>
         <v>=XLOOKUP(B475,A471:A473,B471:B473,"Not Found")</v>
       </c>
-      <c r="D477" s="41"/>
-      <c r="E477" s="41"/>
+      <c r="D477" s="44"/>
+      <c r="E477" s="44"/>
       <c r="F477" s="4"/>
       <c r="G477" s="4"/>
       <c r="H477" s="4"/>
@@ -7327,11 +7494,11 @@
     </row>
     <row r="500" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A500" s="4"/>
-      <c r="B500" s="41" t="str">
+      <c r="B500" s="44" t="str">
         <f ca="1">_xlfn.FORMULATEXT(B496)</f>
         <v>=INDEX(A485:A492,MATCH(A496,B485:B492,0))</v>
       </c>
-      <c r="C500" s="41"/>
+      <c r="C500" s="44"/>
       <c r="D500" s="4"/>
       <c r="E500" s="4"/>
     </row>
@@ -7555,16 +7722,16 @@
       <c r="D528" s="4"/>
     </row>
     <row r="529" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A529" s="43" t="s">
+      <c r="A529" s="42" t="s">
         <v>582</v>
       </c>
-      <c r="B529" s="43" t="s">
+      <c r="B529" s="42" t="s">
         <v>403</v>
       </c>
-      <c r="C529" s="43" t="s">
+      <c r="C529" s="42" t="s">
         <v>583</v>
       </c>
-      <c r="D529" s="43" t="s">
+      <c r="D529" s="42" t="s">
         <v>584</v>
       </c>
     </row>
@@ -7774,19 +7941,514 @@
       <c r="E548" s="4"/>
     </row>
     <row r="550" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B550" s="44" t="str">
+      <c r="B550" s="43" t="str">
         <f ca="1">_xlfn.FORMULATEXT(B548)</f>
         <v>=INDEX(B540:E544,MATCH(B546,A540:A544),MATCH(B547,B539:E539,0))</v>
       </c>
     </row>
     <row r="551" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B551" s="44"/>
+      <c r="B551" s="43"/>
     </row>
     <row r="552" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B552" s="44"/>
+      <c r="B552" s="43"/>
+    </row>
+    <row r="553" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A553" s="29" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="554" spans="1:5" ht="110.4" x14ac:dyDescent="0.3">
+      <c r="A554" s="2" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="555" spans="1:5" ht="151.80000000000001" x14ac:dyDescent="0.3">
+      <c r="A555" s="2" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="556" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="557" spans="1:5" s="46" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A557" s="46" t="s">
+        <v>46</v>
+      </c>
+      <c r="B557" s="46" t="s">
+        <v>314</v>
+      </c>
+      <c r="C557" s="46" t="s">
+        <v>315</v>
+      </c>
+      <c r="D557" s="46" t="s">
+        <v>316</v>
+      </c>
+      <c r="E557" s="46" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="558" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A558" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="B558" s="2">
+        <v>25.99</v>
+      </c>
+      <c r="C558" s="2">
+        <v>27.49</v>
+      </c>
+      <c r="D558" s="2">
+        <v>26.99</v>
+      </c>
+      <c r="E558" s="2">
+        <v>28.99</v>
+      </c>
+    </row>
+    <row r="559" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A559" s="2" t="s">
+        <v>615</v>
+      </c>
+      <c r="B559" s="2">
+        <v>34.5</v>
+      </c>
+      <c r="C559" s="2">
+        <v>35</v>
+      </c>
+      <c r="D559" s="2">
+        <v>36.25</v>
+      </c>
+      <c r="E559" s="2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="560" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A560" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="B560" s="2">
+        <v>18.75</v>
+      </c>
+      <c r="C560" s="2">
+        <v>19.25</v>
+      </c>
+      <c r="D560" s="2">
+        <v>19</v>
+      </c>
+      <c r="E560" s="2">
+        <v>20.5</v>
+      </c>
+    </row>
+    <row r="561" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A561" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="B561" s="2">
+        <v>42</v>
+      </c>
+      <c r="C561" s="2">
+        <v>43.5</v>
+      </c>
+      <c r="D561" s="2">
+        <v>44</v>
+      </c>
+      <c r="E561" s="2">
+        <v>45.25</v>
+      </c>
+    </row>
+    <row r="562" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A562" s="2" t="s">
+        <v>620</v>
+      </c>
+      <c r="B562" s="2">
+        <v>56.99</v>
+      </c>
+      <c r="C562" s="2">
+        <v>58.49</v>
+      </c>
+      <c r="D562" s="2">
+        <v>59.99</v>
+      </c>
+      <c r="E562" s="2">
+        <v>61.5</v>
+      </c>
+    </row>
+    <row r="563" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A563" s="2" t="s">
+        <v>621</v>
+      </c>
+      <c r="B563" s="2">
+        <v>12.25</v>
+      </c>
+      <c r="C563" s="2">
+        <v>12.75</v>
+      </c>
+      <c r="D563" s="2">
+        <v>13</v>
+      </c>
+      <c r="E563" s="2">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="564" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A564" s="2" t="s">
+        <v>622</v>
+      </c>
+      <c r="B564" s="2">
+        <v>89.99</v>
+      </c>
+      <c r="C564" s="2">
+        <v>92.5</v>
+      </c>
+      <c r="D564" s="2">
+        <v>94</v>
+      </c>
+      <c r="E564" s="2">
+        <v>96.75</v>
+      </c>
+    </row>
+    <row r="565" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="566" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="567" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A567" s="46" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="568" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A568" s="46" t="s">
+        <v>623</v>
+      </c>
+      <c r="B568" s="2" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="569" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A569" s="46" t="s">
+        <v>616</v>
+      </c>
+      <c r="B569" s="2" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="570" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A570" s="46"/>
+    </row>
+    <row r="571" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A571" s="46" t="s">
+        <v>619</v>
+      </c>
+      <c r="B571" s="5" cm="1">
+        <f t="array" ref="B571">_xlfn.XLOOKUP(B568,A558:A564,_xlfn.XLOOKUP(B569,B557:E557,B558:E564))</f>
+        <v>44</v>
+      </c>
+    </row>
+    <row r="572" spans="1:5" s="2" customFormat="1" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B572" s="44" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(B571)</f>
+        <v>=XLOOKUP(B568,A558:A564,XLOOKUP(B569,B557:E557,B558:E564))</v>
+      </c>
+    </row>
+    <row r="573" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B573" s="44"/>
+    </row>
+    <row r="574" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B574" s="44"/>
+    </row>
+    <row r="575" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B575" s="41"/>
+    </row>
+    <row r="576" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A576" s="29" t="s">
+        <v>624</v>
+      </c>
+      <c r="B576" s="47"/>
+    </row>
+    <row r="577" spans="1:7" s="2" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A577" s="2" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="578" spans="1:7" s="2" customFormat="1" ht="82.8" x14ac:dyDescent="0.3">
+      <c r="A578" s="2" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="579" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="580" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A580" s="49" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="581" spans="1:7" s="2" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="B581" s="49" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="582" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A582" s="49" t="s">
+        <v>403</v>
+      </c>
+      <c r="B582" s="48">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="583" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="C583" s="49" t="s">
+        <v>629</v>
+      </c>
+      <c r="D583" s="49" t="s">
+        <v>553</v>
+      </c>
+      <c r="E583" s="49" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="584" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="C584" s="2" t="str" cm="1">
+        <f t="array" ref="C584:E584">_xlfn.XLOOKUP(B582,A588:A594,B588:D594)</f>
+        <v>Keira Lewis</v>
+      </c>
+      <c r="D584" s="2" t="str">
+        <v>keira.lewis@northwind.com</v>
+      </c>
+      <c r="E584" s="2" t="str">
+        <v>(555) 010-1188</v>
+      </c>
+    </row>
+    <row r="585" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="C585" s="2" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(C584)</f>
+        <v>=XLOOKUP(B582,A588:A594,B588:D594)</v>
+      </c>
+    </row>
+    <row r="586" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A586" s="49" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="587" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A587" s="49" t="s">
+        <v>403</v>
+      </c>
+      <c r="B587" s="49" t="s">
+        <v>629</v>
+      </c>
+      <c r="C587" s="49" t="s">
+        <v>553</v>
+      </c>
+      <c r="D587" s="49" t="s">
+        <v>630</v>
+      </c>
+      <c r="E587" s="49" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="588" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A588" s="2">
+        <v>1001</v>
+      </c>
+      <c r="B588" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="C588" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D588" s="2" t="s">
+        <v>636</v>
+      </c>
+      <c r="E588" s="2" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="589" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A589" s="2">
+        <v>1002</v>
+      </c>
+      <c r="B589" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="C589" s="2" t="s">
+        <v>638</v>
+      </c>
+      <c r="D589" s="2" t="s">
+        <v>639</v>
+      </c>
+      <c r="E589" s="2" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="590" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A590" s="2">
+        <v>1003</v>
+      </c>
+      <c r="B590" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="C590" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="D590" s="2" t="s">
+        <v>642</v>
+      </c>
+      <c r="E590" s="2" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="591" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A591" s="2">
+        <v>1004</v>
+      </c>
+      <c r="B591" s="2" t="s">
+        <v>631</v>
+      </c>
+      <c r="C591" s="2" t="s">
+        <v>632</v>
+      </c>
+      <c r="D591" s="2" t="s">
+        <v>633</v>
+      </c>
+      <c r="E591" s="2" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="592" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A592" s="2">
+        <v>1005</v>
+      </c>
+      <c r="B592" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="C592" s="2" t="s">
+        <v>644</v>
+      </c>
+      <c r="D592" s="2" t="s">
+        <v>645</v>
+      </c>
+      <c r="E592" s="2" t="s">
+        <v>637</v>
+      </c>
+      <c r="F592" s="2"/>
+      <c r="G592" s="2"/>
+    </row>
+    <row r="593" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A593" s="2">
+        <v>1006</v>
+      </c>
+      <c r="B593" s="2" t="s">
+        <v>646</v>
+      </c>
+      <c r="C593" s="2" t="s">
+        <v>647</v>
+      </c>
+      <c r="D593" s="2" t="s">
+        <v>648</v>
+      </c>
+      <c r="E593" s="2" t="s">
+        <v>637</v>
+      </c>
+      <c r="F593" s="2"/>
+      <c r="G593" s="2"/>
+    </row>
+    <row r="594" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A594" s="2">
+        <v>1007</v>
+      </c>
+      <c r="B594" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C594" s="2" t="s">
+        <v>649</v>
+      </c>
+      <c r="D594" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="E594" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="F594" s="2"/>
+      <c r="G594" s="2"/>
+    </row>
+    <row r="595" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A595" s="2"/>
+      <c r="B595" s="2"/>
+      <c r="C595" s="2"/>
+      <c r="D595" s="2"/>
+      <c r="E595" s="2"/>
+      <c r="F595" s="2"/>
+      <c r="G595" s="2"/>
+    </row>
+    <row r="596" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A596" s="2"/>
+      <c r="B596" s="2"/>
+      <c r="C596" s="2"/>
+      <c r="D596" s="2"/>
+      <c r="E596" s="2"/>
+      <c r="F596" s="2"/>
+      <c r="G596" s="2"/>
+    </row>
+    <row r="597" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A597" s="2"/>
+      <c r="B597" s="2"/>
+      <c r="C597" s="2"/>
+      <c r="D597" s="2"/>
+      <c r="E597" s="2"/>
+      <c r="F597" s="2"/>
+      <c r="G597" s="2"/>
+    </row>
+    <row r="598" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A598" s="2"/>
+      <c r="B598" s="2"/>
+      <c r="C598" s="2"/>
+      <c r="D598" s="2"/>
+      <c r="E598" s="2"/>
+      <c r="F598" s="2"/>
+      <c r="G598" s="2"/>
+    </row>
+    <row r="599" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A599" s="2"/>
+      <c r="B599" s="2"/>
+      <c r="C599" s="2"/>
+      <c r="D599" s="2"/>
+      <c r="E599" s="2"/>
+      <c r="F599" s="2"/>
+      <c r="G599" s="2"/>
+    </row>
+    <row r="600" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A600" s="2"/>
+      <c r="B600" s="2"/>
+      <c r="C600" s="2"/>
+      <c r="D600" s="2"/>
+      <c r="E600" s="2"/>
+      <c r="F600" s="2"/>
+      <c r="G600" s="2"/>
+    </row>
+    <row r="601" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A601" s="2"/>
+      <c r="B601" s="2"/>
+      <c r="C601" s="2"/>
+      <c r="D601" s="2"/>
+      <c r="E601" s="2"/>
+      <c r="F601" s="2"/>
+      <c r="G601" s="2"/>
+    </row>
+    <row r="602" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A602" s="2"/>
+      <c r="B602" s="2"/>
+      <c r="C602" s="2"/>
+      <c r="D602" s="2"/>
+      <c r="E602" s="2"/>
+      <c r="F602" s="2"/>
+      <c r="G602" s="2"/>
+    </row>
+    <row r="603" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A603" s="2"/>
+      <c r="B603" s="2"/>
+      <c r="C603" s="2"/>
+      <c r="D603" s="2"/>
+      <c r="E603" s="2"/>
+      <c r="F603" s="2"/>
+      <c r="G603" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
+    <mergeCell ref="B572:B574"/>
     <mergeCell ref="B550:B552"/>
     <mergeCell ref="B500:C500"/>
     <mergeCell ref="C236:C237"/>

--- a/Daily Excel/Online Practice Excel.xlsx
+++ b/Daily Excel/Online Practice Excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d58d4d655bee1e81/Desktop/Github/Daily_practice/Daily Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="268" documentId="11_F25DC773A252ABDACC1048BD89DC52D45ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FDCEA1E1-08CA-4924-AE70-36B15105FF76}"/>
+  <xr:revisionPtr revIDLastSave="274" documentId="11_F25DC773A252ABDACC1048BD89DC52D45ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AFC609AE-257E-4F25-85DD-14A22100BFFA}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="966" uniqueCount="747">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="987" uniqueCount="767">
   <si>
     <t>Double-click on cell A1 in the spreadsheet editor. Replace the placeholder text with:</t>
   </si>
@@ -2557,6 +2557,76 @@
   </si>
   <si>
     <t>0–9,999 = 3% | 10,000–24,999 = 5% | 25,000+ = 7%</t>
+  </si>
+  <si>
+    <t>Assign shipping methods with IFS</t>
+  </si>
+  <si>
+    <t>When you need to test multiple conditions and return different results, the IFS function is cleaner and easier to read than nested IF statements.
+The IFS function checks conditions in order and returns the value for the first condition that is TRUE:
+=IFS(condition1, value1, condition2, value2, ...)
+For example: =IFS(A1&lt;10, "Small", A1&lt;50, "Medium", A1&gt;=50, "Large")
+This returns "Small" if A1 is less than 10, "Medium" if less than 50, or "Large" otherwise.
+Important: IFS evaluates conditions from left to right and stops at the first TRUE condition. Order matters. If you check smaller thresholds first, you will get correct results.</t>
+  </si>
+  <si>
+    <t>A warehouse needs to assign shipping methods based on package weight. The shipping rules are shown in columns E and F:
+Up to 1 lb: Letter
+Up to 5 lbs: Standard
+Up to 20 lbs: Ground
+Up to 50 lbs: Freight
+Over 50 lbs: Heavy freight</t>
+  </si>
+  <si>
+    <t>Package ID</t>
+  </si>
+  <si>
+    <t>Weight (lbs)</t>
+  </si>
+  <si>
+    <t>Shipping method</t>
+  </si>
+  <si>
+    <t>Weight limit</t>
+  </si>
+  <si>
+    <t>Method</t>
+  </si>
+  <si>
+    <t>PKG-001</t>
+  </si>
+  <si>
+    <t>Letter</t>
+  </si>
+  <si>
+    <t>PKG-002</t>
+  </si>
+  <si>
+    <t>PKG-003</t>
+  </si>
+  <si>
+    <t>Ground</t>
+  </si>
+  <si>
+    <t>PKG-004</t>
+  </si>
+  <si>
+    <t>Freight</t>
+  </si>
+  <si>
+    <t>PKG-005</t>
+  </si>
+  <si>
+    <t>Heavy freight</t>
+  </si>
+  <si>
+    <t>PKG-006</t>
+  </si>
+  <si>
+    <t>PKG-007</t>
+  </si>
+  <si>
+    <t>PKG-008</t>
   </si>
 </sst>
 </file>
@@ -2777,7 +2847,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -2906,12 +2976,6 @@
     <xf numFmtId="0" fontId="1" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -2925,13 +2989,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2948,8 +3006,23 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3231,7 +3304,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W739"/>
+  <dimension ref="A1:W740"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="149.88671875" style="1" bestFit="1" customWidth="1"/>
@@ -3348,32 +3421,32 @@
       <c r="W16" s="26"/>
     </row>
     <row r="18" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A18" s="45">
+      <c r="A18" s="48">
         <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A19" s="45">
+      <c r="A19" s="48">
         <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A20" s="45">
+      <c r="A20" s="48">
         <v>35</v>
       </c>
     </row>
     <row r="21" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A21" s="45">
+      <c r="A21" s="48">
         <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A22" s="45">
+      <c r="A22" s="48">
         <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A23" s="45"/>
+      <c r="A23" s="48"/>
     </row>
     <row r="24" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A24" s="4">
@@ -3423,7 +3496,7 @@
       </c>
     </row>
     <row r="28" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A28" s="45" t="s">
+      <c r="A28" s="48" t="s">
         <v>11</v>
       </c>
       <c r="B28" s="7">
@@ -3438,7 +3511,7 @@
       </c>
     </row>
     <row r="29" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A29" s="45" t="s">
+      <c r="A29" s="48" t="s">
         <v>12</v>
       </c>
       <c r="B29" s="7">
@@ -3453,7 +3526,7 @@
       </c>
     </row>
     <row r="30" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A30" s="45" t="s">
+      <c r="A30" s="48" t="s">
         <v>13</v>
       </c>
       <c r="B30" s="7">
@@ -3468,7 +3541,7 @@
       </c>
     </row>
     <row r="31" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A31" s="45" t="s">
+      <c r="A31" s="48" t="s">
         <v>14</v>
       </c>
       <c r="B31" s="7">
@@ -3483,7 +3556,7 @@
       </c>
     </row>
     <row r="32" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A32" s="45" t="s">
+      <c r="A32" s="48" t="s">
         <v>15</v>
       </c>
       <c r="B32" s="7">
@@ -3498,7 +3571,7 @@
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" s="45" t="s">
+      <c r="A33" s="48" t="s">
         <v>16</v>
       </c>
       <c r="B33" s="7">
@@ -3513,7 +3586,7 @@
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A34" s="45"/>
+      <c r="A34" s="48"/>
       <c r="B34" s="7"/>
       <c r="C34" s="7"/>
       <c r="D34" s="8"/>
@@ -3540,7 +3613,7 @@
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A39" s="45" t="s">
+      <c r="A39" s="48" t="s">
         <v>20</v>
       </c>
       <c r="B39" s="10">
@@ -3552,7 +3625,7 @@
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A40" s="45" t="s">
+      <c r="A40" s="48" t="s">
         <v>21</v>
       </c>
       <c r="B40" s="10">
@@ -3564,7 +3637,7 @@
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A41" s="45" t="s">
+      <c r="A41" s="48" t="s">
         <v>22</v>
       </c>
       <c r="B41" s="10">
@@ -3576,7 +3649,7 @@
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A42" s="45" t="s">
+      <c r="A42" s="48" t="s">
         <v>23</v>
       </c>
       <c r="B42" s="10">
@@ -3588,7 +3661,7 @@
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A43" s="45" t="s">
+      <c r="A43" s="48" t="s">
         <v>24</v>
       </c>
       <c r="B43" s="10">
@@ -3600,7 +3673,7 @@
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A44" s="45" t="s">
+      <c r="A44" s="48" t="s">
         <v>25</v>
       </c>
       <c r="B44" s="10">
@@ -3612,10 +3685,10 @@
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A45" s="45" t="s">
+      <c r="A45" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="B45" s="45">
+      <c r="B45" s="48">
         <v>0</v>
       </c>
       <c r="C45" s="12">
@@ -3651,7 +3724,7 @@
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A51" s="45" t="s">
+      <c r="A51" s="48" t="s">
         <v>33</v>
       </c>
       <c r="B51" s="13">
@@ -3667,7 +3740,7 @@
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A52" s="45" t="s">
+      <c r="A52" s="48" t="s">
         <v>34</v>
       </c>
       <c r="B52" s="13">
@@ -3683,7 +3756,7 @@
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A53" s="45" t="s">
+      <c r="A53" s="48" t="s">
         <v>35</v>
       </c>
       <c r="B53" s="13">
@@ -3699,7 +3772,7 @@
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A54" s="45" t="s">
+      <c r="A54" s="48" t="s">
         <v>36</v>
       </c>
       <c r="B54" s="13">
@@ -3715,7 +3788,7 @@
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A55" s="45" t="s">
+      <c r="A55" s="48" t="s">
         <v>37</v>
       </c>
       <c r="B55" s="13">
@@ -3731,7 +3804,7 @@
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A56" s="45" t="s">
+      <c r="A56" s="48" t="s">
         <v>38</v>
       </c>
       <c r="B56" s="13">
@@ -3747,7 +3820,7 @@
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A57" s="45" t="s">
+      <c r="A57" s="48" t="s">
         <v>39</v>
       </c>
       <c r="B57" s="13">
@@ -3763,7 +3836,7 @@
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A58" s="45" t="s">
+      <c r="A58" s="48" t="s">
         <v>40</v>
       </c>
       <c r="B58" s="13">
@@ -3779,7 +3852,7 @@
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A59" s="45" t="s">
+      <c r="A59" s="48" t="s">
         <v>41</v>
       </c>
       <c r="B59" s="13">
@@ -3795,7 +3868,7 @@
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A60" s="45" t="s">
+      <c r="A60" s="48" t="s">
         <v>42</v>
       </c>
       <c r="B60" s="13">
@@ -3811,7 +3884,7 @@
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A61" s="45" t="s">
+      <c r="A61" s="48" t="s">
         <v>43</v>
       </c>
       <c r="B61" s="13">
@@ -3854,98 +3927,98 @@
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A67" s="45" t="s">
+      <c r="A67" s="48" t="s">
         <v>49</v>
       </c>
-      <c r="B67" s="45" t="s">
+      <c r="B67" s="48" t="s">
         <v>50</v>
       </c>
-      <c r="C67" s="45">
+      <c r="C67" s="48">
         <v>48</v>
       </c>
-      <c r="D67" s="45" t="s">
+      <c r="D67" s="48" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A68" s="45" t="s">
+      <c r="A68" s="48" t="s">
         <v>52</v>
       </c>
-      <c r="B68" s="45" t="s">
+      <c r="B68" s="48" t="s">
         <v>53</v>
       </c>
-      <c r="C68" s="45">
+      <c r="C68" s="48">
         <v>15</v>
       </c>
-      <c r="D68" s="45" t="s">
+      <c r="D68" s="48" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A69" s="45" t="s">
+      <c r="A69" s="48" t="s">
         <v>55</v>
       </c>
-      <c r="B69" s="45" t="s">
+      <c r="B69" s="48" t="s">
         <v>56</v>
       </c>
-      <c r="C69" s="45">
+      <c r="C69" s="48">
         <v>22</v>
       </c>
-      <c r="D69" s="45" t="s">
+      <c r="D69" s="48" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A70" s="45" t="s">
+      <c r="A70" s="48" t="s">
         <v>58</v>
       </c>
-      <c r="B70" s="45" t="s">
+      <c r="B70" s="48" t="s">
         <v>56</v>
       </c>
-      <c r="C70" s="45">
+      <c r="C70" s="48">
         <v>10</v>
       </c>
-      <c r="D70" s="45" t="s">
+      <c r="D70" s="48" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A71" s="45" t="s">
+      <c r="A71" s="48" t="s">
         <v>60</v>
       </c>
-      <c r="B71" s="45" t="s">
+      <c r="B71" s="48" t="s">
         <v>61</v>
       </c>
-      <c r="C71" s="45"/>
-      <c r="D71" s="45" t="s">
+      <c r="C71" s="48"/>
+      <c r="D71" s="48" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A72" s="45" t="s">
+      <c r="A72" s="48" t="s">
         <v>63</v>
       </c>
-      <c r="B72" s="45" t="s">
+      <c r="B72" s="48" t="s">
         <v>64</v>
       </c>
-      <c r="C72" s="45">
+      <c r="C72" s="48">
         <v>5</v>
       </c>
-      <c r="D72" s="45" t="s">
+      <c r="D72" s="48" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A73" s="45" t="s">
+      <c r="A73" s="48" t="s">
         <v>66</v>
       </c>
-      <c r="B73" s="45" t="s">
+      <c r="B73" s="48" t="s">
         <v>67</v>
       </c>
-      <c r="C73" s="45">
+      <c r="C73" s="48">
         <v>2</v>
       </c>
-      <c r="D73" s="45" t="s">
+      <c r="D73" s="48" t="s">
         <v>68</v>
       </c>
     </row>
@@ -3984,71 +4057,71 @@
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A79" s="45" t="s">
+      <c r="A79" s="48" t="s">
         <v>75</v>
       </c>
-      <c r="B79" s="45">
+      <c r="B79" s="48">
         <v>18500</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A80" s="45" t="s">
+      <c r="A80" s="48" t="s">
         <v>76</v>
       </c>
-      <c r="B80" s="45">
+      <c r="B80" s="48">
         <v>21250</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A81" s="45" t="s">
+      <c r="A81" s="48" t="s">
         <v>77</v>
       </c>
-      <c r="B81" s="45">
+      <c r="B81" s="48">
         <v>19800</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A82" s="45" t="s">
+      <c r="A82" s="48" t="s">
         <v>78</v>
       </c>
-      <c r="B82" s="45">
+      <c r="B82" s="48">
         <v>25000</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A83" s="45" t="s">
+      <c r="A83" s="48" t="s">
         <v>79</v>
       </c>
-      <c r="B83" s="45">
+      <c r="B83" s="48">
         <v>23750</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A84" s="45" t="s">
+      <c r="A84" s="48" t="s">
         <v>80</v>
       </c>
-      <c r="B84" s="45">
+      <c r="B84" s="48">
         <v>22100</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A85" s="45" t="s">
+      <c r="A85" s="48" t="s">
         <v>81</v>
       </c>
-      <c r="B85" s="45">
+      <c r="B85" s="48">
         <v>26400</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A86" s="45" t="s">
+      <c r="A86" s="48" t="s">
         <v>82</v>
       </c>
-      <c r="B86" s="45">
+      <c r="B86" s="48">
         <v>24300</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A87" s="45" t="s">
+      <c r="A87" s="48" t="s">
         <v>83</v>
       </c>
       <c r="B87" s="4">
@@ -4080,10 +4153,10 @@
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A93" s="45" t="s">
+      <c r="A93" s="48" t="s">
         <v>89</v>
       </c>
-      <c r="B93" s="45" t="s">
+      <c r="B93" s="48" t="s">
         <v>90</v>
       </c>
       <c r="C93" s="14">
@@ -4091,10 +4164,10 @@
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A94" s="45" t="s">
+      <c r="A94" s="48" t="s">
         <v>91</v>
       </c>
-      <c r="B94" s="45" t="s">
+      <c r="B94" s="48" t="s">
         <v>92</v>
       </c>
       <c r="C94" s="14">
@@ -4102,10 +4175,10 @@
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A95" s="45" t="s">
+      <c r="A95" s="48" t="s">
         <v>93</v>
       </c>
-      <c r="B95" s="45" t="s">
+      <c r="B95" s="48" t="s">
         <v>94</v>
       </c>
       <c r="C95" s="14">
@@ -4113,10 +4186,10 @@
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A96" s="45" t="s">
+      <c r="A96" s="48" t="s">
         <v>95</v>
       </c>
-      <c r="B96" s="45" t="s">
+      <c r="B96" s="48" t="s">
         <v>96</v>
       </c>
       <c r="C96" s="14">
@@ -4124,10 +4197,10 @@
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A97" s="45" t="s">
+      <c r="A97" s="48" t="s">
         <v>97</v>
       </c>
-      <c r="B97" s="45" t="s">
+      <c r="B97" s="48" t="s">
         <v>98</v>
       </c>
       <c r="C97" s="14">
@@ -4135,10 +4208,10 @@
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A98" s="45" t="s">
+      <c r="A98" s="48" t="s">
         <v>99</v>
       </c>
-      <c r="B98" s="45" t="s">
+      <c r="B98" s="48" t="s">
         <v>90</v>
       </c>
       <c r="C98" s="14">
@@ -4146,10 +4219,10 @@
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A99" s="45" t="s">
+      <c r="A99" s="48" t="s">
         <v>100</v>
       </c>
-      <c r="B99" s="45"/>
+      <c r="B99" s="48"/>
       <c r="C99" s="8">
         <f>MIN(C93:C98)</f>
         <v>95</v>
@@ -4185,107 +4258,107 @@
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A105" s="45">
+      <c r="A105" s="48">
         <v>1001</v>
       </c>
       <c r="B105" s="16">
         <v>46025</v>
       </c>
-      <c r="C105" s="45" t="s">
+      <c r="C105" s="48" t="s">
         <v>106</v>
       </c>
-      <c r="D105" s="45">
+      <c r="D105" s="48">
         <v>249.99</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A106" s="45">
+      <c r="A106" s="48">
         <v>1002</v>
       </c>
       <c r="B106" s="16">
         <v>46026</v>
       </c>
-      <c r="C106" s="45" t="s">
+      <c r="C106" s="48" t="s">
         <v>107</v>
       </c>
-      <c r="D106" s="45">
+      <c r="D106" s="48">
         <v>39.5</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A107" s="45">
+      <c r="A107" s="48">
         <v>1003</v>
       </c>
       <c r="B107" s="16">
         <v>46027</v>
       </c>
-      <c r="C107" s="45" t="s">
+      <c r="C107" s="48" t="s">
         <v>106</v>
       </c>
-      <c r="D107" s="45">
+      <c r="D107" s="48">
         <v>89</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A108" s="45">
+      <c r="A108" s="48">
         <v>1004</v>
       </c>
       <c r="B108" s="16">
         <v>46027</v>
       </c>
-      <c r="C108" s="45" t="s">
+      <c r="C108" s="48" t="s">
         <v>108</v>
       </c>
-      <c r="D108" s="45">
+      <c r="D108" s="48">
         <v>59.99</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A109" s="45">
+      <c r="A109" s="48">
         <v>1005</v>
       </c>
       <c r="B109" s="16">
         <v>46028</v>
       </c>
-      <c r="C109" s="45" t="s">
+      <c r="C109" s="48" t="s">
         <v>106</v>
       </c>
-      <c r="D109" s="45">
+      <c r="D109" s="48">
         <v>129</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A110" s="45">
+      <c r="A110" s="48">
         <v>1006</v>
       </c>
       <c r="B110" s="16">
         <v>46028</v>
       </c>
-      <c r="C110" s="45" t="s">
+      <c r="C110" s="48" t="s">
         <v>109</v>
       </c>
-      <c r="D110" s="45">
+      <c r="D110" s="48">
         <v>24.99</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A111" s="45">
+      <c r="A111" s="48">
         <v>1007</v>
       </c>
       <c r="B111" s="16">
         <v>46029</v>
       </c>
-      <c r="C111" s="45" t="s">
+      <c r="C111" s="48" t="s">
         <v>107</v>
       </c>
-      <c r="D111" s="45">
+      <c r="D111" s="48">
         <v>75</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A112" s="45"/>
-      <c r="B112" s="45"/>
-      <c r="C112" s="45" t="s">
+      <c r="A112" s="48"/>
+      <c r="B112" s="48"/>
+      <c r="C112" s="48" t="s">
         <v>110</v>
       </c>
       <c r="D112" s="4">
@@ -4314,10 +4387,10 @@
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A117" s="45" t="s">
+      <c r="A117" s="48" t="s">
         <v>115</v>
       </c>
-      <c r="B117" s="45" t="s">
+      <c r="B117" s="48" t="s">
         <v>116</v>
       </c>
       <c r="C117" s="7">
@@ -4325,10 +4398,10 @@
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A118" s="45" t="s">
+      <c r="A118" s="48" t="s">
         <v>117</v>
       </c>
-      <c r="B118" s="45" t="s">
+      <c r="B118" s="48" t="s">
         <v>90</v>
       </c>
       <c r="C118" s="7">
@@ -4336,10 +4409,10 @@
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A119" s="45" t="s">
+      <c r="A119" s="48" t="s">
         <v>118</v>
       </c>
-      <c r="B119" s="45" t="s">
+      <c r="B119" s="48" t="s">
         <v>119</v>
       </c>
       <c r="C119" s="7">
@@ -4347,10 +4420,10 @@
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A120" s="45" t="s">
+      <c r="A120" s="48" t="s">
         <v>120</v>
       </c>
-      <c r="B120" s="45" t="s">
+      <c r="B120" s="48" t="s">
         <v>92</v>
       </c>
       <c r="C120" s="7">
@@ -4358,10 +4431,10 @@
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A121" s="45" t="s">
+      <c r="A121" s="48" t="s">
         <v>121</v>
       </c>
-      <c r="B121" s="45" t="s">
+      <c r="B121" s="48" t="s">
         <v>96</v>
       </c>
       <c r="C121" s="7">
@@ -4369,10 +4442,10 @@
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A122" s="45" t="s">
+      <c r="A122" s="48" t="s">
         <v>122</v>
       </c>
-      <c r="B122" s="45" t="s">
+      <c r="B122" s="48" t="s">
         <v>123</v>
       </c>
       <c r="C122" s="7">
@@ -4380,10 +4453,10 @@
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A123" s="45" t="s">
+      <c r="A123" s="48" t="s">
         <v>124</v>
       </c>
-      <c r="B123" s="45" t="s">
+      <c r="B123" s="48" t="s">
         <v>46</v>
       </c>
       <c r="C123" s="7">
@@ -4391,10 +4464,10 @@
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A124" s="45" t="s">
+      <c r="A124" s="48" t="s">
         <v>125</v>
       </c>
-      <c r="B124" s="45" t="s">
+      <c r="B124" s="48" t="s">
         <v>126</v>
       </c>
       <c r="C124" s="7">
@@ -4402,26 +4475,26 @@
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A125" s="45" t="s">
+      <c r="A125" s="48" t="s">
         <v>127</v>
       </c>
       <c r="B125" s="8">
         <f>MEDIAN(C117:C124)</f>
         <v>60500</v>
       </c>
-      <c r="C125" s="45"/>
+      <c r="C125" s="48"/>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A126" s="45" t="s">
+      <c r="A126" s="48" t="s">
         <v>128</v>
       </c>
-      <c r="B126" s="45" t="s">
+      <c r="B126" s="48" t="s">
         <v>129</v>
       </c>
-      <c r="C126" s="45"/>
+      <c r="C126" s="48"/>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A127" s="45"/>
+      <c r="A127" s="48"/>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A128" s="28" t="s">
@@ -4429,31 +4502,31 @@
       </c>
     </row>
     <row r="129" spans="1:4" ht="179.4" x14ac:dyDescent="0.3">
-      <c r="A129" s="45" t="s">
+      <c r="A129" s="48" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A130" s="45"/>
+      <c r="A130" s="48"/>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A131" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="B131" s="45"/>
-      <c r="C131" s="45"/>
+      <c r="B131" s="48"/>
+      <c r="C131" s="48"/>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A132" s="17">
         <v>8.2500000000000004E-2</v>
       </c>
-      <c r="B132" s="45"/>
-      <c r="C132" s="45"/>
+      <c r="B132" s="48"/>
+      <c r="C132" s="48"/>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A133" s="45"/>
-      <c r="B133" s="45"/>
-      <c r="C133" s="45"/>
+      <c r="A133" s="48"/>
+      <c r="B133" s="48"/>
+      <c r="C133" s="48"/>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A134" s="9" t="s">
@@ -4470,10 +4543,10 @@
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A135" s="45" t="s">
+      <c r="A135" s="48" t="s">
         <v>13</v>
       </c>
-      <c r="B135" s="45">
+      <c r="B135" s="48">
         <v>24.99</v>
       </c>
       <c r="C135" s="4">
@@ -4486,10 +4559,10 @@
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A136" s="45" t="s">
+      <c r="A136" s="48" t="s">
         <v>133</v>
       </c>
-      <c r="B136" s="45">
+      <c r="B136" s="48">
         <v>15.5</v>
       </c>
       <c r="C136" s="4">
@@ -4502,10 +4575,10 @@
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A137" s="45" t="s">
+      <c r="A137" s="48" t="s">
         <v>134</v>
       </c>
-      <c r="B137" s="45">
+      <c r="B137" s="48">
         <v>89</v>
       </c>
       <c r="C137" s="4" t="e">
@@ -4518,10 +4591,10 @@
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A138" s="45" t="s">
+      <c r="A138" s="48" t="s">
         <v>135</v>
       </c>
-      <c r="B138" s="45">
+      <c r="B138" s="48">
         <v>5.25</v>
       </c>
       <c r="C138" s="4" t="e">
@@ -4534,10 +4607,10 @@
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A139" s="45" t="s">
+      <c r="A139" s="48" t="s">
         <v>136</v>
       </c>
-      <c r="B139" s="45">
+      <c r="B139" s="48">
         <v>12.75</v>
       </c>
       <c r="C139" s="4" t="e">
@@ -4550,7 +4623,7 @@
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A140" s="45"/>
+      <c r="A140" s="48"/>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A141" s="27" t="s">
@@ -4558,12 +4631,12 @@
       </c>
     </row>
     <row r="142" spans="1:4" ht="82.8" x14ac:dyDescent="0.3">
-      <c r="A142" s="45" t="s">
+      <c r="A142" s="48" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A143" s="45"/>
+      <c r="A143" s="48"/>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A144" s="9" t="s">
@@ -4577,7 +4650,7 @@
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A145" s="45" t="s">
+      <c r="A145" s="48" t="s">
         <v>119</v>
       </c>
       <c r="B145" s="18">
@@ -4589,7 +4662,7 @@
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A146" s="45" t="s">
+      <c r="A146" s="48" t="s">
         <v>96</v>
       </c>
       <c r="B146" s="18">
@@ -4601,7 +4674,7 @@
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A147" s="45" t="s">
+      <c r="A147" s="48" t="s">
         <v>90</v>
       </c>
       <c r="B147" s="18">
@@ -4613,7 +4686,7 @@
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A148" s="45" t="s">
+      <c r="A148" s="48" t="s">
         <v>143</v>
       </c>
       <c r="B148" s="18">
@@ -4625,7 +4698,7 @@
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A149" s="45" t="s">
+      <c r="A149" s="48" t="s">
         <v>116</v>
       </c>
       <c r="B149" s="18">
@@ -4637,7 +4710,7 @@
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A150" s="45" t="s">
+      <c r="A150" s="48" t="s">
         <v>144</v>
       </c>
       <c r="B150" s="20">
@@ -4647,26 +4720,26 @@
       <c r="C150" s="13"/>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A151" s="45"/>
-      <c r="B151" s="45"/>
+      <c r="A151" s="48"/>
+      <c r="B151" s="48"/>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A152" s="28" t="s">
         <v>145</v>
       </c>
-      <c r="B152" s="45"/>
+      <c r="B152" s="48"/>
     </row>
     <row r="153" spans="1:3" ht="138" x14ac:dyDescent="0.3">
-      <c r="A153" s="45" t="s">
+      <c r="A153" s="48" t="s">
         <v>146</v>
       </c>
-      <c r="B153" s="45"/>
+      <c r="B153" s="48"/>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A154" s="45" t="s">
+      <c r="A154" s="48" t="s">
         <v>147</v>
       </c>
-      <c r="B154" s="45" t="s">
+      <c r="B154" s="48" t="s">
         <v>148</v>
       </c>
       <c r="C154" s="4" t="str">
@@ -4675,10 +4748,10 @@
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A155" s="45" t="s">
+      <c r="A155" s="48" t="s">
         <v>149</v>
       </c>
-      <c r="B155" s="45" t="s">
+      <c r="B155" s="48" t="s">
         <v>150</v>
       </c>
       <c r="C155" s="4" t="str">
@@ -4687,10 +4760,10 @@
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A156" s="45" t="s">
+      <c r="A156" s="48" t="s">
         <v>151</v>
       </c>
-      <c r="B156" s="45" t="s">
+      <c r="B156" s="48" t="s">
         <v>152</v>
       </c>
       <c r="C156" s="4" t="str">
@@ -4699,10 +4772,10 @@
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A157" s="45" t="s">
+      <c r="A157" s="48" t="s">
         <v>153</v>
       </c>
-      <c r="B157" s="45" t="s">
+      <c r="B157" s="48" t="s">
         <v>154</v>
       </c>
       <c r="C157" s="4" t="str">
@@ -4711,10 +4784,10 @@
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A158" s="45" t="s">
+      <c r="A158" s="48" t="s">
         <v>155</v>
       </c>
-      <c r="B158" s="45" t="s">
+      <c r="B158" s="48" t="s">
         <v>156</v>
       </c>
       <c r="C158" s="4" t="str">
@@ -4723,10 +4796,10 @@
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A159" s="45" t="s">
+      <c r="A159" s="48" t="s">
         <v>157</v>
       </c>
-      <c r="B159" s="45" t="s">
+      <c r="B159" s="48" t="s">
         <v>158</v>
       </c>
       <c r="C159" s="4" t="str">
@@ -4735,10 +4808,10 @@
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A160" s="45" t="s">
+      <c r="A160" s="48" t="s">
         <v>159</v>
       </c>
-      <c r="B160" s="45" t="s">
+      <c r="B160" s="48" t="s">
         <v>160</v>
       </c>
       <c r="C160" s="4" t="str">
@@ -4747,10 +4820,10 @@
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A161" s="45" t="s">
+      <c r="A161" s="48" t="s">
         <v>161</v>
       </c>
-      <c r="B161" s="45" t="s">
+      <c r="B161" s="48" t="s">
         <v>162</v>
       </c>
       <c r="C161" s="4" t="str">
@@ -4759,7 +4832,7 @@
       </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A162" s="45"/>
+      <c r="A162" s="48"/>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A163" s="28" t="s">
@@ -4767,23 +4840,23 @@
       </c>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A164" s="45"/>
+      <c r="A164" s="48"/>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A165" s="45" t="s">
+      <c r="A165" s="48" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A166" s="45"/>
+      <c r="A166" s="48"/>
     </row>
     <row r="167" spans="1:4" ht="69" x14ac:dyDescent="0.3">
-      <c r="A167" s="45" t="s">
+      <c r="A167" s="48" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A168" s="45"/>
+      <c r="A168" s="48"/>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A169" s="9" t="s">
@@ -4800,13 +4873,13 @@
       </c>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A170" s="45" t="s">
+      <c r="A170" s="48" t="s">
         <v>168</v>
       </c>
       <c r="B170" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="C170" s="45" t="s">
+      <c r="C170" s="48" t="s">
         <v>170</v>
       </c>
       <c r="D170" s="4" t="s">
@@ -4814,13 +4887,13 @@
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A171" s="45" t="s">
+      <c r="A171" s="48" t="s">
         <v>171</v>
       </c>
       <c r="B171" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="C171" s="45" t="s">
+      <c r="C171" s="48" t="s">
         <v>173</v>
       </c>
       <c r="D171" s="4" t="s">
@@ -4828,13 +4901,13 @@
       </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A172" s="45" t="s">
+      <c r="A172" s="48" t="s">
         <v>174</v>
       </c>
       <c r="B172" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="C172" s="45" t="s">
+      <c r="C172" s="48" t="s">
         <v>176</v>
       </c>
       <c r="D172" s="4" t="s">
@@ -4842,13 +4915,13 @@
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A173" s="45" t="s">
+      <c r="A173" s="48" t="s">
         <v>177</v>
       </c>
       <c r="B173" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="C173" s="45" t="s">
+      <c r="C173" s="48" t="s">
         <v>179</v>
       </c>
       <c r="D173" s="4" t="s">
@@ -4856,13 +4929,13 @@
       </c>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A174" s="45" t="s">
+      <c r="A174" s="48" t="s">
         <v>180</v>
       </c>
       <c r="B174" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="C174" s="45" t="s">
+      <c r="C174" s="48" t="s">
         <v>182</v>
       </c>
       <c r="D174" s="4" t="s">
@@ -4870,13 +4943,13 @@
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A175" s="45" t="s">
+      <c r="A175" s="48" t="s">
         <v>183</v>
       </c>
       <c r="B175" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="C175" s="45" t="s">
+      <c r="C175" s="48" t="s">
         <v>185</v>
       </c>
       <c r="D175" s="4" t="s">
@@ -4884,13 +4957,13 @@
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A176" s="45" t="s">
+      <c r="A176" s="48" t="s">
         <v>186</v>
       </c>
       <c r="B176" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="C176" s="45" t="s">
+      <c r="C176" s="48" t="s">
         <v>188</v>
       </c>
       <c r="D176" s="4" t="s">
@@ -4898,13 +4971,13 @@
       </c>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A177" s="45" t="s">
+      <c r="A177" s="48" t="s">
         <v>189</v>
       </c>
       <c r="B177" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="C177" s="45" t="s">
+      <c r="C177" s="48" t="s">
         <v>191</v>
       </c>
       <c r="D177" s="4" t="s">
@@ -4912,13 +4985,13 @@
       </c>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A178" s="45" t="s">
+      <c r="A178" s="48" t="s">
         <v>192</v>
       </c>
       <c r="B178" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="C178" s="45" t="s">
+      <c r="C178" s="48" t="s">
         <v>194</v>
       </c>
       <c r="D178" s="4" t="s">
@@ -4926,13 +4999,13 @@
       </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A179" s="45" t="s">
+      <c r="A179" s="48" t="s">
         <v>195</v>
       </c>
       <c r="B179" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="C179" s="45" t="s">
+      <c r="C179" s="48" t="s">
         <v>197</v>
       </c>
       <c r="D179" s="4" t="s">
@@ -4958,7 +5031,7 @@
       </c>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A184" s="45" t="s">
+      <c r="A184" s="48" t="s">
         <v>204</v>
       </c>
       <c r="B184" s="21" t="str">
@@ -4967,7 +5040,7 @@
       </c>
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A185" s="45" t="s">
+      <c r="A185" s="48" t="s">
         <v>205</v>
       </c>
       <c r="B185" s="21" t="str">
@@ -4976,7 +5049,7 @@
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A186" s="45" t="s">
+      <c r="A186" s="48" t="s">
         <v>206</v>
       </c>
       <c r="B186" s="21" t="str">
@@ -4985,7 +5058,7 @@
       </c>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A187" s="45" t="s">
+      <c r="A187" s="48" t="s">
         <v>207</v>
       </c>
       <c r="B187" s="21" t="str">
@@ -4994,7 +5067,7 @@
       </c>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A188" s="45" t="s">
+      <c r="A188" s="48" t="s">
         <v>208</v>
       </c>
       <c r="B188" s="21" t="str">
@@ -5003,7 +5076,7 @@
       </c>
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A189" s="45" t="s">
+      <c r="A189" s="48" t="s">
         <v>209</v>
       </c>
       <c r="B189" s="21" t="str">
@@ -5012,7 +5085,7 @@
       </c>
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A190" s="45" t="s">
+      <c r="A190" s="48" t="s">
         <v>210</v>
       </c>
       <c r="B190" s="21" t="str">
@@ -5036,21 +5109,21 @@
       </c>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A195" s="45" t="s">
+      <c r="A195" s="48" t="s">
         <v>219</v>
       </c>
-      <c r="B195" s="45" t="s">
+      <c r="B195" s="48" t="s">
         <v>220</v>
       </c>
-      <c r="C195" s="45" t="s">
+      <c r="C195" s="48" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A196" s="45" t="s">
+      <c r="A196" s="48" t="s">
         <v>222</v>
       </c>
-      <c r="B196" s="45">
+      <c r="B196" s="48">
         <v>96</v>
       </c>
       <c r="C196" s="21" t="str">
@@ -5059,10 +5132,10 @@
       </c>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A197" s="45" t="s">
+      <c r="A197" s="48" t="s">
         <v>223</v>
       </c>
-      <c r="B197" s="45">
+      <c r="B197" s="48">
         <v>43</v>
       </c>
       <c r="C197" s="21" t="str">
@@ -5071,10 +5144,10 @@
       </c>
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A198" s="45" t="s">
+      <c r="A198" s="48" t="s">
         <v>224</v>
       </c>
-      <c r="B198" s="45">
+      <c r="B198" s="48">
         <v>20</v>
       </c>
       <c r="C198" s="21" t="str">
@@ -5083,10 +5156,10 @@
       </c>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A199" s="45" t="s">
+      <c r="A199" s="48" t="s">
         <v>225</v>
       </c>
-      <c r="B199" s="45">
+      <c r="B199" s="48">
         <v>77</v>
       </c>
       <c r="C199" s="21" t="str">
@@ -5095,10 +5168,10 @@
       </c>
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A200" s="45" t="s">
+      <c r="A200" s="48" t="s">
         <v>226</v>
       </c>
-      <c r="B200" s="45">
+      <c r="B200" s="48">
         <v>76</v>
       </c>
       <c r="C200" s="21" t="str">
@@ -5112,23 +5185,23 @@
       </c>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A203" s="45" t="s">
+      <c r="A203" s="48" t="s">
         <v>8</v>
       </c>
-      <c r="B203" s="45"/>
-      <c r="C203" s="45" t="s">
+      <c r="B203" s="48"/>
+      <c r="C203" s="48" t="s">
         <v>228</v>
       </c>
-      <c r="D203" s="45" t="s">
+      <c r="D203" s="48" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A204" s="45">
+      <c r="A204" s="48">
         <v>0</v>
       </c>
-      <c r="B204" s="45"/>
-      <c r="C204" s="45" t="s">
+      <c r="B204" s="48"/>
+      <c r="C204" s="48" t="s">
         <v>230</v>
       </c>
       <c r="D204" s="4" t="str">
@@ -5141,11 +5214,11 @@
       </c>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A205" s="45">
+      <c r="A205" s="48">
         <v>15</v>
       </c>
-      <c r="B205" s="45"/>
-      <c r="C205" s="45" t="s">
+      <c r="B205" s="48"/>
+      <c r="C205" s="48" t="s">
         <v>230</v>
       </c>
       <c r="D205" s="4" t="str">
@@ -5154,11 +5227,11 @@
       </c>
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A206" s="45">
+      <c r="A206" s="48">
         <v>16</v>
       </c>
-      <c r="B206" s="45"/>
-      <c r="C206" s="45" t="s">
+      <c r="B206" s="48"/>
+      <c r="C206" s="48" t="s">
         <v>231</v>
       </c>
       <c r="D206" s="4" t="str">
@@ -5167,11 +5240,11 @@
       </c>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A207" s="45">
+      <c r="A207" s="48">
         <v>29</v>
       </c>
-      <c r="B207" s="45"/>
-      <c r="C207" s="45" t="s">
+      <c r="B207" s="48"/>
+      <c r="C207" s="48" t="s">
         <v>231</v>
       </c>
       <c r="D207" s="4" t="str">
@@ -5180,11 +5253,11 @@
       </c>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A208" s="45">
+      <c r="A208" s="48">
         <v>30</v>
       </c>
-      <c r="B208" s="45"/>
-      <c r="C208" s="45" t="s">
+      <c r="B208" s="48"/>
+      <c r="C208" s="48" t="s">
         <v>230</v>
       </c>
       <c r="D208" s="4" t="str">
@@ -5193,11 +5266,11 @@
       </c>
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A209" s="45">
+      <c r="A209" s="48">
         <v>55</v>
       </c>
-      <c r="B209" s="45"/>
-      <c r="C209" s="45" t="s">
+      <c r="B209" s="48"/>
+      <c r="C209" s="48" t="s">
         <v>230</v>
       </c>
       <c r="D209" s="4" t="str">
@@ -5206,11 +5279,11 @@
       </c>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A210" s="45">
+      <c r="A210" s="48">
         <v>56</v>
       </c>
-      <c r="B210" s="45"/>
-      <c r="C210" s="45" t="s">
+      <c r="B210" s="48"/>
+      <c r="C210" s="48" t="s">
         <v>231</v>
       </c>
       <c r="D210" s="4" t="str">
@@ -5254,10 +5327,10 @@
       </c>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A216" s="45" t="s">
+      <c r="A216" s="48" t="s">
         <v>239</v>
       </c>
-      <c r="B216" s="45" t="s">
+      <c r="B216" s="48" t="s">
         <v>240</v>
       </c>
       <c r="C216" s="16">
@@ -5273,10 +5346,10 @@
       </c>
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A217" s="45" t="s">
+      <c r="A217" s="48" t="s">
         <v>241</v>
       </c>
-      <c r="B217" s="45" t="s">
+      <c r="B217" s="48" t="s">
         <v>242</v>
       </c>
       <c r="C217" s="16">
@@ -5292,10 +5365,10 @@
       </c>
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A218" s="45" t="s">
+      <c r="A218" s="48" t="s">
         <v>243</v>
       </c>
-      <c r="B218" s="45" t="s">
+      <c r="B218" s="48" t="s">
         <v>244</v>
       </c>
       <c r="C218" s="16">
@@ -5311,10 +5384,10 @@
       </c>
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A219" s="45" t="s">
+      <c r="A219" s="48" t="s">
         <v>245</v>
       </c>
-      <c r="B219" s="45" t="s">
+      <c r="B219" s="48" t="s">
         <v>246</v>
       </c>
       <c r="C219" s="16">
@@ -5330,10 +5403,10 @@
       </c>
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A220" s="45" t="s">
+      <c r="A220" s="48" t="s">
         <v>247</v>
       </c>
-      <c r="B220" s="45" t="s">
+      <c r="B220" s="48" t="s">
         <v>248</v>
       </c>
       <c r="C220" s="16">
@@ -5349,10 +5422,10 @@
       </c>
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A221" s="45" t="s">
+      <c r="A221" s="48" t="s">
         <v>249</v>
       </c>
-      <c r="B221" s="45" t="s">
+      <c r="B221" s="48" t="s">
         <v>250</v>
       </c>
       <c r="C221" s="16">
@@ -5394,95 +5467,95 @@
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A227" s="45" t="s">
+      <c r="A227" s="48" t="s">
         <v>257</v>
       </c>
-      <c r="B227" s="45" t="s">
+      <c r="B227" s="48" t="s">
         <v>258</v>
       </c>
-      <c r="C227" s="45" t="s">
+      <c r="C227" s="48" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A228" s="45" t="s">
+      <c r="A228" s="48" t="s">
         <v>259</v>
       </c>
-      <c r="B228" s="45" t="s">
+      <c r="B228" s="48" t="s">
         <v>260</v>
       </c>
-      <c r="C228" s="45" t="s">
+      <c r="C228" s="48" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A229" s="45" t="s">
+      <c r="A229" s="48" t="s">
         <v>261</v>
       </c>
-      <c r="B229" s="45" t="s">
+      <c r="B229" s="48" t="s">
         <v>262</v>
       </c>
-      <c r="C229" s="45" t="s">
+      <c r="C229" s="48" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A230" s="45" t="s">
+      <c r="A230" s="48" t="s">
         <v>264</v>
       </c>
-      <c r="B230" s="45" t="s">
+      <c r="B230" s="48" t="s">
         <v>265</v>
       </c>
-      <c r="C230" s="45" t="s">
+      <c r="C230" s="48" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A231" s="45" t="s">
+      <c r="A231" s="48" t="s">
         <v>266</v>
       </c>
-      <c r="B231" s="45" t="s">
+      <c r="B231" s="48" t="s">
         <v>267</v>
       </c>
-      <c r="C231" s="45" t="s">
+      <c r="C231" s="48" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A232" s="45" t="s">
+      <c r="A232" s="48" t="s">
         <v>268</v>
       </c>
-      <c r="B232" s="45" t="s">
+      <c r="B232" s="48" t="s">
         <v>269</v>
       </c>
-      <c r="C232" s="45" t="s">
+      <c r="C232" s="48" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A233" s="45" t="s">
+      <c r="A233" s="48" t="s">
         <v>270</v>
       </c>
-      <c r="B233" s="45" t="s">
+      <c r="B233" s="48" t="s">
         <v>271</v>
       </c>
-      <c r="C233" s="45" t="s">
+      <c r="C233" s="48" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A234" s="45"/>
-      <c r="B234" s="45"/>
-      <c r="C234" s="45"/>
+      <c r="A234" s="48"/>
+      <c r="B234" s="48"/>
+      <c r="C234" s="48"/>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A235" s="13" t="s">
         <v>272</v>
       </c>
-      <c r="B235" s="45" t="s">
+      <c r="B235" s="48" t="s">
         <v>261</v>
       </c>
-      <c r="C235" s="45"/>
+      <c r="C235" s="48"/>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A236" s="13" t="s">
@@ -5492,13 +5565,13 @@
         <f>_xlfn.XLOOKUP(B235,A227:A233,C227:C233,0)</f>
         <v>Office equipment</v>
       </c>
-      <c r="C236" s="49" t="str">
+      <c r="C236" s="56" t="str">
         <f ca="1">_xlfn.FORMULATEXT(B236)</f>
         <v>=XLOOKUP(B235,A227:A233,C227:C233,0)</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C237" s="49"/>
+      <c r="C237" s="56"/>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A238" s="28" t="s">
@@ -5522,86 +5595,86 @@
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A242" s="45" t="s">
+      <c r="A242" s="48" t="s">
         <v>277</v>
       </c>
-      <c r="B242" s="45" t="s">
+      <c r="B242" s="48" t="s">
         <v>278</v>
       </c>
-      <c r="C242" s="45">
+      <c r="C242" s="48">
         <v>342</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A243" s="45" t="s">
+      <c r="A243" s="48" t="s">
         <v>279</v>
       </c>
-      <c r="B243" s="45" t="s">
+      <c r="B243" s="48" t="s">
         <v>280</v>
       </c>
-      <c r="C243" s="45">
+      <c r="C243" s="48">
         <v>128</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A244" s="45" t="s">
+      <c r="A244" s="48" t="s">
         <v>281</v>
       </c>
-      <c r="B244" s="45" t="s">
+      <c r="B244" s="48" t="s">
         <v>282</v>
       </c>
-      <c r="C244" s="45">
+      <c r="C244" s="48">
         <v>56</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A245" s="45" t="s">
+      <c r="A245" s="48" t="s">
         <v>283</v>
       </c>
-      <c r="B245" s="45" t="s">
+      <c r="B245" s="48" t="s">
         <v>284</v>
       </c>
-      <c r="C245" s="45">
+      <c r="C245" s="48">
         <v>89</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A246" s="45" t="s">
+      <c r="A246" s="48" t="s">
         <v>285</v>
       </c>
-      <c r="B246" s="45" t="s">
+      <c r="B246" s="48" t="s">
         <v>286</v>
       </c>
-      <c r="C246" s="45">
+      <c r="C246" s="48">
         <v>203</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A247" s="45" t="s">
+      <c r="A247" s="48" t="s">
         <v>287</v>
       </c>
-      <c r="B247" s="45" t="s">
+      <c r="B247" s="48" t="s">
         <v>288</v>
       </c>
-      <c r="C247" s="45">
+      <c r="C247" s="48">
         <v>74</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A248" s="45" t="s">
+      <c r="A248" s="48" t="s">
         <v>289</v>
       </c>
-      <c r="B248" s="45" t="s">
+      <c r="B248" s="48" t="s">
         <v>290</v>
       </c>
-      <c r="C248" s="45">
+      <c r="C248" s="48">
         <v>165</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A249" s="45"/>
-      <c r="B249" s="45"/>
-      <c r="C249" s="45"/>
+      <c r="A249" s="48"/>
+      <c r="B249" s="48"/>
+      <c r="C249" s="48"/>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A250" s="9" t="s">
@@ -5615,10 +5688,10 @@
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A251" s="45" t="s">
+      <c r="A251" s="48" t="s">
         <v>283</v>
       </c>
-      <c r="B251" s="45" t="s">
+      <c r="B251" s="48" t="s">
         <v>284</v>
       </c>
       <c r="C251" s="4">
@@ -5627,10 +5700,10 @@
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A252" s="45" t="s">
+      <c r="A252" s="48" t="s">
         <v>277</v>
       </c>
-      <c r="B252" s="45" t="s">
+      <c r="B252" s="48" t="s">
         <v>278</v>
       </c>
       <c r="C252" s="4">
@@ -5639,10 +5712,10 @@
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A253" s="45" t="s">
+      <c r="A253" s="48" t="s">
         <v>289</v>
       </c>
-      <c r="B253" s="45" t="s">
+      <c r="B253" s="48" t="s">
         <v>290</v>
       </c>
       <c r="C253" s="4">
@@ -5651,10 +5724,10 @@
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A254" s="45" t="s">
+      <c r="A254" s="48" t="s">
         <v>285</v>
       </c>
-      <c r="B254" s="45" t="s">
+      <c r="B254" s="48" t="s">
         <v>286</v>
       </c>
       <c r="C254" s="4">
@@ -5663,11 +5736,11 @@
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B256" s="52" t="str">
+      <c r="B256" s="57" t="str">
         <f ca="1">_xlfn.FORMULATEXT(C251)</f>
         <v>=XLOOKUP(A251,A$242:A$248,$C$242:$C$248,0)</v>
       </c>
-      <c r="C256" s="52"/>
+      <c r="C256" s="57"/>
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A258" s="28" t="s">
@@ -5699,7 +5772,7 @@
       </c>
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A262" s="45" t="s">
+      <c r="A262" s="48" t="s">
         <v>297</v>
       </c>
       <c r="B262" s="18">
@@ -5714,7 +5787,7 @@
       </c>
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A263" s="45" t="s">
+      <c r="A263" s="48" t="s">
         <v>298</v>
       </c>
       <c r="B263" s="18">
@@ -5729,7 +5802,7 @@
       </c>
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A264" s="45" t="s">
+      <c r="A264" s="48" t="s">
         <v>299</v>
       </c>
       <c r="B264" s="18">
@@ -5744,7 +5817,7 @@
       </c>
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A265" s="45" t="s">
+      <c r="A265" s="48" t="s">
         <v>225</v>
       </c>
       <c r="B265" s="18">
@@ -5759,7 +5832,7 @@
       </c>
     </row>
     <row r="266" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A266" s="45" t="s">
+      <c r="A266" s="48" t="s">
         <v>300</v>
       </c>
       <c r="B266" s="18">
@@ -5774,7 +5847,7 @@
       </c>
     </row>
     <row r="267" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A267" s="45" t="s">
+      <c r="A267" s="48" t="s">
         <v>301</v>
       </c>
       <c r="B267" s="18">
@@ -5789,7 +5862,7 @@
       </c>
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A268" s="45" t="s">
+      <c r="A268" s="48" t="s">
         <v>302</v>
       </c>
       <c r="B268" s="18">
@@ -5839,7 +5912,7 @@
       </c>
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A275" s="45" t="s">
+      <c r="A275" s="48" t="s">
         <v>297</v>
       </c>
       <c r="B275" s="18">
@@ -5854,7 +5927,7 @@
       </c>
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A276" s="45" t="s">
+      <c r="A276" s="48" t="s">
         <v>298</v>
       </c>
       <c r="B276" s="18">
@@ -5869,7 +5942,7 @@
       </c>
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A277" s="45" t="s">
+      <c r="A277" s="48" t="s">
         <v>299</v>
       </c>
       <c r="B277" s="18">
@@ -5884,7 +5957,7 @@
       </c>
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A278" s="45" t="s">
+      <c r="A278" s="48" t="s">
         <v>225</v>
       </c>
       <c r="B278" s="18">
@@ -5899,7 +5972,7 @@
       </c>
     </row>
     <row r="279" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A279" s="45" t="s">
+      <c r="A279" s="48" t="s">
         <v>300</v>
       </c>
       <c r="B279" s="18">
@@ -5914,7 +5987,7 @@
       </c>
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A280" s="45" t="s">
+      <c r="A280" s="48" t="s">
         <v>301</v>
       </c>
       <c r="B280" s="18">
@@ -5929,7 +6002,7 @@
       </c>
     </row>
     <row r="281" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A281" s="45" t="s">
+      <c r="A281" s="48" t="s">
         <v>302</v>
       </c>
       <c r="B281" s="18">
@@ -6012,7 +6085,7 @@
       </c>
     </row>
     <row r="295" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A295" s="45" t="s">
+      <c r="A295" s="48" t="s">
         <v>314</v>
       </c>
       <c r="B295" s="18">
@@ -6031,7 +6104,7 @@
       </c>
     </row>
     <row r="296" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A296" s="45" t="s">
+      <c r="A296" s="48" t="s">
         <v>315</v>
       </c>
       <c r="B296" s="18">
@@ -6046,7 +6119,7 @@
       </c>
     </row>
     <row r="297" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A297" s="45" t="s">
+      <c r="A297" s="48" t="s">
         <v>316</v>
       </c>
       <c r="B297" s="18">
@@ -6061,7 +6134,7 @@
       </c>
     </row>
     <row r="298" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A298" s="45" t="s">
+      <c r="A298" s="48" t="s">
         <v>317</v>
       </c>
       <c r="B298" s="18">
@@ -6098,7 +6171,7 @@
       </c>
     </row>
     <row r="302" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A302" s="45" t="s">
+      <c r="A302" s="48" t="s">
         <v>346</v>
       </c>
     </row>
@@ -6119,7 +6192,7 @@
       <c r="A306" s="15"/>
     </row>
     <row r="307" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A307" s="45" t="s">
+      <c r="A307" s="48" t="s">
         <v>327</v>
       </c>
     </row>
@@ -6165,19 +6238,19 @@
       <c r="F314" s="6"/>
     </row>
     <row r="315" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A315" s="45" t="s">
+      <c r="A315" s="48" t="s">
         <v>332</v>
       </c>
-      <c r="B315" s="45" t="s">
+      <c r="B315" s="48" t="s">
         <v>333</v>
       </c>
-      <c r="C315" s="45">
+      <c r="C315" s="48">
         <v>25.2</v>
       </c>
-      <c r="D315" s="45">
+      <c r="D315" s="48">
         <v>100</v>
       </c>
-      <c r="E315" s="45" t="s">
+      <c r="E315" s="48" t="s">
         <v>334</v>
       </c>
       <c r="F315" s="4">
@@ -6190,19 +6263,19 @@
       </c>
     </row>
     <row r="316" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A316" s="45" t="s">
+      <c r="A316" s="48" t="s">
         <v>335</v>
       </c>
-      <c r="B316" s="45" t="s">
+      <c r="B316" s="48" t="s">
         <v>336</v>
       </c>
-      <c r="C316" s="45">
+      <c r="C316" s="48">
         <v>24.2</v>
       </c>
-      <c r="D316" s="45">
+      <c r="D316" s="48">
         <v>120</v>
       </c>
-      <c r="E316" s="45" t="s">
+      <c r="E316" s="48" t="s">
         <v>337</v>
       </c>
       <c r="F316" s="4" cm="1">
@@ -6211,19 +6284,19 @@
       </c>
     </row>
     <row r="317" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A317" s="45" t="s">
+      <c r="A317" s="48" t="s">
         <v>338</v>
       </c>
-      <c r="B317" s="45" t="s">
+      <c r="B317" s="48" t="s">
         <v>339</v>
       </c>
-      <c r="C317" s="45">
+      <c r="C317" s="48">
         <v>23.75</v>
       </c>
-      <c r="D317" s="45">
+      <c r="D317" s="48">
         <v>80</v>
       </c>
-      <c r="E317" s="45" t="s">
+      <c r="E317" s="48" t="s">
         <v>340</v>
       </c>
       <c r="F317" s="4">
@@ -6232,89 +6305,89 @@
       </c>
     </row>
     <row r="318" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A318" s="45" t="s">
+      <c r="A318" s="48" t="s">
         <v>341</v>
       </c>
-      <c r="B318" s="45" t="s">
+      <c r="B318" s="48" t="s">
         <v>333</v>
       </c>
-      <c r="C318" s="45">
+      <c r="C318" s="48">
         <v>24.1</v>
       </c>
-      <c r="D318" s="45">
+      <c r="D318" s="48">
         <v>150</v>
       </c>
-      <c r="E318" s="45"/>
-      <c r="F318" s="45"/>
-      <c r="G318" s="45"/>
+      <c r="E318" s="48"/>
+      <c r="F318" s="48"/>
+      <c r="G318" s="48"/>
     </row>
     <row r="319" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A319" s="45" t="s">
+      <c r="A319" s="48" t="s">
         <v>342</v>
       </c>
-      <c r="B319" s="45" t="s">
+      <c r="B319" s="48" t="s">
         <v>336</v>
       </c>
-      <c r="C319" s="45">
+      <c r="C319" s="48">
         <v>23.9</v>
       </c>
-      <c r="D319" s="45">
+      <c r="D319" s="48">
         <v>60</v>
       </c>
-      <c r="E319" s="45"/>
-      <c r="F319" s="45"/>
-      <c r="G319" s="45"/>
+      <c r="E319" s="48"/>
+      <c r="F319" s="48"/>
+      <c r="G319" s="48"/>
     </row>
     <row r="320" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A320" s="45" t="s">
+      <c r="A320" s="48" t="s">
         <v>343</v>
       </c>
-      <c r="B320" s="45" t="s">
+      <c r="B320" s="48" t="s">
         <v>339</v>
       </c>
-      <c r="C320" s="45">
+      <c r="C320" s="48">
         <v>24.8</v>
       </c>
-      <c r="D320" s="45">
+      <c r="D320" s="48">
         <v>40</v>
       </c>
-      <c r="E320" s="45"/>
-      <c r="F320" s="45"/>
-      <c r="G320" s="45"/>
+      <c r="E320" s="48"/>
+      <c r="F320" s="48"/>
+      <c r="G320" s="48"/>
     </row>
     <row r="321" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A321" s="45" t="s">
+      <c r="A321" s="48" t="s">
         <v>344</v>
       </c>
-      <c r="B321" s="45" t="s">
+      <c r="B321" s="48" t="s">
         <v>333</v>
       </c>
-      <c r="C321" s="45">
+      <c r="C321" s="48">
         <v>23.6</v>
       </c>
-      <c r="D321" s="45">
+      <c r="D321" s="48">
         <v>90</v>
       </c>
-      <c r="E321" s="45"/>
-      <c r="F321" s="45"/>
-      <c r="G321" s="45"/>
+      <c r="E321" s="48"/>
+      <c r="F321" s="48"/>
+      <c r="G321" s="48"/>
     </row>
     <row r="322" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A322" s="45" t="s">
+      <c r="A322" s="48" t="s">
         <v>345</v>
       </c>
-      <c r="B322" s="45" t="s">
+      <c r="B322" s="48" t="s">
         <v>336</v>
       </c>
-      <c r="C322" s="45">
+      <c r="C322" s="48">
         <v>24.3</v>
       </c>
-      <c r="D322" s="45">
+      <c r="D322" s="48">
         <v>60</v>
       </c>
-      <c r="E322" s="45"/>
-      <c r="F322" s="45"/>
-      <c r="G322" s="45"/>
+      <c r="E322" s="48"/>
+      <c r="F322" s="48"/>
+      <c r="G322" s="48"/>
     </row>
     <row r="324" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A324" s="28" t="s">
@@ -6357,10 +6430,10 @@
       </c>
     </row>
     <row r="333" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A333" s="45" t="s">
+      <c r="A333" s="48" t="s">
         <v>354</v>
       </c>
-      <c r="B333" s="45"/>
+      <c r="B333" s="48"/>
     </row>
     <row r="334" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A334" s="6" t="s">
@@ -6371,54 +6444,54 @@
       </c>
     </row>
     <row r="335" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A335" s="45">
+      <c r="A335" s="48">
         <v>1040</v>
       </c>
-      <c r="B335" s="45" t="s">
+      <c r="B335" s="48" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="336" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A336" s="45">
+      <c r="A336" s="48">
         <v>1042</v>
       </c>
-      <c r="B336" s="45" t="s">
+      <c r="B336" s="48" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A337" s="45">
+      <c r="A337" s="48">
         <v>1051</v>
       </c>
-      <c r="B337" s="45" t="s">
+      <c r="B337" s="48" t="s">
         <v>355</v>
       </c>
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A338" s="45">
+      <c r="A338" s="48">
         <v>1063</v>
       </c>
-      <c r="B338" s="45" t="s">
+      <c r="B338" s="48" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A339" s="45">
+      <c r="A339" s="48">
         <v>1038</v>
       </c>
-      <c r="B339" s="45" t="s">
+      <c r="B339" s="48" t="s">
         <v>356</v>
       </c>
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A340" s="45"/>
-      <c r="B340" s="45"/>
+      <c r="A340" s="48"/>
+      <c r="B340" s="48"/>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A341" s="45" t="s">
+      <c r="A341" s="48" t="s">
         <v>357</v>
       </c>
-      <c r="B341" s="45"/>
+      <c r="B341" s="48"/>
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A342" s="6" t="s">
@@ -6429,7 +6502,7 @@
       </c>
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A343" s="45">
+      <c r="A343" s="48">
         <v>1042</v>
       </c>
       <c r="B343" s="4" t="str">
@@ -6442,7 +6515,7 @@
       </c>
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A344" s="45">
+      <c r="A344" s="48">
         <v>1038</v>
       </c>
       <c r="B344" s="4" t="str">
@@ -6451,7 +6524,7 @@
       </c>
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A345" s="45">
+      <c r="A345" s="48">
         <v>1051</v>
       </c>
       <c r="B345" s="4" t="str">
@@ -6460,7 +6533,7 @@
       </c>
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A346" s="45">
+      <c r="A346" s="48">
         <v>1040</v>
       </c>
       <c r="B346" s="4" t="str">
@@ -6469,7 +6542,7 @@
       </c>
     </row>
     <row r="347" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A347" s="45"/>
+      <c r="A347" s="48"/>
     </row>
     <row r="348" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A348" s="28" t="s">
@@ -6519,26 +6592,26 @@
       </c>
     </row>
     <row r="356" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A356" s="45" t="s">
+      <c r="A356" s="48" t="s">
         <v>363</v>
       </c>
-      <c r="B356" s="45">
+      <c r="B356" s="48">
         <v>85000</v>
       </c>
-      <c r="C356" s="45">
+      <c r="C356" s="48">
         <v>95000</v>
       </c>
-      <c r="D356" s="45">
+      <c r="D356" s="48">
         <v>110000</v>
       </c>
-      <c r="E356" s="45">
+      <c r="E356" s="48">
         <v>120000</v>
       </c>
     </row>
     <row r="357" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="C357" s="45"/>
-      <c r="D357" s="45"/>
-      <c r="E357" s="45"/>
+      <c r="C357" s="48"/>
+      <c r="D357" s="48"/>
+      <c r="E357" s="48"/>
     </row>
     <row r="358" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A358" s="1" t="s">
@@ -6551,22 +6624,22 @@
         <f>HLOOKUP(B358,A355:E356,2,0)</f>
         <v>110000</v>
       </c>
-      <c r="D358" s="45"/>
-      <c r="E358" s="45"/>
+      <c r="D358" s="48"/>
+      <c r="E358" s="48"/>
     </row>
     <row r="359" spans="1:5" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A359" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="C359" s="49" t="str">
+      <c r="C359" s="56" t="str">
         <f ca="1">_xlfn.FORMULATEXT(C358)</f>
         <v>=HLOOKUP(B358,A355:E356,2,0)</v>
       </c>
-      <c r="D359" s="45"/>
-      <c r="E359" s="45"/>
+      <c r="D359" s="48"/>
+      <c r="E359" s="48"/>
     </row>
     <row r="360" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="C360" s="49"/>
+      <c r="C360" s="56"/>
     </row>
     <row r="362" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A362" s="28" t="s">
@@ -6589,7 +6662,7 @@
       </c>
     </row>
     <row r="367" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A367" s="45" t="s">
+      <c r="A367" s="48" t="s">
         <v>398</v>
       </c>
     </row>
@@ -6597,7 +6670,7 @@
       <c r="A368" s="15"/>
     </row>
     <row r="369" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A369" s="45" t="s">
+      <c r="A369" s="48" t="s">
         <v>376</v>
       </c>
     </row>
@@ -6620,41 +6693,41 @@
       </c>
     </row>
     <row r="375" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A375" s="45" t="s">
+      <c r="A375" s="48" t="s">
         <v>378</v>
       </c>
-      <c r="B375" s="45"/>
-      <c r="C375" s="45"/>
-      <c r="D375" s="45"/>
-      <c r="E375" s="45"/>
-      <c r="F375" s="45"/>
-      <c r="G375" s="45"/>
-      <c r="H375" s="45"/>
+      <c r="B375" s="48"/>
+      <c r="C375" s="48"/>
+      <c r="D375" s="48"/>
+      <c r="E375" s="48"/>
+      <c r="F375" s="48"/>
+      <c r="G375" s="48"/>
+      <c r="H375" s="48"/>
     </row>
     <row r="376" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A376" s="32" t="s">
         <v>379</v>
       </c>
-      <c r="B376" s="45"/>
-      <c r="C376" s="45"/>
-      <c r="D376" s="45"/>
-      <c r="E376" s="45"/>
-      <c r="F376" s="45"/>
-      <c r="G376" s="45"/>
-      <c r="H376" s="45"/>
+      <c r="B376" s="48"/>
+      <c r="C376" s="48"/>
+      <c r="D376" s="48"/>
+      <c r="E376" s="48"/>
+      <c r="F376" s="48"/>
+      <c r="G376" s="48"/>
+      <c r="H376" s="48"/>
     </row>
     <row r="377" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A377" s="33" t="s">
         <v>380</v>
       </c>
-      <c r="B377" s="45"/>
-      <c r="C377" s="45"/>
-      <c r="E377" s="45"/>
-      <c r="F377" s="45"/>
+      <c r="B377" s="48"/>
+      <c r="C377" s="48"/>
+      <c r="E377" s="48"/>
+      <c r="F377" s="48"/>
       <c r="G377" s="33" t="s">
         <v>381</v>
       </c>
-      <c r="H377" s="45"/>
+      <c r="H377" s="48"/>
     </row>
     <row r="378" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A378" s="6" t="s">
@@ -6672,7 +6745,7 @@
       <c r="E378" s="6" t="s">
         <v>386</v>
       </c>
-      <c r="F378" s="45"/>
+      <c r="F378" s="48"/>
       <c r="G378" s="6" t="s">
         <v>387</v>
       </c>
@@ -6681,127 +6754,127 @@
       </c>
     </row>
     <row r="379" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A379" s="45" t="s">
+      <c r="A379" s="48" t="s">
         <v>388</v>
       </c>
-      <c r="B379" s="45" t="s">
+      <c r="B379" s="48" t="s">
         <v>389</v>
       </c>
-      <c r="C379" s="45">
+      <c r="C379" s="48">
         <v>0.8</v>
       </c>
       <c r="D379" s="4">
         <f>VLOOKUP(C379,G379:H383,2,1)</f>
         <v>6.5</v>
       </c>
-      <c r="E379" s="45">
+      <c r="E379" s="48">
         <v>5.2</v>
       </c>
-      <c r="F379" s="45"/>
-      <c r="G379" s="45">
+      <c r="F379" s="48"/>
+      <c r="G379" s="48">
         <v>0</v>
       </c>
-      <c r="H379" s="45">
+      <c r="H379" s="48">
         <v>6.5</v>
       </c>
     </row>
     <row r="380" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A380" s="45" t="s">
+      <c r="A380" s="48" t="s">
         <v>390</v>
       </c>
-      <c r="B380" s="45" t="s">
+      <c r="B380" s="48" t="s">
         <v>389</v>
       </c>
-      <c r="C380" s="45">
+      <c r="C380" s="48">
         <v>2.4</v>
       </c>
       <c r="D380" s="4">
         <f t="shared" ref="D380:D383" si="17">VLOOKUP(C380,G380:H384,2,1)</f>
         <v>5.75</v>
       </c>
-      <c r="E380" s="45">
+      <c r="E380" s="48">
         <v>13.8</v>
       </c>
-      <c r="F380" s="45"/>
-      <c r="G380" s="45">
+      <c r="F380" s="48"/>
+      <c r="G380" s="48">
         <v>1</v>
       </c>
-      <c r="H380" s="45">
+      <c r="H380" s="48">
         <v>5.75</v>
       </c>
     </row>
     <row r="381" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A381" s="45" t="s">
+      <c r="A381" s="48" t="s">
         <v>391</v>
       </c>
-      <c r="B381" s="45" t="s">
+      <c r="B381" s="48" t="s">
         <v>392</v>
       </c>
-      <c r="C381" s="45">
+      <c r="C381" s="48">
         <v>6.2</v>
       </c>
       <c r="D381" s="4">
         <f>VLOOKUP(C381,G381:H385,2,1)</f>
         <v>5</v>
       </c>
-      <c r="E381" s="45">
+      <c r="E381" s="48">
         <v>31</v>
       </c>
-      <c r="F381" s="45"/>
-      <c r="G381" s="45">
+      <c r="F381" s="48"/>
+      <c r="G381" s="48">
         <v>5</v>
       </c>
-      <c r="H381" s="45">
+      <c r="H381" s="48">
         <v>5</v>
       </c>
     </row>
     <row r="382" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A382" s="45" t="s">
+      <c r="A382" s="48" t="s">
         <v>393</v>
       </c>
-      <c r="B382" s="45" t="s">
+      <c r="B382" s="48" t="s">
         <v>394</v>
       </c>
-      <c r="C382" s="45">
+      <c r="C382" s="48">
         <v>12</v>
       </c>
       <c r="D382" s="4">
         <f t="shared" si="17"/>
         <v>4.25</v>
       </c>
-      <c r="E382" s="45">
+      <c r="E382" s="48">
         <v>51</v>
       </c>
-      <c r="F382" s="45"/>
-      <c r="G382" s="45">
+      <c r="F382" s="48"/>
+      <c r="G382" s="48">
         <v>10</v>
       </c>
-      <c r="H382" s="45">
+      <c r="H382" s="48">
         <v>4.25</v>
       </c>
     </row>
     <row r="383" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A383" s="45" t="s">
+      <c r="A383" s="48" t="s">
         <v>395</v>
       </c>
-      <c r="B383" s="45" t="s">
+      <c r="B383" s="48" t="s">
         <v>389</v>
       </c>
-      <c r="C383" s="45">
+      <c r="C383" s="48">
         <v>24.5</v>
       </c>
       <c r="D383" s="4">
         <f t="shared" si="17"/>
         <v>3.75</v>
       </c>
-      <c r="E383" s="45">
+      <c r="E383" s="48">
         <v>91.875</v>
       </c>
-      <c r="F383" s="45"/>
-      <c r="G383" s="45">
+      <c r="F383" s="48"/>
+      <c r="G383" s="48">
         <v>20</v>
       </c>
-      <c r="H383" s="45">
+      <c r="H383" s="48">
         <v>3.75</v>
       </c>
     </row>
@@ -6842,7 +6915,7 @@
       </c>
     </row>
     <row r="394" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A394" s="45" t="s">
+      <c r="A394" s="48" t="s">
         <v>435</v>
       </c>
     </row>
@@ -6884,115 +6957,115 @@
       </c>
     </row>
     <row r="402" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A402" s="45" t="s">
+      <c r="A402" s="48" t="s">
         <v>407</v>
       </c>
-      <c r="B402" s="45" t="s">
+      <c r="B402" s="48" t="s">
         <v>408</v>
       </c>
-      <c r="C402" s="45" t="s">
+      <c r="C402" s="48" t="s">
         <v>409</v>
       </c>
-      <c r="D402" s="45" t="s">
+      <c r="D402" s="48" t="s">
         <v>410</v>
       </c>
     </row>
     <row r="403" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A403" s="45" t="s">
+      <c r="A403" s="48" t="s">
         <v>411</v>
       </c>
-      <c r="B403" s="45" t="s">
+      <c r="B403" s="48" t="s">
         <v>412</v>
       </c>
-      <c r="C403" s="45" t="s">
+      <c r="C403" s="48" t="s">
         <v>413</v>
       </c>
-      <c r="D403" s="45" t="s">
+      <c r="D403" s="48" t="s">
         <v>414</v>
       </c>
     </row>
     <row r="404" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A404" s="45" t="s">
+      <c r="A404" s="48" t="s">
         <v>415</v>
       </c>
-      <c r="B404" s="45" t="s">
+      <c r="B404" s="48" t="s">
         <v>416</v>
       </c>
-      <c r="C404" s="45" t="s">
+      <c r="C404" s="48" t="s">
         <v>417</v>
       </c>
-      <c r="D404" s="45" t="s">
+      <c r="D404" s="48" t="s">
         <v>418</v>
       </c>
     </row>
     <row r="405" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A405" s="45" t="s">
+      <c r="A405" s="48" t="s">
         <v>419</v>
       </c>
-      <c r="B405" s="45" t="s">
+      <c r="B405" s="48" t="s">
         <v>420</v>
       </c>
-      <c r="C405" s="45" t="s">
+      <c r="C405" s="48" t="s">
         <v>421</v>
       </c>
-      <c r="D405" s="45" t="s">
+      <c r="D405" s="48" t="s">
         <v>422</v>
       </c>
     </row>
     <row r="406" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A406" s="45" t="s">
+      <c r="A406" s="48" t="s">
         <v>423</v>
       </c>
-      <c r="B406" s="45" t="s">
+      <c r="B406" s="48" t="s">
         <v>424</v>
       </c>
-      <c r="C406" s="45" t="s">
+      <c r="C406" s="48" t="s">
         <v>425</v>
       </c>
-      <c r="D406" s="45" t="s">
+      <c r="D406" s="48" t="s">
         <v>426</v>
       </c>
     </row>
     <row r="407" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A407" s="45" t="s">
+      <c r="A407" s="48" t="s">
         <v>427</v>
       </c>
-      <c r="B407" s="45" t="s">
+      <c r="B407" s="48" t="s">
         <v>428</v>
       </c>
-      <c r="C407" s="45" t="s">
+      <c r="C407" s="48" t="s">
         <v>429</v>
       </c>
-      <c r="D407" s="45" t="s">
+      <c r="D407" s="48" t="s">
         <v>430</v>
       </c>
     </row>
     <row r="408" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A408" s="45"/>
-      <c r="B408" s="45"/>
-      <c r="C408" s="45"/>
-      <c r="D408" s="45"/>
+      <c r="A408" s="48"/>
+      <c r="B408" s="48"/>
+      <c r="C408" s="48"/>
+      <c r="D408" s="48"/>
     </row>
     <row r="409" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A409" s="45" t="s">
+      <c r="A409" s="48" t="s">
         <v>403</v>
       </c>
-      <c r="B409" s="45" t="s">
+      <c r="B409" s="48" t="s">
         <v>419</v>
       </c>
-      <c r="C409" s="45"/>
-      <c r="D409" s="45"/>
+      <c r="C409" s="48"/>
+      <c r="D409" s="48"/>
     </row>
     <row r="410" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A410" s="45" t="s">
+      <c r="A410" s="48" t="s">
         <v>405</v>
       </c>
       <c r="B410" s="4" t="str">
         <f>VLOOKUP(B409,A402:C407,3,0)</f>
         <v>Denver</v>
       </c>
-      <c r="C410" s="45"/>
-      <c r="D410" s="45"/>
+      <c r="C410" s="48"/>
+      <c r="D410" s="48"/>
     </row>
     <row r="411" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B411" s="1" t="str">
@@ -7030,58 +7103,58 @@
       </c>
     </row>
     <row r="419" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A419" s="45" t="s">
+      <c r="A419" s="48" t="s">
         <v>442</v>
       </c>
-      <c r="B419" s="45" t="s">
+      <c r="B419" s="48" t="s">
         <v>443</v>
       </c>
-      <c r="C419" s="45" t="s">
+      <c r="C419" s="48" t="s">
         <v>444</v>
       </c>
-      <c r="D419" s="45">
+      <c r="D419" s="48">
         <v>12</v>
       </c>
     </row>
     <row r="420" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A420" s="45" t="s">
+      <c r="A420" s="48" t="s">
         <v>445</v>
       </c>
-      <c r="B420" s="45" t="s">
+      <c r="B420" s="48" t="s">
         <v>446</v>
       </c>
-      <c r="C420" s="45" t="s">
+      <c r="C420" s="48" t="s">
         <v>447</v>
       </c>
-      <c r="D420" s="45">
+      <c r="D420" s="48">
         <v>18</v>
       </c>
     </row>
     <row r="421" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A421" s="45" t="s">
+      <c r="A421" s="48" t="s">
         <v>448</v>
       </c>
-      <c r="B421" s="45" t="s">
+      <c r="B421" s="48" t="s">
         <v>449</v>
       </c>
-      <c r="C421" s="45" t="s">
+      <c r="C421" s="48" t="s">
         <v>106</v>
       </c>
-      <c r="D421" s="45">
+      <c r="D421" s="48">
         <v>24</v>
       </c>
     </row>
     <row r="422" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A422" s="45" t="s">
+      <c r="A422" s="48" t="s">
         <v>450</v>
       </c>
-      <c r="B422" s="45" t="s">
+      <c r="B422" s="48" t="s">
         <v>60</v>
       </c>
-      <c r="C422" s="45" t="s">
+      <c r="C422" s="48" t="s">
         <v>447</v>
       </c>
-      <c r="D422" s="45">
+      <c r="D422" s="48">
         <v>35</v>
       </c>
     </row>
@@ -7136,7 +7209,7 @@
       <c r="D432" s="6" t="s">
         <v>454</v>
       </c>
-      <c r="E432" s="45"/>
+      <c r="E432" s="48"/>
       <c r="F432" s="6" t="s">
         <v>455</v>
       </c>
@@ -7145,19 +7218,19 @@
       </c>
     </row>
     <row r="433" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A433" s="45" t="s">
+      <c r="A433" s="48" t="s">
         <v>456</v>
       </c>
-      <c r="B433" s="45" t="s">
+      <c r="B433" s="48" t="s">
         <v>457</v>
       </c>
-      <c r="C433" s="45" t="s">
+      <c r="C433" s="48" t="s">
         <v>458</v>
       </c>
-      <c r="D433" s="45">
+      <c r="D433" s="48">
         <v>6.25</v>
       </c>
-      <c r="E433" s="45"/>
+      <c r="E433" s="48"/>
       <c r="F433" s="34" t="s">
         <v>456</v>
       </c>
@@ -7167,19 +7240,19 @@
       </c>
     </row>
     <row r="434" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A434" s="45" t="s">
+      <c r="A434" s="48" t="s">
         <v>459</v>
       </c>
-      <c r="B434" s="45" t="s">
+      <c r="B434" s="48" t="s">
         <v>460</v>
       </c>
-      <c r="C434" s="45" t="s">
+      <c r="C434" s="48" t="s">
         <v>461</v>
       </c>
-      <c r="D434" s="45">
+      <c r="D434" s="48">
         <v>3.4</v>
       </c>
-      <c r="E434" s="45"/>
+      <c r="E434" s="48"/>
       <c r="F434" s="34" t="s">
         <v>462</v>
       </c>
@@ -7189,19 +7262,19 @@
       </c>
     </row>
     <row r="435" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A435" s="45" t="s">
+      <c r="A435" s="48" t="s">
         <v>463</v>
       </c>
-      <c r="B435" s="45" t="s">
+      <c r="B435" s="48" t="s">
         <v>464</v>
       </c>
-      <c r="C435" s="45" t="s">
+      <c r="C435" s="48" t="s">
         <v>461</v>
       </c>
-      <c r="D435" s="45">
+      <c r="D435" s="48">
         <v>19.989999999999998</v>
       </c>
-      <c r="E435" s="45"/>
+      <c r="E435" s="48"/>
       <c r="F435" s="34" t="s">
         <v>463</v>
       </c>
@@ -7211,19 +7284,19 @@
       </c>
     </row>
     <row r="436" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A436" s="45" t="s">
+      <c r="A436" s="48" t="s">
         <v>465</v>
       </c>
-      <c r="B436" s="45" t="s">
+      <c r="B436" s="48" t="s">
         <v>466</v>
       </c>
-      <c r="C436" s="45" t="s">
+      <c r="C436" s="48" t="s">
         <v>461</v>
       </c>
-      <c r="D436" s="45">
+      <c r="D436" s="48">
         <v>14.5</v>
       </c>
-      <c r="E436" s="45"/>
+      <c r="E436" s="48"/>
       <c r="F436" s="34" t="s">
         <v>467</v>
       </c>
@@ -7233,19 +7306,19 @@
       </c>
     </row>
     <row r="437" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A437" s="45" t="s">
+      <c r="A437" s="48" t="s">
         <v>468</v>
       </c>
-      <c r="B437" s="45" t="s">
+      <c r="B437" s="48" t="s">
         <v>469</v>
       </c>
-      <c r="C437" s="45" t="s">
+      <c r="C437" s="48" t="s">
         <v>470</v>
       </c>
-      <c r="D437" s="45">
+      <c r="D437" s="48">
         <v>8.75</v>
       </c>
-      <c r="E437" s="45"/>
+      <c r="E437" s="48"/>
       <c r="F437" s="34" t="s">
         <v>468</v>
       </c>
@@ -7255,19 +7328,19 @@
       </c>
     </row>
     <row r="438" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A438" s="45" t="s">
+      <c r="A438" s="48" t="s">
         <v>471</v>
       </c>
-      <c r="B438" s="45" t="s">
+      <c r="B438" s="48" t="s">
         <v>472</v>
       </c>
-      <c r="C438" s="45" t="s">
+      <c r="C438" s="48" t="s">
         <v>447</v>
       </c>
-      <c r="D438" s="45">
+      <c r="D438" s="48">
         <v>27.5</v>
       </c>
-      <c r="E438" s="45"/>
+      <c r="E438" s="48"/>
       <c r="F438" s="34" t="s">
         <v>473</v>
       </c>
@@ -7277,19 +7350,19 @@
       </c>
     </row>
     <row r="439" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A439" s="45" t="s">
+      <c r="A439" s="48" t="s">
         <v>474</v>
       </c>
-      <c r="B439" s="45" t="s">
+      <c r="B439" s="48" t="s">
         <v>475</v>
       </c>
-      <c r="C439" s="45" t="s">
+      <c r="C439" s="48" t="s">
         <v>470</v>
       </c>
-      <c r="D439" s="45">
+      <c r="D439" s="48">
         <v>12</v>
       </c>
-      <c r="E439" s="45"/>
+      <c r="E439" s="48"/>
       <c r="F439" s="34" t="s">
         <v>474</v>
       </c>
@@ -7308,7 +7381,7 @@
       </c>
     </row>
     <row r="442" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A442" s="45" t="s">
+      <c r="A442" s="48" t="s">
         <v>479</v>
       </c>
     </row>
@@ -7316,7 +7389,7 @@
       <c r="A443" s="15"/>
     </row>
     <row r="444" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A444" s="45" t="s">
+      <c r="A444" s="48" t="s">
         <v>505</v>
       </c>
     </row>
@@ -7324,7 +7397,7 @@
       <c r="A445" s="15"/>
     </row>
     <row r="446" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A446" s="45" t="s">
+      <c r="A446" s="48" t="s">
         <v>480</v>
       </c>
     </row>
@@ -7332,7 +7405,7 @@
       <c r="A447" s="15"/>
     </row>
     <row r="448" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A448" s="45" t="s">
+      <c r="A448" s="48" t="s">
         <v>481</v>
       </c>
     </row>
@@ -7351,122 +7424,122 @@
       </c>
     </row>
     <row r="451" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A451" s="45" t="s">
+      <c r="A451" s="48" t="s">
         <v>483</v>
       </c>
-      <c r="B451" s="45" t="s">
+      <c r="B451" s="48" t="s">
         <v>484</v>
       </c>
-      <c r="C451" s="45" t="s">
+      <c r="C451" s="48" t="s">
         <v>461</v>
       </c>
-      <c r="D451" s="45">
+      <c r="D451" s="48">
         <v>22.4</v>
       </c>
     </row>
     <row r="452" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A452" s="45" t="s">
+      <c r="A452" s="48" t="s">
         <v>485</v>
       </c>
-      <c r="B452" s="45" t="s">
+      <c r="B452" s="48" t="s">
         <v>486</v>
       </c>
-      <c r="C452" s="45" t="s">
+      <c r="C452" s="48" t="s">
         <v>487</v>
       </c>
-      <c r="D452" s="45">
+      <c r="D452" s="48">
         <v>18.5</v>
       </c>
     </row>
     <row r="453" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A453" s="45" t="s">
+      <c r="A453" s="48" t="s">
         <v>488</v>
       </c>
-      <c r="B453" s="45" t="s">
+      <c r="B453" s="48" t="s">
         <v>489</v>
       </c>
-      <c r="C453" s="45" t="s">
+      <c r="C453" s="48" t="s">
         <v>490</v>
       </c>
-      <c r="D453" s="45">
+      <c r="D453" s="48">
         <v>7.2</v>
       </c>
     </row>
     <row r="454" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A454" s="45" t="s">
+      <c r="A454" s="48" t="s">
         <v>491</v>
       </c>
-      <c r="B454" s="45" t="s">
+      <c r="B454" s="48" t="s">
         <v>492</v>
       </c>
-      <c r="C454" s="45" t="s">
+      <c r="C454" s="48" t="s">
         <v>487</v>
       </c>
-      <c r="D454" s="45">
+      <c r="D454" s="48">
         <v>9.75</v>
       </c>
     </row>
     <row r="455" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A455" s="45" t="s">
+      <c r="A455" s="48" t="s">
         <v>493</v>
       </c>
-      <c r="B455" s="45" t="s">
+      <c r="B455" s="48" t="s">
         <v>494</v>
       </c>
-      <c r="C455" s="45" t="s">
+      <c r="C455" s="48" t="s">
         <v>470</v>
       </c>
-      <c r="D455" s="45">
+      <c r="D455" s="48">
         <v>31</v>
       </c>
     </row>
     <row r="456" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A456" s="45" t="s">
+      <c r="A456" s="48" t="s">
         <v>495</v>
       </c>
-      <c r="B456" s="45" t="s">
+      <c r="B456" s="48" t="s">
         <v>496</v>
       </c>
-      <c r="C456" s="45" t="s">
+      <c r="C456" s="48" t="s">
         <v>487</v>
       </c>
-      <c r="D456" s="45">
+      <c r="D456" s="48">
         <v>12.6</v>
       </c>
     </row>
     <row r="457" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A457" s="45" t="s">
+      <c r="A457" s="48" t="s">
         <v>497</v>
       </c>
-      <c r="B457" s="45" t="s">
+      <c r="B457" s="48" t="s">
         <v>498</v>
       </c>
-      <c r="C457" s="45" t="s">
+      <c r="C457" s="48" t="s">
         <v>499</v>
       </c>
-      <c r="D457" s="45">
+      <c r="D457" s="48">
         <v>14.25</v>
       </c>
     </row>
     <row r="458" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A458" s="45" t="s">
+      <c r="A458" s="48" t="s">
         <v>500</v>
       </c>
-      <c r="B458" s="45" t="s">
+      <c r="B458" s="48" t="s">
         <v>501</v>
       </c>
-      <c r="C458" s="45" t="s">
+      <c r="C458" s="48" t="s">
         <v>487</v>
       </c>
-      <c r="D458" s="45">
+      <c r="D458" s="48">
         <v>24.9</v>
       </c>
     </row>
     <row r="459" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A459" s="45"/>
-      <c r="B459" s="45"/>
-      <c r="C459" s="45"/>
-      <c r="D459" s="45"/>
+      <c r="A459" s="48"/>
+      <c r="B459" s="48"/>
+      <c r="C459" s="48"/>
+      <c r="D459" s="48"/>
     </row>
     <row r="460" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A460" s="13" t="s">
@@ -7475,8 +7548,8 @@
       <c r="B460" s="36" t="s">
         <v>503</v>
       </c>
-      <c r="C460" s="45"/>
-      <c r="D460" s="45"/>
+      <c r="C460" s="48"/>
+      <c r="D460" s="48"/>
     </row>
     <row r="461" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A461" s="13" t="s">
@@ -7486,8 +7559,8 @@
         <f>_xlfn.XLOOKUP("*"&amp;B460&amp;"*",B451:B458,B451:B458,,2)</f>
         <v>Citrus Surface Cleaner</v>
       </c>
-      <c r="C461" s="45"/>
-      <c r="D461" s="45"/>
+      <c r="C461" s="48"/>
+      <c r="D461" s="48"/>
     </row>
     <row r="462" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A462" s="13" t="s">
@@ -7497,8 +7570,8 @@
         <f>_xlfn.XLOOKUP("*"&amp;B460&amp;"*",B451:B458,D451:D458,,2)</f>
         <v>12.6</v>
       </c>
-      <c r="C462" s="45"/>
-      <c r="D462" s="45"/>
+      <c r="C462" s="48"/>
+      <c r="D462" s="48"/>
     </row>
     <row r="464" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B464" s="1" t="str">
@@ -7507,60 +7580,60 @@
       </c>
     </row>
     <row r="465" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A465" s="45"/>
-      <c r="B465" s="45"/>
-      <c r="C465" s="45"/>
-      <c r="D465" s="45"/>
-      <c r="E465" s="45"/>
-      <c r="F465" s="45"/>
-      <c r="G465" s="45"/>
-      <c r="H465" s="45"/>
+      <c r="A465" s="48"/>
+      <c r="B465" s="48"/>
+      <c r="C465" s="48"/>
+      <c r="D465" s="48"/>
+      <c r="E465" s="48"/>
+      <c r="F465" s="48"/>
+      <c r="G465" s="48"/>
+      <c r="H465" s="48"/>
     </row>
     <row r="466" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A466" s="28" t="s">
         <v>506</v>
       </c>
-      <c r="B466" s="45"/>
-      <c r="C466" s="45"/>
-      <c r="D466" s="45"/>
-      <c r="E466" s="45"/>
-      <c r="F466" s="45"/>
-      <c r="G466" s="45"/>
-      <c r="H466" s="45"/>
+      <c r="B466" s="48"/>
+      <c r="C466" s="48"/>
+      <c r="D466" s="48"/>
+      <c r="E466" s="48"/>
+      <c r="F466" s="48"/>
+      <c r="G466" s="48"/>
+      <c r="H466" s="48"/>
     </row>
     <row r="467" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A467" s="45" t="s">
+      <c r="A467" s="48" t="s">
         <v>507</v>
       </c>
-      <c r="B467" s="45"/>
-      <c r="C467" s="45"/>
-      <c r="D467" s="45"/>
-      <c r="E467" s="45"/>
-      <c r="F467" s="45"/>
-      <c r="G467" s="45"/>
-      <c r="H467" s="45"/>
+      <c r="B467" s="48"/>
+      <c r="C467" s="48"/>
+      <c r="D467" s="48"/>
+      <c r="E467" s="48"/>
+      <c r="F467" s="48"/>
+      <c r="G467" s="48"/>
+      <c r="H467" s="48"/>
     </row>
     <row r="468" spans="1:8" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A468" s="45" t="s">
+      <c r="A468" s="48" t="s">
         <v>508</v>
       </c>
-      <c r="B468" s="45"/>
-      <c r="C468" s="45"/>
-      <c r="D468" s="45"/>
-      <c r="E468" s="45"/>
-      <c r="F468" s="45"/>
-      <c r="G468" s="45"/>
-      <c r="H468" s="45"/>
+      <c r="B468" s="48"/>
+      <c r="C468" s="48"/>
+      <c r="D468" s="48"/>
+      <c r="E468" s="48"/>
+      <c r="F468" s="48"/>
+      <c r="G468" s="48"/>
+      <c r="H468" s="48"/>
     </row>
     <row r="469" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A469" s="45"/>
-      <c r="B469" s="45"/>
-      <c r="C469" s="45"/>
-      <c r="D469" s="45"/>
-      <c r="E469" s="45"/>
-      <c r="F469" s="45"/>
-      <c r="G469" s="45"/>
-      <c r="H469" s="45"/>
+      <c r="A469" s="48"/>
+      <c r="B469" s="48"/>
+      <c r="C469" s="48"/>
+      <c r="D469" s="48"/>
+      <c r="E469" s="48"/>
+      <c r="F469" s="48"/>
+      <c r="G469" s="48"/>
+      <c r="H469" s="48"/>
     </row>
     <row r="470" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A470" s="9" t="s">
@@ -7572,83 +7645,83 @@
       <c r="C470" s="9" t="s">
         <v>509</v>
       </c>
-      <c r="D470" s="45"/>
-      <c r="E470" s="45"/>
-      <c r="F470" s="45"/>
-      <c r="G470" s="45"/>
-      <c r="H470" s="45"/>
+      <c r="D470" s="48"/>
+      <c r="E470" s="48"/>
+      <c r="F470" s="48"/>
+      <c r="G470" s="48"/>
+      <c r="H470" s="48"/>
     </row>
     <row r="471" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A471" s="45" t="s">
+      <c r="A471" s="48" t="s">
         <v>510</v>
       </c>
-      <c r="B471" s="45" t="s">
+      <c r="B471" s="48" t="s">
         <v>511</v>
       </c>
-      <c r="C471" s="45">
+      <c r="C471" s="48">
         <v>120</v>
       </c>
-      <c r="D471" s="45"/>
-      <c r="E471" s="45"/>
-      <c r="F471" s="45"/>
-      <c r="G471" s="45"/>
-      <c r="H471" s="45"/>
+      <c r="D471" s="48"/>
+      <c r="E471" s="48"/>
+      <c r="F471" s="48"/>
+      <c r="G471" s="48"/>
+      <c r="H471" s="48"/>
     </row>
     <row r="472" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A472" s="45" t="s">
+      <c r="A472" s="48" t="s">
         <v>512</v>
       </c>
-      <c r="B472" s="45" t="s">
+      <c r="B472" s="48" t="s">
         <v>513</v>
       </c>
-      <c r="C472" s="45">
+      <c r="C472" s="48">
         <v>50</v>
       </c>
-      <c r="D472" s="45"/>
-      <c r="E472" s="45"/>
-      <c r="F472" s="45"/>
-      <c r="G472" s="45"/>
-      <c r="H472" s="45"/>
+      <c r="D472" s="48"/>
+      <c r="E472" s="48"/>
+      <c r="F472" s="48"/>
+      <c r="G472" s="48"/>
+      <c r="H472" s="48"/>
     </row>
     <row r="473" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A473" s="45" t="s">
+      <c r="A473" s="48" t="s">
         <v>514</v>
       </c>
-      <c r="B473" s="45" t="s">
+      <c r="B473" s="48" t="s">
         <v>515</v>
       </c>
-      <c r="C473" s="45">
+      <c r="C473" s="48">
         <v>0</v>
       </c>
-      <c r="D473" s="45"/>
-      <c r="E473" s="45"/>
-      <c r="F473" s="45"/>
-      <c r="G473" s="45"/>
-      <c r="H473" s="45"/>
+      <c r="D473" s="48"/>
+      <c r="E473" s="48"/>
+      <c r="F473" s="48"/>
+      <c r="G473" s="48"/>
+      <c r="H473" s="48"/>
     </row>
     <row r="474" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A474" s="45"/>
-      <c r="B474" s="45"/>
-      <c r="C474" s="45"/>
-      <c r="D474" s="45"/>
-      <c r="E474" s="45"/>
-      <c r="F474" s="45"/>
-      <c r="G474" s="45"/>
-      <c r="H474" s="45"/>
+      <c r="A474" s="48"/>
+      <c r="B474" s="48"/>
+      <c r="C474" s="48"/>
+      <c r="D474" s="48"/>
+      <c r="E474" s="48"/>
+      <c r="F474" s="48"/>
+      <c r="G474" s="48"/>
+      <c r="H474" s="48"/>
     </row>
     <row r="475" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A475" s="45" t="s">
+      <c r="A475" s="48" t="s">
         <v>516</v>
       </c>
       <c r="B475" s="37" t="s">
         <v>517</v>
       </c>
-      <c r="C475" s="45"/>
-      <c r="D475" s="45"/>
-      <c r="E475" s="45"/>
-      <c r="F475" s="45"/>
-      <c r="G475" s="45"/>
-      <c r="H475" s="45"/>
+      <c r="C475" s="48"/>
+      <c r="D475" s="48"/>
+      <c r="E475" s="48"/>
+      <c r="F475" s="48"/>
+      <c r="G475" s="48"/>
+      <c r="H475" s="48"/>
     </row>
     <row r="476" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A476" s="38" t="s">
@@ -7658,15 +7731,15 @@
         <f>_xlfn.IFNA(VLOOKUP(B475,A471:C473,2,0),"Not Found")</f>
         <v>Not Found</v>
       </c>
-      <c r="C476" s="49" t="str">
+      <c r="C476" s="56" t="str">
         <f ca="1">_xlfn.FORMULATEXT(B476)</f>
         <v>=IFNA(VLOOKUP(B475,A471:C473,2,0),"Not Found")</v>
       </c>
-      <c r="D476" s="49"/>
-      <c r="E476" s="49"/>
-      <c r="F476" s="45"/>
-      <c r="G476" s="45"/>
-      <c r="H476" s="45"/>
+      <c r="D476" s="56"/>
+      <c r="E476" s="56"/>
+      <c r="F476" s="48"/>
+      <c r="G476" s="48"/>
+      <c r="H476" s="48"/>
     </row>
     <row r="477" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A477" s="38" t="s">
@@ -7676,81 +7749,81 @@
         <f>_xlfn.XLOOKUP(B475,A471:A473,B471:B473,"Not Found")</f>
         <v>Not Found</v>
       </c>
-      <c r="C477" s="49" t="str">
+      <c r="C477" s="56" t="str">
         <f ca="1">_xlfn.FORMULATEXT(B477)</f>
         <v>=XLOOKUP(B475,A471:A473,B471:B473,"Not Found")</v>
       </c>
-      <c r="D477" s="49"/>
-      <c r="E477" s="49"/>
-      <c r="F477" s="45"/>
-      <c r="G477" s="45"/>
-      <c r="H477" s="45"/>
+      <c r="D477" s="56"/>
+      <c r="E477" s="56"/>
+      <c r="F477" s="48"/>
+      <c r="G477" s="48"/>
+      <c r="H477" s="48"/>
     </row>
     <row r="478" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A478" s="45"/>
-      <c r="B478" s="45"/>
-      <c r="C478" s="45"/>
-      <c r="D478" s="45"/>
-      <c r="E478" s="45"/>
-      <c r="F478" s="45"/>
-      <c r="G478" s="45"/>
-      <c r="H478" s="45"/>
+      <c r="A478" s="48"/>
+      <c r="B478" s="48"/>
+      <c r="C478" s="48"/>
+      <c r="D478" s="48"/>
+      <c r="E478" s="48"/>
+      <c r="F478" s="48"/>
+      <c r="G478" s="48"/>
+      <c r="H478" s="48"/>
     </row>
     <row r="479" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A479" s="45"/>
-      <c r="B479" s="45"/>
-      <c r="C479" s="45"/>
-      <c r="D479" s="45"/>
-      <c r="E479" s="45"/>
-      <c r="F479" s="45"/>
-      <c r="G479" s="45"/>
-      <c r="H479" s="45"/>
+      <c r="A479" s="48"/>
+      <c r="B479" s="48"/>
+      <c r="C479" s="48"/>
+      <c r="D479" s="48"/>
+      <c r="E479" s="48"/>
+      <c r="F479" s="48"/>
+      <c r="G479" s="48"/>
+      <c r="H479" s="48"/>
     </row>
     <row r="480" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A480" s="28" t="s">
         <v>545</v>
       </c>
-      <c r="B480" s="45"/>
-      <c r="C480" s="45"/>
-      <c r="D480" s="45"/>
-      <c r="E480" s="45"/>
-      <c r="F480" s="45"/>
-      <c r="G480" s="45"/>
-      <c r="H480" s="45"/>
+      <c r="B480" s="48"/>
+      <c r="C480" s="48"/>
+      <c r="D480" s="48"/>
+      <c r="E480" s="48"/>
+      <c r="F480" s="48"/>
+      <c r="G480" s="48"/>
+      <c r="H480" s="48"/>
     </row>
     <row r="481" spans="1:8" ht="124.2" x14ac:dyDescent="0.3">
-      <c r="A481" s="45" t="s">
+      <c r="A481" s="48" t="s">
         <v>546</v>
       </c>
-      <c r="B481" s="45"/>
-      <c r="C481" s="45"/>
-      <c r="D481" s="45"/>
-      <c r="E481" s="45"/>
-      <c r="F481" s="45"/>
-      <c r="G481" s="45"/>
-      <c r="H481" s="45"/>
+      <c r="B481" s="48"/>
+      <c r="C481" s="48"/>
+      <c r="D481" s="48"/>
+      <c r="E481" s="48"/>
+      <c r="F481" s="48"/>
+      <c r="G481" s="48"/>
+      <c r="H481" s="48"/>
     </row>
     <row r="482" spans="1:8" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A482" s="45" t="s">
+      <c r="A482" s="48" t="s">
         <v>547</v>
       </c>
-      <c r="B482" s="45"/>
-      <c r="C482" s="45"/>
-      <c r="D482" s="45"/>
-      <c r="E482" s="45"/>
-      <c r="F482" s="45"/>
-      <c r="G482" s="45"/>
-      <c r="H482" s="45"/>
+      <c r="B482" s="48"/>
+      <c r="C482" s="48"/>
+      <c r="D482" s="48"/>
+      <c r="E482" s="48"/>
+      <c r="F482" s="48"/>
+      <c r="G482" s="48"/>
+      <c r="H482" s="48"/>
     </row>
     <row r="483" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A483" s="45"/>
-      <c r="B483" s="45"/>
-      <c r="C483" s="45"/>
-      <c r="D483" s="45"/>
-      <c r="E483" s="45"/>
-      <c r="F483" s="45"/>
-      <c r="G483" s="45"/>
-      <c r="H483" s="45"/>
+      <c r="A483" s="48"/>
+      <c r="B483" s="48"/>
+      <c r="C483" s="48"/>
+      <c r="D483" s="48"/>
+      <c r="E483" s="48"/>
+      <c r="F483" s="48"/>
+      <c r="G483" s="48"/>
+      <c r="H483" s="48"/>
     </row>
     <row r="484" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A484" s="9" t="s">
@@ -7765,164 +7838,164 @@
       <c r="D484" s="9" t="s">
         <v>522</v>
       </c>
-      <c r="E484" s="45"/>
-      <c r="F484" s="45"/>
-      <c r="G484" s="45"/>
-      <c r="H484" s="45"/>
+      <c r="E484" s="48"/>
+      <c r="F484" s="48"/>
+      <c r="G484" s="48"/>
+      <c r="H484" s="48"/>
     </row>
     <row r="485" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A485" s="45" t="s">
+      <c r="A485" s="48" t="s">
         <v>523</v>
       </c>
-      <c r="B485" s="45" t="s">
+      <c r="B485" s="48" t="s">
         <v>524</v>
       </c>
-      <c r="C485" s="45" t="s">
+      <c r="C485" s="48" t="s">
         <v>525</v>
       </c>
-      <c r="D485" s="45" t="s">
+      <c r="D485" s="48" t="s">
         <v>526</v>
       </c>
-      <c r="E485" s="45"/>
-      <c r="F485" s="45"/>
-      <c r="G485" s="45"/>
-      <c r="H485" s="45"/>
+      <c r="E485" s="48"/>
+      <c r="F485" s="48"/>
+      <c r="G485" s="48"/>
+      <c r="H485" s="48"/>
     </row>
     <row r="486" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A486" s="45" t="s">
+      <c r="A486" s="48" t="s">
         <v>523</v>
       </c>
-      <c r="B486" s="45" t="s">
+      <c r="B486" s="48" t="s">
         <v>117</v>
       </c>
-      <c r="C486" s="45" t="s">
+      <c r="C486" s="48" t="s">
         <v>525</v>
       </c>
-      <c r="D486" s="45" t="s">
+      <c r="D486" s="48" t="s">
         <v>526</v>
       </c>
-      <c r="E486" s="45"/>
-      <c r="F486" s="45"/>
-      <c r="G486" s="45"/>
-      <c r="H486" s="45"/>
+      <c r="E486" s="48"/>
+      <c r="F486" s="48"/>
+      <c r="G486" s="48"/>
+      <c r="H486" s="48"/>
     </row>
     <row r="487" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A487" s="45" t="s">
+      <c r="A487" s="48" t="s">
         <v>527</v>
       </c>
-      <c r="B487" s="45" t="s">
+      <c r="B487" s="48" t="s">
         <v>528</v>
       </c>
-      <c r="C487" s="45" t="s">
+      <c r="C487" s="48" t="s">
         <v>356</v>
       </c>
-      <c r="D487" s="45" t="s">
+      <c r="D487" s="48" t="s">
         <v>529</v>
       </c>
-      <c r="E487" s="45"/>
-      <c r="F487" s="45"/>
-      <c r="G487" s="45"/>
-      <c r="H487" s="45"/>
+      <c r="E487" s="48"/>
+      <c r="F487" s="48"/>
+      <c r="G487" s="48"/>
+      <c r="H487" s="48"/>
     </row>
     <row r="488" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A488" s="45" t="s">
+      <c r="A488" s="48" t="s">
         <v>527</v>
       </c>
-      <c r="B488" s="45" t="s">
+      <c r="B488" s="48" t="s">
         <v>530</v>
       </c>
-      <c r="C488" s="45" t="s">
+      <c r="C488" s="48" t="s">
         <v>356</v>
       </c>
-      <c r="D488" s="45" t="s">
+      <c r="D488" s="48" t="s">
         <v>529</v>
       </c>
-      <c r="E488" s="45"/>
-      <c r="F488" s="45"/>
-      <c r="G488" s="45"/>
-      <c r="H488" s="45"/>
+      <c r="E488" s="48"/>
+      <c r="F488" s="48"/>
+      <c r="G488" s="48"/>
+      <c r="H488" s="48"/>
     </row>
     <row r="489" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A489" s="45" t="s">
+      <c r="A489" s="48" t="s">
         <v>124</v>
       </c>
-      <c r="B489" s="45" t="s">
+      <c r="B489" s="48" t="s">
         <v>531</v>
       </c>
-      <c r="C489" s="45" t="s">
+      <c r="C489" s="48" t="s">
         <v>532</v>
       </c>
-      <c r="D489" s="45" t="s">
+      <c r="D489" s="48" t="s">
         <v>526</v>
       </c>
-      <c r="E489" s="45"/>
-      <c r="F489" s="45"/>
-      <c r="G489" s="45"/>
-      <c r="H489" s="45"/>
+      <c r="E489" s="48"/>
+      <c r="F489" s="48"/>
+      <c r="G489" s="48"/>
+      <c r="H489" s="48"/>
     </row>
     <row r="490" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A490" s="45" t="s">
+      <c r="A490" s="48" t="s">
         <v>124</v>
       </c>
-      <c r="B490" s="45" t="s">
+      <c r="B490" s="48" t="s">
         <v>533</v>
       </c>
-      <c r="C490" s="45" t="s">
+      <c r="C490" s="48" t="s">
         <v>532</v>
       </c>
-      <c r="D490" s="45" t="s">
+      <c r="D490" s="48" t="s">
         <v>526</v>
       </c>
-      <c r="E490" s="45"/>
-      <c r="F490" s="45"/>
-      <c r="G490" s="45"/>
-      <c r="H490" s="45"/>
+      <c r="E490" s="48"/>
+      <c r="F490" s="48"/>
+      <c r="G490" s="48"/>
+      <c r="H490" s="48"/>
     </row>
     <row r="491" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A491" s="45" t="s">
+      <c r="A491" s="48" t="s">
         <v>534</v>
       </c>
-      <c r="B491" s="45" t="s">
+      <c r="B491" s="48" t="s">
         <v>535</v>
       </c>
-      <c r="C491" s="45" t="s">
+      <c r="C491" s="48" t="s">
         <v>536</v>
       </c>
-      <c r="D491" s="45" t="s">
+      <c r="D491" s="48" t="s">
         <v>537</v>
       </c>
-      <c r="E491" s="45"/>
+      <c r="E491" s="48"/>
     </row>
     <row r="492" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A492" s="45" t="s">
+      <c r="A492" s="48" t="s">
         <v>534</v>
       </c>
-      <c r="B492" s="45" t="s">
+      <c r="B492" s="48" t="s">
         <v>538</v>
       </c>
-      <c r="C492" s="45" t="s">
+      <c r="C492" s="48" t="s">
         <v>536</v>
       </c>
-      <c r="D492" s="45" t="s">
+      <c r="D492" s="48" t="s">
         <v>537</v>
       </c>
-      <c r="E492" s="45"/>
+      <c r="E492" s="48"/>
     </row>
     <row r="493" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A493" s="45"/>
-      <c r="B493" s="45"/>
-      <c r="C493" s="45"/>
-      <c r="D493" s="45"/>
-      <c r="E493" s="45"/>
+      <c r="A493" s="48"/>
+      <c r="B493" s="48"/>
+      <c r="C493" s="48"/>
+      <c r="D493" s="48"/>
+      <c r="E493" s="48"/>
     </row>
     <row r="494" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A494" s="39" t="s">
         <v>539</v>
       </c>
-      <c r="B494" s="45"/>
-      <c r="C494" s="45"/>
-      <c r="D494" s="45"/>
-      <c r="E494" s="45"/>
+      <c r="B494" s="48"/>
+      <c r="C494" s="48"/>
+      <c r="D494" s="48"/>
+      <c r="E494" s="48"/>
     </row>
     <row r="495" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A495" s="39" t="s">
@@ -7934,152 +8007,152 @@
       <c r="C495" s="39" t="s">
         <v>541</v>
       </c>
-      <c r="D495" s="45"/>
-      <c r="E495" s="45"/>
+      <c r="D495" s="48"/>
+      <c r="E495" s="48"/>
     </row>
     <row r="496" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A496" s="45" t="s">
+      <c r="A496" s="48" t="s">
         <v>530</v>
       </c>
       <c r="B496" s="39" t="str">
         <f>INDEX(A485:A492,MATCH(A496,B485:B492,0))</f>
         <v>Thomas Nguyen</v>
       </c>
-      <c r="C496" s="45" t="s">
+      <c r="C496" s="48" t="s">
         <v>542</v>
       </c>
-      <c r="D496" s="45"/>
-      <c r="E496" s="45"/>
+      <c r="D496" s="48"/>
+      <c r="E496" s="48"/>
     </row>
     <row r="497" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A497" s="45" t="s">
+      <c r="A497" s="48" t="s">
         <v>535</v>
       </c>
       <c r="B497" s="39" t="str">
         <f>INDEX(A485:A492,MATCH(A497,B485:B492,0))</f>
         <v>David Brown</v>
       </c>
-      <c r="C497" s="45" t="s">
+      <c r="C497" s="48" t="s">
         <v>543</v>
       </c>
-      <c r="D497" s="45"/>
-      <c r="E497" s="45"/>
+      <c r="D497" s="48"/>
+      <c r="E497" s="48"/>
     </row>
     <row r="498" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A498" s="45" t="s">
+      <c r="A498" s="48" t="s">
         <v>117</v>
       </c>
       <c r="B498" s="39" t="str">
         <f>INDEX(A485:A492,MATCH(A498,B485:B492,0))</f>
         <v>Maria Gomez</v>
       </c>
-      <c r="C498" s="45" t="s">
+      <c r="C498" s="48" t="s">
         <v>544</v>
       </c>
-      <c r="D498" s="45"/>
-      <c r="E498" s="45"/>
+      <c r="D498" s="48"/>
+      <c r="E498" s="48"/>
     </row>
     <row r="499" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A499" s="45"/>
-      <c r="B499" s="45"/>
-      <c r="C499" s="45"/>
-      <c r="D499" s="45"/>
-      <c r="E499" s="45"/>
+      <c r="A499" s="48"/>
+      <c r="B499" s="48"/>
+      <c r="C499" s="48"/>
+      <c r="D499" s="48"/>
+      <c r="E499" s="48"/>
     </row>
     <row r="500" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A500" s="45"/>
-      <c r="B500" s="49" t="str">
+      <c r="A500" s="48"/>
+      <c r="B500" s="56" t="str">
         <f ca="1">_xlfn.FORMULATEXT(B496)</f>
         <v>=INDEX(A485:A492,MATCH(A496,B485:B492,0))</v>
       </c>
-      <c r="C500" s="49"/>
-      <c r="D500" s="45"/>
-      <c r="E500" s="45"/>
+      <c r="C500" s="56"/>
+      <c r="D500" s="48"/>
+      <c r="E500" s="48"/>
     </row>
     <row r="501" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A501" s="45"/>
-      <c r="B501" s="45"/>
-      <c r="C501" s="45"/>
-      <c r="D501" s="45"/>
-      <c r="E501" s="45"/>
+      <c r="A501" s="48"/>
+      <c r="B501" s="48"/>
+      <c r="C501" s="48"/>
+      <c r="D501" s="48"/>
+      <c r="E501" s="48"/>
     </row>
     <row r="502" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A502" s="28" t="s">
         <v>548</v>
       </c>
-      <c r="B502" s="45"/>
-      <c r="C502" s="45"/>
-      <c r="D502" s="45"/>
-      <c r="E502" s="45"/>
+      <c r="B502" s="48"/>
+      <c r="C502" s="48"/>
+      <c r="D502" s="48"/>
+      <c r="E502" s="48"/>
     </row>
     <row r="503" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A503" s="45" t="s">
+      <c r="A503" s="48" t="s">
         <v>549</v>
       </c>
-      <c r="B503" s="45"/>
-      <c r="C503" s="45"/>
-      <c r="D503" s="45"/>
-      <c r="E503" s="45"/>
+      <c r="B503" s="48"/>
+      <c r="C503" s="48"/>
+      <c r="D503" s="48"/>
+      <c r="E503" s="48"/>
     </row>
     <row r="504" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A504" s="45"/>
-      <c r="B504" s="45"/>
-      <c r="C504" s="45"/>
-      <c r="D504" s="45"/>
-      <c r="E504" s="45"/>
+      <c r="A504" s="48"/>
+      <c r="B504" s="48"/>
+      <c r="C504" s="48"/>
+      <c r="D504" s="48"/>
+      <c r="E504" s="48"/>
     </row>
     <row r="505" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A505" s="45" t="s">
+      <c r="A505" s="48" t="s">
         <v>550</v>
       </c>
     </row>
     <row r="506" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A506" s="45"/>
+      <c r="A506" s="48"/>
     </row>
     <row r="507" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A507" s="45" t="s">
+      <c r="A507" s="48" t="s">
         <v>591</v>
       </c>
     </row>
     <row r="508" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A508" s="45" t="s">
+      <c r="A508" s="48" t="s">
         <v>592</v>
       </c>
     </row>
     <row r="509" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A509" s="45"/>
+      <c r="A509" s="48"/>
     </row>
     <row r="510" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A510" s="45" t="s">
+      <c r="A510" s="48" t="s">
         <v>593</v>
       </c>
     </row>
     <row r="511" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A511" s="45"/>
+      <c r="A511" s="48"/>
     </row>
     <row r="512" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A512" s="45" t="s">
+      <c r="A512" s="48" t="s">
         <v>551</v>
       </c>
     </row>
     <row r="513" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A513" s="45"/>
+      <c r="A513" s="48"/>
     </row>
     <row r="514" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A514" s="45" t="s">
+      <c r="A514" s="48" t="s">
         <v>594</v>
       </c>
     </row>
     <row r="515" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A515" s="45" t="s">
+      <c r="A515" s="48" t="s">
         <v>595</v>
       </c>
     </row>
     <row r="516" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A516" s="45"/>
+      <c r="A516" s="48"/>
     </row>
     <row r="517" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A517" s="45" t="s">
+      <c r="A517" s="48" t="s">
         <v>552</v>
       </c>
     </row>
@@ -8097,123 +8170,123 @@
         <v>554</v>
       </c>
     </row>
-    <row r="520" spans="1:4" s="45" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A520" s="45" t="s">
+    <row r="520" spans="1:4" s="48" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A520" s="48" t="s">
         <v>555</v>
       </c>
-      <c r="B520" s="45" t="s">
+      <c r="B520" s="48" t="s">
         <v>556</v>
       </c>
-      <c r="C520" s="45" t="s">
+      <c r="C520" s="48" t="s">
         <v>557</v>
       </c>
-      <c r="D520" s="45" t="s">
+      <c r="D520" s="48" t="s">
         <v>558</v>
       </c>
     </row>
-    <row r="521" spans="1:4" s="45" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A521" s="45" t="s">
+    <row r="521" spans="1:4" s="48" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A521" s="48" t="s">
         <v>559</v>
       </c>
-      <c r="B521" s="45" t="s">
+      <c r="B521" s="48" t="s">
         <v>560</v>
       </c>
-      <c r="C521" s="45" t="s">
+      <c r="C521" s="48" t="s">
         <v>561</v>
       </c>
-      <c r="D521" s="45" t="s">
+      <c r="D521" s="48" t="s">
         <v>558</v>
       </c>
     </row>
-    <row r="522" spans="1:4" s="45" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A522" s="45" t="s">
+    <row r="522" spans="1:4" s="48" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A522" s="48" t="s">
         <v>562</v>
       </c>
-      <c r="B522" s="45" t="s">
+      <c r="B522" s="48" t="s">
         <v>563</v>
       </c>
-      <c r="C522" s="45" t="s">
+      <c r="C522" s="48" t="s">
         <v>564</v>
       </c>
-      <c r="D522" s="45" t="s">
+      <c r="D522" s="48" t="s">
         <v>565</v>
       </c>
     </row>
-    <row r="523" spans="1:4" s="45" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A523" s="45" t="s">
+    <row r="523" spans="1:4" s="48" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A523" s="48" t="s">
         <v>566</v>
       </c>
-      <c r="B523" s="45" t="s">
+      <c r="B523" s="48" t="s">
         <v>567</v>
       </c>
-      <c r="C523" s="45" t="s">
+      <c r="C523" s="48" t="s">
         <v>568</v>
       </c>
-      <c r="D523" s="45" t="s">
+      <c r="D523" s="48" t="s">
         <v>569</v>
       </c>
     </row>
-    <row r="524" spans="1:4" s="45" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A524" s="45" t="s">
+    <row r="524" spans="1:4" s="48" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A524" s="48" t="s">
         <v>570</v>
       </c>
-      <c r="B524" s="45" t="s">
+      <c r="B524" s="48" t="s">
         <v>571</v>
       </c>
-      <c r="C524" s="45" t="s">
+      <c r="C524" s="48" t="s">
         <v>572</v>
       </c>
-      <c r="D524" s="45" t="s">
+      <c r="D524" s="48" t="s">
         <v>565</v>
       </c>
     </row>
-    <row r="525" spans="1:4" s="45" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A525" s="45" t="s">
+    <row r="525" spans="1:4" s="48" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A525" s="48" t="s">
         <v>573</v>
       </c>
-      <c r="B525" s="45" t="s">
+      <c r="B525" s="48" t="s">
         <v>574</v>
       </c>
-      <c r="C525" s="45" t="s">
+      <c r="C525" s="48" t="s">
         <v>575</v>
       </c>
-      <c r="D525" s="45" t="s">
+      <c r="D525" s="48" t="s">
         <v>558</v>
       </c>
     </row>
-    <row r="526" spans="1:4" s="45" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A526" s="45" t="s">
+    <row r="526" spans="1:4" s="48" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A526" s="48" t="s">
         <v>576</v>
       </c>
-      <c r="B526" s="45" t="s">
+      <c r="B526" s="48" t="s">
         <v>577</v>
       </c>
-      <c r="C526" s="45" t="s">
+      <c r="C526" s="48" t="s">
         <v>578</v>
       </c>
-      <c r="D526" s="45" t="s">
+      <c r="D526" s="48" t="s">
         <v>569</v>
       </c>
     </row>
-    <row r="527" spans="1:4" s="45" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A527" s="45" t="s">
+    <row r="527" spans="1:4" s="48" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A527" s="48" t="s">
         <v>579</v>
       </c>
-      <c r="B527" s="45" t="s">
+      <c r="B527" s="48" t="s">
         <v>580</v>
       </c>
-      <c r="C527" s="45" t="s">
+      <c r="C527" s="48" t="s">
         <v>581</v>
       </c>
-      <c r="D527" s="45" t="s">
+      <c r="D527" s="48" t="s">
         <v>565</v>
       </c>
     </row>
     <row r="528" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A528" s="45"/>
-      <c r="B528" s="45"/>
-      <c r="C528" s="45"/>
-      <c r="D528" s="45"/>
+      <c r="A528" s="48"/>
+      <c r="B528" s="48"/>
+      <c r="C528" s="48"/>
+      <c r="D528" s="48"/>
     </row>
     <row r="529" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A529" s="40" t="s">
@@ -8229,54 +8302,54 @@
         <v>584</v>
       </c>
     </row>
-    <row r="530" spans="1:5" s="45" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A530" s="45" t="s">
+    <row r="530" spans="1:5" s="48" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A530" s="48" t="s">
         <v>585</v>
       </c>
-      <c r="B530" s="45" t="s">
+      <c r="B530" s="48" t="s">
         <v>577</v>
       </c>
       <c r="C530" s="4" t="str">
         <f>INDEX(A520:A527,MATCH(B530,B520:B527,0))</f>
         <v>ingrid.larsen@northwind.com</v>
       </c>
-      <c r="D530" s="45" t="s">
+      <c r="D530" s="48" t="s">
         <v>586</v>
       </c>
     </row>
-    <row r="531" spans="1:5" s="45" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A531" s="45" t="s">
+    <row r="531" spans="1:5" s="48" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A531" s="48" t="s">
         <v>587</v>
       </c>
-      <c r="B531" s="45" t="s">
+      <c r="B531" s="48" t="s">
         <v>560</v>
       </c>
       <c r="C531" s="4" t="str">
         <f t="shared" ref="C531:C532" si="19">INDEX(A521:A528,MATCH(B531,B521:B528,0))</f>
         <v>bianca.chen@northwind.com</v>
       </c>
-      <c r="D531" s="45" t="s">
+      <c r="D531" s="48" t="s">
         <v>588</v>
       </c>
     </row>
-    <row r="532" spans="1:5" s="45" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A532" s="45" t="s">
+    <row r="532" spans="1:5" s="48" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A532" s="48" t="s">
         <v>589</v>
       </c>
-      <c r="B532" s="45" t="s">
+      <c r="B532" s="48" t="s">
         <v>563</v>
       </c>
       <c r="C532" s="4" t="str">
         <f t="shared" si="19"/>
         <v>diego.souza@northwind.com</v>
       </c>
-      <c r="D532" s="45" t="s">
+      <c r="D532" s="48" t="s">
         <v>590</v>
       </c>
     </row>
-    <row r="533" spans="1:5" s="45" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="534" spans="1:5" s="45" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C534" s="45" t="str">
+    <row r="533" spans="1:5" s="48" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="534" spans="1:5" s="48" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="C534" s="48" t="str">
         <f ca="1">_xlfn.FORMULATEXT(C530)</f>
         <v>=INDEX(A520:A527,MATCH(B530,B520:B527,0))</v>
       </c>
@@ -8309,142 +8382,142 @@
       </c>
     </row>
     <row r="540" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A540" s="45" t="s">
+      <c r="A540" s="48" t="s">
         <v>602</v>
       </c>
-      <c r="B540" s="45">
+      <c r="B540" s="48">
         <v>5</v>
       </c>
-      <c r="C540" s="45">
+      <c r="C540" s="48">
         <v>7</v>
       </c>
-      <c r="D540" s="45">
+      <c r="D540" s="48">
         <v>10</v>
       </c>
-      <c r="E540" s="45">
+      <c r="E540" s="48">
         <v>14</v>
       </c>
     </row>
     <row r="541" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A541" s="45" t="s">
+      <c r="A541" s="48" t="s">
         <v>603</v>
       </c>
-      <c r="B541" s="45">
+      <c r="B541" s="48">
         <v>9</v>
       </c>
-      <c r="C541" s="45">
+      <c r="C541" s="48">
         <v>12</v>
       </c>
-      <c r="D541" s="45">
+      <c r="D541" s="48">
         <v>16</v>
       </c>
-      <c r="E541" s="45">
+      <c r="E541" s="48">
         <v>22</v>
       </c>
     </row>
     <row r="542" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A542" s="45" t="s">
+      <c r="A542" s="48" t="s">
         <v>604</v>
       </c>
-      <c r="B542" s="45">
+      <c r="B542" s="48">
         <v>14</v>
       </c>
-      <c r="C542" s="45">
+      <c r="C542" s="48">
         <v>19</v>
       </c>
-      <c r="D542" s="45">
+      <c r="D542" s="48">
         <v>28</v>
       </c>
-      <c r="E542" s="45">
+      <c r="E542" s="48">
         <v>40</v>
       </c>
     </row>
     <row r="543" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A543" s="45" t="s">
+      <c r="A543" s="48" t="s">
         <v>605</v>
       </c>
-      <c r="B543" s="45">
+      <c r="B543" s="48">
         <v>24</v>
       </c>
-      <c r="C543" s="45">
+      <c r="C543" s="48">
         <v>33</v>
       </c>
-      <c r="D543" s="45">
+      <c r="D543" s="48">
         <v>48</v>
       </c>
-      <c r="E543" s="45">
+      <c r="E543" s="48">
         <v>68</v>
       </c>
     </row>
     <row r="544" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A544" s="45" t="s">
+      <c r="A544" s="48" t="s">
         <v>606</v>
       </c>
-      <c r="B544" s="45">
+      <c r="B544" s="48">
         <v>30</v>
       </c>
-      <c r="C544" s="45">
+      <c r="C544" s="48">
         <v>42</v>
       </c>
-      <c r="D544" s="45">
+      <c r="D544" s="48">
         <v>60</v>
       </c>
-      <c r="E544" s="45">
+      <c r="E544" s="48">
         <v>85</v>
       </c>
     </row>
     <row r="545" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A545" s="45"/>
-      <c r="B545" s="45"/>
-      <c r="C545" s="45"/>
-      <c r="D545" s="45"/>
-      <c r="E545" s="45"/>
+      <c r="A545" s="48"/>
+      <c r="B545" s="48"/>
+      <c r="C545" s="48"/>
+      <c r="D545" s="48"/>
+      <c r="E545" s="48"/>
     </row>
     <row r="546" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A546" s="45" t="s">
+      <c r="A546" s="48" t="s">
         <v>607</v>
       </c>
-      <c r="B546" s="45" t="s">
+      <c r="B546" s="48" t="s">
         <v>604</v>
       </c>
-      <c r="C546" s="45"/>
-      <c r="D546" s="45"/>
-      <c r="E546" s="45"/>
+      <c r="C546" s="48"/>
+      <c r="D546" s="48"/>
+      <c r="E546" s="48"/>
     </row>
     <row r="547" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A547" s="45" t="s">
+      <c r="A547" s="48" t="s">
         <v>608</v>
       </c>
-      <c r="B547" s="45" t="s">
+      <c r="B547" s="48" t="s">
         <v>600</v>
       </c>
-      <c r="C547" s="45"/>
-      <c r="D547" s="45"/>
-      <c r="E547" s="45"/>
+      <c r="C547" s="48"/>
+      <c r="D547" s="48"/>
+      <c r="E547" s="48"/>
     </row>
     <row r="548" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A548" s="45" t="s">
+      <c r="A548" s="48" t="s">
         <v>609</v>
       </c>
       <c r="B548" s="4">
         <f>INDEX(B540:E544,MATCH(B546,A540:A544),MATCH(B547,B539:E539,0))</f>
         <v>28</v>
       </c>
-      <c r="C548" s="45"/>
-      <c r="D548" s="45"/>
-      <c r="E548" s="45"/>
+      <c r="C548" s="48"/>
+      <c r="D548" s="48"/>
+      <c r="E548" s="48"/>
     </row>
     <row r="550" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B550" s="51" t="str">
+      <c r="B550" s="58" t="str">
         <f ca="1">_xlfn.FORMULATEXT(B548)</f>
         <v>=INDEX(B540:E544,MATCH(B546,A540:A544),MATCH(B547,B539:E539,0))</v>
       </c>
     </row>
     <row r="551" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B551" s="51"/>
+      <c r="B551" s="58"/>
     </row>
     <row r="552" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B552" s="51"/>
+      <c r="B552" s="58"/>
     </row>
     <row r="553" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A553" s="28" t="s">
@@ -8632,19 +8705,19 @@
       </c>
     </row>
     <row r="572" spans="1:5" s="2" customFormat="1" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B572" s="49" t="str">
+      <c r="B572" s="56" t="str">
         <f ca="1">_xlfn.FORMULATEXT(B571)</f>
         <v>=XLOOKUP(B568,A558:A564,XLOOKUP(B569,B557:E557,B558:E564))</v>
       </c>
     </row>
     <row r="573" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B573" s="49"/>
+      <c r="B573" s="56"/>
     </row>
     <row r="574" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B574" s="49"/>
+      <c r="B574" s="56"/>
     </row>
     <row r="575" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B575" s="44"/>
+      <c r="B575" s="47"/>
     </row>
     <row r="576" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A576" s="28" t="s">
@@ -8904,13 +8977,13 @@
       <c r="A600" s="2" t="s">
         <v>654</v>
       </c>
-      <c r="B600" s="47" t="s">
+      <c r="B600" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="C600" s="47" t="s">
+      <c r="C600" s="45" t="s">
         <v>655</v>
       </c>
-      <c r="D600" s="47" t="s">
+      <c r="D600" s="45" t="s">
         <v>656</v>
       </c>
     </row>
@@ -9006,16 +9079,16 @@
     </row>
     <row r="607" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="608" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A608" s="46" t="s">
+      <c r="A608" s="44" t="s">
         <v>663</v>
       </c>
-      <c r="B608" s="47">
+      <c r="B608" s="45">
         <v>10</v>
       </c>
-      <c r="C608" s="46" t="s">
+      <c r="C608" s="44" t="s">
         <v>664</v>
       </c>
-      <c r="D608" s="47">
+      <c r="D608" s="45">
         <v>2500</v>
       </c>
     </row>
@@ -9052,24 +9125,24 @@
       <c r="E615" s="6" t="s">
         <v>668</v>
       </c>
-      <c r="F615" s="48" t="s">
+      <c r="F615" s="46" t="s">
         <v>669</v>
       </c>
     </row>
     <row r="616" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A616" s="45">
+      <c r="A616" s="48">
         <v>10021</v>
       </c>
-      <c r="B616" s="45" t="s">
+      <c r="B616" s="48" t="s">
         <v>637</v>
       </c>
-      <c r="C616" s="45" t="s">
+      <c r="C616" s="48" t="s">
         <v>670</v>
       </c>
       <c r="D616" s="16">
         <v>45932</v>
       </c>
-      <c r="E616" s="45">
+      <c r="E616" s="48">
         <v>8500</v>
       </c>
       <c r="F616" s="4" t="str">
@@ -9078,19 +9151,19 @@
       </c>
     </row>
     <row r="617" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A617" s="45">
+      <c r="A617" s="48">
         <v>10022</v>
       </c>
-      <c r="B617" s="45" t="s">
+      <c r="B617" s="48" t="s">
         <v>671</v>
       </c>
-      <c r="C617" s="45" t="s">
+      <c r="C617" s="48" t="s">
         <v>672</v>
       </c>
       <c r="D617" s="16">
         <v>45933</v>
       </c>
-      <c r="E617" s="45">
+      <c r="E617" s="48">
         <v>4200</v>
       </c>
       <c r="F617" s="4" t="str">
@@ -9099,19 +9172,19 @@
       </c>
     </row>
     <row r="618" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A618" s="45">
+      <c r="A618" s="48">
         <v>10023</v>
       </c>
-      <c r="B618" s="45" t="s">
+      <c r="B618" s="48" t="s">
         <v>637</v>
       </c>
-      <c r="C618" s="45" t="s">
+      <c r="C618" s="48" t="s">
         <v>673</v>
       </c>
       <c r="D618" s="16">
         <v>45933</v>
       </c>
-      <c r="E618" s="45">
+      <c r="E618" s="48">
         <v>12500</v>
       </c>
       <c r="F618" s="4" t="str">
@@ -9120,19 +9193,19 @@
       </c>
     </row>
     <row r="619" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A619" s="45">
+      <c r="A619" s="48">
         <v>10024</v>
       </c>
-      <c r="B619" s="45" t="s">
+      <c r="B619" s="48" t="s">
         <v>637</v>
       </c>
-      <c r="C619" s="45" t="s">
+      <c r="C619" s="48" t="s">
         <v>674</v>
       </c>
       <c r="D619" s="16">
         <v>45934</v>
       </c>
-      <c r="E619" s="45">
+      <c r="E619" s="48">
         <v>9999</v>
       </c>
       <c r="F619" s="4" t="str">
@@ -9141,19 +9214,19 @@
       </c>
     </row>
     <row r="620" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A620" s="45">
+      <c r="A620" s="48">
         <v>10025</v>
       </c>
-      <c r="B620" s="45" t="s">
+      <c r="B620" s="48" t="s">
         <v>671</v>
       </c>
-      <c r="C620" s="45" t="s">
+      <c r="C620" s="48" t="s">
         <v>670</v>
       </c>
       <c r="D620" s="16">
         <v>45934</v>
       </c>
-      <c r="E620" s="45">
+      <c r="E620" s="48">
         <v>10000</v>
       </c>
       <c r="F620" s="4" t="str">
@@ -9162,19 +9235,19 @@
       </c>
     </row>
     <row r="621" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A621" s="45">
+      <c r="A621" s="48">
         <v>10026</v>
       </c>
-      <c r="B621" s="45" t="s">
+      <c r="B621" s="48" t="s">
         <v>637</v>
       </c>
-      <c r="C621" s="45" t="s">
+      <c r="C621" s="48" t="s">
         <v>672</v>
       </c>
       <c r="D621" s="16">
         <v>45935</v>
       </c>
-      <c r="E621" s="45">
+      <c r="E621" s="48">
         <v>10001</v>
       </c>
       <c r="F621" s="4" t="str">
@@ -9183,19 +9256,19 @@
       </c>
     </row>
     <row r="622" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A622" s="45">
+      <c r="A622" s="48">
         <v>10027</v>
       </c>
-      <c r="B622" s="45" t="s">
+      <c r="B622" s="48" t="s">
         <v>637</v>
       </c>
-      <c r="C622" s="45" t="s">
+      <c r="C622" s="48" t="s">
         <v>673</v>
       </c>
       <c r="D622" s="16">
         <v>45936</v>
       </c>
-      <c r="E622" s="45">
+      <c r="E622" s="48">
         <v>17500</v>
       </c>
       <c r="F622" s="4" t="str">
@@ -9204,19 +9277,19 @@
       </c>
     </row>
     <row r="623" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A623" s="45">
+      <c r="A623" s="48">
         <v>10028</v>
       </c>
-      <c r="B623" s="45" t="s">
+      <c r="B623" s="48" t="s">
         <v>637</v>
       </c>
-      <c r="C623" s="45" t="s">
+      <c r="C623" s="48" t="s">
         <v>674</v>
       </c>
       <c r="D623" s="16">
         <v>45936</v>
       </c>
-      <c r="E623" s="45">
+      <c r="E623" s="48">
         <v>5400</v>
       </c>
       <c r="F623" s="4" t="str">
@@ -9225,19 +9298,19 @@
       </c>
     </row>
     <row r="624" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A624" s="45">
+      <c r="A624" s="48">
         <v>10029</v>
       </c>
-      <c r="B624" s="45" t="s">
+      <c r="B624" s="48" t="s">
         <v>671</v>
       </c>
-      <c r="C624" s="45" t="s">
+      <c r="C624" s="48" t="s">
         <v>672</v>
       </c>
       <c r="D624" s="16">
         <v>45937</v>
       </c>
-      <c r="E624" s="45">
+      <c r="E624" s="48">
         <v>15000</v>
       </c>
       <c r="F624" s="4" t="str">
@@ -9246,19 +9319,19 @@
       </c>
     </row>
     <row r="625" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A625" s="45">
+      <c r="A625" s="48">
         <v>10030</v>
       </c>
-      <c r="B625" s="45" t="s">
+      <c r="B625" s="48" t="s">
         <v>637</v>
       </c>
-      <c r="C625" s="45" t="s">
+      <c r="C625" s="48" t="s">
         <v>670</v>
       </c>
       <c r="D625" s="16">
         <v>45937</v>
       </c>
-      <c r="E625" s="45">
+      <c r="E625" s="48">
         <v>10250</v>
       </c>
       <c r="F625" s="4" t="str">
@@ -9271,11 +9344,11 @@
       <c r="B627" s="2"/>
       <c r="C627" s="2"/>
       <c r="D627" s="2"/>
-      <c r="E627" s="49" t="str">
+      <c r="E627" s="56" t="str">
         <f ca="1">_xlfn.FORMULATEXT(F616)</f>
         <v>=IF(OR(E616&gt;10000,B616="VIP"),"High","Standard")</v>
       </c>
-      <c r="F627" s="49"/>
+      <c r="F627" s="56"/>
       <c r="G627" s="2"/>
     </row>
     <row r="628" spans="1:7" x14ac:dyDescent="0.3">
@@ -9656,17 +9729,17 @@
       <c r="A659" s="9" t="s">
         <v>700</v>
       </c>
-      <c r="B659" s="53">
+      <c r="B659" s="49">
         <v>45731</v>
       </c>
-      <c r="C659" s="45"/>
-      <c r="D659" s="45"/>
+      <c r="C659" s="48"/>
+      <c r="D659" s="48"/>
     </row>
     <row r="660" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A660" s="45"/>
-      <c r="B660" s="45"/>
-      <c r="C660" s="45"/>
-      <c r="D660" s="45"/>
+      <c r="A660" s="48"/>
+      <c r="B660" s="48"/>
+      <c r="C660" s="48"/>
+      <c r="D660" s="48"/>
     </row>
     <row r="661" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A661" s="9" t="s">
@@ -9678,18 +9751,18 @@
       <c r="C661" s="9" t="s">
         <v>307</v>
       </c>
-      <c r="D661" s="54" t="s">
+      <c r="D661" s="50" t="s">
         <v>703</v>
       </c>
     </row>
     <row r="662" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A662" s="45" t="s">
+      <c r="A662" s="48" t="s">
         <v>704</v>
       </c>
       <c r="B662" s="16">
         <v>45716</v>
       </c>
-      <c r="C662" s="45" t="s">
+      <c r="C662" s="48" t="s">
         <v>705</v>
       </c>
       <c r="D662" s="4" t="str">
@@ -9698,13 +9771,13 @@
       </c>
     </row>
     <row r="663" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A663" s="45" t="s">
+      <c r="A663" s="48" t="s">
         <v>706</v>
       </c>
       <c r="B663" s="16">
         <v>45688</v>
       </c>
-      <c r="C663" s="45" t="s">
+      <c r="C663" s="48" t="s">
         <v>707</v>
       </c>
       <c r="D663" s="4" t="str">
@@ -9713,13 +9786,13 @@
       </c>
     </row>
     <row r="664" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A664" s="45" t="s">
+      <c r="A664" s="48" t="s">
         <v>708</v>
       </c>
       <c r="B664" s="16">
         <v>45726</v>
       </c>
-      <c r="C664" s="45" t="s">
+      <c r="C664" s="48" t="s">
         <v>709</v>
       </c>
       <c r="D664" s="4" t="str">
@@ -9728,13 +9801,13 @@
       </c>
     </row>
     <row r="665" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A665" s="45" t="s">
+      <c r="A665" s="48" t="s">
         <v>710</v>
       </c>
       <c r="B665" s="16">
         <v>45703</v>
       </c>
-      <c r="C665" s="45" t="s">
+      <c r="C665" s="48" t="s">
         <v>711</v>
       </c>
       <c r="D665" s="4" t="str">
@@ -9743,13 +9816,13 @@
       </c>
     </row>
     <row r="666" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A666" s="45" t="s">
+      <c r="A666" s="48" t="s">
         <v>712</v>
       </c>
       <c r="B666" s="16">
         <v>45717</v>
       </c>
-      <c r="C666" s="45" t="s">
+      <c r="C666" s="48" t="s">
         <v>713</v>
       </c>
       <c r="D666" s="4" t="str">
@@ -9758,13 +9831,13 @@
       </c>
     </row>
     <row r="667" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A667" s="45" t="s">
+      <c r="A667" s="48" t="s">
         <v>714</v>
       </c>
       <c r="B667" s="16">
         <v>45698</v>
       </c>
-      <c r="C667" s="45" t="s">
+      <c r="C667" s="48" t="s">
         <v>707</v>
       </c>
       <c r="D667" s="4" t="str">
@@ -9774,11 +9847,11 @@
     </row>
     <row r="668" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="669" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C669" s="50" t="str">
+      <c r="C669" s="54" t="str">
         <f ca="1">_xlfn.FORMULATEXT(D662)</f>
         <v>=IF(NOT(C662="Paid"),"Overdue","")</v>
       </c>
-      <c r="D669" s="50"/>
+      <c r="D669" s="54"/>
     </row>
     <row r="670" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="671" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -9802,161 +9875,161 @@
       <c r="C674" s="6" t="s">
         <v>718</v>
       </c>
-      <c r="D674" s="55" t="s">
+      <c r="D674" s="51" t="s">
         <v>719</v>
       </c>
-      <c r="E674" s="55" t="s">
+      <c r="E674" s="51" t="s">
         <v>720</v>
       </c>
     </row>
     <row r="675" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A675" s="45" t="s">
+      <c r="A675" s="48" t="s">
         <v>524</v>
       </c>
-      <c r="B675" s="45">
+      <c r="B675" s="48">
         <v>96</v>
       </c>
       <c r="C675" s="4" t="str">
         <f>IF(B675&gt;=90,"A",IF(B675&gt;=80,"B",IF(B675&gt;=70,"C",IF(B675&gt;=60,"D","F"))))</f>
         <v>A</v>
       </c>
-      <c r="D675" s="45" t="s">
+      <c r="D675" s="48" t="s">
         <v>721</v>
       </c>
-      <c r="E675" s="45">
+      <c r="E675" s="48">
         <v>90</v>
       </c>
     </row>
     <row r="676" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A676" s="45" t="s">
+      <c r="A676" s="48" t="s">
         <v>530</v>
       </c>
-      <c r="B676" s="45">
+      <c r="B676" s="48">
         <v>88</v>
       </c>
       <c r="C676" s="4" t="str">
         <f t="shared" ref="C676:C682" si="24">IF(B676&gt;=90,"A",IF(B676&gt;=80,"B",IF(B676&gt;=70,"C",IF(B676&gt;=60,"D","F"))))</f>
         <v>B</v>
       </c>
-      <c r="D676" s="45" t="s">
+      <c r="D676" s="48" t="s">
         <v>722</v>
       </c>
-      <c r="E676" s="45">
+      <c r="E676" s="48">
         <v>80</v>
       </c>
     </row>
     <row r="677" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A677" s="45" t="s">
+      <c r="A677" s="48" t="s">
         <v>640</v>
       </c>
-      <c r="B677" s="45">
+      <c r="B677" s="48">
         <v>73</v>
       </c>
       <c r="C677" s="4" t="str">
         <f t="shared" si="24"/>
         <v>C</v>
       </c>
-      <c r="D677" s="45" t="s">
+      <c r="D677" s="48" t="s">
         <v>723</v>
       </c>
-      <c r="E677" s="45">
+      <c r="E677" s="48">
         <v>70</v>
       </c>
     </row>
     <row r="678" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A678" s="45" t="s">
+      <c r="A678" s="48" t="s">
         <v>120</v>
       </c>
-      <c r="B678" s="45">
+      <c r="B678" s="48">
         <v>67</v>
       </c>
       <c r="C678" s="4" t="str">
         <f t="shared" si="24"/>
         <v>D</v>
       </c>
-      <c r="D678" s="45" t="s">
+      <c r="D678" s="48" t="s">
         <v>724</v>
       </c>
-      <c r="E678" s="45">
+      <c r="E678" s="48">
         <v>60</v>
       </c>
     </row>
     <row r="679" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A679" s="45" t="s">
+      <c r="A679" s="48" t="s">
         <v>646</v>
       </c>
-      <c r="B679" s="45">
+      <c r="B679" s="48">
         <v>59</v>
       </c>
       <c r="C679" s="4" t="str">
         <f t="shared" si="24"/>
         <v>F</v>
       </c>
-      <c r="D679" s="45" t="s">
+      <c r="D679" s="48" t="s">
         <v>725</v>
       </c>
-      <c r="E679" s="45">
+      <c r="E679" s="48">
         <v>0</v>
       </c>
     </row>
     <row r="680" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A680" s="45" t="s">
+      <c r="A680" s="48" t="s">
         <v>531</v>
       </c>
-      <c r="B680" s="45">
+      <c r="B680" s="48">
         <v>80</v>
       </c>
       <c r="C680" s="4" t="str">
         <f t="shared" si="24"/>
         <v>B</v>
       </c>
-      <c r="D680" s="45"/>
-      <c r="E680" s="45"/>
+      <c r="D680" s="48"/>
+      <c r="E680" s="48"/>
     </row>
     <row r="681" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A681" s="45" t="s">
+      <c r="A681" s="48" t="s">
         <v>631</v>
       </c>
-      <c r="B681" s="45">
+      <c r="B681" s="48">
         <v>90</v>
       </c>
       <c r="C681" s="4" t="str">
         <f t="shared" si="24"/>
         <v>A</v>
       </c>
-      <c r="D681" s="45"/>
-      <c r="E681" s="45"/>
+      <c r="D681" s="48"/>
+      <c r="E681" s="48"/>
     </row>
     <row r="682" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A682" s="45" t="s">
+      <c r="A682" s="48" t="s">
         <v>726</v>
       </c>
-      <c r="B682" s="45">
+      <c r="B682" s="48">
         <v>70</v>
       </c>
       <c r="C682" s="4" t="str">
         <f t="shared" si="24"/>
         <v>C</v>
       </c>
-      <c r="D682" s="45"/>
-      <c r="E682" s="45"/>
+      <c r="D682" s="48"/>
+      <c r="E682" s="48"/>
     </row>
     <row r="683" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="684" spans="1:5" s="2" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B684" s="50" t="str">
+      <c r="B684" s="54" t="str">
         <f ca="1">_xlfn.FORMULATEXT(C675)</f>
         <v>=IF(B675&gt;=90,"A",IF(B675&gt;=80,"B",IF(B675&gt;=70,"C",IF(B675&gt;=60,"D","F"))))</v>
       </c>
-      <c r="C684" s="50"/>
+      <c r="C684" s="54"/>
     </row>
     <row r="685" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A685" s="56" t="s">
+      <c r="A685" s="52" t="s">
         <v>728</v>
       </c>
-      <c r="B685" s="50" t="s">
+      <c r="B685" s="54" t="s">
         <v>727</v>
       </c>
-      <c r="C685" s="50"/>
+      <c r="C685" s="54"/>
     </row>
     <row r="686" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="687" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -9965,12 +10038,12 @@
       </c>
     </row>
     <row r="688" spans="1:5" s="2" customFormat="1" ht="124.2" x14ac:dyDescent="0.3">
-      <c r="A688" s="45" t="s">
+      <c r="A688" s="48" t="s">
         <v>730</v>
       </c>
     </row>
     <row r="689" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A689" s="45"/>
+      <c r="A689" s="48"/>
     </row>
     <row r="690" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A690" s="6" t="s">
@@ -9982,315 +10055,666 @@
       <c r="C690" s="6" t="s">
         <v>732</v>
       </c>
-      <c r="D690" s="55" t="s">
+      <c r="D690" s="51" t="s">
         <v>667</v>
       </c>
-      <c r="E690" s="55" t="s">
+      <c r="E690" s="51" t="s">
         <v>733</v>
       </c>
-      <c r="F690" s="55" t="s">
+      <c r="F690" s="51" t="s">
         <v>734</v>
       </c>
     </row>
     <row r="691" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A691" s="45" t="s">
+      <c r="A691" s="48" t="s">
         <v>117</v>
       </c>
-      <c r="B691" s="45">
+      <c r="B691" s="48">
         <v>8200</v>
       </c>
       <c r="C691" s="4">
         <f>IF(B691&gt;=$E$691,B691*$F$691,IF(B691&gt;=$E$692,B691*$F$692,B691*$F$693))</f>
         <v>246</v>
       </c>
-      <c r="D691" s="45" t="s">
+      <c r="D691" s="48" t="s">
         <v>735</v>
       </c>
-      <c r="E691" s="45">
+      <c r="E691" s="48">
         <v>25000</v>
       </c>
-      <c r="F691" s="45">
+      <c r="F691" s="48">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="692" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A692" s="45" t="s">
+      <c r="A692" s="48" t="s">
         <v>736</v>
       </c>
-      <c r="B692" s="45">
+      <c r="B692" s="48">
         <v>12000</v>
       </c>
       <c r="C692" s="4">
         <f t="shared" ref="C692:C698" si="25">IF(B692&gt;=$E$691,B692*$F$691,IF(B692&gt;=$E$692,B692*$F$692,B692*$F$693))</f>
         <v>600</v>
       </c>
-      <c r="D692" s="45" t="s">
+      <c r="D692" s="48" t="s">
         <v>737</v>
       </c>
-      <c r="E692" s="45">
+      <c r="E692" s="48">
         <v>10000</v>
       </c>
-      <c r="F692" s="45">
+      <c r="F692" s="48">
         <v>0.05</v>
       </c>
     </row>
     <row r="693" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A693" s="45" t="s">
+      <c r="A693" s="48" t="s">
         <v>738</v>
       </c>
-      <c r="B693" s="45">
+      <c r="B693" s="48">
         <v>25750</v>
       </c>
       <c r="C693" s="4">
         <f t="shared" si="25"/>
         <v>1802.5000000000002</v>
       </c>
-      <c r="D693" s="45" t="s">
+      <c r="D693" s="48" t="s">
         <v>739</v>
       </c>
-      <c r="E693" s="45">
+      <c r="E693" s="48">
         <v>0</v>
       </c>
-      <c r="F693" s="45">
+      <c r="F693" s="48">
         <v>0.03</v>
       </c>
     </row>
     <row r="694" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A694" s="45" t="s">
+      <c r="A694" s="48" t="s">
         <v>740</v>
       </c>
-      <c r="B694" s="45">
+      <c r="B694" s="48">
         <v>18150</v>
       </c>
       <c r="C694" s="4">
         <f t="shared" si="25"/>
         <v>907.5</v>
       </c>
-      <c r="D694" s="45"/>
-      <c r="E694" s="45"/>
-      <c r="F694" s="45"/>
+      <c r="D694" s="48"/>
+      <c r="E694" s="48"/>
+      <c r="F694" s="48"/>
     </row>
     <row r="695" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A695" s="45" t="s">
+      <c r="A695" s="48" t="s">
         <v>741</v>
       </c>
-      <c r="B695" s="45">
+      <c r="B695" s="48">
         <v>9500</v>
       </c>
       <c r="C695" s="4">
         <f t="shared" si="25"/>
         <v>285</v>
       </c>
-      <c r="D695" s="45"/>
-      <c r="E695" s="45"/>
-      <c r="F695" s="45"/>
+      <c r="D695" s="48"/>
+      <c r="E695" s="48"/>
+      <c r="F695" s="48"/>
     </row>
     <row r="696" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A696" s="45" t="s">
+      <c r="A696" s="48" t="s">
         <v>742</v>
       </c>
-      <c r="B696" s="45">
+      <c r="B696" s="48">
         <v>30500</v>
       </c>
       <c r="C696" s="4">
         <f t="shared" si="25"/>
         <v>2135</v>
       </c>
-      <c r="D696" s="45"/>
-      <c r="E696" s="45"/>
-      <c r="F696" s="45"/>
+      <c r="D696" s="48"/>
+      <c r="E696" s="48"/>
+      <c r="F696" s="48"/>
     </row>
     <row r="697" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A697" s="45" t="s">
+      <c r="A697" s="48" t="s">
         <v>743</v>
       </c>
-      <c r="B697" s="45">
+      <c r="B697" s="48">
         <v>24000</v>
       </c>
       <c r="C697" s="4">
         <f t="shared" si="25"/>
         <v>1200</v>
       </c>
-      <c r="D697" s="45"/>
-      <c r="E697" s="45"/>
-      <c r="F697" s="45"/>
+      <c r="D697" s="48"/>
+      <c r="E697" s="48"/>
+      <c r="F697" s="48"/>
     </row>
     <row r="698" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A698" s="45" t="s">
+      <c r="A698" s="48" t="s">
         <v>744</v>
       </c>
-      <c r="B698" s="45">
+      <c r="B698" s="48">
         <v>10000</v>
       </c>
       <c r="C698" s="4">
         <f t="shared" si="25"/>
         <v>500</v>
       </c>
-      <c r="D698" s="45"/>
-      <c r="E698" s="45"/>
-      <c r="F698" s="45"/>
+      <c r="D698" s="48"/>
+      <c r="E698" s="48"/>
+      <c r="F698" s="48"/>
     </row>
     <row r="699" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A699" s="45"/>
-      <c r="B699" s="45"/>
-      <c r="C699" s="45"/>
-      <c r="D699" s="45"/>
-      <c r="E699" s="45"/>
-      <c r="F699" s="45"/>
+      <c r="A699" s="48"/>
+      <c r="B699" s="48"/>
+      <c r="C699" s="48"/>
+      <c r="D699" s="48"/>
+      <c r="E699" s="48"/>
+      <c r="F699" s="48"/>
     </row>
     <row r="700" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A700" s="57" t="s">
+      <c r="A700" s="53" t="s">
         <v>745</v>
       </c>
-      <c r="B700" s="58" t="s">
+      <c r="B700" s="55" t="s">
         <v>746</v>
       </c>
-      <c r="C700" s="58"/>
-      <c r="D700" s="45"/>
-      <c r="E700" s="45"/>
-      <c r="F700" s="45"/>
+      <c r="C700" s="55"/>
+      <c r="D700" s="48"/>
+      <c r="E700" s="48"/>
+      <c r="F700" s="48"/>
     </row>
     <row r="701" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="702" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B702" s="50" t="str">
+      <c r="B702" s="54" t="str">
         <f ca="1">_xlfn.FORMULATEXT(C691)</f>
         <v>=IF(B691&gt;=$E$691,B691*$F$691,IF(B691&gt;=$E$692,B691*$F$692,B691*$F$693))</v>
       </c>
-      <c r="C702" s="50"/>
-    </row>
-    <row r="703" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="704" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="705" s="2" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="706" s="2" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="707" s="2" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="708" s="2" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="709" s="2" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="710" s="2" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="711" s="2" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="712" s="2" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="713" s="2" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="714" s="2" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="715" s="2" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="716" s="2" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="717" s="2" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="718" s="2" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="719" s="2" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="720" s="2" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="721" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="722" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="723" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="724" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="725" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="726" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="727" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="728" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="729" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="730" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A730" s="2"/>
-      <c r="B730" s="2"/>
-      <c r="C730" s="2"/>
-      <c r="D730" s="2"/>
-      <c r="E730" s="2"/>
-      <c r="F730" s="2"/>
-      <c r="G730" s="2"/>
-    </row>
-    <row r="731" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A731" s="2"/>
-      <c r="B731" s="2"/>
-      <c r="C731" s="2"/>
-      <c r="D731" s="2"/>
-      <c r="E731" s="2"/>
-      <c r="F731" s="2"/>
-      <c r="G731" s="2"/>
-    </row>
-    <row r="732" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A732" s="2"/>
-      <c r="B732" s="2"/>
-      <c r="C732" s="2"/>
-      <c r="D732" s="2"/>
-      <c r="E732" s="2"/>
-      <c r="F732" s="2"/>
-      <c r="G732" s="2"/>
-    </row>
-    <row r="733" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A733" s="2"/>
-      <c r="B733" s="2"/>
-      <c r="C733" s="2"/>
-      <c r="D733" s="2"/>
-      <c r="E733" s="2"/>
-      <c r="F733" s="2"/>
-      <c r="G733" s="2"/>
-    </row>
-    <row r="734" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A734" s="2"/>
-      <c r="B734" s="2"/>
-      <c r="C734" s="2"/>
-      <c r="D734" s="2"/>
-      <c r="E734" s="2"/>
-      <c r="F734" s="2"/>
-      <c r="G734" s="2"/>
-    </row>
-    <row r="735" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A735" s="2"/>
-      <c r="B735" s="2"/>
-      <c r="C735" s="2"/>
-      <c r="D735" s="2"/>
-      <c r="E735" s="2"/>
-      <c r="F735" s="2"/>
-      <c r="G735" s="2"/>
-    </row>
-    <row r="736" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A736" s="2"/>
-      <c r="B736" s="2"/>
-      <c r="C736" s="2"/>
-      <c r="D736" s="2"/>
-      <c r="E736" s="2"/>
-      <c r="F736" s="2"/>
-      <c r="G736" s="2"/>
-    </row>
-    <row r="737" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A737" s="2"/>
-      <c r="B737" s="2"/>
-      <c r="C737" s="2"/>
-      <c r="D737" s="2"/>
-      <c r="E737" s="2"/>
-      <c r="F737" s="2"/>
-      <c r="G737" s="2"/>
-    </row>
-    <row r="738" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A738" s="2"/>
-      <c r="B738" s="2"/>
-      <c r="C738" s="2"/>
-      <c r="D738" s="2"/>
-      <c r="E738" s="2"/>
-      <c r="F738" s="2"/>
-      <c r="G738" s="2"/>
-    </row>
-    <row r="739" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A739" s="2"/>
-      <c r="B739" s="2"/>
-      <c r="C739" s="2"/>
-      <c r="D739" s="2"/>
-      <c r="E739" s="2"/>
-      <c r="F739" s="2"/>
-      <c r="G739" s="2"/>
+      <c r="C702" s="54"/>
+    </row>
+    <row r="703" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A703" s="48"/>
+    </row>
+    <row r="704" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A704" s="28" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="705" spans="1:9" s="2" customFormat="1" ht="151.80000000000001" x14ac:dyDescent="0.3">
+      <c r="A705" s="48" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="706" spans="1:9" s="2" customFormat="1" ht="96.6" x14ac:dyDescent="0.3">
+      <c r="A706" s="48" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="707" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A707" s="48"/>
+    </row>
+    <row r="708" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A708" s="6" t="s">
+        <v>750</v>
+      </c>
+      <c r="B708" s="6" t="s">
+        <v>751</v>
+      </c>
+      <c r="C708" s="6" t="s">
+        <v>752</v>
+      </c>
+      <c r="D708" s="48"/>
+      <c r="E708" s="51" t="s">
+        <v>753</v>
+      </c>
+      <c r="F708" s="51" t="s">
+        <v>754</v>
+      </c>
+      <c r="G708" s="48"/>
+      <c r="H708" s="48"/>
+      <c r="I708" s="48"/>
+    </row>
+    <row r="709" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A709" s="48" t="s">
+        <v>755</v>
+      </c>
+      <c r="B709" s="48">
+        <v>0.8</v>
+      </c>
+      <c r="C709" s="4" t="str" cm="1">
+        <f t="array" ref="C709">_xlfn.IFS(B709&lt;=$E$709,$F$709,B709&lt;=$E$710,$F$710,B709&lt;=$E$711,$F$711,B709&lt;=$E$712,$F$712,B709&gt;$E$712,$F$713)</f>
+        <v>Letter</v>
+      </c>
+      <c r="D709" s="48"/>
+      <c r="E709" s="48">
+        <v>1</v>
+      </c>
+      <c r="F709" s="48" t="s">
+        <v>756</v>
+      </c>
+      <c r="G709" s="48"/>
+      <c r="H709" s="48"/>
+      <c r="I709" s="48"/>
+    </row>
+    <row r="710" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A710" s="48" t="s">
+        <v>757</v>
+      </c>
+      <c r="B710" s="48">
+        <v>3.5</v>
+      </c>
+      <c r="C710" s="4" t="str" cm="1">
+        <f t="array" ref="C710">_xlfn.IFS(B710&lt;=$E$709,$F$709,B710&lt;=$E$710,$F$710,B710&lt;=$E$711,$F$711,B710&lt;=$E$712,$F$712,B710&gt;$E$712,$F$713)</f>
+        <v>Standard</v>
+      </c>
+      <c r="D710" s="48"/>
+      <c r="E710" s="48">
+        <v>5</v>
+      </c>
+      <c r="F710" s="48" t="s">
+        <v>637</v>
+      </c>
+      <c r="G710" s="48"/>
+      <c r="H710" s="48"/>
+      <c r="I710" s="48"/>
+    </row>
+    <row r="711" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A711" s="48" t="s">
+        <v>758</v>
+      </c>
+      <c r="B711" s="48">
+        <v>12</v>
+      </c>
+      <c r="C711" s="4" t="str" cm="1">
+        <f t="array" ref="C711">_xlfn.IFS(B711&lt;=$E$709,$F$709,B711&lt;=$E$710,$F$710,B711&lt;=$E$711,$F$711,B711&lt;=$E$712,$F$712,B711&gt;$E$712,$F$713)</f>
+        <v>Ground</v>
+      </c>
+      <c r="D711" s="48"/>
+      <c r="E711" s="48">
+        <v>20</v>
+      </c>
+      <c r="F711" s="48" t="s">
+        <v>759</v>
+      </c>
+      <c r="G711" s="48"/>
+      <c r="H711" s="48"/>
+      <c r="I711" s="48"/>
+    </row>
+    <row r="712" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A712" s="48" t="s">
+        <v>760</v>
+      </c>
+      <c r="B712" s="48">
+        <v>0.3</v>
+      </c>
+      <c r="C712" s="4" t="str" cm="1">
+        <f t="array" ref="C712">_xlfn.IFS(B712&lt;=$E$709,$F$709,B712&lt;=$E$710,$F$710,B712&lt;=$E$711,$F$711,B712&lt;=$E$712,$F$712,B712&gt;$E$712,$F$713)</f>
+        <v>Letter</v>
+      </c>
+      <c r="D712" s="48"/>
+      <c r="E712" s="48">
+        <v>50</v>
+      </c>
+      <c r="F712" s="48" t="s">
+        <v>761</v>
+      </c>
+      <c r="G712" s="48"/>
+      <c r="H712" s="48"/>
+      <c r="I712" s="48"/>
+    </row>
+    <row r="713" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A713" s="48" t="s">
+        <v>762</v>
+      </c>
+      <c r="B713" s="48">
+        <v>28</v>
+      </c>
+      <c r="C713" s="4" t="str" cm="1">
+        <f t="array" ref="C713">_xlfn.IFS(B713&lt;=$E$709,$F$709,B713&lt;=$E$710,$F$710,B713&lt;=$E$711,$F$711,B713&lt;=$E$712,$F$712,B713&gt;$E$712,$F$713)</f>
+        <v>Freight</v>
+      </c>
+      <c r="D713" s="48"/>
+      <c r="E713" s="48"/>
+      <c r="F713" s="48" t="s">
+        <v>763</v>
+      </c>
+      <c r="G713" s="48"/>
+      <c r="H713" s="48"/>
+      <c r="I713" s="48"/>
+    </row>
+    <row r="714" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A714" s="48" t="s">
+        <v>764</v>
+      </c>
+      <c r="B714" s="48">
+        <v>7</v>
+      </c>
+      <c r="C714" s="4" t="str" cm="1">
+        <f t="array" ref="C714">_xlfn.IFS(B714&lt;=$E$709,$F$709,B714&lt;=$E$710,$F$710,B714&lt;=$E$711,$F$711,B714&lt;=$E$712,$F$712,B714&gt;$E$712,$F$713)</f>
+        <v>Ground</v>
+      </c>
+      <c r="D714" s="48"/>
+      <c r="E714" s="48"/>
+      <c r="F714" s="48"/>
+      <c r="G714" s="48"/>
+      <c r="H714" s="48"/>
+      <c r="I714" s="48"/>
+    </row>
+    <row r="715" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A715" s="48" t="s">
+        <v>765</v>
+      </c>
+      <c r="B715" s="48">
+        <v>55</v>
+      </c>
+      <c r="C715" s="4" t="str" cm="1">
+        <f t="array" ref="C715">_xlfn.IFS(B715&lt;=$E$709,$F$709,B715&lt;=$E$710,$F$710,B715&lt;=$E$711,$F$711,B715&lt;=$E$712,$F$712,B715&gt;$E$712,$F$713)</f>
+        <v>Heavy freight</v>
+      </c>
+      <c r="D715" s="48"/>
+      <c r="E715" s="48"/>
+      <c r="F715" s="48"/>
+      <c r="G715" s="48"/>
+      <c r="H715" s="48"/>
+      <c r="I715" s="48"/>
+    </row>
+    <row r="716" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A716" s="48" t="s">
+        <v>766</v>
+      </c>
+      <c r="B716" s="48">
+        <v>18</v>
+      </c>
+      <c r="C716" s="4" t="str" cm="1">
+        <f t="array" ref="C716">_xlfn.IFS(B716&lt;=$E$709,$F$709,B716&lt;=$E$710,$F$710,B716&lt;=$E$711,$F$711,B716&lt;=$E$712,$F$712,B716&gt;$E$712,$F$713)</f>
+        <v>Ground</v>
+      </c>
+      <c r="D716" s="48"/>
+      <c r="E716" s="48"/>
+      <c r="F716" s="48"/>
+      <c r="G716" s="48"/>
+      <c r="H716" s="48"/>
+      <c r="I716" s="48"/>
+    </row>
+    <row r="717" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A717" s="48"/>
+      <c r="B717" s="48"/>
+      <c r="C717" s="48"/>
+      <c r="D717" s="48"/>
+      <c r="E717" s="48"/>
+      <c r="F717" s="48"/>
+      <c r="G717" s="48"/>
+      <c r="H717" s="48"/>
+      <c r="I717" s="48"/>
+    </row>
+    <row r="718" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A718" s="48"/>
+      <c r="B718" s="59"/>
+      <c r="C718" s="59"/>
+      <c r="D718" s="48"/>
+      <c r="E718" s="48"/>
+      <c r="F718" s="48"/>
+      <c r="G718" s="48"/>
+      <c r="H718" s="48"/>
+      <c r="I718" s="48"/>
+    </row>
+    <row r="719" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A719" s="48"/>
+      <c r="B719" s="48"/>
+      <c r="C719" s="48"/>
+      <c r="D719" s="48"/>
+      <c r="E719" s="48"/>
+      <c r="F719" s="48"/>
+      <c r="G719" s="48"/>
+      <c r="H719" s="48"/>
+      <c r="I719" s="48"/>
+    </row>
+    <row r="720" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A720" s="48"/>
+      <c r="B720" s="48"/>
+      <c r="C720" s="48"/>
+      <c r="D720" s="48"/>
+      <c r="E720" s="48"/>
+      <c r="F720" s="48"/>
+      <c r="G720" s="48"/>
+      <c r="H720" s="48"/>
+      <c r="I720" s="48"/>
+    </row>
+    <row r="721" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A721" s="48"/>
+      <c r="B721" s="48"/>
+      <c r="C721" s="48"/>
+      <c r="D721" s="48"/>
+      <c r="E721" s="48"/>
+      <c r="F721" s="48"/>
+      <c r="G721" s="48"/>
+      <c r="H721" s="48"/>
+      <c r="I721" s="48"/>
+    </row>
+    <row r="722" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A722" s="48"/>
+      <c r="B722" s="48"/>
+      <c r="C722" s="48"/>
+      <c r="D722" s="48"/>
+      <c r="E722" s="48"/>
+      <c r="F722" s="48"/>
+      <c r="G722" s="48"/>
+      <c r="H722" s="48"/>
+      <c r="I722" s="48"/>
+    </row>
+    <row r="723" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A723" s="48"/>
+      <c r="B723" s="48"/>
+      <c r="C723" s="48"/>
+      <c r="D723" s="48"/>
+      <c r="E723" s="48"/>
+      <c r="F723" s="48"/>
+      <c r="G723" s="48"/>
+      <c r="H723" s="48"/>
+      <c r="I723" s="48"/>
+    </row>
+    <row r="724" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A724" s="48"/>
+      <c r="B724" s="48"/>
+      <c r="C724" s="48"/>
+      <c r="D724" s="48"/>
+      <c r="E724" s="48"/>
+      <c r="F724" s="48"/>
+      <c r="G724" s="48"/>
+      <c r="H724" s="48"/>
+      <c r="I724" s="48"/>
+    </row>
+    <row r="725" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A725" s="48"/>
+      <c r="B725" s="48"/>
+      <c r="C725" s="48"/>
+      <c r="D725" s="48"/>
+      <c r="E725" s="48"/>
+      <c r="F725" s="48"/>
+      <c r="G725" s="48"/>
+      <c r="H725" s="48"/>
+      <c r="I725" s="48"/>
+    </row>
+    <row r="726" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A726" s="48"/>
+      <c r="B726" s="48"/>
+      <c r="C726" s="48"/>
+      <c r="D726" s="48"/>
+      <c r="E726" s="48"/>
+      <c r="F726" s="48"/>
+      <c r="G726" s="48"/>
+      <c r="H726" s="48"/>
+      <c r="I726" s="48"/>
+    </row>
+    <row r="727" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A727" s="48"/>
+      <c r="B727" s="48"/>
+      <c r="C727" s="48"/>
+      <c r="D727" s="48"/>
+      <c r="E727" s="48"/>
+      <c r="F727" s="48"/>
+      <c r="G727" s="48"/>
+      <c r="H727" s="48"/>
+      <c r="I727" s="48"/>
+    </row>
+    <row r="728" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A728" s="48"/>
+      <c r="B728" s="48"/>
+      <c r="C728" s="48"/>
+      <c r="D728" s="48"/>
+      <c r="E728" s="48"/>
+      <c r="F728" s="48"/>
+      <c r="G728" s="48"/>
+      <c r="H728" s="48"/>
+      <c r="I728" s="48"/>
+    </row>
+    <row r="729" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A729" s="48"/>
+      <c r="B729" s="48"/>
+      <c r="C729" s="48"/>
+      <c r="D729" s="48"/>
+      <c r="E729" s="48"/>
+      <c r="F729" s="48"/>
+      <c r="G729" s="48"/>
+      <c r="H729" s="48"/>
+      <c r="I729" s="48"/>
+    </row>
+    <row r="730" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A730" s="48"/>
+      <c r="B730" s="48"/>
+      <c r="C730" s="48"/>
+      <c r="D730" s="48"/>
+      <c r="E730" s="48"/>
+      <c r="F730" s="48"/>
+      <c r="G730" s="48"/>
+      <c r="H730" s="48"/>
+      <c r="I730" s="48"/>
+    </row>
+    <row r="731" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A731" s="48"/>
+      <c r="B731" s="48"/>
+      <c r="C731" s="48"/>
+      <c r="D731" s="48"/>
+      <c r="E731" s="48"/>
+      <c r="F731" s="48"/>
+      <c r="G731" s="48"/>
+      <c r="H731" s="48"/>
+      <c r="I731" s="48"/>
+    </row>
+    <row r="732" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A732" s="48"/>
+      <c r="B732" s="48"/>
+      <c r="C732" s="48"/>
+      <c r="D732" s="48"/>
+      <c r="E732" s="48"/>
+      <c r="F732" s="48"/>
+      <c r="G732" s="48"/>
+      <c r="H732" s="48"/>
+      <c r="I732" s="48"/>
+    </row>
+    <row r="733" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A733" s="48"/>
+      <c r="B733" s="48"/>
+      <c r="C733" s="48"/>
+      <c r="D733" s="48"/>
+      <c r="E733" s="48"/>
+      <c r="F733" s="48"/>
+      <c r="G733" s="48"/>
+      <c r="H733" s="48"/>
+      <c r="I733" s="48"/>
+    </row>
+    <row r="734" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A734" s="48"/>
+      <c r="B734" s="48"/>
+      <c r="C734" s="48"/>
+      <c r="D734" s="48"/>
+      <c r="E734" s="48"/>
+      <c r="F734" s="48"/>
+      <c r="G734" s="48"/>
+      <c r="H734" s="48"/>
+      <c r="I734" s="48"/>
+    </row>
+    <row r="735" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A735" s="48"/>
+      <c r="B735" s="48"/>
+      <c r="C735" s="48"/>
+      <c r="D735" s="48"/>
+      <c r="E735" s="48"/>
+      <c r="F735" s="48"/>
+      <c r="G735" s="48"/>
+      <c r="H735" s="48"/>
+      <c r="I735" s="48"/>
+    </row>
+    <row r="736" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A736" s="48"/>
+      <c r="B736" s="48"/>
+      <c r="C736" s="48"/>
+      <c r="D736" s="48"/>
+      <c r="E736" s="48"/>
+      <c r="F736" s="48"/>
+      <c r="G736" s="48"/>
+      <c r="H736" s="48"/>
+      <c r="I736" s="48"/>
+    </row>
+    <row r="737" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A737" s="48"/>
+      <c r="B737" s="48"/>
+      <c r="C737" s="48"/>
+      <c r="D737" s="48"/>
+      <c r="E737" s="48"/>
+      <c r="F737" s="48"/>
+      <c r="G737" s="48"/>
+      <c r="H737" s="48"/>
+      <c r="I737" s="48"/>
+    </row>
+    <row r="738" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A738" s="48"/>
+      <c r="B738" s="48"/>
+      <c r="C738" s="48"/>
+      <c r="D738" s="48"/>
+      <c r="E738" s="48"/>
+      <c r="F738" s="48"/>
+      <c r="G738" s="48"/>
+      <c r="H738" s="48"/>
+      <c r="I738" s="48"/>
+    </row>
+    <row r="739" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A739" s="48"/>
+      <c r="B739" s="48"/>
+      <c r="C739" s="48"/>
+      <c r="D739" s="48"/>
+      <c r="E739" s="48"/>
+      <c r="F739" s="48"/>
+      <c r="G739" s="48"/>
+      <c r="H739" s="48"/>
+      <c r="I739" s="48"/>
+    </row>
+    <row r="740" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A740" s="48"/>
+      <c r="B740" s="48"/>
+      <c r="C740" s="48"/>
+      <c r="D740" s="48"/>
+      <c r="E740" s="48"/>
+      <c r="F740" s="48"/>
+      <c r="G740" s="48"/>
+      <c r="H740" s="48"/>
+      <c r="I740" s="48"/>
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="E627:F627"/>
+    <mergeCell ref="B572:B574"/>
+    <mergeCell ref="B550:B552"/>
+    <mergeCell ref="B500:C500"/>
+    <mergeCell ref="C236:C237"/>
+    <mergeCell ref="B256:C256"/>
+    <mergeCell ref="C359:C360"/>
+    <mergeCell ref="C476:E476"/>
+    <mergeCell ref="C477:E477"/>
     <mergeCell ref="C669:D669"/>
     <mergeCell ref="B684:C684"/>
     <mergeCell ref="B685:C685"/>
     <mergeCell ref="B700:C700"/>
     <mergeCell ref="B702:C702"/>
-    <mergeCell ref="C236:C237"/>
-    <mergeCell ref="B256:C256"/>
-    <mergeCell ref="C359:C360"/>
-    <mergeCell ref="C476:E476"/>
-    <mergeCell ref="C477:E477"/>
-    <mergeCell ref="E627:F627"/>
-    <mergeCell ref="B572:B574"/>
-    <mergeCell ref="B550:B552"/>
-    <mergeCell ref="B500:C500"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Daily Excel/Online Practice Excel.xlsx
+++ b/Daily Excel/Online Practice Excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d58d4d655bee1e81/Desktop/Github/Daily_practice/Daily Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="274" documentId="11_F25DC773A252ABDACC1048BD89DC52D45ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AFC609AE-257E-4F25-85DD-14A22100BFFA}"/>
+  <xr:revisionPtr revIDLastSave="289" documentId="11_F25DC773A252ABDACC1048BD89DC52D45ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{09165068-B08E-4F4C-BB84-B867E6A1CED2}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="987" uniqueCount="767">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1046" uniqueCount="804">
   <si>
     <t>Double-click on cell A1 in the spreadsheet editor. Replace the placeholder text with:</t>
   </si>
@@ -2628,6 +2628,193 @@
   <si>
     <t>PKG-008</t>
   </si>
+  <si>
+    <t>SWITCH for department budget codes</t>
+  </si>
+  <si>
+    <t>When a quarterly budget report uses short department codes, SWITCH is a clean way to translate each code into a readable label. It is often easier to audit than a long chain of nested IF statements because each exact match is paired directly with the result you want to return.
+The SWITCH function works like this:
+=SWITCH(value, match1, result1, match2, result2, ..., default)
+It checks one value, looks for an exact match in your list, and returns the corresponding result. This is useful when one code should always map to one label.</t>
+  </si>
+  <si>
+    <t>In this budget review, column E already shows each employee's quarterly budget amount. Your job is to label each budget line correctly by translating the department codes in column B for each employee row. Use the lookup table in A12:C16 as your mapping guide.
+In C2, use SWITCH to return the full department name for the code in B2, using the mappings shown in A12:B16.
+In D2, use SWITCH again to return the budget category for the same code, using the mappings shown in A12:C16.
+Fill both formulas down through row 9.
+Use one SWITCH formula for the department name column and a separate SWITCH formula for the budget category column. The same department code should drive both outputs, but each column needs its own result list.</t>
+  </si>
+  <si>
+    <t>Department name</t>
+  </si>
+  <si>
+    <t>Budget category</t>
+  </si>
+  <si>
+    <t>Quarterly budget</t>
+  </si>
+  <si>
+    <t>Maya Chen</t>
+  </si>
+  <si>
+    <t>MKT</t>
+  </si>
+  <si>
+    <t>$18,000</t>
+  </si>
+  <si>
+    <t>ENG</t>
+  </si>
+  <si>
+    <t>$85,000</t>
+  </si>
+  <si>
+    <t>Priya Patel</t>
+  </si>
+  <si>
+    <t>FIN</t>
+  </si>
+  <si>
+    <t>$42,000</t>
+  </si>
+  <si>
+    <t>OPS</t>
+  </si>
+  <si>
+    <t>$36,000</t>
+  </si>
+  <si>
+    <t>Elena Garcia</t>
+  </si>
+  <si>
+    <t>$24,000</t>
+  </si>
+  <si>
+    <t>Noah Davis</t>
+  </si>
+  <si>
+    <t>$79,000</t>
+  </si>
+  <si>
+    <t>Ava Wilson</t>
+  </si>
+  <si>
+    <t>$15,000</t>
+  </si>
+  <si>
+    <t>Ethan Clark</t>
+  </si>
+  <si>
+    <t>$12,000</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Growth</t>
+  </si>
+  <si>
+    <t>Engineering</t>
+  </si>
+  <si>
+    <t>Human Resources</t>
+  </si>
+  <si>
+    <t>Basic IFERROR exercise</t>
+  </si>
+  <si>
+    <t>In this exercise, we're looking at the IFERROR function. This function can be handy when you expect errors to exist, but you want to handle them gracefully.</t>
+  </si>
+  <si>
+    <t>Guests</t>
+  </si>
+  <si>
+    <t>Drinks</t>
+  </si>
+  <si>
+    <t>Drinks per guest</t>
+  </si>
+  <si>
+    <r>
+      <t>In the exercise, we are expecting an error, namely a </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri Light"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>#DIV/0!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri Light"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t> error that you get when you divide a number by 0. Since that's not allowed in mathematics, the error is reasonable, yet we still would like to return something other than an error. That's where IFERROR comes in.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Return the number of </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri Light"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Drinks per guest</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri Light"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t> in cells C2:C4. For each row, divide the number of drinks by the number of guests, and wrap that division in IFERROR so the formula returns the division result when there is no error and 0 otherwise.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Rows 2 and 3 should return the normal division result. Row 4 has 0 guests, so your IFERROR formula should return 0 instead of a </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri Light"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>#DIV/0!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri Light"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t> error.</t>
+    </r>
+  </si>
+  <si>
+    <t>s</t>
+  </si>
 </sst>
 </file>
 
@@ -2636,7 +2823,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;₹&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2684,6 +2871,14 @@
       <i/>
       <sz val="10"/>
       <color rgb="FF444444"/>
+      <name val="Calibri Light"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="Calibri Light"/>
       <family val="2"/>
       <scheme val="major"/>
@@ -2847,7 +3042,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -2985,12 +3180,6 @@
     <xf numFmtId="0" fontId="1" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -3007,22 +3196,31 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3304,7 +3502,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W740"/>
+  <dimension ref="A1:W759"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="149.88671875" style="1" bestFit="1" customWidth="1"/>
@@ -3421,32 +3619,32 @@
       <c r="W16" s="26"/>
     </row>
     <row r="18" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A18" s="48">
+      <c r="A18" s="53">
         <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A19" s="48">
+      <c r="A19" s="53">
         <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A20" s="48">
+      <c r="A20" s="53">
         <v>35</v>
       </c>
     </row>
     <row r="21" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A21" s="48">
+      <c r="A21" s="53">
         <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A22" s="48">
+      <c r="A22" s="53">
         <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A23" s="48"/>
+      <c r="A23" s="53"/>
     </row>
     <row r="24" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A24" s="4">
@@ -3496,7 +3694,7 @@
       </c>
     </row>
     <row r="28" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A28" s="48" t="s">
+      <c r="A28" s="53" t="s">
         <v>11</v>
       </c>
       <c r="B28" s="7">
@@ -3511,7 +3709,7 @@
       </c>
     </row>
     <row r="29" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A29" s="48" t="s">
+      <c r="A29" s="53" t="s">
         <v>12</v>
       </c>
       <c r="B29" s="7">
@@ -3526,7 +3724,7 @@
       </c>
     </row>
     <row r="30" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A30" s="48" t="s">
+      <c r="A30" s="53" t="s">
         <v>13</v>
       </c>
       <c r="B30" s="7">
@@ -3541,7 +3739,7 @@
       </c>
     </row>
     <row r="31" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A31" s="48" t="s">
+      <c r="A31" s="53" t="s">
         <v>14</v>
       </c>
       <c r="B31" s="7">
@@ -3556,7 +3754,7 @@
       </c>
     </row>
     <row r="32" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A32" s="48" t="s">
+      <c r="A32" s="53" t="s">
         <v>15</v>
       </c>
       <c r="B32" s="7">
@@ -3571,7 +3769,7 @@
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" s="48" t="s">
+      <c r="A33" s="53" t="s">
         <v>16</v>
       </c>
       <c r="B33" s="7">
@@ -3586,7 +3784,7 @@
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A34" s="48"/>
+      <c r="A34" s="53"/>
       <c r="B34" s="7"/>
       <c r="C34" s="7"/>
       <c r="D34" s="8"/>
@@ -3613,7 +3811,7 @@
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A39" s="48" t="s">
+      <c r="A39" s="53" t="s">
         <v>20</v>
       </c>
       <c r="B39" s="10">
@@ -3625,7 +3823,7 @@
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A40" s="48" t="s">
+      <c r="A40" s="53" t="s">
         <v>21</v>
       </c>
       <c r="B40" s="10">
@@ -3637,7 +3835,7 @@
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A41" s="48" t="s">
+      <c r="A41" s="53" t="s">
         <v>22</v>
       </c>
       <c r="B41" s="10">
@@ -3649,7 +3847,7 @@
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A42" s="48" t="s">
+      <c r="A42" s="53" t="s">
         <v>23</v>
       </c>
       <c r="B42" s="10">
@@ -3661,7 +3859,7 @@
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A43" s="48" t="s">
+      <c r="A43" s="53" t="s">
         <v>24</v>
       </c>
       <c r="B43" s="10">
@@ -3673,7 +3871,7 @@
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A44" s="48" t="s">
+      <c r="A44" s="53" t="s">
         <v>25</v>
       </c>
       <c r="B44" s="10">
@@ -3685,10 +3883,10 @@
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A45" s="48" t="s">
+      <c r="A45" s="53" t="s">
         <v>26</v>
       </c>
-      <c r="B45" s="48">
+      <c r="B45" s="53">
         <v>0</v>
       </c>
       <c r="C45" s="12">
@@ -3724,7 +3922,7 @@
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A51" s="48" t="s">
+      <c r="A51" s="53" t="s">
         <v>33</v>
       </c>
       <c r="B51" s="13">
@@ -3740,7 +3938,7 @@
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A52" s="48" t="s">
+      <c r="A52" s="53" t="s">
         <v>34</v>
       </c>
       <c r="B52" s="13">
@@ -3756,7 +3954,7 @@
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A53" s="48" t="s">
+      <c r="A53" s="53" t="s">
         <v>35</v>
       </c>
       <c r="B53" s="13">
@@ -3772,7 +3970,7 @@
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A54" s="48" t="s">
+      <c r="A54" s="53" t="s">
         <v>36</v>
       </c>
       <c r="B54" s="13">
@@ -3788,7 +3986,7 @@
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A55" s="48" t="s">
+      <c r="A55" s="53" t="s">
         <v>37</v>
       </c>
       <c r="B55" s="13">
@@ -3804,7 +4002,7 @@
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A56" s="48" t="s">
+      <c r="A56" s="53" t="s">
         <v>38</v>
       </c>
       <c r="B56" s="13">
@@ -3820,7 +4018,7 @@
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A57" s="48" t="s">
+      <c r="A57" s="53" t="s">
         <v>39</v>
       </c>
       <c r="B57" s="13">
@@ -3836,7 +4034,7 @@
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A58" s="48" t="s">
+      <c r="A58" s="53" t="s">
         <v>40</v>
       </c>
       <c r="B58" s="13">
@@ -3852,7 +4050,7 @@
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A59" s="48" t="s">
+      <c r="A59" s="53" t="s">
         <v>41</v>
       </c>
       <c r="B59" s="13">
@@ -3868,7 +4066,7 @@
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A60" s="48" t="s">
+      <c r="A60" s="53" t="s">
         <v>42</v>
       </c>
       <c r="B60" s="13">
@@ -3884,7 +4082,7 @@
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A61" s="48" t="s">
+      <c r="A61" s="53" t="s">
         <v>43</v>
       </c>
       <c r="B61" s="13">
@@ -3927,98 +4125,98 @@
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A67" s="48" t="s">
+      <c r="A67" s="53" t="s">
         <v>49</v>
       </c>
-      <c r="B67" s="48" t="s">
+      <c r="B67" s="53" t="s">
         <v>50</v>
       </c>
-      <c r="C67" s="48">
+      <c r="C67" s="53">
         <v>48</v>
       </c>
-      <c r="D67" s="48" t="s">
+      <c r="D67" s="53" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A68" s="48" t="s">
+      <c r="A68" s="53" t="s">
         <v>52</v>
       </c>
-      <c r="B68" s="48" t="s">
+      <c r="B68" s="53" t="s">
         <v>53</v>
       </c>
-      <c r="C68" s="48">
+      <c r="C68" s="53">
         <v>15</v>
       </c>
-      <c r="D68" s="48" t="s">
+      <c r="D68" s="53" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A69" s="48" t="s">
+      <c r="A69" s="53" t="s">
         <v>55</v>
       </c>
-      <c r="B69" s="48" t="s">
+      <c r="B69" s="53" t="s">
         <v>56</v>
       </c>
-      <c r="C69" s="48">
+      <c r="C69" s="53">
         <v>22</v>
       </c>
-      <c r="D69" s="48" t="s">
+      <c r="D69" s="53" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A70" s="48" t="s">
+      <c r="A70" s="53" t="s">
         <v>58</v>
       </c>
-      <c r="B70" s="48" t="s">
+      <c r="B70" s="53" t="s">
         <v>56</v>
       </c>
-      <c r="C70" s="48">
+      <c r="C70" s="53">
         <v>10</v>
       </c>
-      <c r="D70" s="48" t="s">
+      <c r="D70" s="53" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A71" s="48" t="s">
+      <c r="A71" s="53" t="s">
         <v>60</v>
       </c>
-      <c r="B71" s="48" t="s">
+      <c r="B71" s="53" t="s">
         <v>61</v>
       </c>
-      <c r="C71" s="48"/>
-      <c r="D71" s="48" t="s">
+      <c r="C71" s="53"/>
+      <c r="D71" s="53" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A72" s="48" t="s">
+      <c r="A72" s="53" t="s">
         <v>63</v>
       </c>
-      <c r="B72" s="48" t="s">
+      <c r="B72" s="53" t="s">
         <v>64</v>
       </c>
-      <c r="C72" s="48">
+      <c r="C72" s="53">
         <v>5</v>
       </c>
-      <c r="D72" s="48" t="s">
+      <c r="D72" s="53" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A73" s="48" t="s">
+      <c r="A73" s="53" t="s">
         <v>66</v>
       </c>
-      <c r="B73" s="48" t="s">
+      <c r="B73" s="53" t="s">
         <v>67</v>
       </c>
-      <c r="C73" s="48">
+      <c r="C73" s="53">
         <v>2</v>
       </c>
-      <c r="D73" s="48" t="s">
+      <c r="D73" s="53" t="s">
         <v>68</v>
       </c>
     </row>
@@ -4057,71 +4255,71 @@
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A79" s="48" t="s">
+      <c r="A79" s="53" t="s">
         <v>75</v>
       </c>
-      <c r="B79" s="48">
+      <c r="B79" s="53">
         <v>18500</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A80" s="48" t="s">
+      <c r="A80" s="53" t="s">
         <v>76</v>
       </c>
-      <c r="B80" s="48">
+      <c r="B80" s="53">
         <v>21250</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A81" s="48" t="s">
+      <c r="A81" s="53" t="s">
         <v>77</v>
       </c>
-      <c r="B81" s="48">
+      <c r="B81" s="53">
         <v>19800</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A82" s="48" t="s">
+      <c r="A82" s="53" t="s">
         <v>78</v>
       </c>
-      <c r="B82" s="48">
+      <c r="B82" s="53">
         <v>25000</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A83" s="48" t="s">
+      <c r="A83" s="53" t="s">
         <v>79</v>
       </c>
-      <c r="B83" s="48">
+      <c r="B83" s="53">
         <v>23750</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A84" s="48" t="s">
+      <c r="A84" s="53" t="s">
         <v>80</v>
       </c>
-      <c r="B84" s="48">
+      <c r="B84" s="53">
         <v>22100</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A85" s="48" t="s">
+      <c r="A85" s="53" t="s">
         <v>81</v>
       </c>
-      <c r="B85" s="48">
+      <c r="B85" s="53">
         <v>26400</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A86" s="48" t="s">
+      <c r="A86" s="53" t="s">
         <v>82</v>
       </c>
-      <c r="B86" s="48">
+      <c r="B86" s="53">
         <v>24300</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A87" s="48" t="s">
+      <c r="A87" s="53" t="s">
         <v>83</v>
       </c>
       <c r="B87" s="4">
@@ -4153,10 +4351,10 @@
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A93" s="48" t="s">
+      <c r="A93" s="53" t="s">
         <v>89</v>
       </c>
-      <c r="B93" s="48" t="s">
+      <c r="B93" s="53" t="s">
         <v>90</v>
       </c>
       <c r="C93" s="14">
@@ -4164,10 +4362,10 @@
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A94" s="48" t="s">
+      <c r="A94" s="53" t="s">
         <v>91</v>
       </c>
-      <c r="B94" s="48" t="s">
+      <c r="B94" s="53" t="s">
         <v>92</v>
       </c>
       <c r="C94" s="14">
@@ -4175,10 +4373,10 @@
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A95" s="48" t="s">
+      <c r="A95" s="53" t="s">
         <v>93</v>
       </c>
-      <c r="B95" s="48" t="s">
+      <c r="B95" s="53" t="s">
         <v>94</v>
       </c>
       <c r="C95" s="14">
@@ -4186,10 +4384,10 @@
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A96" s="48" t="s">
+      <c r="A96" s="53" t="s">
         <v>95</v>
       </c>
-      <c r="B96" s="48" t="s">
+      <c r="B96" s="53" t="s">
         <v>96</v>
       </c>
       <c r="C96" s="14">
@@ -4197,10 +4395,10 @@
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A97" s="48" t="s">
+      <c r="A97" s="53" t="s">
         <v>97</v>
       </c>
-      <c r="B97" s="48" t="s">
+      <c r="B97" s="53" t="s">
         <v>98</v>
       </c>
       <c r="C97" s="14">
@@ -4208,10 +4406,10 @@
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A98" s="48" t="s">
+      <c r="A98" s="53" t="s">
         <v>99</v>
       </c>
-      <c r="B98" s="48" t="s">
+      <c r="B98" s="53" t="s">
         <v>90</v>
       </c>
       <c r="C98" s="14">
@@ -4219,10 +4417,10 @@
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A99" s="48" t="s">
+      <c r="A99" s="53" t="s">
         <v>100</v>
       </c>
-      <c r="B99" s="48"/>
+      <c r="B99" s="53"/>
       <c r="C99" s="8">
         <f>MIN(C93:C98)</f>
         <v>95</v>
@@ -4258,107 +4456,107 @@
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A105" s="48">
+      <c r="A105" s="53">
         <v>1001</v>
       </c>
       <c r="B105" s="16">
         <v>46025</v>
       </c>
-      <c r="C105" s="48" t="s">
+      <c r="C105" s="53" t="s">
         <v>106</v>
       </c>
-      <c r="D105" s="48">
+      <c r="D105" s="53">
         <v>249.99</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A106" s="48">
+      <c r="A106" s="53">
         <v>1002</v>
       </c>
       <c r="B106" s="16">
         <v>46026</v>
       </c>
-      <c r="C106" s="48" t="s">
+      <c r="C106" s="53" t="s">
         <v>107</v>
       </c>
-      <c r="D106" s="48">
+      <c r="D106" s="53">
         <v>39.5</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A107" s="48">
+      <c r="A107" s="53">
         <v>1003</v>
       </c>
       <c r="B107" s="16">
         <v>46027</v>
       </c>
-      <c r="C107" s="48" t="s">
+      <c r="C107" s="53" t="s">
         <v>106</v>
       </c>
-      <c r="D107" s="48">
+      <c r="D107" s="53">
         <v>89</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A108" s="48">
+      <c r="A108" s="53">
         <v>1004</v>
       </c>
       <c r="B108" s="16">
         <v>46027</v>
       </c>
-      <c r="C108" s="48" t="s">
+      <c r="C108" s="53" t="s">
         <v>108</v>
       </c>
-      <c r="D108" s="48">
+      <c r="D108" s="53">
         <v>59.99</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A109" s="48">
+      <c r="A109" s="53">
         <v>1005</v>
       </c>
       <c r="B109" s="16">
         <v>46028</v>
       </c>
-      <c r="C109" s="48" t="s">
+      <c r="C109" s="53" t="s">
         <v>106</v>
       </c>
-      <c r="D109" s="48">
+      <c r="D109" s="53">
         <v>129</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A110" s="48">
+      <c r="A110" s="53">
         <v>1006</v>
       </c>
       <c r="B110" s="16">
         <v>46028</v>
       </c>
-      <c r="C110" s="48" t="s">
+      <c r="C110" s="53" t="s">
         <v>109</v>
       </c>
-      <c r="D110" s="48">
+      <c r="D110" s="53">
         <v>24.99</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A111" s="48">
+      <c r="A111" s="53">
         <v>1007</v>
       </c>
       <c r="B111" s="16">
         <v>46029</v>
       </c>
-      <c r="C111" s="48" t="s">
+      <c r="C111" s="53" t="s">
         <v>107</v>
       </c>
-      <c r="D111" s="48">
+      <c r="D111" s="53">
         <v>75</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A112" s="48"/>
-      <c r="B112" s="48"/>
-      <c r="C112" s="48" t="s">
+      <c r="A112" s="53"/>
+      <c r="B112" s="53"/>
+      <c r="C112" s="53" t="s">
         <v>110</v>
       </c>
       <c r="D112" s="4">
@@ -4387,10 +4585,10 @@
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A117" s="48" t="s">
+      <c r="A117" s="53" t="s">
         <v>115</v>
       </c>
-      <c r="B117" s="48" t="s">
+      <c r="B117" s="53" t="s">
         <v>116</v>
       </c>
       <c r="C117" s="7">
@@ -4398,10 +4596,10 @@
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A118" s="48" t="s">
+      <c r="A118" s="53" t="s">
         <v>117</v>
       </c>
-      <c r="B118" s="48" t="s">
+      <c r="B118" s="53" t="s">
         <v>90</v>
       </c>
       <c r="C118" s="7">
@@ -4409,10 +4607,10 @@
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A119" s="48" t="s">
+      <c r="A119" s="53" t="s">
         <v>118</v>
       </c>
-      <c r="B119" s="48" t="s">
+      <c r="B119" s="53" t="s">
         <v>119</v>
       </c>
       <c r="C119" s="7">
@@ -4420,10 +4618,10 @@
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A120" s="48" t="s">
+      <c r="A120" s="53" t="s">
         <v>120</v>
       </c>
-      <c r="B120" s="48" t="s">
+      <c r="B120" s="53" t="s">
         <v>92</v>
       </c>
       <c r="C120" s="7">
@@ -4431,10 +4629,10 @@
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A121" s="48" t="s">
+      <c r="A121" s="53" t="s">
         <v>121</v>
       </c>
-      <c r="B121" s="48" t="s">
+      <c r="B121" s="53" t="s">
         <v>96</v>
       </c>
       <c r="C121" s="7">
@@ -4442,10 +4640,10 @@
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A122" s="48" t="s">
+      <c r="A122" s="53" t="s">
         <v>122</v>
       </c>
-      <c r="B122" s="48" t="s">
+      <c r="B122" s="53" t="s">
         <v>123</v>
       </c>
       <c r="C122" s="7">
@@ -4453,10 +4651,10 @@
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A123" s="48" t="s">
+      <c r="A123" s="53" t="s">
         <v>124</v>
       </c>
-      <c r="B123" s="48" t="s">
+      <c r="B123" s="53" t="s">
         <v>46</v>
       </c>
       <c r="C123" s="7">
@@ -4464,10 +4662,10 @@
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A124" s="48" t="s">
+      <c r="A124" s="53" t="s">
         <v>125</v>
       </c>
-      <c r="B124" s="48" t="s">
+      <c r="B124" s="53" t="s">
         <v>126</v>
       </c>
       <c r="C124" s="7">
@@ -4475,26 +4673,26 @@
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A125" s="48" t="s">
+      <c r="A125" s="53" t="s">
         <v>127</v>
       </c>
       <c r="B125" s="8">
         <f>MEDIAN(C117:C124)</f>
         <v>60500</v>
       </c>
-      <c r="C125" s="48"/>
+      <c r="C125" s="53"/>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A126" s="48" t="s">
+      <c r="A126" s="53" t="s">
         <v>128</v>
       </c>
-      <c r="B126" s="48" t="s">
+      <c r="B126" s="53" t="s">
         <v>129</v>
       </c>
-      <c r="C126" s="48"/>
+      <c r="C126" s="53"/>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A127" s="48"/>
+      <c r="A127" s="53"/>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A128" s="28" t="s">
@@ -4502,31 +4700,31 @@
       </c>
     </row>
     <row r="129" spans="1:4" ht="179.4" x14ac:dyDescent="0.3">
-      <c r="A129" s="48" t="s">
+      <c r="A129" s="53" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A130" s="48"/>
+      <c r="A130" s="53"/>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A131" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="B131" s="48"/>
-      <c r="C131" s="48"/>
+      <c r="B131" s="53"/>
+      <c r="C131" s="53"/>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A132" s="17">
         <v>8.2500000000000004E-2</v>
       </c>
-      <c r="B132" s="48"/>
-      <c r="C132" s="48"/>
+      <c r="B132" s="53"/>
+      <c r="C132" s="53"/>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A133" s="48"/>
-      <c r="B133" s="48"/>
-      <c r="C133" s="48"/>
+      <c r="A133" s="53"/>
+      <c r="B133" s="53"/>
+      <c r="C133" s="53"/>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A134" s="9" t="s">
@@ -4543,10 +4741,10 @@
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A135" s="48" t="s">
+      <c r="A135" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="B135" s="48">
+      <c r="B135" s="53">
         <v>24.99</v>
       </c>
       <c r="C135" s="4">
@@ -4559,10 +4757,10 @@
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A136" s="48" t="s">
+      <c r="A136" s="53" t="s">
         <v>133</v>
       </c>
-      <c r="B136" s="48">
+      <c r="B136" s="53">
         <v>15.5</v>
       </c>
       <c r="C136" s="4">
@@ -4575,10 +4773,10 @@
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A137" s="48" t="s">
+      <c r="A137" s="53" t="s">
         <v>134</v>
       </c>
-      <c r="B137" s="48">
+      <c r="B137" s="53">
         <v>89</v>
       </c>
       <c r="C137" s="4" t="e">
@@ -4591,10 +4789,10 @@
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A138" s="48" t="s">
+      <c r="A138" s="53" t="s">
         <v>135</v>
       </c>
-      <c r="B138" s="48">
+      <c r="B138" s="53">
         <v>5.25</v>
       </c>
       <c r="C138" s="4" t="e">
@@ -4607,10 +4805,10 @@
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A139" s="48" t="s">
+      <c r="A139" s="53" t="s">
         <v>136</v>
       </c>
-      <c r="B139" s="48">
+      <c r="B139" s="53">
         <v>12.75</v>
       </c>
       <c r="C139" s="4" t="e">
@@ -4623,7 +4821,7 @@
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A140" s="48"/>
+      <c r="A140" s="53"/>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A141" s="27" t="s">
@@ -4631,12 +4829,12 @@
       </c>
     </row>
     <row r="142" spans="1:4" ht="82.8" x14ac:dyDescent="0.3">
-      <c r="A142" s="48" t="s">
+      <c r="A142" s="53" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A143" s="48"/>
+      <c r="A143" s="53"/>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A144" s="9" t="s">
@@ -4650,7 +4848,7 @@
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A145" s="48" t="s">
+      <c r="A145" s="53" t="s">
         <v>119</v>
       </c>
       <c r="B145" s="18">
@@ -4662,7 +4860,7 @@
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A146" s="48" t="s">
+      <c r="A146" s="53" t="s">
         <v>96</v>
       </c>
       <c r="B146" s="18">
@@ -4674,7 +4872,7 @@
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A147" s="48" t="s">
+      <c r="A147" s="53" t="s">
         <v>90</v>
       </c>
       <c r="B147" s="18">
@@ -4686,7 +4884,7 @@
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A148" s="48" t="s">
+      <c r="A148" s="53" t="s">
         <v>143</v>
       </c>
       <c r="B148" s="18">
@@ -4698,7 +4896,7 @@
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A149" s="48" t="s">
+      <c r="A149" s="53" t="s">
         <v>116</v>
       </c>
       <c r="B149" s="18">
@@ -4710,7 +4908,7 @@
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A150" s="48" t="s">
+      <c r="A150" s="53" t="s">
         <v>144</v>
       </c>
       <c r="B150" s="20">
@@ -4720,26 +4918,26 @@
       <c r="C150" s="13"/>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A151" s="48"/>
-      <c r="B151" s="48"/>
+      <c r="A151" s="53"/>
+      <c r="B151" s="53"/>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A152" s="28" t="s">
         <v>145</v>
       </c>
-      <c r="B152" s="48"/>
+      <c r="B152" s="53"/>
     </row>
     <row r="153" spans="1:3" ht="138" x14ac:dyDescent="0.3">
-      <c r="A153" s="48" t="s">
+      <c r="A153" s="53" t="s">
         <v>146</v>
       </c>
-      <c r="B153" s="48"/>
+      <c r="B153" s="53"/>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A154" s="48" t="s">
+      <c r="A154" s="53" t="s">
         <v>147</v>
       </c>
-      <c r="B154" s="48" t="s">
+      <c r="B154" s="53" t="s">
         <v>148</v>
       </c>
       <c r="C154" s="4" t="str">
@@ -4748,10 +4946,10 @@
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A155" s="48" t="s">
+      <c r="A155" s="53" t="s">
         <v>149</v>
       </c>
-      <c r="B155" s="48" t="s">
+      <c r="B155" s="53" t="s">
         <v>150</v>
       </c>
       <c r="C155" s="4" t="str">
@@ -4760,10 +4958,10 @@
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A156" s="48" t="s">
+      <c r="A156" s="53" t="s">
         <v>151</v>
       </c>
-      <c r="B156" s="48" t="s">
+      <c r="B156" s="53" t="s">
         <v>152</v>
       </c>
       <c r="C156" s="4" t="str">
@@ -4772,10 +4970,10 @@
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A157" s="48" t="s">
+      <c r="A157" s="53" t="s">
         <v>153</v>
       </c>
-      <c r="B157" s="48" t="s">
+      <c r="B157" s="53" t="s">
         <v>154</v>
       </c>
       <c r="C157" s="4" t="str">
@@ -4784,10 +4982,10 @@
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A158" s="48" t="s">
+      <c r="A158" s="53" t="s">
         <v>155</v>
       </c>
-      <c r="B158" s="48" t="s">
+      <c r="B158" s="53" t="s">
         <v>156</v>
       </c>
       <c r="C158" s="4" t="str">
@@ -4796,10 +4994,10 @@
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A159" s="48" t="s">
+      <c r="A159" s="53" t="s">
         <v>157</v>
       </c>
-      <c r="B159" s="48" t="s">
+      <c r="B159" s="53" t="s">
         <v>158</v>
       </c>
       <c r="C159" s="4" t="str">
@@ -4808,10 +5006,10 @@
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A160" s="48" t="s">
+      <c r="A160" s="53" t="s">
         <v>159</v>
       </c>
-      <c r="B160" s="48" t="s">
+      <c r="B160" s="53" t="s">
         <v>160</v>
       </c>
       <c r="C160" s="4" t="str">
@@ -4820,10 +5018,10 @@
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A161" s="48" t="s">
+      <c r="A161" s="53" t="s">
         <v>161</v>
       </c>
-      <c r="B161" s="48" t="s">
+      <c r="B161" s="53" t="s">
         <v>162</v>
       </c>
       <c r="C161" s="4" t="str">
@@ -4832,7 +5030,7 @@
       </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A162" s="48"/>
+      <c r="A162" s="53"/>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A163" s="28" t="s">
@@ -4840,23 +5038,23 @@
       </c>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A164" s="48"/>
+      <c r="A164" s="53"/>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A165" s="48" t="s">
+      <c r="A165" s="53" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A166" s="48"/>
+      <c r="A166" s="53"/>
     </row>
     <row r="167" spans="1:4" ht="69" x14ac:dyDescent="0.3">
-      <c r="A167" s="48" t="s">
+      <c r="A167" s="53" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A168" s="48"/>
+      <c r="A168" s="53"/>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A169" s="9" t="s">
@@ -4873,13 +5071,13 @@
       </c>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A170" s="48" t="s">
+      <c r="A170" s="53" t="s">
         <v>168</v>
       </c>
       <c r="B170" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="C170" s="48" t="s">
+      <c r="C170" s="53" t="s">
         <v>170</v>
       </c>
       <c r="D170" s="4" t="s">
@@ -4887,13 +5085,13 @@
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A171" s="48" t="s">
+      <c r="A171" s="53" t="s">
         <v>171</v>
       </c>
       <c r="B171" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="C171" s="48" t="s">
+      <c r="C171" s="53" t="s">
         <v>173</v>
       </c>
       <c r="D171" s="4" t="s">
@@ -4901,13 +5099,13 @@
       </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A172" s="48" t="s">
+      <c r="A172" s="53" t="s">
         <v>174</v>
       </c>
       <c r="B172" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="C172" s="48" t="s">
+      <c r="C172" s="53" t="s">
         <v>176</v>
       </c>
       <c r="D172" s="4" t="s">
@@ -4915,13 +5113,13 @@
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A173" s="48" t="s">
+      <c r="A173" s="53" t="s">
         <v>177</v>
       </c>
       <c r="B173" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="C173" s="48" t="s">
+      <c r="C173" s="53" t="s">
         <v>179</v>
       </c>
       <c r="D173" s="4" t="s">
@@ -4929,13 +5127,13 @@
       </c>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A174" s="48" t="s">
+      <c r="A174" s="53" t="s">
         <v>180</v>
       </c>
       <c r="B174" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="C174" s="48" t="s">
+      <c r="C174" s="53" t="s">
         <v>182</v>
       </c>
       <c r="D174" s="4" t="s">
@@ -4943,13 +5141,13 @@
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A175" s="48" t="s">
+      <c r="A175" s="53" t="s">
         <v>183</v>
       </c>
       <c r="B175" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="C175" s="48" t="s">
+      <c r="C175" s="53" t="s">
         <v>185</v>
       </c>
       <c r="D175" s="4" t="s">
@@ -4957,13 +5155,13 @@
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A176" s="48" t="s">
+      <c r="A176" s="53" t="s">
         <v>186</v>
       </c>
       <c r="B176" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="C176" s="48" t="s">
+      <c r="C176" s="53" t="s">
         <v>188</v>
       </c>
       <c r="D176" s="4" t="s">
@@ -4971,13 +5169,13 @@
       </c>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A177" s="48" t="s">
+      <c r="A177" s="53" t="s">
         <v>189</v>
       </c>
       <c r="B177" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="C177" s="48" t="s">
+      <c r="C177" s="53" t="s">
         <v>191</v>
       </c>
       <c r="D177" s="4" t="s">
@@ -4985,13 +5183,13 @@
       </c>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A178" s="48" t="s">
+      <c r="A178" s="53" t="s">
         <v>192</v>
       </c>
       <c r="B178" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="C178" s="48" t="s">
+      <c r="C178" s="53" t="s">
         <v>194</v>
       </c>
       <c r="D178" s="4" t="s">
@@ -4999,13 +5197,13 @@
       </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A179" s="48" t="s">
+      <c r="A179" s="53" t="s">
         <v>195</v>
       </c>
       <c r="B179" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="C179" s="48" t="s">
+      <c r="C179" s="53" t="s">
         <v>197</v>
       </c>
       <c r="D179" s="4" t="s">
@@ -5031,7 +5229,7 @@
       </c>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A184" s="48" t="s">
+      <c r="A184" s="53" t="s">
         <v>204</v>
       </c>
       <c r="B184" s="21" t="str">
@@ -5040,7 +5238,7 @@
       </c>
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A185" s="48" t="s">
+      <c r="A185" s="53" t="s">
         <v>205</v>
       </c>
       <c r="B185" s="21" t="str">
@@ -5049,7 +5247,7 @@
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A186" s="48" t="s">
+      <c r="A186" s="53" t="s">
         <v>206</v>
       </c>
       <c r="B186" s="21" t="str">
@@ -5058,7 +5256,7 @@
       </c>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A187" s="48" t="s">
+      <c r="A187" s="53" t="s">
         <v>207</v>
       </c>
       <c r="B187" s="21" t="str">
@@ -5067,7 +5265,7 @@
       </c>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A188" s="48" t="s">
+      <c r="A188" s="53" t="s">
         <v>208</v>
       </c>
       <c r="B188" s="21" t="str">
@@ -5076,7 +5274,7 @@
       </c>
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A189" s="48" t="s">
+      <c r="A189" s="53" t="s">
         <v>209</v>
       </c>
       <c r="B189" s="21" t="str">
@@ -5085,7 +5283,7 @@
       </c>
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A190" s="48" t="s">
+      <c r="A190" s="53" t="s">
         <v>210</v>
       </c>
       <c r="B190" s="21" t="str">
@@ -5109,21 +5307,21 @@
       </c>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A195" s="48" t="s">
+      <c r="A195" s="53" t="s">
         <v>219</v>
       </c>
-      <c r="B195" s="48" t="s">
+      <c r="B195" s="53" t="s">
         <v>220</v>
       </c>
-      <c r="C195" s="48" t="s">
+      <c r="C195" s="53" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A196" s="48" t="s">
+      <c r="A196" s="53" t="s">
         <v>222</v>
       </c>
-      <c r="B196" s="48">
+      <c r="B196" s="53">
         <v>96</v>
       </c>
       <c r="C196" s="21" t="str">
@@ -5132,10 +5330,10 @@
       </c>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A197" s="48" t="s">
+      <c r="A197" s="53" t="s">
         <v>223</v>
       </c>
-      <c r="B197" s="48">
+      <c r="B197" s="53">
         <v>43</v>
       </c>
       <c r="C197" s="21" t="str">
@@ -5144,10 +5342,10 @@
       </c>
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A198" s="48" t="s">
+      <c r="A198" s="53" t="s">
         <v>224</v>
       </c>
-      <c r="B198" s="48">
+      <c r="B198" s="53">
         <v>20</v>
       </c>
       <c r="C198" s="21" t="str">
@@ -5156,10 +5354,10 @@
       </c>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A199" s="48" t="s">
+      <c r="A199" s="53" t="s">
         <v>225</v>
       </c>
-      <c r="B199" s="48">
+      <c r="B199" s="53">
         <v>77</v>
       </c>
       <c r="C199" s="21" t="str">
@@ -5168,10 +5366,10 @@
       </c>
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A200" s="48" t="s">
+      <c r="A200" s="53" t="s">
         <v>226</v>
       </c>
-      <c r="B200" s="48">
+      <c r="B200" s="53">
         <v>76</v>
       </c>
       <c r="C200" s="21" t="str">
@@ -5185,23 +5383,23 @@
       </c>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A203" s="48" t="s">
+      <c r="A203" s="53" t="s">
         <v>8</v>
       </c>
-      <c r="B203" s="48"/>
-      <c r="C203" s="48" t="s">
+      <c r="B203" s="53"/>
+      <c r="C203" s="53" t="s">
         <v>228</v>
       </c>
-      <c r="D203" s="48" t="s">
+      <c r="D203" s="53" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A204" s="48">
+      <c r="A204" s="53">
         <v>0</v>
       </c>
-      <c r="B204" s="48"/>
-      <c r="C204" s="48" t="s">
+      <c r="B204" s="53"/>
+      <c r="C204" s="53" t="s">
         <v>230</v>
       </c>
       <c r="D204" s="4" t="str">
@@ -5214,11 +5412,11 @@
       </c>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A205" s="48">
+      <c r="A205" s="53">
         <v>15</v>
       </c>
-      <c r="B205" s="48"/>
-      <c r="C205" s="48" t="s">
+      <c r="B205" s="53"/>
+      <c r="C205" s="53" t="s">
         <v>230</v>
       </c>
       <c r="D205" s="4" t="str">
@@ -5227,11 +5425,11 @@
       </c>
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A206" s="48">
+      <c r="A206" s="53">
         <v>16</v>
       </c>
-      <c r="B206" s="48"/>
-      <c r="C206" s="48" t="s">
+      <c r="B206" s="53"/>
+      <c r="C206" s="53" t="s">
         <v>231</v>
       </c>
       <c r="D206" s="4" t="str">
@@ -5240,11 +5438,11 @@
       </c>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A207" s="48">
+      <c r="A207" s="53">
         <v>29</v>
       </c>
-      <c r="B207" s="48"/>
-      <c r="C207" s="48" t="s">
+      <c r="B207" s="53"/>
+      <c r="C207" s="53" t="s">
         <v>231</v>
       </c>
       <c r="D207" s="4" t="str">
@@ -5253,11 +5451,11 @@
       </c>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A208" s="48">
+      <c r="A208" s="53">
         <v>30</v>
       </c>
-      <c r="B208" s="48"/>
-      <c r="C208" s="48" t="s">
+      <c r="B208" s="53"/>
+      <c r="C208" s="53" t="s">
         <v>230</v>
       </c>
       <c r="D208" s="4" t="str">
@@ -5266,11 +5464,11 @@
       </c>
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A209" s="48">
+      <c r="A209" s="53">
         <v>55</v>
       </c>
-      <c r="B209" s="48"/>
-      <c r="C209" s="48" t="s">
+      <c r="B209" s="53"/>
+      <c r="C209" s="53" t="s">
         <v>230</v>
       </c>
       <c r="D209" s="4" t="str">
@@ -5279,11 +5477,11 @@
       </c>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A210" s="48">
+      <c r="A210" s="53">
         <v>56</v>
       </c>
-      <c r="B210" s="48"/>
-      <c r="C210" s="48" t="s">
+      <c r="B210" s="53"/>
+      <c r="C210" s="53" t="s">
         <v>231</v>
       </c>
       <c r="D210" s="4" t="str">
@@ -5327,10 +5525,10 @@
       </c>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A216" s="48" t="s">
+      <c r="A216" s="53" t="s">
         <v>239</v>
       </c>
-      <c r="B216" s="48" t="s">
+      <c r="B216" s="53" t="s">
         <v>240</v>
       </c>
       <c r="C216" s="16">
@@ -5346,10 +5544,10 @@
       </c>
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A217" s="48" t="s">
+      <c r="A217" s="53" t="s">
         <v>241</v>
       </c>
-      <c r="B217" s="48" t="s">
+      <c r="B217" s="53" t="s">
         <v>242</v>
       </c>
       <c r="C217" s="16">
@@ -5365,10 +5563,10 @@
       </c>
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A218" s="48" t="s">
+      <c r="A218" s="53" t="s">
         <v>243</v>
       </c>
-      <c r="B218" s="48" t="s">
+      <c r="B218" s="53" t="s">
         <v>244</v>
       </c>
       <c r="C218" s="16">
@@ -5384,10 +5582,10 @@
       </c>
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A219" s="48" t="s">
+      <c r="A219" s="53" t="s">
         <v>245</v>
       </c>
-      <c r="B219" s="48" t="s">
+      <c r="B219" s="53" t="s">
         <v>246</v>
       </c>
       <c r="C219" s="16">
@@ -5403,10 +5601,10 @@
       </c>
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A220" s="48" t="s">
+      <c r="A220" s="53" t="s">
         <v>247</v>
       </c>
-      <c r="B220" s="48" t="s">
+      <c r="B220" s="53" t="s">
         <v>248</v>
       </c>
       <c r="C220" s="16">
@@ -5422,10 +5620,10 @@
       </c>
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A221" s="48" t="s">
+      <c r="A221" s="53" t="s">
         <v>249</v>
       </c>
-      <c r="B221" s="48" t="s">
+      <c r="B221" s="53" t="s">
         <v>250</v>
       </c>
       <c r="C221" s="16">
@@ -5467,95 +5665,95 @@
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A227" s="48" t="s">
+      <c r="A227" s="53" t="s">
         <v>257</v>
       </c>
-      <c r="B227" s="48" t="s">
+      <c r="B227" s="53" t="s">
         <v>258</v>
       </c>
-      <c r="C227" s="48" t="s">
+      <c r="C227" s="53" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A228" s="48" t="s">
+      <c r="A228" s="53" t="s">
         <v>259</v>
       </c>
-      <c r="B228" s="48" t="s">
+      <c r="B228" s="53" t="s">
         <v>260</v>
       </c>
-      <c r="C228" s="48" t="s">
+      <c r="C228" s="53" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A229" s="48" t="s">
+      <c r="A229" s="53" t="s">
         <v>261</v>
       </c>
-      <c r="B229" s="48" t="s">
+      <c r="B229" s="53" t="s">
         <v>262</v>
       </c>
-      <c r="C229" s="48" t="s">
+      <c r="C229" s="53" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A230" s="48" t="s">
+      <c r="A230" s="53" t="s">
         <v>264</v>
       </c>
-      <c r="B230" s="48" t="s">
+      <c r="B230" s="53" t="s">
         <v>265</v>
       </c>
-      <c r="C230" s="48" t="s">
+      <c r="C230" s="53" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A231" s="48" t="s">
+      <c r="A231" s="53" t="s">
         <v>266</v>
       </c>
-      <c r="B231" s="48" t="s">
+      <c r="B231" s="53" t="s">
         <v>267</v>
       </c>
-      <c r="C231" s="48" t="s">
+      <c r="C231" s="53" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A232" s="48" t="s">
+      <c r="A232" s="53" t="s">
         <v>268</v>
       </c>
-      <c r="B232" s="48" t="s">
+      <c r="B232" s="53" t="s">
         <v>269</v>
       </c>
-      <c r="C232" s="48" t="s">
+      <c r="C232" s="53" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A233" s="48" t="s">
+      <c r="A233" s="53" t="s">
         <v>270</v>
       </c>
-      <c r="B233" s="48" t="s">
+      <c r="B233" s="53" t="s">
         <v>271</v>
       </c>
-      <c r="C233" s="48" t="s">
+      <c r="C233" s="53" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A234" s="48"/>
-      <c r="B234" s="48"/>
-      <c r="C234" s="48"/>
+      <c r="A234" s="53"/>
+      <c r="B234" s="53"/>
+      <c r="C234" s="53"/>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A235" s="13" t="s">
         <v>272</v>
       </c>
-      <c r="B235" s="48" t="s">
+      <c r="B235" s="53" t="s">
         <v>261</v>
       </c>
-      <c r="C235" s="48"/>
+      <c r="C235" s="53"/>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A236" s="13" t="s">
@@ -5565,13 +5763,13 @@
         <f>_xlfn.XLOOKUP(B235,A227:A233,C227:C233,0)</f>
         <v>Office equipment</v>
       </c>
-      <c r="C236" s="56" t="str">
+      <c r="C236" s="54" t="str">
         <f ca="1">_xlfn.FORMULATEXT(B236)</f>
         <v>=XLOOKUP(B235,A227:A233,C227:C233,0)</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C237" s="56"/>
+      <c r="C237" s="54"/>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A238" s="28" t="s">
@@ -5595,86 +5793,86 @@
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A242" s="48" t="s">
+      <c r="A242" s="53" t="s">
         <v>277</v>
       </c>
-      <c r="B242" s="48" t="s">
+      <c r="B242" s="53" t="s">
         <v>278</v>
       </c>
-      <c r="C242" s="48">
+      <c r="C242" s="53">
         <v>342</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A243" s="48" t="s">
+      <c r="A243" s="53" t="s">
         <v>279</v>
       </c>
-      <c r="B243" s="48" t="s">
+      <c r="B243" s="53" t="s">
         <v>280</v>
       </c>
-      <c r="C243" s="48">
+      <c r="C243" s="53">
         <v>128</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A244" s="48" t="s">
+      <c r="A244" s="53" t="s">
         <v>281</v>
       </c>
-      <c r="B244" s="48" t="s">
+      <c r="B244" s="53" t="s">
         <v>282</v>
       </c>
-      <c r="C244" s="48">
+      <c r="C244" s="53">
         <v>56</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A245" s="48" t="s">
+      <c r="A245" s="53" t="s">
         <v>283</v>
       </c>
-      <c r="B245" s="48" t="s">
+      <c r="B245" s="53" t="s">
         <v>284</v>
       </c>
-      <c r="C245" s="48">
+      <c r="C245" s="53">
         <v>89</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A246" s="48" t="s">
+      <c r="A246" s="53" t="s">
         <v>285</v>
       </c>
-      <c r="B246" s="48" t="s">
+      <c r="B246" s="53" t="s">
         <v>286</v>
       </c>
-      <c r="C246" s="48">
+      <c r="C246" s="53">
         <v>203</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A247" s="48" t="s">
+      <c r="A247" s="53" t="s">
         <v>287</v>
       </c>
-      <c r="B247" s="48" t="s">
+      <c r="B247" s="53" t="s">
         <v>288</v>
       </c>
-      <c r="C247" s="48">
+      <c r="C247" s="53">
         <v>74</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A248" s="48" t="s">
+      <c r="A248" s="53" t="s">
         <v>289</v>
       </c>
-      <c r="B248" s="48" t="s">
+      <c r="B248" s="53" t="s">
         <v>290</v>
       </c>
-      <c r="C248" s="48">
+      <c r="C248" s="53">
         <v>165</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A249" s="48"/>
-      <c r="B249" s="48"/>
-      <c r="C249" s="48"/>
+      <c r="A249" s="53"/>
+      <c r="B249" s="53"/>
+      <c r="C249" s="53"/>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A250" s="9" t="s">
@@ -5688,10 +5886,10 @@
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A251" s="48" t="s">
+      <c r="A251" s="53" t="s">
         <v>283</v>
       </c>
-      <c r="B251" s="48" t="s">
+      <c r="B251" s="53" t="s">
         <v>284</v>
       </c>
       <c r="C251" s="4">
@@ -5700,10 +5898,10 @@
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A252" s="48" t="s">
+      <c r="A252" s="53" t="s">
         <v>277</v>
       </c>
-      <c r="B252" s="48" t="s">
+      <c r="B252" s="53" t="s">
         <v>278</v>
       </c>
       <c r="C252" s="4">
@@ -5712,10 +5910,10 @@
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A253" s="48" t="s">
+      <c r="A253" s="53" t="s">
         <v>289</v>
       </c>
-      <c r="B253" s="48" t="s">
+      <c r="B253" s="53" t="s">
         <v>290</v>
       </c>
       <c r="C253" s="4">
@@ -5724,10 +5922,10 @@
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A254" s="48" t="s">
+      <c r="A254" s="53" t="s">
         <v>285</v>
       </c>
-      <c r="B254" s="48" t="s">
+      <c r="B254" s="53" t="s">
         <v>286</v>
       </c>
       <c r="C254" s="4">
@@ -5736,11 +5934,11 @@
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B256" s="57" t="str">
+      <c r="B256" s="56" t="str">
         <f ca="1">_xlfn.FORMULATEXT(C251)</f>
         <v>=XLOOKUP(A251,A$242:A$248,$C$242:$C$248,0)</v>
       </c>
-      <c r="C256" s="57"/>
+      <c r="C256" s="56"/>
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A258" s="28" t="s">
@@ -5772,7 +5970,7 @@
       </c>
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A262" s="48" t="s">
+      <c r="A262" s="53" t="s">
         <v>297</v>
       </c>
       <c r="B262" s="18">
@@ -5787,7 +5985,7 @@
       </c>
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A263" s="48" t="s">
+      <c r="A263" s="53" t="s">
         <v>298</v>
       </c>
       <c r="B263" s="18">
@@ -5802,7 +6000,7 @@
       </c>
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A264" s="48" t="s">
+      <c r="A264" s="53" t="s">
         <v>299</v>
       </c>
       <c r="B264" s="18">
@@ -5817,7 +6015,7 @@
       </c>
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A265" s="48" t="s">
+      <c r="A265" s="53" t="s">
         <v>225</v>
       </c>
       <c r="B265" s="18">
@@ -5832,7 +6030,7 @@
       </c>
     </row>
     <row r="266" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A266" s="48" t="s">
+      <c r="A266" s="53" t="s">
         <v>300</v>
       </c>
       <c r="B266" s="18">
@@ -5847,7 +6045,7 @@
       </c>
     </row>
     <row r="267" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A267" s="48" t="s">
+      <c r="A267" s="53" t="s">
         <v>301</v>
       </c>
       <c r="B267" s="18">
@@ -5862,7 +6060,7 @@
       </c>
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A268" s="48" t="s">
+      <c r="A268" s="53" t="s">
         <v>302</v>
       </c>
       <c r="B268" s="18">
@@ -5912,7 +6110,7 @@
       </c>
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A275" s="48" t="s">
+      <c r="A275" s="53" t="s">
         <v>297</v>
       </c>
       <c r="B275" s="18">
@@ -5927,7 +6125,7 @@
       </c>
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A276" s="48" t="s">
+      <c r="A276" s="53" t="s">
         <v>298</v>
       </c>
       <c r="B276" s="18">
@@ -5942,7 +6140,7 @@
       </c>
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A277" s="48" t="s">
+      <c r="A277" s="53" t="s">
         <v>299</v>
       </c>
       <c r="B277" s="18">
@@ -5957,7 +6155,7 @@
       </c>
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A278" s="48" t="s">
+      <c r="A278" s="53" t="s">
         <v>225</v>
       </c>
       <c r="B278" s="18">
@@ -5972,7 +6170,7 @@
       </c>
     </row>
     <row r="279" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A279" s="48" t="s">
+      <c r="A279" s="53" t="s">
         <v>300</v>
       </c>
       <c r="B279" s="18">
@@ -5987,7 +6185,7 @@
       </c>
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A280" s="48" t="s">
+      <c r="A280" s="53" t="s">
         <v>301</v>
       </c>
       <c r="B280" s="18">
@@ -6002,7 +6200,7 @@
       </c>
     </row>
     <row r="281" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A281" s="48" t="s">
+      <c r="A281" s="53" t="s">
         <v>302</v>
       </c>
       <c r="B281" s="18">
@@ -6085,7 +6283,7 @@
       </c>
     </row>
     <row r="295" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A295" s="48" t="s">
+      <c r="A295" s="53" t="s">
         <v>314</v>
       </c>
       <c r="B295" s="18">
@@ -6104,7 +6302,7 @@
       </c>
     </row>
     <row r="296" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A296" s="48" t="s">
+      <c r="A296" s="53" t="s">
         <v>315</v>
       </c>
       <c r="B296" s="18">
@@ -6119,7 +6317,7 @@
       </c>
     </row>
     <row r="297" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A297" s="48" t="s">
+      <c r="A297" s="53" t="s">
         <v>316</v>
       </c>
       <c r="B297" s="18">
@@ -6134,7 +6332,7 @@
       </c>
     </row>
     <row r="298" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A298" s="48" t="s">
+      <c r="A298" s="53" t="s">
         <v>317</v>
       </c>
       <c r="B298" s="18">
@@ -6171,7 +6369,7 @@
       </c>
     </row>
     <row r="302" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A302" s="48" t="s">
+      <c r="A302" s="53" t="s">
         <v>346</v>
       </c>
     </row>
@@ -6192,7 +6390,7 @@
       <c r="A306" s="15"/>
     </row>
     <row r="307" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A307" s="48" t="s">
+      <c r="A307" s="53" t="s">
         <v>327</v>
       </c>
     </row>
@@ -6238,19 +6436,19 @@
       <c r="F314" s="6"/>
     </row>
     <row r="315" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A315" s="48" t="s">
+      <c r="A315" s="53" t="s">
         <v>332</v>
       </c>
-      <c r="B315" s="48" t="s">
+      <c r="B315" s="53" t="s">
         <v>333</v>
       </c>
-      <c r="C315" s="48">
+      <c r="C315" s="53">
         <v>25.2</v>
       </c>
-      <c r="D315" s="48">
+      <c r="D315" s="53">
         <v>100</v>
       </c>
-      <c r="E315" s="48" t="s">
+      <c r="E315" s="53" t="s">
         <v>334</v>
       </c>
       <c r="F315" s="4">
@@ -6263,19 +6461,19 @@
       </c>
     </row>
     <row r="316" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A316" s="48" t="s">
+      <c r="A316" s="53" t="s">
         <v>335</v>
       </c>
-      <c r="B316" s="48" t="s">
+      <c r="B316" s="53" t="s">
         <v>336</v>
       </c>
-      <c r="C316" s="48">
+      <c r="C316" s="53">
         <v>24.2</v>
       </c>
-      <c r="D316" s="48">
+      <c r="D316" s="53">
         <v>120</v>
       </c>
-      <c r="E316" s="48" t="s">
+      <c r="E316" s="53" t="s">
         <v>337</v>
       </c>
       <c r="F316" s="4" cm="1">
@@ -6284,19 +6482,19 @@
       </c>
     </row>
     <row r="317" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A317" s="48" t="s">
+      <c r="A317" s="53" t="s">
         <v>338</v>
       </c>
-      <c r="B317" s="48" t="s">
+      <c r="B317" s="53" t="s">
         <v>339</v>
       </c>
-      <c r="C317" s="48">
+      <c r="C317" s="53">
         <v>23.75</v>
       </c>
-      <c r="D317" s="48">
+      <c r="D317" s="53">
         <v>80</v>
       </c>
-      <c r="E317" s="48" t="s">
+      <c r="E317" s="53" t="s">
         <v>340</v>
       </c>
       <c r="F317" s="4">
@@ -6305,89 +6503,89 @@
       </c>
     </row>
     <row r="318" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A318" s="48" t="s">
+      <c r="A318" s="53" t="s">
         <v>341</v>
       </c>
-      <c r="B318" s="48" t="s">
+      <c r="B318" s="53" t="s">
         <v>333</v>
       </c>
-      <c r="C318" s="48">
+      <c r="C318" s="53">
         <v>24.1</v>
       </c>
-      <c r="D318" s="48">
+      <c r="D318" s="53">
         <v>150</v>
       </c>
-      <c r="E318" s="48"/>
-      <c r="F318" s="48"/>
-      <c r="G318" s="48"/>
+      <c r="E318" s="53"/>
+      <c r="F318" s="53"/>
+      <c r="G318" s="53"/>
     </row>
     <row r="319" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A319" s="48" t="s">
+      <c r="A319" s="53" t="s">
         <v>342</v>
       </c>
-      <c r="B319" s="48" t="s">
+      <c r="B319" s="53" t="s">
         <v>336</v>
       </c>
-      <c r="C319" s="48">
+      <c r="C319" s="53">
         <v>23.9</v>
       </c>
-      <c r="D319" s="48">
+      <c r="D319" s="53">
         <v>60</v>
       </c>
-      <c r="E319" s="48"/>
-      <c r="F319" s="48"/>
-      <c r="G319" s="48"/>
+      <c r="E319" s="53"/>
+      <c r="F319" s="53"/>
+      <c r="G319" s="53"/>
     </row>
     <row r="320" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A320" s="48" t="s">
+      <c r="A320" s="53" t="s">
         <v>343</v>
       </c>
-      <c r="B320" s="48" t="s">
+      <c r="B320" s="53" t="s">
         <v>339</v>
       </c>
-      <c r="C320" s="48">
+      <c r="C320" s="53">
         <v>24.8</v>
       </c>
-      <c r="D320" s="48">
+      <c r="D320" s="53">
         <v>40</v>
       </c>
-      <c r="E320" s="48"/>
-      <c r="F320" s="48"/>
-      <c r="G320" s="48"/>
+      <c r="E320" s="53"/>
+      <c r="F320" s="53"/>
+      <c r="G320" s="53"/>
     </row>
     <row r="321" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A321" s="48" t="s">
+      <c r="A321" s="53" t="s">
         <v>344</v>
       </c>
-      <c r="B321" s="48" t="s">
+      <c r="B321" s="53" t="s">
         <v>333</v>
       </c>
-      <c r="C321" s="48">
+      <c r="C321" s="53">
         <v>23.6</v>
       </c>
-      <c r="D321" s="48">
+      <c r="D321" s="53">
         <v>90</v>
       </c>
-      <c r="E321" s="48"/>
-      <c r="F321" s="48"/>
-      <c r="G321" s="48"/>
+      <c r="E321" s="53"/>
+      <c r="F321" s="53"/>
+      <c r="G321" s="53"/>
     </row>
     <row r="322" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A322" s="48" t="s">
+      <c r="A322" s="53" t="s">
         <v>345</v>
       </c>
-      <c r="B322" s="48" t="s">
+      <c r="B322" s="53" t="s">
         <v>336</v>
       </c>
-      <c r="C322" s="48">
+      <c r="C322" s="53">
         <v>24.3</v>
       </c>
-      <c r="D322" s="48">
+      <c r="D322" s="53">
         <v>60</v>
       </c>
-      <c r="E322" s="48"/>
-      <c r="F322" s="48"/>
-      <c r="G322" s="48"/>
+      <c r="E322" s="53"/>
+      <c r="F322" s="53"/>
+      <c r="G322" s="53"/>
     </row>
     <row r="324" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A324" s="28" t="s">
@@ -6430,10 +6628,10 @@
       </c>
     </row>
     <row r="333" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A333" s="48" t="s">
+      <c r="A333" s="53" t="s">
         <v>354</v>
       </c>
-      <c r="B333" s="48"/>
+      <c r="B333" s="53"/>
     </row>
     <row r="334" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A334" s="6" t="s">
@@ -6444,54 +6642,54 @@
       </c>
     </row>
     <row r="335" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A335" s="48">
+      <c r="A335" s="53">
         <v>1040</v>
       </c>
-      <c r="B335" s="48" t="s">
+      <c r="B335" s="53" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="336" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A336" s="48">
+      <c r="A336" s="53">
         <v>1042</v>
       </c>
-      <c r="B336" s="48" t="s">
+      <c r="B336" s="53" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A337" s="48">
+      <c r="A337" s="53">
         <v>1051</v>
       </c>
-      <c r="B337" s="48" t="s">
+      <c r="B337" s="53" t="s">
         <v>355</v>
       </c>
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A338" s="48">
+      <c r="A338" s="53">
         <v>1063</v>
       </c>
-      <c r="B338" s="48" t="s">
+      <c r="B338" s="53" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A339" s="48">
+      <c r="A339" s="53">
         <v>1038</v>
       </c>
-      <c r="B339" s="48" t="s">
+      <c r="B339" s="53" t="s">
         <v>356</v>
       </c>
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A340" s="48"/>
-      <c r="B340" s="48"/>
+      <c r="A340" s="53"/>
+      <c r="B340" s="53"/>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A341" s="48" t="s">
+      <c r="A341" s="53" t="s">
         <v>357</v>
       </c>
-      <c r="B341" s="48"/>
+      <c r="B341" s="53"/>
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A342" s="6" t="s">
@@ -6502,7 +6700,7 @@
       </c>
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A343" s="48">
+      <c r="A343" s="53">
         <v>1042</v>
       </c>
       <c r="B343" s="4" t="str">
@@ -6515,7 +6713,7 @@
       </c>
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A344" s="48">
+      <c r="A344" s="53">
         <v>1038</v>
       </c>
       <c r="B344" s="4" t="str">
@@ -6524,7 +6722,7 @@
       </c>
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A345" s="48">
+      <c r="A345" s="53">
         <v>1051</v>
       </c>
       <c r="B345" s="4" t="str">
@@ -6533,7 +6731,7 @@
       </c>
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A346" s="48">
+      <c r="A346" s="53">
         <v>1040</v>
       </c>
       <c r="B346" s="4" t="str">
@@ -6542,7 +6740,7 @@
       </c>
     </row>
     <row r="347" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A347" s="48"/>
+      <c r="A347" s="53"/>
     </row>
     <row r="348" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A348" s="28" t="s">
@@ -6592,26 +6790,26 @@
       </c>
     </row>
     <row r="356" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A356" s="48" t="s">
+      <c r="A356" s="53" t="s">
         <v>363</v>
       </c>
-      <c r="B356" s="48">
+      <c r="B356" s="53">
         <v>85000</v>
       </c>
-      <c r="C356" s="48">
+      <c r="C356" s="53">
         <v>95000</v>
       </c>
-      <c r="D356" s="48">
+      <c r="D356" s="53">
         <v>110000</v>
       </c>
-      <c r="E356" s="48">
+      <c r="E356" s="53">
         <v>120000</v>
       </c>
     </row>
     <row r="357" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="C357" s="48"/>
-      <c r="D357" s="48"/>
-      <c r="E357" s="48"/>
+      <c r="C357" s="53"/>
+      <c r="D357" s="53"/>
+      <c r="E357" s="53"/>
     </row>
     <row r="358" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A358" s="1" t="s">
@@ -6624,22 +6822,22 @@
         <f>HLOOKUP(B358,A355:E356,2,0)</f>
         <v>110000</v>
       </c>
-      <c r="D358" s="48"/>
-      <c r="E358" s="48"/>
+      <c r="D358" s="53"/>
+      <c r="E358" s="53"/>
     </row>
     <row r="359" spans="1:5" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A359" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="C359" s="56" t="str">
+      <c r="C359" s="54" t="str">
         <f ca="1">_xlfn.FORMULATEXT(C358)</f>
         <v>=HLOOKUP(B358,A355:E356,2,0)</v>
       </c>
-      <c r="D359" s="48"/>
-      <c r="E359" s="48"/>
+      <c r="D359" s="53"/>
+      <c r="E359" s="53"/>
     </row>
     <row r="360" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="C360" s="56"/>
+      <c r="C360" s="54"/>
     </row>
     <row r="362" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A362" s="28" t="s">
@@ -6662,7 +6860,7 @@
       </c>
     </row>
     <row r="367" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A367" s="48" t="s">
+      <c r="A367" s="53" t="s">
         <v>398</v>
       </c>
     </row>
@@ -6670,7 +6868,7 @@
       <c r="A368" s="15"/>
     </row>
     <row r="369" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A369" s="48" t="s">
+      <c r="A369" s="53" t="s">
         <v>376</v>
       </c>
     </row>
@@ -6693,41 +6891,41 @@
       </c>
     </row>
     <row r="375" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A375" s="48" t="s">
+      <c r="A375" s="53" t="s">
         <v>378</v>
       </c>
-      <c r="B375" s="48"/>
-      <c r="C375" s="48"/>
-      <c r="D375" s="48"/>
-      <c r="E375" s="48"/>
-      <c r="F375" s="48"/>
-      <c r="G375" s="48"/>
-      <c r="H375" s="48"/>
+      <c r="B375" s="53"/>
+      <c r="C375" s="53"/>
+      <c r="D375" s="53"/>
+      <c r="E375" s="53"/>
+      <c r="F375" s="53"/>
+      <c r="G375" s="53"/>
+      <c r="H375" s="53"/>
     </row>
     <row r="376" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A376" s="32" t="s">
         <v>379</v>
       </c>
-      <c r="B376" s="48"/>
-      <c r="C376" s="48"/>
-      <c r="D376" s="48"/>
-      <c r="E376" s="48"/>
-      <c r="F376" s="48"/>
-      <c r="G376" s="48"/>
-      <c r="H376" s="48"/>
+      <c r="B376" s="53"/>
+      <c r="C376" s="53"/>
+      <c r="D376" s="53"/>
+      <c r="E376" s="53"/>
+      <c r="F376" s="53"/>
+      <c r="G376" s="53"/>
+      <c r="H376" s="53"/>
     </row>
     <row r="377" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A377" s="33" t="s">
         <v>380</v>
       </c>
-      <c r="B377" s="48"/>
-      <c r="C377" s="48"/>
-      <c r="E377" s="48"/>
-      <c r="F377" s="48"/>
+      <c r="B377" s="53"/>
+      <c r="C377" s="53"/>
+      <c r="E377" s="53"/>
+      <c r="F377" s="53"/>
       <c r="G377" s="33" t="s">
         <v>381</v>
       </c>
-      <c r="H377" s="48"/>
+      <c r="H377" s="53"/>
     </row>
     <row r="378" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A378" s="6" t="s">
@@ -6745,7 +6943,7 @@
       <c r="E378" s="6" t="s">
         <v>386</v>
       </c>
-      <c r="F378" s="48"/>
+      <c r="F378" s="53"/>
       <c r="G378" s="6" t="s">
         <v>387</v>
       </c>
@@ -6754,127 +6952,127 @@
       </c>
     </row>
     <row r="379" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A379" s="48" t="s">
+      <c r="A379" s="53" t="s">
         <v>388</v>
       </c>
-      <c r="B379" s="48" t="s">
+      <c r="B379" s="53" t="s">
         <v>389</v>
       </c>
-      <c r="C379" s="48">
+      <c r="C379" s="53">
         <v>0.8</v>
       </c>
       <c r="D379" s="4">
         <f>VLOOKUP(C379,G379:H383,2,1)</f>
         <v>6.5</v>
       </c>
-      <c r="E379" s="48">
+      <c r="E379" s="53">
         <v>5.2</v>
       </c>
-      <c r="F379" s="48"/>
-      <c r="G379" s="48">
+      <c r="F379" s="53"/>
+      <c r="G379" s="53">
         <v>0</v>
       </c>
-      <c r="H379" s="48">
+      <c r="H379" s="53">
         <v>6.5</v>
       </c>
     </row>
     <row r="380" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A380" s="48" t="s">
+      <c r="A380" s="53" t="s">
         <v>390</v>
       </c>
-      <c r="B380" s="48" t="s">
+      <c r="B380" s="53" t="s">
         <v>389</v>
       </c>
-      <c r="C380" s="48">
+      <c r="C380" s="53">
         <v>2.4</v>
       </c>
       <c r="D380" s="4">
         <f t="shared" ref="D380:D383" si="17">VLOOKUP(C380,G380:H384,2,1)</f>
         <v>5.75</v>
       </c>
-      <c r="E380" s="48">
+      <c r="E380" s="53">
         <v>13.8</v>
       </c>
-      <c r="F380" s="48"/>
-      <c r="G380" s="48">
+      <c r="F380" s="53"/>
+      <c r="G380" s="53">
         <v>1</v>
       </c>
-      <c r="H380" s="48">
+      <c r="H380" s="53">
         <v>5.75</v>
       </c>
     </row>
     <row r="381" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A381" s="48" t="s">
+      <c r="A381" s="53" t="s">
         <v>391</v>
       </c>
-      <c r="B381" s="48" t="s">
+      <c r="B381" s="53" t="s">
         <v>392</v>
       </c>
-      <c r="C381" s="48">
+      <c r="C381" s="53">
         <v>6.2</v>
       </c>
       <c r="D381" s="4">
         <f>VLOOKUP(C381,G381:H385,2,1)</f>
         <v>5</v>
       </c>
-      <c r="E381" s="48">
+      <c r="E381" s="53">
         <v>31</v>
       </c>
-      <c r="F381" s="48"/>
-      <c r="G381" s="48">
+      <c r="F381" s="53"/>
+      <c r="G381" s="53">
         <v>5</v>
       </c>
-      <c r="H381" s="48">
+      <c r="H381" s="53">
         <v>5</v>
       </c>
     </row>
     <row r="382" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A382" s="48" t="s">
+      <c r="A382" s="53" t="s">
         <v>393</v>
       </c>
-      <c r="B382" s="48" t="s">
+      <c r="B382" s="53" t="s">
         <v>394</v>
       </c>
-      <c r="C382" s="48">
+      <c r="C382" s="53">
         <v>12</v>
       </c>
       <c r="D382" s="4">
         <f t="shared" si="17"/>
         <v>4.25</v>
       </c>
-      <c r="E382" s="48">
+      <c r="E382" s="53">
         <v>51</v>
       </c>
-      <c r="F382" s="48"/>
-      <c r="G382" s="48">
+      <c r="F382" s="53"/>
+      <c r="G382" s="53">
         <v>10</v>
       </c>
-      <c r="H382" s="48">
+      <c r="H382" s="53">
         <v>4.25</v>
       </c>
     </row>
     <row r="383" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A383" s="48" t="s">
+      <c r="A383" s="53" t="s">
         <v>395</v>
       </c>
-      <c r="B383" s="48" t="s">
+      <c r="B383" s="53" t="s">
         <v>389</v>
       </c>
-      <c r="C383" s="48">
+      <c r="C383" s="53">
         <v>24.5</v>
       </c>
       <c r="D383" s="4">
         <f t="shared" si="17"/>
         <v>3.75</v>
       </c>
-      <c r="E383" s="48">
+      <c r="E383" s="53">
         <v>91.875</v>
       </c>
-      <c r="F383" s="48"/>
-      <c r="G383" s="48">
+      <c r="F383" s="53"/>
+      <c r="G383" s="53">
         <v>20</v>
       </c>
-      <c r="H383" s="48">
+      <c r="H383" s="53">
         <v>3.75</v>
       </c>
     </row>
@@ -6915,7 +7113,7 @@
       </c>
     </row>
     <row r="394" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A394" s="48" t="s">
+      <c r="A394" s="53" t="s">
         <v>435</v>
       </c>
     </row>
@@ -6957,115 +7155,115 @@
       </c>
     </row>
     <row r="402" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A402" s="48" t="s">
+      <c r="A402" s="53" t="s">
         <v>407</v>
       </c>
-      <c r="B402" s="48" t="s">
+      <c r="B402" s="53" t="s">
         <v>408</v>
       </c>
-      <c r="C402" s="48" t="s">
+      <c r="C402" s="53" t="s">
         <v>409</v>
       </c>
-      <c r="D402" s="48" t="s">
+      <c r="D402" s="53" t="s">
         <v>410</v>
       </c>
     </row>
     <row r="403" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A403" s="48" t="s">
+      <c r="A403" s="53" t="s">
         <v>411</v>
       </c>
-      <c r="B403" s="48" t="s">
+      <c r="B403" s="53" t="s">
         <v>412</v>
       </c>
-      <c r="C403" s="48" t="s">
+      <c r="C403" s="53" t="s">
         <v>413</v>
       </c>
-      <c r="D403" s="48" t="s">
+      <c r="D403" s="53" t="s">
         <v>414</v>
       </c>
     </row>
     <row r="404" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A404" s="48" t="s">
+      <c r="A404" s="53" t="s">
         <v>415</v>
       </c>
-      <c r="B404" s="48" t="s">
+      <c r="B404" s="53" t="s">
         <v>416</v>
       </c>
-      <c r="C404" s="48" t="s">
+      <c r="C404" s="53" t="s">
         <v>417</v>
       </c>
-      <c r="D404" s="48" t="s">
+      <c r="D404" s="53" t="s">
         <v>418</v>
       </c>
     </row>
     <row r="405" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A405" s="48" t="s">
+      <c r="A405" s="53" t="s">
         <v>419</v>
       </c>
-      <c r="B405" s="48" t="s">
+      <c r="B405" s="53" t="s">
         <v>420</v>
       </c>
-      <c r="C405" s="48" t="s">
+      <c r="C405" s="53" t="s">
         <v>421</v>
       </c>
-      <c r="D405" s="48" t="s">
+      <c r="D405" s="53" t="s">
         <v>422</v>
       </c>
     </row>
     <row r="406" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A406" s="48" t="s">
+      <c r="A406" s="53" t="s">
         <v>423</v>
       </c>
-      <c r="B406" s="48" t="s">
+      <c r="B406" s="53" t="s">
         <v>424</v>
       </c>
-      <c r="C406" s="48" t="s">
+      <c r="C406" s="53" t="s">
         <v>425</v>
       </c>
-      <c r="D406" s="48" t="s">
+      <c r="D406" s="53" t="s">
         <v>426</v>
       </c>
     </row>
     <row r="407" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A407" s="48" t="s">
+      <c r="A407" s="53" t="s">
         <v>427</v>
       </c>
-      <c r="B407" s="48" t="s">
+      <c r="B407" s="53" t="s">
         <v>428</v>
       </c>
-      <c r="C407" s="48" t="s">
+      <c r="C407" s="53" t="s">
         <v>429</v>
       </c>
-      <c r="D407" s="48" t="s">
+      <c r="D407" s="53" t="s">
         <v>430</v>
       </c>
     </row>
     <row r="408" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A408" s="48"/>
-      <c r="B408" s="48"/>
-      <c r="C408" s="48"/>
-      <c r="D408" s="48"/>
+      <c r="A408" s="53"/>
+      <c r="B408" s="53"/>
+      <c r="C408" s="53"/>
+      <c r="D408" s="53"/>
     </row>
     <row r="409" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A409" s="48" t="s">
+      <c r="A409" s="53" t="s">
         <v>403</v>
       </c>
-      <c r="B409" s="48" t="s">
+      <c r="B409" s="53" t="s">
         <v>419</v>
       </c>
-      <c r="C409" s="48"/>
-      <c r="D409" s="48"/>
+      <c r="C409" s="53"/>
+      <c r="D409" s="53"/>
     </row>
     <row r="410" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A410" s="48" t="s">
+      <c r="A410" s="53" t="s">
         <v>405</v>
       </c>
       <c r="B410" s="4" t="str">
         <f>VLOOKUP(B409,A402:C407,3,0)</f>
         <v>Denver</v>
       </c>
-      <c r="C410" s="48"/>
-      <c r="D410" s="48"/>
+      <c r="C410" s="53"/>
+      <c r="D410" s="53"/>
     </row>
     <row r="411" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B411" s="1" t="str">
@@ -7103,58 +7301,58 @@
       </c>
     </row>
     <row r="419" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A419" s="48" t="s">
+      <c r="A419" s="53" t="s">
         <v>442</v>
       </c>
-      <c r="B419" s="48" t="s">
+      <c r="B419" s="53" t="s">
         <v>443</v>
       </c>
-      <c r="C419" s="48" t="s">
+      <c r="C419" s="53" t="s">
         <v>444</v>
       </c>
-      <c r="D419" s="48">
+      <c r="D419" s="53">
         <v>12</v>
       </c>
     </row>
     <row r="420" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A420" s="48" t="s">
+      <c r="A420" s="53" t="s">
         <v>445</v>
       </c>
-      <c r="B420" s="48" t="s">
+      <c r="B420" s="53" t="s">
         <v>446</v>
       </c>
-      <c r="C420" s="48" t="s">
+      <c r="C420" s="53" t="s">
         <v>447</v>
       </c>
-      <c r="D420" s="48">
+      <c r="D420" s="53">
         <v>18</v>
       </c>
     </row>
     <row r="421" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A421" s="48" t="s">
+      <c r="A421" s="53" t="s">
         <v>448</v>
       </c>
-      <c r="B421" s="48" t="s">
+      <c r="B421" s="53" t="s">
         <v>449</v>
       </c>
-      <c r="C421" s="48" t="s">
+      <c r="C421" s="53" t="s">
         <v>106</v>
       </c>
-      <c r="D421" s="48">
+      <c r="D421" s="53">
         <v>24</v>
       </c>
     </row>
     <row r="422" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A422" s="48" t="s">
+      <c r="A422" s="53" t="s">
         <v>450</v>
       </c>
-      <c r="B422" s="48" t="s">
+      <c r="B422" s="53" t="s">
         <v>60</v>
       </c>
-      <c r="C422" s="48" t="s">
+      <c r="C422" s="53" t="s">
         <v>447</v>
       </c>
-      <c r="D422" s="48">
+      <c r="D422" s="53">
         <v>35</v>
       </c>
     </row>
@@ -7209,7 +7407,7 @@
       <c r="D432" s="6" t="s">
         <v>454</v>
       </c>
-      <c r="E432" s="48"/>
+      <c r="E432" s="53"/>
       <c r="F432" s="6" t="s">
         <v>455</v>
       </c>
@@ -7218,19 +7416,19 @@
       </c>
     </row>
     <row r="433" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A433" s="48" t="s">
+      <c r="A433" s="53" t="s">
         <v>456</v>
       </c>
-      <c r="B433" s="48" t="s">
+      <c r="B433" s="53" t="s">
         <v>457</v>
       </c>
-      <c r="C433" s="48" t="s">
+      <c r="C433" s="53" t="s">
         <v>458</v>
       </c>
-      <c r="D433" s="48">
+      <c r="D433" s="53">
         <v>6.25</v>
       </c>
-      <c r="E433" s="48"/>
+      <c r="E433" s="53"/>
       <c r="F433" s="34" t="s">
         <v>456</v>
       </c>
@@ -7240,19 +7438,19 @@
       </c>
     </row>
     <row r="434" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A434" s="48" t="s">
+      <c r="A434" s="53" t="s">
         <v>459</v>
       </c>
-      <c r="B434" s="48" t="s">
+      <c r="B434" s="53" t="s">
         <v>460</v>
       </c>
-      <c r="C434" s="48" t="s">
+      <c r="C434" s="53" t="s">
         <v>461</v>
       </c>
-      <c r="D434" s="48">
+      <c r="D434" s="53">
         <v>3.4</v>
       </c>
-      <c r="E434" s="48"/>
+      <c r="E434" s="53"/>
       <c r="F434" s="34" t="s">
         <v>462</v>
       </c>
@@ -7262,19 +7460,19 @@
       </c>
     </row>
     <row r="435" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A435" s="48" t="s">
+      <c r="A435" s="53" t="s">
         <v>463</v>
       </c>
-      <c r="B435" s="48" t="s">
+      <c r="B435" s="53" t="s">
         <v>464</v>
       </c>
-      <c r="C435" s="48" t="s">
+      <c r="C435" s="53" t="s">
         <v>461</v>
       </c>
-      <c r="D435" s="48">
+      <c r="D435" s="53">
         <v>19.989999999999998</v>
       </c>
-      <c r="E435" s="48"/>
+      <c r="E435" s="53"/>
       <c r="F435" s="34" t="s">
         <v>463</v>
       </c>
@@ -7284,19 +7482,19 @@
       </c>
     </row>
     <row r="436" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A436" s="48" t="s">
+      <c r="A436" s="53" t="s">
         <v>465</v>
       </c>
-      <c r="B436" s="48" t="s">
+      <c r="B436" s="53" t="s">
         <v>466</v>
       </c>
-      <c r="C436" s="48" t="s">
+      <c r="C436" s="53" t="s">
         <v>461</v>
       </c>
-      <c r="D436" s="48">
+      <c r="D436" s="53">
         <v>14.5</v>
       </c>
-      <c r="E436" s="48"/>
+      <c r="E436" s="53"/>
       <c r="F436" s="34" t="s">
         <v>467</v>
       </c>
@@ -7306,19 +7504,19 @@
       </c>
     </row>
     <row r="437" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A437" s="48" t="s">
+      <c r="A437" s="53" t="s">
         <v>468</v>
       </c>
-      <c r="B437" s="48" t="s">
+      <c r="B437" s="53" t="s">
         <v>469</v>
       </c>
-      <c r="C437" s="48" t="s">
+      <c r="C437" s="53" t="s">
         <v>470</v>
       </c>
-      <c r="D437" s="48">
+      <c r="D437" s="53">
         <v>8.75</v>
       </c>
-      <c r="E437" s="48"/>
+      <c r="E437" s="53"/>
       <c r="F437" s="34" t="s">
         <v>468</v>
       </c>
@@ -7328,19 +7526,19 @@
       </c>
     </row>
     <row r="438" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A438" s="48" t="s">
+      <c r="A438" s="53" t="s">
         <v>471</v>
       </c>
-      <c r="B438" s="48" t="s">
+      <c r="B438" s="53" t="s">
         <v>472</v>
       </c>
-      <c r="C438" s="48" t="s">
+      <c r="C438" s="53" t="s">
         <v>447</v>
       </c>
-      <c r="D438" s="48">
+      <c r="D438" s="53">
         <v>27.5</v>
       </c>
-      <c r="E438" s="48"/>
+      <c r="E438" s="53"/>
       <c r="F438" s="34" t="s">
         <v>473</v>
       </c>
@@ -7350,19 +7548,19 @@
       </c>
     </row>
     <row r="439" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A439" s="48" t="s">
+      <c r="A439" s="53" t="s">
         <v>474</v>
       </c>
-      <c r="B439" s="48" t="s">
+      <c r="B439" s="53" t="s">
         <v>475</v>
       </c>
-      <c r="C439" s="48" t="s">
+      <c r="C439" s="53" t="s">
         <v>470</v>
       </c>
-      <c r="D439" s="48">
+      <c r="D439" s="53">
         <v>12</v>
       </c>
-      <c r="E439" s="48"/>
+      <c r="E439" s="53"/>
       <c r="F439" s="34" t="s">
         <v>474</v>
       </c>
@@ -7381,7 +7579,7 @@
       </c>
     </row>
     <row r="442" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A442" s="48" t="s">
+      <c r="A442" s="53" t="s">
         <v>479</v>
       </c>
     </row>
@@ -7389,7 +7587,7 @@
       <c r="A443" s="15"/>
     </row>
     <row r="444" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A444" s="48" t="s">
+      <c r="A444" s="53" t="s">
         <v>505</v>
       </c>
     </row>
@@ -7397,7 +7595,7 @@
       <c r="A445" s="15"/>
     </row>
     <row r="446" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A446" s="48" t="s">
+      <c r="A446" s="53" t="s">
         <v>480</v>
       </c>
     </row>
@@ -7405,7 +7603,7 @@
       <c r="A447" s="15"/>
     </row>
     <row r="448" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A448" s="48" t="s">
+      <c r="A448" s="53" t="s">
         <v>481</v>
       </c>
     </row>
@@ -7424,122 +7622,122 @@
       </c>
     </row>
     <row r="451" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A451" s="48" t="s">
+      <c r="A451" s="53" t="s">
         <v>483</v>
       </c>
-      <c r="B451" s="48" t="s">
+      <c r="B451" s="53" t="s">
         <v>484</v>
       </c>
-      <c r="C451" s="48" t="s">
+      <c r="C451" s="53" t="s">
         <v>461</v>
       </c>
-      <c r="D451" s="48">
+      <c r="D451" s="53">
         <v>22.4</v>
       </c>
     </row>
     <row r="452" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A452" s="48" t="s">
+      <c r="A452" s="53" t="s">
         <v>485</v>
       </c>
-      <c r="B452" s="48" t="s">
+      <c r="B452" s="53" t="s">
         <v>486</v>
       </c>
-      <c r="C452" s="48" t="s">
+      <c r="C452" s="53" t="s">
         <v>487</v>
       </c>
-      <c r="D452" s="48">
+      <c r="D452" s="53">
         <v>18.5</v>
       </c>
     </row>
     <row r="453" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A453" s="48" t="s">
+      <c r="A453" s="53" t="s">
         <v>488</v>
       </c>
-      <c r="B453" s="48" t="s">
+      <c r="B453" s="53" t="s">
         <v>489</v>
       </c>
-      <c r="C453" s="48" t="s">
+      <c r="C453" s="53" t="s">
         <v>490</v>
       </c>
-      <c r="D453" s="48">
+      <c r="D453" s="53">
         <v>7.2</v>
       </c>
     </row>
     <row r="454" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A454" s="48" t="s">
+      <c r="A454" s="53" t="s">
         <v>491</v>
       </c>
-      <c r="B454" s="48" t="s">
+      <c r="B454" s="53" t="s">
         <v>492</v>
       </c>
-      <c r="C454" s="48" t="s">
+      <c r="C454" s="53" t="s">
         <v>487</v>
       </c>
-      <c r="D454" s="48">
+      <c r="D454" s="53">
         <v>9.75</v>
       </c>
     </row>
     <row r="455" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A455" s="48" t="s">
+      <c r="A455" s="53" t="s">
         <v>493</v>
       </c>
-      <c r="B455" s="48" t="s">
+      <c r="B455" s="53" t="s">
         <v>494</v>
       </c>
-      <c r="C455" s="48" t="s">
+      <c r="C455" s="53" t="s">
         <v>470</v>
       </c>
-      <c r="D455" s="48">
+      <c r="D455" s="53">
         <v>31</v>
       </c>
     </row>
     <row r="456" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A456" s="48" t="s">
+      <c r="A456" s="53" t="s">
         <v>495</v>
       </c>
-      <c r="B456" s="48" t="s">
+      <c r="B456" s="53" t="s">
         <v>496</v>
       </c>
-      <c r="C456" s="48" t="s">
+      <c r="C456" s="53" t="s">
         <v>487</v>
       </c>
-      <c r="D456" s="48">
+      <c r="D456" s="53">
         <v>12.6</v>
       </c>
     </row>
     <row r="457" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A457" s="48" t="s">
+      <c r="A457" s="53" t="s">
         <v>497</v>
       </c>
-      <c r="B457" s="48" t="s">
+      <c r="B457" s="53" t="s">
         <v>498</v>
       </c>
-      <c r="C457" s="48" t="s">
+      <c r="C457" s="53" t="s">
         <v>499</v>
       </c>
-      <c r="D457" s="48">
+      <c r="D457" s="53">
         <v>14.25</v>
       </c>
     </row>
     <row r="458" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A458" s="48" t="s">
+      <c r="A458" s="53" t="s">
         <v>500</v>
       </c>
-      <c r="B458" s="48" t="s">
+      <c r="B458" s="53" t="s">
         <v>501</v>
       </c>
-      <c r="C458" s="48" t="s">
+      <c r="C458" s="53" t="s">
         <v>487</v>
       </c>
-      <c r="D458" s="48">
+      <c r="D458" s="53">
         <v>24.9</v>
       </c>
     </row>
     <row r="459" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A459" s="48"/>
-      <c r="B459" s="48"/>
-      <c r="C459" s="48"/>
-      <c r="D459" s="48"/>
+      <c r="A459" s="53"/>
+      <c r="B459" s="53"/>
+      <c r="C459" s="53"/>
+      <c r="D459" s="53"/>
     </row>
     <row r="460" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A460" s="13" t="s">
@@ -7548,8 +7746,8 @@
       <c r="B460" s="36" t="s">
         <v>503</v>
       </c>
-      <c r="C460" s="48"/>
-      <c r="D460" s="48"/>
+      <c r="C460" s="53"/>
+      <c r="D460" s="53"/>
     </row>
     <row r="461" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A461" s="13" t="s">
@@ -7559,8 +7757,8 @@
         <f>_xlfn.XLOOKUP("*"&amp;B460&amp;"*",B451:B458,B451:B458,,2)</f>
         <v>Citrus Surface Cleaner</v>
       </c>
-      <c r="C461" s="48"/>
-      <c r="D461" s="48"/>
+      <c r="C461" s="53"/>
+      <c r="D461" s="53"/>
     </row>
     <row r="462" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A462" s="13" t="s">
@@ -7570,8 +7768,8 @@
         <f>_xlfn.XLOOKUP("*"&amp;B460&amp;"*",B451:B458,D451:D458,,2)</f>
         <v>12.6</v>
       </c>
-      <c r="C462" s="48"/>
-      <c r="D462" s="48"/>
+      <c r="C462" s="53"/>
+      <c r="D462" s="53"/>
     </row>
     <row r="464" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B464" s="1" t="str">
@@ -7580,60 +7778,60 @@
       </c>
     </row>
     <row r="465" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A465" s="48"/>
-      <c r="B465" s="48"/>
-      <c r="C465" s="48"/>
-      <c r="D465" s="48"/>
-      <c r="E465" s="48"/>
-      <c r="F465" s="48"/>
-      <c r="G465" s="48"/>
-      <c r="H465" s="48"/>
+      <c r="A465" s="53"/>
+      <c r="B465" s="53"/>
+      <c r="C465" s="53"/>
+      <c r="D465" s="53"/>
+      <c r="E465" s="53"/>
+      <c r="F465" s="53"/>
+      <c r="G465" s="53"/>
+      <c r="H465" s="53"/>
     </row>
     <row r="466" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A466" s="28" t="s">
         <v>506</v>
       </c>
-      <c r="B466" s="48"/>
-      <c r="C466" s="48"/>
-      <c r="D466" s="48"/>
-      <c r="E466" s="48"/>
-      <c r="F466" s="48"/>
-      <c r="G466" s="48"/>
-      <c r="H466" s="48"/>
+      <c r="B466" s="53"/>
+      <c r="C466" s="53"/>
+      <c r="D466" s="53"/>
+      <c r="E466" s="53"/>
+      <c r="F466" s="53"/>
+      <c r="G466" s="53"/>
+      <c r="H466" s="53"/>
     </row>
     <row r="467" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A467" s="48" t="s">
+      <c r="A467" s="53" t="s">
         <v>507</v>
       </c>
-      <c r="B467" s="48"/>
-      <c r="C467" s="48"/>
-      <c r="D467" s="48"/>
-      <c r="E467" s="48"/>
-      <c r="F467" s="48"/>
-      <c r="G467" s="48"/>
-      <c r="H467" s="48"/>
+      <c r="B467" s="53"/>
+      <c r="C467" s="53"/>
+      <c r="D467" s="53"/>
+      <c r="E467" s="53"/>
+      <c r="F467" s="53"/>
+      <c r="G467" s="53"/>
+      <c r="H467" s="53"/>
     </row>
     <row r="468" spans="1:8" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A468" s="48" t="s">
+      <c r="A468" s="53" t="s">
         <v>508</v>
       </c>
-      <c r="B468" s="48"/>
-      <c r="C468" s="48"/>
-      <c r="D468" s="48"/>
-      <c r="E468" s="48"/>
-      <c r="F468" s="48"/>
-      <c r="G468" s="48"/>
-      <c r="H468" s="48"/>
+      <c r="B468" s="53"/>
+      <c r="C468" s="53"/>
+      <c r="D468" s="53"/>
+      <c r="E468" s="53"/>
+      <c r="F468" s="53"/>
+      <c r="G468" s="53"/>
+      <c r="H468" s="53"/>
     </row>
     <row r="469" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A469" s="48"/>
-      <c r="B469" s="48"/>
-      <c r="C469" s="48"/>
-      <c r="D469" s="48"/>
-      <c r="E469" s="48"/>
-      <c r="F469" s="48"/>
-      <c r="G469" s="48"/>
-      <c r="H469" s="48"/>
+      <c r="A469" s="53"/>
+      <c r="B469" s="53"/>
+      <c r="C469" s="53"/>
+      <c r="D469" s="53"/>
+      <c r="E469" s="53"/>
+      <c r="F469" s="53"/>
+      <c r="G469" s="53"/>
+      <c r="H469" s="53"/>
     </row>
     <row r="470" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A470" s="9" t="s">
@@ -7645,83 +7843,83 @@
       <c r="C470" s="9" t="s">
         <v>509</v>
       </c>
-      <c r="D470" s="48"/>
-      <c r="E470" s="48"/>
-      <c r="F470" s="48"/>
-      <c r="G470" s="48"/>
-      <c r="H470" s="48"/>
+      <c r="D470" s="53"/>
+      <c r="E470" s="53"/>
+      <c r="F470" s="53"/>
+      <c r="G470" s="53"/>
+      <c r="H470" s="53"/>
     </row>
     <row r="471" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A471" s="48" t="s">
+      <c r="A471" s="53" t="s">
         <v>510</v>
       </c>
-      <c r="B471" s="48" t="s">
+      <c r="B471" s="53" t="s">
         <v>511</v>
       </c>
-      <c r="C471" s="48">
+      <c r="C471" s="53">
         <v>120</v>
       </c>
-      <c r="D471" s="48"/>
-      <c r="E471" s="48"/>
-      <c r="F471" s="48"/>
-      <c r="G471" s="48"/>
-      <c r="H471" s="48"/>
+      <c r="D471" s="53"/>
+      <c r="E471" s="53"/>
+      <c r="F471" s="53"/>
+      <c r="G471" s="53"/>
+      <c r="H471" s="53"/>
     </row>
     <row r="472" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A472" s="48" t="s">
+      <c r="A472" s="53" t="s">
         <v>512</v>
       </c>
-      <c r="B472" s="48" t="s">
+      <c r="B472" s="53" t="s">
         <v>513</v>
       </c>
-      <c r="C472" s="48">
+      <c r="C472" s="53">
         <v>50</v>
       </c>
-      <c r="D472" s="48"/>
-      <c r="E472" s="48"/>
-      <c r="F472" s="48"/>
-      <c r="G472" s="48"/>
-      <c r="H472" s="48"/>
+      <c r="D472" s="53"/>
+      <c r="E472" s="53"/>
+      <c r="F472" s="53"/>
+      <c r="G472" s="53"/>
+      <c r="H472" s="53"/>
     </row>
     <row r="473" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A473" s="48" t="s">
+      <c r="A473" s="53" t="s">
         <v>514</v>
       </c>
-      <c r="B473" s="48" t="s">
+      <c r="B473" s="53" t="s">
         <v>515</v>
       </c>
-      <c r="C473" s="48">
+      <c r="C473" s="53">
         <v>0</v>
       </c>
-      <c r="D473" s="48"/>
-      <c r="E473" s="48"/>
-      <c r="F473" s="48"/>
-      <c r="G473" s="48"/>
-      <c r="H473" s="48"/>
+      <c r="D473" s="53"/>
+      <c r="E473" s="53"/>
+      <c r="F473" s="53"/>
+      <c r="G473" s="53"/>
+      <c r="H473" s="53"/>
     </row>
     <row r="474" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A474" s="48"/>
-      <c r="B474" s="48"/>
-      <c r="C474" s="48"/>
-      <c r="D474" s="48"/>
-      <c r="E474" s="48"/>
-      <c r="F474" s="48"/>
-      <c r="G474" s="48"/>
-      <c r="H474" s="48"/>
+      <c r="A474" s="53"/>
+      <c r="B474" s="53"/>
+      <c r="C474" s="53"/>
+      <c r="D474" s="53"/>
+      <c r="E474" s="53"/>
+      <c r="F474" s="53"/>
+      <c r="G474" s="53"/>
+      <c r="H474" s="53"/>
     </row>
     <row r="475" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A475" s="48" t="s">
+      <c r="A475" s="53" t="s">
         <v>516</v>
       </c>
       <c r="B475" s="37" t="s">
         <v>517</v>
       </c>
-      <c r="C475" s="48"/>
-      <c r="D475" s="48"/>
-      <c r="E475" s="48"/>
-      <c r="F475" s="48"/>
-      <c r="G475" s="48"/>
-      <c r="H475" s="48"/>
+      <c r="C475" s="53"/>
+      <c r="D475" s="53"/>
+      <c r="E475" s="53"/>
+      <c r="F475" s="53"/>
+      <c r="G475" s="53"/>
+      <c r="H475" s="53"/>
     </row>
     <row r="476" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A476" s="38" t="s">
@@ -7731,15 +7929,15 @@
         <f>_xlfn.IFNA(VLOOKUP(B475,A471:C473,2,0),"Not Found")</f>
         <v>Not Found</v>
       </c>
-      <c r="C476" s="56" t="str">
+      <c r="C476" s="54" t="str">
         <f ca="1">_xlfn.FORMULATEXT(B476)</f>
         <v>=IFNA(VLOOKUP(B475,A471:C473,2,0),"Not Found")</v>
       </c>
-      <c r="D476" s="56"/>
-      <c r="E476" s="56"/>
-      <c r="F476" s="48"/>
-      <c r="G476" s="48"/>
-      <c r="H476" s="48"/>
+      <c r="D476" s="54"/>
+      <c r="E476" s="54"/>
+      <c r="F476" s="53"/>
+      <c r="G476" s="53"/>
+      <c r="H476" s="53"/>
     </row>
     <row r="477" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A477" s="38" t="s">
@@ -7749,81 +7947,81 @@
         <f>_xlfn.XLOOKUP(B475,A471:A473,B471:B473,"Not Found")</f>
         <v>Not Found</v>
       </c>
-      <c r="C477" s="56" t="str">
+      <c r="C477" s="54" t="str">
         <f ca="1">_xlfn.FORMULATEXT(B477)</f>
         <v>=XLOOKUP(B475,A471:A473,B471:B473,"Not Found")</v>
       </c>
-      <c r="D477" s="56"/>
-      <c r="E477" s="56"/>
-      <c r="F477" s="48"/>
-      <c r="G477" s="48"/>
-      <c r="H477" s="48"/>
+      <c r="D477" s="54"/>
+      <c r="E477" s="54"/>
+      <c r="F477" s="53"/>
+      <c r="G477" s="53"/>
+      <c r="H477" s="53"/>
     </row>
     <row r="478" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A478" s="48"/>
-      <c r="B478" s="48"/>
-      <c r="C478" s="48"/>
-      <c r="D478" s="48"/>
-      <c r="E478" s="48"/>
-      <c r="F478" s="48"/>
-      <c r="G478" s="48"/>
-      <c r="H478" s="48"/>
+      <c r="A478" s="53"/>
+      <c r="B478" s="53"/>
+      <c r="C478" s="53"/>
+      <c r="D478" s="53"/>
+      <c r="E478" s="53"/>
+      <c r="F478" s="53"/>
+      <c r="G478" s="53"/>
+      <c r="H478" s="53"/>
     </row>
     <row r="479" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A479" s="48"/>
-      <c r="B479" s="48"/>
-      <c r="C479" s="48"/>
-      <c r="D479" s="48"/>
-      <c r="E479" s="48"/>
-      <c r="F479" s="48"/>
-      <c r="G479" s="48"/>
-      <c r="H479" s="48"/>
+      <c r="A479" s="53"/>
+      <c r="B479" s="53"/>
+      <c r="C479" s="53"/>
+      <c r="D479" s="53"/>
+      <c r="E479" s="53"/>
+      <c r="F479" s="53"/>
+      <c r="G479" s="53"/>
+      <c r="H479" s="53"/>
     </row>
     <row r="480" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A480" s="28" t="s">
         <v>545</v>
       </c>
-      <c r="B480" s="48"/>
-      <c r="C480" s="48"/>
-      <c r="D480" s="48"/>
-      <c r="E480" s="48"/>
-      <c r="F480" s="48"/>
-      <c r="G480" s="48"/>
-      <c r="H480" s="48"/>
+      <c r="B480" s="53"/>
+      <c r="C480" s="53"/>
+      <c r="D480" s="53"/>
+      <c r="E480" s="53"/>
+      <c r="F480" s="53"/>
+      <c r="G480" s="53"/>
+      <c r="H480" s="53"/>
     </row>
     <row r="481" spans="1:8" ht="124.2" x14ac:dyDescent="0.3">
-      <c r="A481" s="48" t="s">
+      <c r="A481" s="53" t="s">
         <v>546</v>
       </c>
-      <c r="B481" s="48"/>
-      <c r="C481" s="48"/>
-      <c r="D481" s="48"/>
-      <c r="E481" s="48"/>
-      <c r="F481" s="48"/>
-      <c r="G481" s="48"/>
-      <c r="H481" s="48"/>
+      <c r="B481" s="53"/>
+      <c r="C481" s="53"/>
+      <c r="D481" s="53"/>
+      <c r="E481" s="53"/>
+      <c r="F481" s="53"/>
+      <c r="G481" s="53"/>
+      <c r="H481" s="53"/>
     </row>
     <row r="482" spans="1:8" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A482" s="48" t="s">
+      <c r="A482" s="53" t="s">
         <v>547</v>
       </c>
-      <c r="B482" s="48"/>
-      <c r="C482" s="48"/>
-      <c r="D482" s="48"/>
-      <c r="E482" s="48"/>
-      <c r="F482" s="48"/>
-      <c r="G482" s="48"/>
-      <c r="H482" s="48"/>
+      <c r="B482" s="53"/>
+      <c r="C482" s="53"/>
+      <c r="D482" s="53"/>
+      <c r="E482" s="53"/>
+      <c r="F482" s="53"/>
+      <c r="G482" s="53"/>
+      <c r="H482" s="53"/>
     </row>
     <row r="483" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A483" s="48"/>
-      <c r="B483" s="48"/>
-      <c r="C483" s="48"/>
-      <c r="D483" s="48"/>
-      <c r="E483" s="48"/>
-      <c r="F483" s="48"/>
-      <c r="G483" s="48"/>
-      <c r="H483" s="48"/>
+      <c r="A483" s="53"/>
+      <c r="B483" s="53"/>
+      <c r="C483" s="53"/>
+      <c r="D483" s="53"/>
+      <c r="E483" s="53"/>
+      <c r="F483" s="53"/>
+      <c r="G483" s="53"/>
+      <c r="H483" s="53"/>
     </row>
     <row r="484" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A484" s="9" t="s">
@@ -7838,164 +8036,164 @@
       <c r="D484" s="9" t="s">
         <v>522</v>
       </c>
-      <c r="E484" s="48"/>
-      <c r="F484" s="48"/>
-      <c r="G484" s="48"/>
-      <c r="H484" s="48"/>
+      <c r="E484" s="53"/>
+      <c r="F484" s="53"/>
+      <c r="G484" s="53"/>
+      <c r="H484" s="53"/>
     </row>
     <row r="485" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A485" s="48" t="s">
+      <c r="A485" s="53" t="s">
         <v>523</v>
       </c>
-      <c r="B485" s="48" t="s">
+      <c r="B485" s="53" t="s">
         <v>524</v>
       </c>
-      <c r="C485" s="48" t="s">
+      <c r="C485" s="53" t="s">
         <v>525</v>
       </c>
-      <c r="D485" s="48" t="s">
+      <c r="D485" s="53" t="s">
         <v>526</v>
       </c>
-      <c r="E485" s="48"/>
-      <c r="F485" s="48"/>
-      <c r="G485" s="48"/>
-      <c r="H485" s="48"/>
+      <c r="E485" s="53"/>
+      <c r="F485" s="53"/>
+      <c r="G485" s="53"/>
+      <c r="H485" s="53"/>
     </row>
     <row r="486" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A486" s="48" t="s">
+      <c r="A486" s="53" t="s">
         <v>523</v>
       </c>
-      <c r="B486" s="48" t="s">
+      <c r="B486" s="53" t="s">
         <v>117</v>
       </c>
-      <c r="C486" s="48" t="s">
+      <c r="C486" s="53" t="s">
         <v>525</v>
       </c>
-      <c r="D486" s="48" t="s">
+      <c r="D486" s="53" t="s">
         <v>526</v>
       </c>
-      <c r="E486" s="48"/>
-      <c r="F486" s="48"/>
-      <c r="G486" s="48"/>
-      <c r="H486" s="48"/>
+      <c r="E486" s="53"/>
+      <c r="F486" s="53"/>
+      <c r="G486" s="53"/>
+      <c r="H486" s="53"/>
     </row>
     <row r="487" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A487" s="48" t="s">
+      <c r="A487" s="53" t="s">
         <v>527</v>
       </c>
-      <c r="B487" s="48" t="s">
+      <c r="B487" s="53" t="s">
         <v>528</v>
       </c>
-      <c r="C487" s="48" t="s">
+      <c r="C487" s="53" t="s">
         <v>356</v>
       </c>
-      <c r="D487" s="48" t="s">
+      <c r="D487" s="53" t="s">
         <v>529</v>
       </c>
-      <c r="E487" s="48"/>
-      <c r="F487" s="48"/>
-      <c r="G487" s="48"/>
-      <c r="H487" s="48"/>
+      <c r="E487" s="53"/>
+      <c r="F487" s="53"/>
+      <c r="G487" s="53"/>
+      <c r="H487" s="53"/>
     </row>
     <row r="488" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A488" s="48" t="s">
+      <c r="A488" s="53" t="s">
         <v>527</v>
       </c>
-      <c r="B488" s="48" t="s">
+      <c r="B488" s="53" t="s">
         <v>530</v>
       </c>
-      <c r="C488" s="48" t="s">
+      <c r="C488" s="53" t="s">
         <v>356</v>
       </c>
-      <c r="D488" s="48" t="s">
+      <c r="D488" s="53" t="s">
         <v>529</v>
       </c>
-      <c r="E488" s="48"/>
-      <c r="F488" s="48"/>
-      <c r="G488" s="48"/>
-      <c r="H488" s="48"/>
+      <c r="E488" s="53"/>
+      <c r="F488" s="53"/>
+      <c r="G488" s="53"/>
+      <c r="H488" s="53"/>
     </row>
     <row r="489" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A489" s="48" t="s">
+      <c r="A489" s="53" t="s">
         <v>124</v>
       </c>
-      <c r="B489" s="48" t="s">
+      <c r="B489" s="53" t="s">
         <v>531</v>
       </c>
-      <c r="C489" s="48" t="s">
+      <c r="C489" s="53" t="s">
         <v>532</v>
       </c>
-      <c r="D489" s="48" t="s">
+      <c r="D489" s="53" t="s">
         <v>526</v>
       </c>
-      <c r="E489" s="48"/>
-      <c r="F489" s="48"/>
-      <c r="G489" s="48"/>
-      <c r="H489" s="48"/>
+      <c r="E489" s="53"/>
+      <c r="F489" s="53"/>
+      <c r="G489" s="53"/>
+      <c r="H489" s="53"/>
     </row>
     <row r="490" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A490" s="48" t="s">
+      <c r="A490" s="53" t="s">
         <v>124</v>
       </c>
-      <c r="B490" s="48" t="s">
+      <c r="B490" s="53" t="s">
         <v>533</v>
       </c>
-      <c r="C490" s="48" t="s">
+      <c r="C490" s="53" t="s">
         <v>532</v>
       </c>
-      <c r="D490" s="48" t="s">
+      <c r="D490" s="53" t="s">
         <v>526</v>
       </c>
-      <c r="E490" s="48"/>
-      <c r="F490" s="48"/>
-      <c r="G490" s="48"/>
-      <c r="H490" s="48"/>
+      <c r="E490" s="53"/>
+      <c r="F490" s="53"/>
+      <c r="G490" s="53"/>
+      <c r="H490" s="53"/>
     </row>
     <row r="491" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A491" s="48" t="s">
+      <c r="A491" s="53" t="s">
         <v>534</v>
       </c>
-      <c r="B491" s="48" t="s">
+      <c r="B491" s="53" t="s">
         <v>535</v>
       </c>
-      <c r="C491" s="48" t="s">
+      <c r="C491" s="53" t="s">
         <v>536</v>
       </c>
-      <c r="D491" s="48" t="s">
+      <c r="D491" s="53" t="s">
         <v>537</v>
       </c>
-      <c r="E491" s="48"/>
+      <c r="E491" s="53"/>
     </row>
     <row r="492" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A492" s="48" t="s">
+      <c r="A492" s="53" t="s">
         <v>534</v>
       </c>
-      <c r="B492" s="48" t="s">
+      <c r="B492" s="53" t="s">
         <v>538</v>
       </c>
-      <c r="C492" s="48" t="s">
+      <c r="C492" s="53" t="s">
         <v>536</v>
       </c>
-      <c r="D492" s="48" t="s">
+      <c r="D492" s="53" t="s">
         <v>537</v>
       </c>
-      <c r="E492" s="48"/>
+      <c r="E492" s="53"/>
     </row>
     <row r="493" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A493" s="48"/>
-      <c r="B493" s="48"/>
-      <c r="C493" s="48"/>
-      <c r="D493" s="48"/>
-      <c r="E493" s="48"/>
+      <c r="A493" s="53"/>
+      <c r="B493" s="53"/>
+      <c r="C493" s="53"/>
+      <c r="D493" s="53"/>
+      <c r="E493" s="53"/>
     </row>
     <row r="494" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A494" s="39" t="s">
         <v>539</v>
       </c>
-      <c r="B494" s="48"/>
-      <c r="C494" s="48"/>
-      <c r="D494" s="48"/>
-      <c r="E494" s="48"/>
+      <c r="B494" s="53"/>
+      <c r="C494" s="53"/>
+      <c r="D494" s="53"/>
+      <c r="E494" s="53"/>
     </row>
     <row r="495" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A495" s="39" t="s">
@@ -8007,152 +8205,152 @@
       <c r="C495" s="39" t="s">
         <v>541</v>
       </c>
-      <c r="D495" s="48"/>
-      <c r="E495" s="48"/>
+      <c r="D495" s="53"/>
+      <c r="E495" s="53"/>
     </row>
     <row r="496" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A496" s="48" t="s">
+      <c r="A496" s="53" t="s">
         <v>530</v>
       </c>
       <c r="B496" s="39" t="str">
         <f>INDEX(A485:A492,MATCH(A496,B485:B492,0))</f>
         <v>Thomas Nguyen</v>
       </c>
-      <c r="C496" s="48" t="s">
+      <c r="C496" s="53" t="s">
         <v>542</v>
       </c>
-      <c r="D496" s="48"/>
-      <c r="E496" s="48"/>
+      <c r="D496" s="53"/>
+      <c r="E496" s="53"/>
     </row>
     <row r="497" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A497" s="48" t="s">
+      <c r="A497" s="53" t="s">
         <v>535</v>
       </c>
       <c r="B497" s="39" t="str">
         <f>INDEX(A485:A492,MATCH(A497,B485:B492,0))</f>
         <v>David Brown</v>
       </c>
-      <c r="C497" s="48" t="s">
+      <c r="C497" s="53" t="s">
         <v>543</v>
       </c>
-      <c r="D497" s="48"/>
-      <c r="E497" s="48"/>
+      <c r="D497" s="53"/>
+      <c r="E497" s="53"/>
     </row>
     <row r="498" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A498" s="48" t="s">
+      <c r="A498" s="53" t="s">
         <v>117</v>
       </c>
       <c r="B498" s="39" t="str">
         <f>INDEX(A485:A492,MATCH(A498,B485:B492,0))</f>
         <v>Maria Gomez</v>
       </c>
-      <c r="C498" s="48" t="s">
+      <c r="C498" s="53" t="s">
         <v>544</v>
       </c>
-      <c r="D498" s="48"/>
-      <c r="E498" s="48"/>
+      <c r="D498" s="53"/>
+      <c r="E498" s="53"/>
     </row>
     <row r="499" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A499" s="48"/>
-      <c r="B499" s="48"/>
-      <c r="C499" s="48"/>
-      <c r="D499" s="48"/>
-      <c r="E499" s="48"/>
+      <c r="A499" s="53"/>
+      <c r="B499" s="53"/>
+      <c r="C499" s="53"/>
+      <c r="D499" s="53"/>
+      <c r="E499" s="53"/>
     </row>
     <row r="500" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A500" s="48"/>
-      <c r="B500" s="56" t="str">
+      <c r="A500" s="53"/>
+      <c r="B500" s="54" t="str">
         <f ca="1">_xlfn.FORMULATEXT(B496)</f>
         <v>=INDEX(A485:A492,MATCH(A496,B485:B492,0))</v>
       </c>
-      <c r="C500" s="56"/>
-      <c r="D500" s="48"/>
-      <c r="E500" s="48"/>
+      <c r="C500" s="54"/>
+      <c r="D500" s="53"/>
+      <c r="E500" s="53"/>
     </row>
     <row r="501" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A501" s="48"/>
-      <c r="B501" s="48"/>
-      <c r="C501" s="48"/>
-      <c r="D501" s="48"/>
-      <c r="E501" s="48"/>
+      <c r="A501" s="53"/>
+      <c r="B501" s="53"/>
+      <c r="C501" s="53"/>
+      <c r="D501" s="53"/>
+      <c r="E501" s="53"/>
     </row>
     <row r="502" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A502" s="28" t="s">
         <v>548</v>
       </c>
-      <c r="B502" s="48"/>
-      <c r="C502" s="48"/>
-      <c r="D502" s="48"/>
-      <c r="E502" s="48"/>
+      <c r="B502" s="53"/>
+      <c r="C502" s="53"/>
+      <c r="D502" s="53"/>
+      <c r="E502" s="53"/>
     </row>
     <row r="503" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A503" s="48" t="s">
+      <c r="A503" s="53" t="s">
         <v>549</v>
       </c>
-      <c r="B503" s="48"/>
-      <c r="C503" s="48"/>
-      <c r="D503" s="48"/>
-      <c r="E503" s="48"/>
+      <c r="B503" s="53"/>
+      <c r="C503" s="53"/>
+      <c r="D503" s="53"/>
+      <c r="E503" s="53"/>
     </row>
     <row r="504" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A504" s="48"/>
-      <c r="B504" s="48"/>
-      <c r="C504" s="48"/>
-      <c r="D504" s="48"/>
-      <c r="E504" s="48"/>
+      <c r="A504" s="53"/>
+      <c r="B504" s="53"/>
+      <c r="C504" s="53"/>
+      <c r="D504" s="53"/>
+      <c r="E504" s="53"/>
     </row>
     <row r="505" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A505" s="48" t="s">
+      <c r="A505" s="53" t="s">
         <v>550</v>
       </c>
     </row>
     <row r="506" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A506" s="48"/>
+      <c r="A506" s="53"/>
     </row>
     <row r="507" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A507" s="48" t="s">
+      <c r="A507" s="53" t="s">
         <v>591</v>
       </c>
     </row>
     <row r="508" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A508" s="48" t="s">
+      <c r="A508" s="53" t="s">
         <v>592</v>
       </c>
     </row>
     <row r="509" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A509" s="48"/>
+      <c r="A509" s="53"/>
     </row>
     <row r="510" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A510" s="48" t="s">
+      <c r="A510" s="53" t="s">
         <v>593</v>
       </c>
     </row>
     <row r="511" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A511" s="48"/>
+      <c r="A511" s="53"/>
     </row>
     <row r="512" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A512" s="48" t="s">
+      <c r="A512" s="53" t="s">
         <v>551</v>
       </c>
     </row>
     <row r="513" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A513" s="48"/>
+      <c r="A513" s="53"/>
     </row>
     <row r="514" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A514" s="48" t="s">
+      <c r="A514" s="53" t="s">
         <v>594</v>
       </c>
     </row>
     <row r="515" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A515" s="48" t="s">
+      <c r="A515" s="53" t="s">
         <v>595</v>
       </c>
     </row>
     <row r="516" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A516" s="48"/>
+      <c r="A516" s="53"/>
     </row>
     <row r="517" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A517" s="48" t="s">
+      <c r="A517" s="53" t="s">
         <v>552</v>
       </c>
     </row>
@@ -8170,123 +8368,123 @@
         <v>554</v>
       </c>
     </row>
-    <row r="520" spans="1:4" s="48" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A520" s="48" t="s">
+    <row r="520" spans="1:4" s="53" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A520" s="53" t="s">
         <v>555</v>
       </c>
-      <c r="B520" s="48" t="s">
+      <c r="B520" s="53" t="s">
         <v>556</v>
       </c>
-      <c r="C520" s="48" t="s">
+      <c r="C520" s="53" t="s">
         <v>557</v>
       </c>
-      <c r="D520" s="48" t="s">
+      <c r="D520" s="53" t="s">
         <v>558</v>
       </c>
     </row>
-    <row r="521" spans="1:4" s="48" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A521" s="48" t="s">
+    <row r="521" spans="1:4" s="53" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A521" s="53" t="s">
         <v>559</v>
       </c>
-      <c r="B521" s="48" t="s">
+      <c r="B521" s="53" t="s">
         <v>560</v>
       </c>
-      <c r="C521" s="48" t="s">
+      <c r="C521" s="53" t="s">
         <v>561</v>
       </c>
-      <c r="D521" s="48" t="s">
+      <c r="D521" s="53" t="s">
         <v>558</v>
       </c>
     </row>
-    <row r="522" spans="1:4" s="48" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A522" s="48" t="s">
+    <row r="522" spans="1:4" s="53" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A522" s="53" t="s">
         <v>562</v>
       </c>
-      <c r="B522" s="48" t="s">
+      <c r="B522" s="53" t="s">
         <v>563</v>
       </c>
-      <c r="C522" s="48" t="s">
+      <c r="C522" s="53" t="s">
         <v>564</v>
       </c>
-      <c r="D522" s="48" t="s">
+      <c r="D522" s="53" t="s">
         <v>565</v>
       </c>
     </row>
-    <row r="523" spans="1:4" s="48" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A523" s="48" t="s">
+    <row r="523" spans="1:4" s="53" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A523" s="53" t="s">
         <v>566</v>
       </c>
-      <c r="B523" s="48" t="s">
+      <c r="B523" s="53" t="s">
         <v>567</v>
       </c>
-      <c r="C523" s="48" t="s">
+      <c r="C523" s="53" t="s">
         <v>568</v>
       </c>
-      <c r="D523" s="48" t="s">
+      <c r="D523" s="53" t="s">
         <v>569</v>
       </c>
     </row>
-    <row r="524" spans="1:4" s="48" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A524" s="48" t="s">
+    <row r="524" spans="1:4" s="53" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A524" s="53" t="s">
         <v>570</v>
       </c>
-      <c r="B524" s="48" t="s">
+      <c r="B524" s="53" t="s">
         <v>571</v>
       </c>
-      <c r="C524" s="48" t="s">
+      <c r="C524" s="53" t="s">
         <v>572</v>
       </c>
-      <c r="D524" s="48" t="s">
+      <c r="D524" s="53" t="s">
         <v>565</v>
       </c>
     </row>
-    <row r="525" spans="1:4" s="48" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A525" s="48" t="s">
+    <row r="525" spans="1:4" s="53" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A525" s="53" t="s">
         <v>573</v>
       </c>
-      <c r="B525" s="48" t="s">
+      <c r="B525" s="53" t="s">
         <v>574</v>
       </c>
-      <c r="C525" s="48" t="s">
+      <c r="C525" s="53" t="s">
         <v>575</v>
       </c>
-      <c r="D525" s="48" t="s">
+      <c r="D525" s="53" t="s">
         <v>558</v>
       </c>
     </row>
-    <row r="526" spans="1:4" s="48" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A526" s="48" t="s">
+    <row r="526" spans="1:4" s="53" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A526" s="53" t="s">
         <v>576</v>
       </c>
-      <c r="B526" s="48" t="s">
+      <c r="B526" s="53" t="s">
         <v>577</v>
       </c>
-      <c r="C526" s="48" t="s">
+      <c r="C526" s="53" t="s">
         <v>578</v>
       </c>
-      <c r="D526" s="48" t="s">
+      <c r="D526" s="53" t="s">
         <v>569</v>
       </c>
     </row>
-    <row r="527" spans="1:4" s="48" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A527" s="48" t="s">
+    <row r="527" spans="1:4" s="53" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A527" s="53" t="s">
         <v>579</v>
       </c>
-      <c r="B527" s="48" t="s">
+      <c r="B527" s="53" t="s">
         <v>580</v>
       </c>
-      <c r="C527" s="48" t="s">
+      <c r="C527" s="53" t="s">
         <v>581</v>
       </c>
-      <c r="D527" s="48" t="s">
+      <c r="D527" s="53" t="s">
         <v>565</v>
       </c>
     </row>
     <row r="528" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A528" s="48"/>
-      <c r="B528" s="48"/>
-      <c r="C528" s="48"/>
-      <c r="D528" s="48"/>
+      <c r="A528" s="53"/>
+      <c r="B528" s="53"/>
+      <c r="C528" s="53"/>
+      <c r="D528" s="53"/>
     </row>
     <row r="529" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A529" s="40" t="s">
@@ -8302,54 +8500,54 @@
         <v>584</v>
       </c>
     </row>
-    <row r="530" spans="1:5" s="48" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A530" s="48" t="s">
+    <row r="530" spans="1:5" s="53" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A530" s="53" t="s">
         <v>585</v>
       </c>
-      <c r="B530" s="48" t="s">
+      <c r="B530" s="53" t="s">
         <v>577</v>
       </c>
       <c r="C530" s="4" t="str">
         <f>INDEX(A520:A527,MATCH(B530,B520:B527,0))</f>
         <v>ingrid.larsen@northwind.com</v>
       </c>
-      <c r="D530" s="48" t="s">
+      <c r="D530" s="53" t="s">
         <v>586</v>
       </c>
     </row>
-    <row r="531" spans="1:5" s="48" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A531" s="48" t="s">
+    <row r="531" spans="1:5" s="53" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A531" s="53" t="s">
         <v>587</v>
       </c>
-      <c r="B531" s="48" t="s">
+      <c r="B531" s="53" t="s">
         <v>560</v>
       </c>
       <c r="C531" s="4" t="str">
         <f t="shared" ref="C531:C532" si="19">INDEX(A521:A528,MATCH(B531,B521:B528,0))</f>
         <v>bianca.chen@northwind.com</v>
       </c>
-      <c r="D531" s="48" t="s">
+      <c r="D531" s="53" t="s">
         <v>588</v>
       </c>
     </row>
-    <row r="532" spans="1:5" s="48" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A532" s="48" t="s">
+    <row r="532" spans="1:5" s="53" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A532" s="53" t="s">
         <v>589</v>
       </c>
-      <c r="B532" s="48" t="s">
+      <c r="B532" s="53" t="s">
         <v>563</v>
       </c>
       <c r="C532" s="4" t="str">
         <f t="shared" si="19"/>
         <v>diego.souza@northwind.com</v>
       </c>
-      <c r="D532" s="48" t="s">
+      <c r="D532" s="53" t="s">
         <v>590</v>
       </c>
     </row>
-    <row r="533" spans="1:5" s="48" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="534" spans="1:5" s="48" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C534" s="48" t="str">
+    <row r="533" spans="1:5" s="53" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="534" spans="1:5" s="53" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="C534" s="53" t="str">
         <f ca="1">_xlfn.FORMULATEXT(C530)</f>
         <v>=INDEX(A520:A527,MATCH(B530,B520:B527,0))</v>
       </c>
@@ -8382,142 +8580,142 @@
       </c>
     </row>
     <row r="540" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A540" s="48" t="s">
+      <c r="A540" s="53" t="s">
         <v>602</v>
       </c>
-      <c r="B540" s="48">
+      <c r="B540" s="53">
         <v>5</v>
       </c>
-      <c r="C540" s="48">
+      <c r="C540" s="53">
         <v>7</v>
       </c>
-      <c r="D540" s="48">
+      <c r="D540" s="53">
         <v>10</v>
       </c>
-      <c r="E540" s="48">
+      <c r="E540" s="53">
         <v>14</v>
       </c>
     </row>
     <row r="541" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A541" s="48" t="s">
+      <c r="A541" s="53" t="s">
         <v>603</v>
       </c>
-      <c r="B541" s="48">
+      <c r="B541" s="53">
         <v>9</v>
       </c>
-      <c r="C541" s="48">
+      <c r="C541" s="53">
         <v>12</v>
       </c>
-      <c r="D541" s="48">
+      <c r="D541" s="53">
         <v>16</v>
       </c>
-      <c r="E541" s="48">
+      <c r="E541" s="53">
         <v>22</v>
       </c>
     </row>
     <row r="542" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A542" s="48" t="s">
+      <c r="A542" s="53" t="s">
         <v>604</v>
       </c>
-      <c r="B542" s="48">
+      <c r="B542" s="53">
         <v>14</v>
       </c>
-      <c r="C542" s="48">
+      <c r="C542" s="53">
         <v>19</v>
       </c>
-      <c r="D542" s="48">
+      <c r="D542" s="53">
         <v>28</v>
       </c>
-      <c r="E542" s="48">
+      <c r="E542" s="53">
         <v>40</v>
       </c>
     </row>
     <row r="543" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A543" s="48" t="s">
+      <c r="A543" s="53" t="s">
         <v>605</v>
       </c>
-      <c r="B543" s="48">
+      <c r="B543" s="53">
         <v>24</v>
       </c>
-      <c r="C543" s="48">
+      <c r="C543" s="53">
         <v>33</v>
       </c>
-      <c r="D543" s="48">
+      <c r="D543" s="53">
         <v>48</v>
       </c>
-      <c r="E543" s="48">
+      <c r="E543" s="53">
         <v>68</v>
       </c>
     </row>
     <row r="544" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A544" s="48" t="s">
+      <c r="A544" s="53" t="s">
         <v>606</v>
       </c>
-      <c r="B544" s="48">
+      <c r="B544" s="53">
         <v>30</v>
       </c>
-      <c r="C544" s="48">
+      <c r="C544" s="53">
         <v>42</v>
       </c>
-      <c r="D544" s="48">
+      <c r="D544" s="53">
         <v>60</v>
       </c>
-      <c r="E544" s="48">
+      <c r="E544" s="53">
         <v>85</v>
       </c>
     </row>
     <row r="545" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A545" s="48"/>
-      <c r="B545" s="48"/>
-      <c r="C545" s="48"/>
-      <c r="D545" s="48"/>
-      <c r="E545" s="48"/>
+      <c r="A545" s="53"/>
+      <c r="B545" s="53"/>
+      <c r="C545" s="53"/>
+      <c r="D545" s="53"/>
+      <c r="E545" s="53"/>
     </row>
     <row r="546" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A546" s="48" t="s">
+      <c r="A546" s="53" t="s">
         <v>607</v>
       </c>
-      <c r="B546" s="48" t="s">
+      <c r="B546" s="53" t="s">
         <v>604</v>
       </c>
-      <c r="C546" s="48"/>
-      <c r="D546" s="48"/>
-      <c r="E546" s="48"/>
+      <c r="C546" s="53"/>
+      <c r="D546" s="53"/>
+      <c r="E546" s="53"/>
     </row>
     <row r="547" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A547" s="48" t="s">
+      <c r="A547" s="53" t="s">
         <v>608</v>
       </c>
-      <c r="B547" s="48" t="s">
+      <c r="B547" s="53" t="s">
         <v>600</v>
       </c>
-      <c r="C547" s="48"/>
-      <c r="D547" s="48"/>
-      <c r="E547" s="48"/>
+      <c r="C547" s="53"/>
+      <c r="D547" s="53"/>
+      <c r="E547" s="53"/>
     </row>
     <row r="548" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A548" s="48" t="s">
+      <c r="A548" s="53" t="s">
         <v>609</v>
       </c>
       <c r="B548" s="4">
         <f>INDEX(B540:E544,MATCH(B546,A540:A544),MATCH(B547,B539:E539,0))</f>
         <v>28</v>
       </c>
-      <c r="C548" s="48"/>
-      <c r="D548" s="48"/>
-      <c r="E548" s="48"/>
+      <c r="C548" s="53"/>
+      <c r="D548" s="53"/>
+      <c r="E548" s="53"/>
     </row>
     <row r="550" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B550" s="58" t="str">
+      <c r="B550" s="55" t="str">
         <f ca="1">_xlfn.FORMULATEXT(B548)</f>
         <v>=INDEX(B540:E544,MATCH(B546,A540:A544),MATCH(B547,B539:E539,0))</v>
       </c>
     </row>
     <row r="551" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B551" s="58"/>
+      <c r="B551" s="55"/>
     </row>
     <row r="552" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B552" s="58"/>
+      <c r="B552" s="55"/>
     </row>
     <row r="553" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A553" s="28" t="s">
@@ -8705,19 +8903,19 @@
       </c>
     </row>
     <row r="572" spans="1:5" s="2" customFormat="1" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B572" s="56" t="str">
+      <c r="B572" s="54" t="str">
         <f ca="1">_xlfn.FORMULATEXT(B571)</f>
         <v>=XLOOKUP(B568,A558:A564,XLOOKUP(B569,B557:E557,B558:E564))</v>
       </c>
     </row>
     <row r="573" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B573" s="56"/>
+      <c r="B573" s="54"/>
     </row>
     <row r="574" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B574" s="56"/>
+      <c r="B574" s="54"/>
     </row>
     <row r="575" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B575" s="47"/>
+      <c r="B575" s="52"/>
     </row>
     <row r="576" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A576" s="28" t="s">
@@ -9130,19 +9328,19 @@
       </c>
     </row>
     <row r="616" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A616" s="48">
+      <c r="A616" s="53">
         <v>10021</v>
       </c>
-      <c r="B616" s="48" t="s">
+      <c r="B616" s="53" t="s">
         <v>637</v>
       </c>
-      <c r="C616" s="48" t="s">
+      <c r="C616" s="53" t="s">
         <v>670</v>
       </c>
       <c r="D616" s="16">
         <v>45932</v>
       </c>
-      <c r="E616" s="48">
+      <c r="E616" s="53">
         <v>8500</v>
       </c>
       <c r="F616" s="4" t="str">
@@ -9151,19 +9349,19 @@
       </c>
     </row>
     <row r="617" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A617" s="48">
+      <c r="A617" s="53">
         <v>10022</v>
       </c>
-      <c r="B617" s="48" t="s">
+      <c r="B617" s="53" t="s">
         <v>671</v>
       </c>
-      <c r="C617" s="48" t="s">
+      <c r="C617" s="53" t="s">
         <v>672</v>
       </c>
       <c r="D617" s="16">
         <v>45933</v>
       </c>
-      <c r="E617" s="48">
+      <c r="E617" s="53">
         <v>4200</v>
       </c>
       <c r="F617" s="4" t="str">
@@ -9172,19 +9370,19 @@
       </c>
     </row>
     <row r="618" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A618" s="48">
+      <c r="A618" s="53">
         <v>10023</v>
       </c>
-      <c r="B618" s="48" t="s">
+      <c r="B618" s="53" t="s">
         <v>637</v>
       </c>
-      <c r="C618" s="48" t="s">
+      <c r="C618" s="53" t="s">
         <v>673</v>
       </c>
       <c r="D618" s="16">
         <v>45933</v>
       </c>
-      <c r="E618" s="48">
+      <c r="E618" s="53">
         <v>12500</v>
       </c>
       <c r="F618" s="4" t="str">
@@ -9193,19 +9391,19 @@
       </c>
     </row>
     <row r="619" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A619" s="48">
+      <c r="A619" s="53">
         <v>10024</v>
       </c>
-      <c r="B619" s="48" t="s">
+      <c r="B619" s="53" t="s">
         <v>637</v>
       </c>
-      <c r="C619" s="48" t="s">
+      <c r="C619" s="53" t="s">
         <v>674</v>
       </c>
       <c r="D619" s="16">
         <v>45934</v>
       </c>
-      <c r="E619" s="48">
+      <c r="E619" s="53">
         <v>9999</v>
       </c>
       <c r="F619" s="4" t="str">
@@ -9214,19 +9412,19 @@
       </c>
     </row>
     <row r="620" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A620" s="48">
+      <c r="A620" s="53">
         <v>10025</v>
       </c>
-      <c r="B620" s="48" t="s">
+      <c r="B620" s="53" t="s">
         <v>671</v>
       </c>
-      <c r="C620" s="48" t="s">
+      <c r="C620" s="53" t="s">
         <v>670</v>
       </c>
       <c r="D620" s="16">
         <v>45934</v>
       </c>
-      <c r="E620" s="48">
+      <c r="E620" s="53">
         <v>10000</v>
       </c>
       <c r="F620" s="4" t="str">
@@ -9235,19 +9433,19 @@
       </c>
     </row>
     <row r="621" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A621" s="48">
+      <c r="A621" s="53">
         <v>10026</v>
       </c>
-      <c r="B621" s="48" t="s">
+      <c r="B621" s="53" t="s">
         <v>637</v>
       </c>
-      <c r="C621" s="48" t="s">
+      <c r="C621" s="53" t="s">
         <v>672</v>
       </c>
       <c r="D621" s="16">
         <v>45935</v>
       </c>
-      <c r="E621" s="48">
+      <c r="E621" s="53">
         <v>10001</v>
       </c>
       <c r="F621" s="4" t="str">
@@ -9256,19 +9454,19 @@
       </c>
     </row>
     <row r="622" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A622" s="48">
+      <c r="A622" s="53">
         <v>10027</v>
       </c>
-      <c r="B622" s="48" t="s">
+      <c r="B622" s="53" t="s">
         <v>637</v>
       </c>
-      <c r="C622" s="48" t="s">
+      <c r="C622" s="53" t="s">
         <v>673</v>
       </c>
       <c r="D622" s="16">
         <v>45936</v>
       </c>
-      <c r="E622" s="48">
+      <c r="E622" s="53">
         <v>17500</v>
       </c>
       <c r="F622" s="4" t="str">
@@ -9277,19 +9475,19 @@
       </c>
     </row>
     <row r="623" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A623" s="48">
+      <c r="A623" s="53">
         <v>10028</v>
       </c>
-      <c r="B623" s="48" t="s">
+      <c r="B623" s="53" t="s">
         <v>637</v>
       </c>
-      <c r="C623" s="48" t="s">
+      <c r="C623" s="53" t="s">
         <v>674</v>
       </c>
       <c r="D623" s="16">
         <v>45936</v>
       </c>
-      <c r="E623" s="48">
+      <c r="E623" s="53">
         <v>5400</v>
       </c>
       <c r="F623" s="4" t="str">
@@ -9298,19 +9496,19 @@
       </c>
     </row>
     <row r="624" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A624" s="48">
+      <c r="A624" s="53">
         <v>10029</v>
       </c>
-      <c r="B624" s="48" t="s">
+      <c r="B624" s="53" t="s">
         <v>671</v>
       </c>
-      <c r="C624" s="48" t="s">
+      <c r="C624" s="53" t="s">
         <v>672</v>
       </c>
       <c r="D624" s="16">
         <v>45937</v>
       </c>
-      <c r="E624" s="48">
+      <c r="E624" s="53">
         <v>15000</v>
       </c>
       <c r="F624" s="4" t="str">
@@ -9319,19 +9517,19 @@
       </c>
     </row>
     <row r="625" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A625" s="48">
+      <c r="A625" s="53">
         <v>10030</v>
       </c>
-      <c r="B625" s="48" t="s">
+      <c r="B625" s="53" t="s">
         <v>637</v>
       </c>
-      <c r="C625" s="48" t="s">
+      <c r="C625" s="53" t="s">
         <v>670</v>
       </c>
       <c r="D625" s="16">
         <v>45937</v>
       </c>
-      <c r="E625" s="48">
+      <c r="E625" s="53">
         <v>10250</v>
       </c>
       <c r="F625" s="4" t="str">
@@ -9344,11 +9542,11 @@
       <c r="B627" s="2"/>
       <c r="C627" s="2"/>
       <c r="D627" s="2"/>
-      <c r="E627" s="56" t="str">
+      <c r="E627" s="54" t="str">
         <f ca="1">_xlfn.FORMULATEXT(F616)</f>
         <v>=IF(OR(E616&gt;10000,B616="VIP"),"High","Standard")</v>
       </c>
-      <c r="F627" s="56"/>
+      <c r="F627" s="54"/>
       <c r="G627" s="2"/>
     </row>
     <row r="628" spans="1:7" x14ac:dyDescent="0.3">
@@ -9729,17 +9927,17 @@
       <c r="A659" s="9" t="s">
         <v>700</v>
       </c>
-      <c r="B659" s="49">
+      <c r="B659" s="47">
         <v>45731</v>
       </c>
-      <c r="C659" s="48"/>
-      <c r="D659" s="48"/>
+      <c r="C659" s="53"/>
+      <c r="D659" s="53"/>
     </row>
     <row r="660" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A660" s="48"/>
-      <c r="B660" s="48"/>
-      <c r="C660" s="48"/>
-      <c r="D660" s="48"/>
+      <c r="A660" s="53"/>
+      <c r="B660" s="53"/>
+      <c r="C660" s="53"/>
+      <c r="D660" s="53"/>
     </row>
     <row r="661" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A661" s="9" t="s">
@@ -9751,18 +9949,18 @@
       <c r="C661" s="9" t="s">
         <v>307</v>
       </c>
-      <c r="D661" s="50" t="s">
+      <c r="D661" s="48" t="s">
         <v>703</v>
       </c>
     </row>
     <row r="662" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A662" s="48" t="s">
+      <c r="A662" s="53" t="s">
         <v>704</v>
       </c>
       <c r="B662" s="16">
         <v>45716</v>
       </c>
-      <c r="C662" s="48" t="s">
+      <c r="C662" s="53" t="s">
         <v>705</v>
       </c>
       <c r="D662" s="4" t="str">
@@ -9771,13 +9969,13 @@
       </c>
     </row>
     <row r="663" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A663" s="48" t="s">
+      <c r="A663" s="53" t="s">
         <v>706</v>
       </c>
       <c r="B663" s="16">
         <v>45688</v>
       </c>
-      <c r="C663" s="48" t="s">
+      <c r="C663" s="53" t="s">
         <v>707</v>
       </c>
       <c r="D663" s="4" t="str">
@@ -9786,13 +9984,13 @@
       </c>
     </row>
     <row r="664" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A664" s="48" t="s">
+      <c r="A664" s="53" t="s">
         <v>708</v>
       </c>
       <c r="B664" s="16">
         <v>45726</v>
       </c>
-      <c r="C664" s="48" t="s">
+      <c r="C664" s="53" t="s">
         <v>709</v>
       </c>
       <c r="D664" s="4" t="str">
@@ -9801,13 +9999,13 @@
       </c>
     </row>
     <row r="665" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A665" s="48" t="s">
+      <c r="A665" s="53" t="s">
         <v>710</v>
       </c>
       <c r="B665" s="16">
         <v>45703</v>
       </c>
-      <c r="C665" s="48" t="s">
+      <c r="C665" s="53" t="s">
         <v>711</v>
       </c>
       <c r="D665" s="4" t="str">
@@ -9816,13 +10014,13 @@
       </c>
     </row>
     <row r="666" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A666" s="48" t="s">
+      <c r="A666" s="53" t="s">
         <v>712</v>
       </c>
       <c r="B666" s="16">
         <v>45717</v>
       </c>
-      <c r="C666" s="48" t="s">
+      <c r="C666" s="53" t="s">
         <v>713</v>
       </c>
       <c r="D666" s="4" t="str">
@@ -9831,13 +10029,13 @@
       </c>
     </row>
     <row r="667" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A667" s="48" t="s">
+      <c r="A667" s="53" t="s">
         <v>714</v>
       </c>
       <c r="B667" s="16">
         <v>45698</v>
       </c>
-      <c r="C667" s="48" t="s">
+      <c r="C667" s="53" t="s">
         <v>707</v>
       </c>
       <c r="D667" s="4" t="str">
@@ -9847,11 +10045,11 @@
     </row>
     <row r="668" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="669" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C669" s="54" t="str">
+      <c r="C669" s="57" t="str">
         <f ca="1">_xlfn.FORMULATEXT(D662)</f>
         <v>=IF(NOT(C662="Paid"),"Overdue","")</v>
       </c>
-      <c r="D669" s="54"/>
+      <c r="D669" s="57"/>
     </row>
     <row r="670" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="671" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -9875,161 +10073,161 @@
       <c r="C674" s="6" t="s">
         <v>718</v>
       </c>
-      <c r="D674" s="51" t="s">
+      <c r="D674" s="49" t="s">
         <v>719</v>
       </c>
-      <c r="E674" s="51" t="s">
+      <c r="E674" s="49" t="s">
         <v>720</v>
       </c>
     </row>
     <row r="675" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A675" s="48" t="s">
+      <c r="A675" s="53" t="s">
         <v>524</v>
       </c>
-      <c r="B675" s="48">
+      <c r="B675" s="53">
         <v>96</v>
       </c>
       <c r="C675" s="4" t="str">
         <f>IF(B675&gt;=90,"A",IF(B675&gt;=80,"B",IF(B675&gt;=70,"C",IF(B675&gt;=60,"D","F"))))</f>
         <v>A</v>
       </c>
-      <c r="D675" s="48" t="s">
+      <c r="D675" s="53" t="s">
         <v>721</v>
       </c>
-      <c r="E675" s="48">
+      <c r="E675" s="53">
         <v>90</v>
       </c>
     </row>
     <row r="676" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A676" s="48" t="s">
+      <c r="A676" s="53" t="s">
         <v>530</v>
       </c>
-      <c r="B676" s="48">
+      <c r="B676" s="53">
         <v>88</v>
       </c>
       <c r="C676" s="4" t="str">
         <f t="shared" ref="C676:C682" si="24">IF(B676&gt;=90,"A",IF(B676&gt;=80,"B",IF(B676&gt;=70,"C",IF(B676&gt;=60,"D","F"))))</f>
         <v>B</v>
       </c>
-      <c r="D676" s="48" t="s">
+      <c r="D676" s="53" t="s">
         <v>722</v>
       </c>
-      <c r="E676" s="48">
+      <c r="E676" s="53">
         <v>80</v>
       </c>
     </row>
     <row r="677" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A677" s="48" t="s">
+      <c r="A677" s="53" t="s">
         <v>640</v>
       </c>
-      <c r="B677" s="48">
+      <c r="B677" s="53">
         <v>73</v>
       </c>
       <c r="C677" s="4" t="str">
         <f t="shared" si="24"/>
         <v>C</v>
       </c>
-      <c r="D677" s="48" t="s">
+      <c r="D677" s="53" t="s">
         <v>723</v>
       </c>
-      <c r="E677" s="48">
+      <c r="E677" s="53">
         <v>70</v>
       </c>
     </row>
     <row r="678" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A678" s="48" t="s">
+      <c r="A678" s="53" t="s">
         <v>120</v>
       </c>
-      <c r="B678" s="48">
+      <c r="B678" s="53">
         <v>67</v>
       </c>
       <c r="C678" s="4" t="str">
         <f t="shared" si="24"/>
         <v>D</v>
       </c>
-      <c r="D678" s="48" t="s">
+      <c r="D678" s="53" t="s">
         <v>724</v>
       </c>
-      <c r="E678" s="48">
+      <c r="E678" s="53">
         <v>60</v>
       </c>
     </row>
     <row r="679" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A679" s="48" t="s">
+      <c r="A679" s="53" t="s">
         <v>646</v>
       </c>
-      <c r="B679" s="48">
+      <c r="B679" s="53">
         <v>59</v>
       </c>
       <c r="C679" s="4" t="str">
         <f t="shared" si="24"/>
         <v>F</v>
       </c>
-      <c r="D679" s="48" t="s">
+      <c r="D679" s="53" t="s">
         <v>725</v>
       </c>
-      <c r="E679" s="48">
+      <c r="E679" s="53">
         <v>0</v>
       </c>
     </row>
     <row r="680" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A680" s="48" t="s">
+      <c r="A680" s="53" t="s">
         <v>531</v>
       </c>
-      <c r="B680" s="48">
+      <c r="B680" s="53">
         <v>80</v>
       </c>
       <c r="C680" s="4" t="str">
         <f t="shared" si="24"/>
         <v>B</v>
       </c>
-      <c r="D680" s="48"/>
-      <c r="E680" s="48"/>
+      <c r="D680" s="53"/>
+      <c r="E680" s="53"/>
     </row>
     <row r="681" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A681" s="48" t="s">
+      <c r="A681" s="53" t="s">
         <v>631</v>
       </c>
-      <c r="B681" s="48">
+      <c r="B681" s="53">
         <v>90</v>
       </c>
       <c r="C681" s="4" t="str">
         <f t="shared" si="24"/>
         <v>A</v>
       </c>
-      <c r="D681" s="48"/>
-      <c r="E681" s="48"/>
+      <c r="D681" s="53"/>
+      <c r="E681" s="53"/>
     </row>
     <row r="682" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A682" s="48" t="s">
+      <c r="A682" s="53" t="s">
         <v>726</v>
       </c>
-      <c r="B682" s="48">
+      <c r="B682" s="53">
         <v>70</v>
       </c>
       <c r="C682" s="4" t="str">
         <f t="shared" si="24"/>
         <v>C</v>
       </c>
-      <c r="D682" s="48"/>
-      <c r="E682" s="48"/>
+      <c r="D682" s="53"/>
+      <c r="E682" s="53"/>
     </row>
     <row r="683" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="684" spans="1:5" s="2" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B684" s="54" t="str">
+      <c r="B684" s="57" t="str">
         <f ca="1">_xlfn.FORMULATEXT(C675)</f>
         <v>=IF(B675&gt;=90,"A",IF(B675&gt;=80,"B",IF(B675&gt;=70,"C",IF(B675&gt;=60,"D","F"))))</v>
       </c>
-      <c r="C684" s="54"/>
+      <c r="C684" s="57"/>
     </row>
     <row r="685" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A685" s="52" t="s">
+      <c r="A685" s="50" t="s">
         <v>728</v>
       </c>
-      <c r="B685" s="54" t="s">
+      <c r="B685" s="57" t="s">
         <v>727</v>
       </c>
-      <c r="C685" s="54"/>
+      <c r="C685" s="57"/>
     </row>
     <row r="686" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="687" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -10038,12 +10236,12 @@
       </c>
     </row>
     <row r="688" spans="1:5" s="2" customFormat="1" ht="124.2" x14ac:dyDescent="0.3">
-      <c r="A688" s="48" t="s">
+      <c r="A688" s="53" t="s">
         <v>730</v>
       </c>
     </row>
     <row r="689" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A689" s="48"/>
+      <c r="A689" s="53"/>
     </row>
     <row r="690" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A690" s="6" t="s">
@@ -10055,184 +10253,184 @@
       <c r="C690" s="6" t="s">
         <v>732</v>
       </c>
-      <c r="D690" s="51" t="s">
+      <c r="D690" s="49" t="s">
         <v>667</v>
       </c>
-      <c r="E690" s="51" t="s">
+      <c r="E690" s="49" t="s">
         <v>733</v>
       </c>
-      <c r="F690" s="51" t="s">
+      <c r="F690" s="49" t="s">
         <v>734</v>
       </c>
     </row>
     <row r="691" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A691" s="48" t="s">
+      <c r="A691" s="53" t="s">
         <v>117</v>
       </c>
-      <c r="B691" s="48">
+      <c r="B691" s="53">
         <v>8200</v>
       </c>
       <c r="C691" s="4">
         <f>IF(B691&gt;=$E$691,B691*$F$691,IF(B691&gt;=$E$692,B691*$F$692,B691*$F$693))</f>
         <v>246</v>
       </c>
-      <c r="D691" s="48" t="s">
+      <c r="D691" s="53" t="s">
         <v>735</v>
       </c>
-      <c r="E691" s="48">
+      <c r="E691" s="53">
         <v>25000</v>
       </c>
-      <c r="F691" s="48">
+      <c r="F691" s="53">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="692" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A692" s="48" t="s">
+      <c r="A692" s="53" t="s">
         <v>736</v>
       </c>
-      <c r="B692" s="48">
+      <c r="B692" s="53">
         <v>12000</v>
       </c>
       <c r="C692" s="4">
         <f t="shared" ref="C692:C698" si="25">IF(B692&gt;=$E$691,B692*$F$691,IF(B692&gt;=$E$692,B692*$F$692,B692*$F$693))</f>
         <v>600</v>
       </c>
-      <c r="D692" s="48" t="s">
+      <c r="D692" s="53" t="s">
         <v>737</v>
       </c>
-      <c r="E692" s="48">
+      <c r="E692" s="53">
         <v>10000</v>
       </c>
-      <c r="F692" s="48">
+      <c r="F692" s="53">
         <v>0.05</v>
       </c>
     </row>
     <row r="693" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A693" s="48" t="s">
+      <c r="A693" s="53" t="s">
         <v>738</v>
       </c>
-      <c r="B693" s="48">
+      <c r="B693" s="53">
         <v>25750</v>
       </c>
       <c r="C693" s="4">
         <f t="shared" si="25"/>
         <v>1802.5000000000002</v>
       </c>
-      <c r="D693" s="48" t="s">
+      <c r="D693" s="53" t="s">
         <v>739</v>
       </c>
-      <c r="E693" s="48">
+      <c r="E693" s="53">
         <v>0</v>
       </c>
-      <c r="F693" s="48">
+      <c r="F693" s="53">
         <v>0.03</v>
       </c>
     </row>
     <row r="694" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A694" s="48" t="s">
+      <c r="A694" s="53" t="s">
         <v>740</v>
       </c>
-      <c r="B694" s="48">
+      <c r="B694" s="53">
         <v>18150</v>
       </c>
       <c r="C694" s="4">
         <f t="shared" si="25"/>
         <v>907.5</v>
       </c>
-      <c r="D694" s="48"/>
-      <c r="E694" s="48"/>
-      <c r="F694" s="48"/>
+      <c r="D694" s="53"/>
+      <c r="E694" s="53"/>
+      <c r="F694" s="53"/>
     </row>
     <row r="695" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A695" s="48" t="s">
+      <c r="A695" s="53" t="s">
         <v>741</v>
       </c>
-      <c r="B695" s="48">
+      <c r="B695" s="53">
         <v>9500</v>
       </c>
       <c r="C695" s="4">
         <f t="shared" si="25"/>
         <v>285</v>
       </c>
-      <c r="D695" s="48"/>
-      <c r="E695" s="48"/>
-      <c r="F695" s="48"/>
+      <c r="D695" s="53"/>
+      <c r="E695" s="53"/>
+      <c r="F695" s="53"/>
     </row>
     <row r="696" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A696" s="48" t="s">
+      <c r="A696" s="53" t="s">
         <v>742</v>
       </c>
-      <c r="B696" s="48">
+      <c r="B696" s="53">
         <v>30500</v>
       </c>
       <c r="C696" s="4">
         <f t="shared" si="25"/>
         <v>2135</v>
       </c>
-      <c r="D696" s="48"/>
-      <c r="E696" s="48"/>
-      <c r="F696" s="48"/>
+      <c r="D696" s="53"/>
+      <c r="E696" s="53"/>
+      <c r="F696" s="53"/>
     </row>
     <row r="697" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A697" s="48" t="s">
+      <c r="A697" s="53" t="s">
         <v>743</v>
       </c>
-      <c r="B697" s="48">
+      <c r="B697" s="53">
         <v>24000</v>
       </c>
       <c r="C697" s="4">
         <f t="shared" si="25"/>
         <v>1200</v>
       </c>
-      <c r="D697" s="48"/>
-      <c r="E697" s="48"/>
-      <c r="F697" s="48"/>
+      <c r="D697" s="53"/>
+      <c r="E697" s="53"/>
+      <c r="F697" s="53"/>
     </row>
     <row r="698" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A698" s="48" t="s">
+      <c r="A698" s="53" t="s">
         <v>744</v>
       </c>
-      <c r="B698" s="48">
+      <c r="B698" s="53">
         <v>10000</v>
       </c>
       <c r="C698" s="4">
         <f t="shared" si="25"/>
         <v>500</v>
       </c>
-      <c r="D698" s="48"/>
-      <c r="E698" s="48"/>
-      <c r="F698" s="48"/>
+      <c r="D698" s="53"/>
+      <c r="E698" s="53"/>
+      <c r="F698" s="53"/>
     </row>
     <row r="699" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A699" s="48"/>
-      <c r="B699" s="48"/>
-      <c r="C699" s="48"/>
-      <c r="D699" s="48"/>
-      <c r="E699" s="48"/>
-      <c r="F699" s="48"/>
+      <c r="A699" s="53"/>
+      <c r="B699" s="53"/>
+      <c r="C699" s="53"/>
+      <c r="D699" s="53"/>
+      <c r="E699" s="53"/>
+      <c r="F699" s="53"/>
     </row>
     <row r="700" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A700" s="53" t="s">
+      <c r="A700" s="51" t="s">
         <v>745</v>
       </c>
-      <c r="B700" s="55" t="s">
+      <c r="B700" s="58" t="s">
         <v>746</v>
       </c>
-      <c r="C700" s="55"/>
-      <c r="D700" s="48"/>
-      <c r="E700" s="48"/>
-      <c r="F700" s="48"/>
+      <c r="C700" s="58"/>
+      <c r="D700" s="53"/>
+      <c r="E700" s="53"/>
+      <c r="F700" s="53"/>
     </row>
     <row r="701" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="702" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B702" s="54" t="str">
+      <c r="B702" s="57" t="str">
         <f ca="1">_xlfn.FORMULATEXT(C691)</f>
         <v>=IF(B691&gt;=$E$691,B691*$F$691,IF(B691&gt;=$E$692,B691*$F$692,B691*$F$693))</v>
       </c>
-      <c r="C702" s="54"/>
+      <c r="C702" s="57"/>
     </row>
     <row r="703" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A703" s="48"/>
+      <c r="A703" s="53"/>
     </row>
     <row r="704" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A704" s="28" t="s">
@@ -10240,17 +10438,17 @@
       </c>
     </row>
     <row r="705" spans="1:9" s="2" customFormat="1" ht="151.80000000000001" x14ac:dyDescent="0.3">
-      <c r="A705" s="48" t="s">
+      <c r="A705" s="53" t="s">
         <v>748</v>
       </c>
     </row>
     <row r="706" spans="1:9" s="2" customFormat="1" ht="96.6" x14ac:dyDescent="0.3">
-      <c r="A706" s="48" t="s">
+      <c r="A706" s="53" t="s">
         <v>749</v>
       </c>
     </row>
     <row r="707" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A707" s="48"/>
+      <c r="A707" s="53"/>
     </row>
     <row r="708" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A708" s="6" t="s">
@@ -10262,445 +10460,721 @@
       <c r="C708" s="6" t="s">
         <v>752</v>
       </c>
-      <c r="D708" s="48"/>
-      <c r="E708" s="51" t="s">
+      <c r="D708" s="53"/>
+      <c r="E708" s="49" t="s">
         <v>753</v>
       </c>
-      <c r="F708" s="51" t="s">
+      <c r="F708" s="49" t="s">
         <v>754</v>
       </c>
-      <c r="G708" s="48"/>
-      <c r="H708" s="48"/>
-      <c r="I708" s="48"/>
+      <c r="G708" s="53"/>
+      <c r="H708" s="53"/>
+      <c r="I708" s="53"/>
     </row>
     <row r="709" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A709" s="48" t="s">
+      <c r="A709" s="53" t="s">
         <v>755</v>
       </c>
-      <c r="B709" s="48">
+      <c r="B709" s="53">
         <v>0.8</v>
       </c>
       <c r="C709" s="4" t="str" cm="1">
         <f t="array" ref="C709">_xlfn.IFS(B709&lt;=$E$709,$F$709,B709&lt;=$E$710,$F$710,B709&lt;=$E$711,$F$711,B709&lt;=$E$712,$F$712,B709&gt;$E$712,$F$713)</f>
         <v>Letter</v>
       </c>
-      <c r="D709" s="48"/>
-      <c r="E709" s="48">
+      <c r="D709" s="53"/>
+      <c r="E709" s="53">
         <v>1</v>
       </c>
-      <c r="F709" s="48" t="s">
+      <c r="F709" s="53" t="s">
         <v>756</v>
       </c>
-      <c r="G709" s="48"/>
-      <c r="H709" s="48"/>
-      <c r="I709" s="48"/>
+      <c r="G709" s="53"/>
+      <c r="H709" s="53"/>
+      <c r="I709" s="53"/>
     </row>
     <row r="710" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A710" s="48" t="s">
+      <c r="A710" s="53" t="s">
         <v>757</v>
       </c>
-      <c r="B710" s="48">
+      <c r="B710" s="53">
         <v>3.5</v>
       </c>
       <c r="C710" s="4" t="str" cm="1">
         <f t="array" ref="C710">_xlfn.IFS(B710&lt;=$E$709,$F$709,B710&lt;=$E$710,$F$710,B710&lt;=$E$711,$F$711,B710&lt;=$E$712,$F$712,B710&gt;$E$712,$F$713)</f>
         <v>Standard</v>
       </c>
-      <c r="D710" s="48"/>
-      <c r="E710" s="48">
+      <c r="D710" s="53"/>
+      <c r="E710" s="53">
         <v>5</v>
       </c>
-      <c r="F710" s="48" t="s">
+      <c r="F710" s="53" t="s">
         <v>637</v>
       </c>
-      <c r="G710" s="48"/>
-      <c r="H710" s="48"/>
-      <c r="I710" s="48"/>
+      <c r="G710" s="53"/>
+      <c r="H710" s="53"/>
+      <c r="I710" s="53"/>
     </row>
     <row r="711" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A711" s="48" t="s">
+      <c r="A711" s="53" t="s">
         <v>758</v>
       </c>
-      <c r="B711" s="48">
+      <c r="B711" s="53">
         <v>12</v>
       </c>
       <c r="C711" s="4" t="str" cm="1">
         <f t="array" ref="C711">_xlfn.IFS(B711&lt;=$E$709,$F$709,B711&lt;=$E$710,$F$710,B711&lt;=$E$711,$F$711,B711&lt;=$E$712,$F$712,B711&gt;$E$712,$F$713)</f>
         <v>Ground</v>
       </c>
-      <c r="D711" s="48"/>
-      <c r="E711" s="48">
+      <c r="D711" s="53"/>
+      <c r="E711" s="53">
         <v>20</v>
       </c>
-      <c r="F711" s="48" t="s">
+      <c r="F711" s="53" t="s">
         <v>759</v>
       </c>
-      <c r="G711" s="48"/>
-      <c r="H711" s="48"/>
-      <c r="I711" s="48"/>
+      <c r="G711" s="53"/>
+      <c r="H711" s="53"/>
+      <c r="I711" s="53"/>
     </row>
     <row r="712" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A712" s="48" t="s">
+      <c r="A712" s="53" t="s">
         <v>760</v>
       </c>
-      <c r="B712" s="48">
+      <c r="B712" s="53">
         <v>0.3</v>
       </c>
       <c r="C712" s="4" t="str" cm="1">
         <f t="array" ref="C712">_xlfn.IFS(B712&lt;=$E$709,$F$709,B712&lt;=$E$710,$F$710,B712&lt;=$E$711,$F$711,B712&lt;=$E$712,$F$712,B712&gt;$E$712,$F$713)</f>
         <v>Letter</v>
       </c>
-      <c r="D712" s="48"/>
-      <c r="E712" s="48">
+      <c r="D712" s="53"/>
+      <c r="E712" s="53">
         <v>50</v>
       </c>
-      <c r="F712" s="48" t="s">
+      <c r="F712" s="53" t="s">
         <v>761</v>
       </c>
-      <c r="G712" s="48"/>
-      <c r="H712" s="48"/>
-      <c r="I712" s="48"/>
+      <c r="G712" s="53"/>
+      <c r="H712" s="53"/>
+      <c r="I712" s="53"/>
     </row>
     <row r="713" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A713" s="48" t="s">
+      <c r="A713" s="53" t="s">
         <v>762</v>
       </c>
-      <c r="B713" s="48">
+      <c r="B713" s="53">
         <v>28</v>
       </c>
       <c r="C713" s="4" t="str" cm="1">
         <f t="array" ref="C713">_xlfn.IFS(B713&lt;=$E$709,$F$709,B713&lt;=$E$710,$F$710,B713&lt;=$E$711,$F$711,B713&lt;=$E$712,$F$712,B713&gt;$E$712,$F$713)</f>
         <v>Freight</v>
       </c>
-      <c r="D713" s="48"/>
-      <c r="E713" s="48"/>
-      <c r="F713" s="48" t="s">
+      <c r="D713" s="53"/>
+      <c r="E713" s="53"/>
+      <c r="F713" s="53" t="s">
         <v>763</v>
       </c>
-      <c r="G713" s="48"/>
-      <c r="H713" s="48"/>
-      <c r="I713" s="48"/>
+      <c r="G713" s="53"/>
+      <c r="H713" s="53"/>
+      <c r="I713" s="53"/>
     </row>
     <row r="714" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A714" s="48" t="s">
+      <c r="A714" s="53" t="s">
         <v>764</v>
       </c>
-      <c r="B714" s="48">
+      <c r="B714" s="53">
         <v>7</v>
       </c>
       <c r="C714" s="4" t="str" cm="1">
         <f t="array" ref="C714">_xlfn.IFS(B714&lt;=$E$709,$F$709,B714&lt;=$E$710,$F$710,B714&lt;=$E$711,$F$711,B714&lt;=$E$712,$F$712,B714&gt;$E$712,$F$713)</f>
         <v>Ground</v>
       </c>
-      <c r="D714" s="48"/>
-      <c r="E714" s="48"/>
-      <c r="F714" s="48"/>
-      <c r="G714" s="48"/>
-      <c r="H714" s="48"/>
-      <c r="I714" s="48"/>
+      <c r="D714" s="53"/>
+      <c r="E714" s="53"/>
+      <c r="F714" s="53"/>
+      <c r="G714" s="53"/>
+      <c r="H714" s="53"/>
+      <c r="I714" s="53"/>
     </row>
     <row r="715" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A715" s="48" t="s">
+      <c r="A715" s="53" t="s">
         <v>765</v>
       </c>
-      <c r="B715" s="48">
+      <c r="B715" s="53">
         <v>55</v>
       </c>
       <c r="C715" s="4" t="str" cm="1">
         <f t="array" ref="C715">_xlfn.IFS(B715&lt;=$E$709,$F$709,B715&lt;=$E$710,$F$710,B715&lt;=$E$711,$F$711,B715&lt;=$E$712,$F$712,B715&gt;$E$712,$F$713)</f>
         <v>Heavy freight</v>
       </c>
-      <c r="D715" s="48"/>
-      <c r="E715" s="48"/>
-      <c r="F715" s="48"/>
-      <c r="G715" s="48"/>
-      <c r="H715" s="48"/>
-      <c r="I715" s="48"/>
+      <c r="D715" s="53"/>
+      <c r="E715" s="53"/>
+      <c r="F715" s="53"/>
+      <c r="G715" s="53"/>
+      <c r="H715" s="53"/>
+      <c r="I715" s="53"/>
     </row>
     <row r="716" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A716" s="48" t="s">
+      <c r="A716" s="53" t="s">
         <v>766</v>
       </c>
-      <c r="B716" s="48">
+      <c r="B716" s="53">
         <v>18</v>
       </c>
       <c r="C716" s="4" t="str" cm="1">
         <f t="array" ref="C716">_xlfn.IFS(B716&lt;=$E$709,$F$709,B716&lt;=$E$710,$F$710,B716&lt;=$E$711,$F$711,B716&lt;=$E$712,$F$712,B716&gt;$E$712,$F$713)</f>
         <v>Ground</v>
       </c>
-      <c r="D716" s="48"/>
-      <c r="E716" s="48"/>
-      <c r="F716" s="48"/>
-      <c r="G716" s="48"/>
-      <c r="H716" s="48"/>
-      <c r="I716" s="48"/>
+      <c r="D716" s="53"/>
+      <c r="E716" s="53"/>
+      <c r="F716" s="53"/>
+      <c r="G716" s="53"/>
+      <c r="H716" s="53"/>
+      <c r="I716" s="53"/>
     </row>
     <row r="717" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A717" s="48"/>
-      <c r="B717" s="48"/>
-      <c r="C717" s="48"/>
-      <c r="D717" s="48"/>
-      <c r="E717" s="48"/>
-      <c r="F717" s="48"/>
-      <c r="G717" s="48"/>
-      <c r="H717" s="48"/>
-      <c r="I717" s="48"/>
+      <c r="A717" s="53"/>
+      <c r="B717" s="53"/>
+      <c r="C717" s="53"/>
+      <c r="D717" s="53"/>
+      <c r="E717" s="53"/>
+      <c r="F717" s="53"/>
+      <c r="G717" s="53"/>
+      <c r="H717" s="53"/>
+      <c r="I717" s="53"/>
     </row>
     <row r="718" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A718" s="48"/>
-      <c r="B718" s="59"/>
+      <c r="A718" s="53"/>
+      <c r="B718" s="59" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(C709)</f>
+        <v>=IFS(B709&lt;=$E$709,$F$709,B709&lt;=$E$710,$F$710,B709&lt;=$E$711,$F$711,B709&lt;=$E$712,$F$712,B709&gt;$E$712,$F$713)</v>
+      </c>
       <c r="C718" s="59"/>
-      <c r="D718" s="48"/>
-      <c r="E718" s="48"/>
-      <c r="F718" s="48"/>
-      <c r="G718" s="48"/>
-      <c r="H718" s="48"/>
-      <c r="I718" s="48"/>
+      <c r="D718" s="59"/>
+      <c r="E718" s="53"/>
+      <c r="F718" s="53"/>
+      <c r="G718" s="53"/>
+      <c r="H718" s="53"/>
+      <c r="I718" s="53"/>
     </row>
     <row r="719" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A719" s="48"/>
-      <c r="B719" s="48"/>
-      <c r="C719" s="48"/>
-      <c r="D719" s="48"/>
-      <c r="E719" s="48"/>
-      <c r="F719" s="48"/>
-      <c r="G719" s="48"/>
-      <c r="H719" s="48"/>
-      <c r="I719" s="48"/>
+      <c r="A719" s="53"/>
+      <c r="B719" s="53"/>
+      <c r="C719" s="53"/>
+      <c r="D719" s="53"/>
+      <c r="E719" s="53"/>
+      <c r="F719" s="53"/>
+      <c r="G719" s="53"/>
+      <c r="H719" s="53"/>
+      <c r="I719" s="53"/>
     </row>
     <row r="720" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A720" s="48"/>
-      <c r="B720" s="48"/>
-      <c r="C720" s="48"/>
-      <c r="D720" s="48"/>
-      <c r="E720" s="48"/>
-      <c r="F720" s="48"/>
-      <c r="G720" s="48"/>
-      <c r="H720" s="48"/>
-      <c r="I720" s="48"/>
-    </row>
-    <row r="721" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A721" s="48"/>
-      <c r="B721" s="48"/>
-      <c r="C721" s="48"/>
-      <c r="D721" s="48"/>
-      <c r="E721" s="48"/>
-      <c r="F721" s="48"/>
-      <c r="G721" s="48"/>
-      <c r="H721" s="48"/>
-      <c r="I721" s="48"/>
-    </row>
-    <row r="722" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A722" s="48"/>
-      <c r="B722" s="48"/>
-      <c r="C722" s="48"/>
-      <c r="D722" s="48"/>
-      <c r="E722" s="48"/>
-      <c r="F722" s="48"/>
-      <c r="G722" s="48"/>
-      <c r="H722" s="48"/>
-      <c r="I722" s="48"/>
+      <c r="A720" s="28" t="s">
+        <v>767</v>
+      </c>
+      <c r="B720" s="53"/>
+      <c r="C720" s="53"/>
+      <c r="D720" s="53"/>
+      <c r="E720" s="53"/>
+      <c r="F720" s="53"/>
+      <c r="G720" s="53"/>
+      <c r="H720" s="53"/>
+      <c r="I720" s="53"/>
+    </row>
+    <row r="721" spans="1:9" s="2" customFormat="1" ht="110.4" x14ac:dyDescent="0.3">
+      <c r="A721" s="53" t="s">
+        <v>768</v>
+      </c>
+      <c r="B721" s="53"/>
+      <c r="C721" s="53"/>
+      <c r="D721" s="53"/>
+      <c r="E721" s="53"/>
+      <c r="F721" s="53"/>
+      <c r="G721" s="53"/>
+      <c r="H721" s="53"/>
+      <c r="I721" s="53"/>
+    </row>
+    <row r="722" spans="1:9" s="2" customFormat="1" ht="110.4" x14ac:dyDescent="0.3">
+      <c r="A722" s="53" t="s">
+        <v>769</v>
+      </c>
+      <c r="B722" s="53"/>
+      <c r="C722" s="53"/>
+      <c r="D722" s="53"/>
+      <c r="E722" s="53"/>
+      <c r="F722" s="53"/>
+      <c r="G722" s="53"/>
+      <c r="H722" s="53"/>
+      <c r="I722" s="53"/>
     </row>
     <row r="723" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A723" s="48"/>
-      <c r="B723" s="48"/>
-      <c r="C723" s="48"/>
-      <c r="D723" s="48"/>
-      <c r="E723" s="48"/>
-      <c r="F723" s="48"/>
-      <c r="G723" s="48"/>
-      <c r="H723" s="48"/>
-      <c r="I723" s="48"/>
+      <c r="A723" s="53"/>
+      <c r="B723" s="53"/>
+      <c r="C723" s="53"/>
+      <c r="D723" s="53"/>
+      <c r="E723" s="53"/>
+      <c r="F723" s="53"/>
+      <c r="G723" s="53"/>
+      <c r="H723" s="53"/>
+      <c r="I723" s="53"/>
     </row>
     <row r="724" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A724" s="48"/>
-      <c r="B724" s="48"/>
-      <c r="C724" s="48"/>
-      <c r="D724" s="48"/>
-      <c r="E724" s="48"/>
-      <c r="F724" s="48"/>
-      <c r="G724" s="48"/>
-      <c r="H724" s="48"/>
-      <c r="I724" s="48"/>
+      <c r="A724" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="B724" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="C724" s="6" t="s">
+        <v>770</v>
+      </c>
+      <c r="D724" s="6" t="s">
+        <v>771</v>
+      </c>
+      <c r="E724" s="6" t="s">
+        <v>772</v>
+      </c>
+      <c r="F724" s="53"/>
+      <c r="G724" s="53"/>
+      <c r="H724" s="53"/>
+      <c r="I724" s="53"/>
     </row>
     <row r="725" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A725" s="48"/>
-      <c r="B725" s="48"/>
-      <c r="C725" s="48"/>
-      <c r="D725" s="48"/>
-      <c r="E725" s="48"/>
-      <c r="F725" s="48"/>
-      <c r="G725" s="48"/>
-      <c r="H725" s="48"/>
-      <c r="I725" s="48"/>
+      <c r="A725" s="53" t="s">
+        <v>773</v>
+      </c>
+      <c r="B725" s="53" t="s">
+        <v>774</v>
+      </c>
+      <c r="C725" s="21" t="str" cm="1">
+        <f t="array" ref="C725">_xlfn.SWITCH(B725,$A$736,$B$736,$A$737,$B$737,$A$738,$B$738,$A$739,$B$739,$A$740,$B$740,"Unknown")</f>
+        <v>Marketing</v>
+      </c>
+      <c r="D725" s="21" t="str" cm="1">
+        <f t="array" ref="D725">_xlfn.SWITCH(B725,$A$736,$C$736,$A$737,$C$737,$A$738,$C$738,$A$739,$C$739,$A$740,$C$740,"Unknown")</f>
+        <v>Growth</v>
+      </c>
+      <c r="E725" s="53" t="s">
+        <v>775</v>
+      </c>
+      <c r="F725" s="53"/>
+      <c r="G725" s="53"/>
+      <c r="H725" s="53"/>
+      <c r="I725" s="53"/>
     </row>
     <row r="726" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A726" s="48"/>
-      <c r="B726" s="48"/>
-      <c r="C726" s="48"/>
-      <c r="D726" s="48"/>
-      <c r="E726" s="48"/>
-      <c r="F726" s="48"/>
-      <c r="G726" s="48"/>
-      <c r="H726" s="48"/>
-      <c r="I726" s="48"/>
+      <c r="A726" s="53" t="s">
+        <v>117</v>
+      </c>
+      <c r="B726" s="53" t="s">
+        <v>776</v>
+      </c>
+      <c r="C726" s="21" t="str" cm="1">
+        <f t="array" ref="C726">_xlfn.SWITCH(B726,$A$736,$B$736,$A$737,$B$737,$A$738,$B$738,$A$739,$B$739,$A$740,$B$740,"Unknown")</f>
+        <v>Engineering</v>
+      </c>
+      <c r="D726" s="21" t="str" cm="1">
+        <f t="array" ref="D726">_xlfn.SWITCH(B726,$A$736,$C$736,$A$737,$C$737,$A$738,$C$738,$A$739,$C$739,$A$740,$C$740,"Unknown")</f>
+        <v>Product</v>
+      </c>
+      <c r="E726" s="53" t="s">
+        <v>777</v>
+      </c>
+      <c r="F726" s="53"/>
+      <c r="G726" s="53"/>
+      <c r="H726" s="53"/>
+      <c r="I726" s="53"/>
     </row>
     <row r="727" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A727" s="48"/>
-      <c r="B727" s="48"/>
-      <c r="C727" s="48"/>
-      <c r="D727" s="48"/>
-      <c r="E727" s="48"/>
-      <c r="F727" s="48"/>
-      <c r="G727" s="48"/>
-      <c r="H727" s="48"/>
-      <c r="I727" s="48"/>
+      <c r="A727" s="53" t="s">
+        <v>778</v>
+      </c>
+      <c r="B727" s="53" t="s">
+        <v>779</v>
+      </c>
+      <c r="C727" s="21" t="str" cm="1">
+        <f t="array" ref="C727">_xlfn.SWITCH(B727,$A$736,$B$736,$A$737,$B$737,$A$738,$B$738,$A$739,$B$739,$A$740,$B$740,"Unknown")</f>
+        <v>Finance</v>
+      </c>
+      <c r="D727" s="21" t="str" cm="1">
+        <f t="array" ref="D727">_xlfn.SWITCH(B727,$A$736,$C$736,$A$737,$C$737,$A$738,$C$738,$A$739,$C$739,$A$740,$C$740,"Unknown")</f>
+        <v>Operations</v>
+      </c>
+      <c r="E727" s="53" t="s">
+        <v>780</v>
+      </c>
+      <c r="F727" s="53"/>
+      <c r="G727" s="53"/>
+      <c r="H727" s="53"/>
+      <c r="I727" s="53"/>
     </row>
     <row r="728" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A728" s="48"/>
-      <c r="B728" s="48"/>
-      <c r="C728" s="48"/>
-      <c r="D728" s="48"/>
-      <c r="E728" s="48"/>
-      <c r="F728" s="48"/>
-      <c r="G728" s="48"/>
-      <c r="H728" s="48"/>
-      <c r="I728" s="48"/>
+      <c r="A728" s="53" t="s">
+        <v>693</v>
+      </c>
+      <c r="B728" s="53" t="s">
+        <v>781</v>
+      </c>
+      <c r="C728" s="21" t="str" cm="1">
+        <f t="array" ref="C728">_xlfn.SWITCH(B728,$A$736,$B$736,$A$737,$B$737,$A$738,$B$738,$A$739,$B$739,$A$740,$B$740,"Unknown")</f>
+        <v>Operations</v>
+      </c>
+      <c r="D728" s="21" t="str" cm="1">
+        <f t="array" ref="D728">_xlfn.SWITCH(B728,$A$736,$C$736,$A$737,$C$737,$A$738,$C$738,$A$739,$C$739,$A$740,$C$740,"Unknown")</f>
+        <v>Operations</v>
+      </c>
+      <c r="E728" s="53" t="s">
+        <v>782</v>
+      </c>
+      <c r="F728" s="53"/>
+      <c r="G728" s="53"/>
+      <c r="H728" s="53"/>
+      <c r="I728" s="53"/>
     </row>
     <row r="729" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A729" s="48"/>
-      <c r="B729" s="48"/>
-      <c r="C729" s="48"/>
-      <c r="D729" s="48"/>
-      <c r="E729" s="48"/>
-      <c r="F729" s="48"/>
-      <c r="G729" s="48"/>
-      <c r="H729" s="48"/>
-      <c r="I729" s="48"/>
+      <c r="A729" s="53" t="s">
+        <v>783</v>
+      </c>
+      <c r="B729" s="53" t="s">
+        <v>116</v>
+      </c>
+      <c r="C729" s="21" t="str" cm="1">
+        <f t="array" ref="C729">_xlfn.SWITCH(B729,$A$736,$B$736,$A$737,$B$737,$A$738,$B$738,$A$739,$B$739,$A$740,$B$740,"Unknown")</f>
+        <v>Human Resources</v>
+      </c>
+      <c r="D729" s="21" t="str" cm="1">
+        <f t="array" ref="D729">_xlfn.SWITCH(B729,$A$736,$C$736,$A$737,$C$737,$A$738,$C$738,$A$739,$C$739,$A$740,$C$740,"Unknown")</f>
+        <v>People</v>
+      </c>
+      <c r="E729" s="53" t="s">
+        <v>784</v>
+      </c>
+      <c r="F729" s="53"/>
+      <c r="G729" s="53"/>
+      <c r="H729" s="53"/>
+      <c r="I729" s="53"/>
     </row>
     <row r="730" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A730" s="48"/>
-      <c r="B730" s="48"/>
-      <c r="C730" s="48"/>
-      <c r="D730" s="48"/>
-      <c r="E730" s="48"/>
-      <c r="F730" s="48"/>
-      <c r="G730" s="48"/>
-      <c r="H730" s="48"/>
-      <c r="I730" s="48"/>
+      <c r="A730" s="53" t="s">
+        <v>785</v>
+      </c>
+      <c r="B730" s="53" t="s">
+        <v>776</v>
+      </c>
+      <c r="C730" s="21" t="str" cm="1">
+        <f t="array" ref="C730">_xlfn.SWITCH(B730,$A$736,$B$736,$A$737,$B$737,$A$738,$B$738,$A$739,$B$739,$A$740,$B$740,"Unknown")</f>
+        <v>Engineering</v>
+      </c>
+      <c r="D730" s="21" t="str" cm="1">
+        <f t="array" ref="D730">_xlfn.SWITCH(B730,$A$736,$C$736,$A$737,$C$737,$A$738,$C$738,$A$739,$C$739,$A$740,$C$740,"Unknown")</f>
+        <v>Product</v>
+      </c>
+      <c r="E730" s="53" t="s">
+        <v>786</v>
+      </c>
+      <c r="F730" s="53"/>
+      <c r="G730" s="53"/>
+      <c r="H730" s="53"/>
+      <c r="I730" s="53"/>
     </row>
     <row r="731" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A731" s="48"/>
-      <c r="B731" s="48"/>
-      <c r="C731" s="48"/>
-      <c r="D731" s="48"/>
-      <c r="E731" s="48"/>
-      <c r="F731" s="48"/>
-      <c r="G731" s="48"/>
-      <c r="H731" s="48"/>
-      <c r="I731" s="48"/>
+      <c r="A731" s="53" t="s">
+        <v>787</v>
+      </c>
+      <c r="B731" s="53" t="s">
+        <v>774</v>
+      </c>
+      <c r="C731" s="21" t="str" cm="1">
+        <f t="array" ref="C731">_xlfn.SWITCH(B731,$A$736,$B$736,$A$737,$B$737,$A$738,$B$738,$A$739,$B$739,$A$740,$B$740,"Unknown")</f>
+        <v>Marketing</v>
+      </c>
+      <c r="D731" s="21" t="str" cm="1">
+        <f t="array" ref="D731">_xlfn.SWITCH(B731,$A$736,$C$736,$A$737,$C$737,$A$738,$C$738,$A$739,$C$739,$A$740,$C$740,"Unknown")</f>
+        <v>Growth</v>
+      </c>
+      <c r="E731" s="53" t="s">
+        <v>788</v>
+      </c>
+      <c r="F731" s="53"/>
+      <c r="G731" s="53"/>
+      <c r="H731" s="53"/>
+      <c r="I731" s="53"/>
     </row>
     <row r="732" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A732" s="48"/>
-      <c r="B732" s="48"/>
-      <c r="C732" s="48"/>
-      <c r="D732" s="48"/>
-      <c r="E732" s="48"/>
-      <c r="F732" s="48"/>
-      <c r="G732" s="48"/>
-      <c r="H732" s="48"/>
-      <c r="I732" s="48"/>
+      <c r="A732" s="53" t="s">
+        <v>789</v>
+      </c>
+      <c r="B732" s="53" t="s">
+        <v>781</v>
+      </c>
+      <c r="C732" s="21" t="str" cm="1">
+        <f t="array" ref="C732">_xlfn.SWITCH(B732,$A$736,$B$736,$A$737,$B$737,$A$738,$B$738,$A$739,$B$739,$A$740,$B$740,"Unknown")</f>
+        <v>Operations</v>
+      </c>
+      <c r="D732" s="21" t="str" cm="1">
+        <f t="array" ref="D732">_xlfn.SWITCH(B732,$A$736,$C$736,$A$737,$C$737,$A$738,$C$738,$A$739,$C$739,$A$740,$C$740,"Unknown")</f>
+        <v>Operations</v>
+      </c>
+      <c r="E732" s="53" t="s">
+        <v>790</v>
+      </c>
+      <c r="F732" s="53"/>
+      <c r="G732" s="53"/>
+      <c r="H732" s="53"/>
+      <c r="I732" s="53"/>
     </row>
     <row r="733" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A733" s="48"/>
-      <c r="B733" s="48"/>
-      <c r="C733" s="48"/>
-      <c r="D733" s="48"/>
-      <c r="E733" s="48"/>
-      <c r="F733" s="48"/>
-      <c r="G733" s="48"/>
-      <c r="H733" s="48"/>
-      <c r="I733" s="48"/>
+      <c r="A733" s="53"/>
+      <c r="B733" s="53"/>
+      <c r="C733" s="53"/>
+      <c r="D733" s="53"/>
+      <c r="E733" s="53"/>
+      <c r="F733" s="53"/>
+      <c r="G733" s="53"/>
+      <c r="H733" s="53"/>
+      <c r="I733" s="53"/>
     </row>
     <row r="734" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A734" s="48"/>
-      <c r="B734" s="48"/>
-      <c r="C734" s="48"/>
-      <c r="D734" s="48"/>
-      <c r="E734" s="48"/>
-      <c r="F734" s="48"/>
-      <c r="G734" s="48"/>
-      <c r="H734" s="48"/>
-      <c r="I734" s="48"/>
+      <c r="A734" s="53"/>
+      <c r="B734" s="53"/>
+      <c r="C734" s="53"/>
+      <c r="D734" s="53"/>
+      <c r="E734" s="53"/>
+      <c r="F734" s="53"/>
+      <c r="G734" s="53"/>
+      <c r="H734" s="53"/>
+      <c r="I734" s="53"/>
     </row>
     <row r="735" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A735" s="48"/>
-      <c r="B735" s="48"/>
-      <c r="C735" s="48"/>
-      <c r="D735" s="48"/>
-      <c r="E735" s="48"/>
-      <c r="F735" s="48"/>
-      <c r="G735" s="48"/>
-      <c r="H735" s="48"/>
-      <c r="I735" s="48"/>
+      <c r="A735" s="60" t="s">
+        <v>791</v>
+      </c>
+      <c r="B735" s="60" t="s">
+        <v>770</v>
+      </c>
+      <c r="C735" s="60" t="s">
+        <v>771</v>
+      </c>
+      <c r="D735" s="53"/>
+      <c r="E735" s="53"/>
+      <c r="F735" s="53"/>
+      <c r="G735" s="53"/>
+      <c r="H735" s="53"/>
+      <c r="I735" s="53"/>
     </row>
     <row r="736" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A736" s="48"/>
-      <c r="B736" s="48"/>
-      <c r="C736" s="48"/>
-      <c r="D736" s="48"/>
-      <c r="E736" s="48"/>
-      <c r="F736" s="48"/>
-      <c r="G736" s="48"/>
-      <c r="H736" s="48"/>
-      <c r="I736" s="48"/>
+      <c r="A736" s="53" t="s">
+        <v>774</v>
+      </c>
+      <c r="B736" s="53" t="s">
+        <v>119</v>
+      </c>
+      <c r="C736" s="53" t="s">
+        <v>792</v>
+      </c>
+      <c r="D736" s="53"/>
+      <c r="E736" s="53"/>
+      <c r="F736" s="53"/>
+      <c r="G736" s="53"/>
+      <c r="H736" s="53"/>
+      <c r="I736" s="53"/>
     </row>
     <row r="737" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A737" s="48"/>
-      <c r="B737" s="48"/>
-      <c r="C737" s="48"/>
-      <c r="D737" s="48"/>
-      <c r="E737" s="48"/>
-      <c r="F737" s="48"/>
-      <c r="G737" s="48"/>
-      <c r="H737" s="48"/>
-      <c r="I737" s="48"/>
+      <c r="A737" s="53" t="s">
+        <v>776</v>
+      </c>
+      <c r="B737" s="53" t="s">
+        <v>793</v>
+      </c>
+      <c r="C737" s="53" t="s">
+        <v>46</v>
+      </c>
+      <c r="D737" s="53"/>
+      <c r="E737" s="53"/>
+      <c r="F737" s="53"/>
+      <c r="G737" s="53"/>
+      <c r="H737" s="53"/>
+      <c r="I737" s="53"/>
     </row>
     <row r="738" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A738" s="48"/>
-      <c r="B738" s="48"/>
-      <c r="C738" s="48"/>
-      <c r="D738" s="48"/>
-      <c r="E738" s="48"/>
-      <c r="F738" s="48"/>
-      <c r="G738" s="48"/>
-      <c r="H738" s="48"/>
-      <c r="I738" s="48"/>
+      <c r="A738" s="53" t="s">
+        <v>779</v>
+      </c>
+      <c r="B738" s="53" t="s">
+        <v>92</v>
+      </c>
+      <c r="C738" s="53" t="s">
+        <v>90</v>
+      </c>
+      <c r="D738" s="53"/>
+      <c r="E738" s="53"/>
+      <c r="F738" s="53"/>
+      <c r="G738" s="53"/>
+      <c r="H738" s="53"/>
+      <c r="I738" s="53"/>
     </row>
     <row r="739" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A739" s="48"/>
-      <c r="B739" s="48"/>
-      <c r="C739" s="48"/>
-      <c r="D739" s="48"/>
-      <c r="E739" s="48"/>
-      <c r="F739" s="48"/>
-      <c r="G739" s="48"/>
-      <c r="H739" s="48"/>
-      <c r="I739" s="48"/>
+      <c r="A739" s="53" t="s">
+        <v>781</v>
+      </c>
+      <c r="B739" s="53" t="s">
+        <v>90</v>
+      </c>
+      <c r="C739" s="53" t="s">
+        <v>90</v>
+      </c>
+      <c r="D739" s="53"/>
+      <c r="E739" s="53"/>
+      <c r="F739" s="53"/>
+      <c r="G739" s="53"/>
+      <c r="H739" s="53"/>
+      <c r="I739" s="53"/>
     </row>
     <row r="740" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A740" s="48"/>
-      <c r="B740" s="48"/>
-      <c r="C740" s="48"/>
-      <c r="D740" s="48"/>
-      <c r="E740" s="48"/>
-      <c r="F740" s="48"/>
-      <c r="G740" s="48"/>
-      <c r="H740" s="48"/>
-      <c r="I740" s="48"/>
+      <c r="A740" s="53" t="s">
+        <v>116</v>
+      </c>
+      <c r="B740" s="53" t="s">
+        <v>794</v>
+      </c>
+      <c r="C740" s="53" t="s">
+        <v>94</v>
+      </c>
+      <c r="D740" s="53"/>
+      <c r="E740" s="53"/>
+      <c r="F740" s="53"/>
+      <c r="G740" s="53"/>
+      <c r="H740" s="53"/>
+      <c r="I740" s="53"/>
+    </row>
+    <row r="742" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B742" s="56" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(C725)</f>
+        <v>=SWITCH(B725,$A$736,$B$736,$A$737,$B$737,$A$738,$B$738,$A$739,$B$739,$A$740,$B$740,"Unknown")</v>
+      </c>
+      <c r="C742" s="56"/>
+      <c r="D742" s="56"/>
+    </row>
+    <row r="743" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B743" s="56" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(D725)</f>
+        <v>=SWITCH(B725,$A$736,$C$736,$A$737,$C$737,$A$738,$C$738,$A$739,$C$739,$A$740,$C$740,"Unknown")</v>
+      </c>
+      <c r="C743" s="56"/>
+      <c r="D743" s="56"/>
+    </row>
+    <row r="744" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A744" s="53"/>
+      <c r="B744" s="24"/>
+      <c r="C744" s="24"/>
+      <c r="D744" s="24"/>
+    </row>
+    <row r="745" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A745" s="28" t="s">
+        <v>795</v>
+      </c>
+      <c r="B745" s="24"/>
+      <c r="C745" s="24"/>
+      <c r="D745" s="24"/>
+    </row>
+    <row r="746" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A746" s="53" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="747" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A747" s="53" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="748" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A748" s="53" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="749" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A749" s="53" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="750" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A750" s="53"/>
+    </row>
+    <row r="751" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A751" s="53" t="s">
+        <v>797</v>
+      </c>
+      <c r="B751" s="53" t="s">
+        <v>798</v>
+      </c>
+      <c r="C751" s="53" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="752" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A752" s="53">
+        <v>8</v>
+      </c>
+      <c r="B752" s="53">
+        <v>10</v>
+      </c>
+      <c r="C752" s="21">
+        <f>IFERROR(B752/A752,0)</f>
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="753" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A753" s="53">
+        <v>2</v>
+      </c>
+      <c r="B753" s="53">
+        <v>20</v>
+      </c>
+      <c r="C753" s="21">
+        <f t="shared" ref="C753:C754" si="26">IFERROR(B753/A753,0)</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="754" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A754" s="53">
+        <v>0</v>
+      </c>
+      <c r="B754" s="53">
+        <v>5</v>
+      </c>
+      <c r="C754" s="21">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="755" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A755" s="53"/>
+    </row>
+    <row r="756" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A756" s="53"/>
+      <c r="B756" s="56" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(C752)</f>
+        <v>=IFERROR(B752/A752,0)</v>
+      </c>
+      <c r="C756" s="56"/>
+    </row>
+    <row r="759" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A759" s="1" t="s">
+        <v>803</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="18">
+    <mergeCell ref="B756:C756"/>
+    <mergeCell ref="B718:D718"/>
+    <mergeCell ref="B742:D742"/>
+    <mergeCell ref="B743:D743"/>
+    <mergeCell ref="C669:D669"/>
+    <mergeCell ref="B684:C684"/>
+    <mergeCell ref="B685:C685"/>
+    <mergeCell ref="B700:C700"/>
+    <mergeCell ref="B702:C702"/>
     <mergeCell ref="E627:F627"/>
     <mergeCell ref="B572:B574"/>
     <mergeCell ref="B550:B552"/>
@@ -10710,11 +11184,6 @@
     <mergeCell ref="C359:C360"/>
     <mergeCell ref="C476:E476"/>
     <mergeCell ref="C477:E477"/>
-    <mergeCell ref="C669:D669"/>
-    <mergeCell ref="B684:C684"/>
-    <mergeCell ref="B685:C685"/>
-    <mergeCell ref="B700:C700"/>
-    <mergeCell ref="B702:C702"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Daily Excel/Online Practice Excel.xlsx
+++ b/Daily Excel/Online Practice Excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d58d4d655bee1e81/Desktop/Github/Daily_practice/Daily Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="327" documentId="11_F25DC773A252ABDACC1048BD89DC52D45ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2CF009D3-617A-41D3-BBDF-7DBB648868E2}"/>
+  <xr:revisionPtr revIDLastSave="345" documentId="11_F25DC773A252ABDACC1048BD89DC52D45ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3A0FE151-D040-4ACB-BAA3-76F2DDD045B4}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1082" uniqueCount="836">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1130" uniqueCount="869">
   <si>
     <t>Double-click on cell A1 in the spreadsheet editor. Replace the placeholder text with:</t>
   </si>
@@ -2753,6 +2753,101 @@
     <t>Fill in the eight calculated fields in the spreadsheet. The Notes column shows mathematical notation for the statistical formulas. For the Z-score, use the pooled standard error from the Results section, where pooled SE is based on pooled conversion rate across both variants. Then return a final Significant? decision based on the 95% two-sided threshold.</t>
   </si>
   <si>
+    <t>AGGREGATE for average ignoring errors</t>
+  </si>
+  <si>
+    <t>When your data has errors scattered through a column, functions like AVERAGE fail on the whole range. AGGREGATE can skip those errors and give you the correct result.</t>
+  </si>
+  <si>
+    <t>How AGGREGATE works</t>
+  </si>
+  <si>
+    <t>AGGREGATE takes three arguments:</t>
+  </si>
+  <si>
+    <t>For example, to sum while ignoring errors:</t>
+  </si>
+  <si>
+    <t>Syntax = AGGREGATE(function_num, options, range)</t>
+  </si>
+  <si>
+    <t>Example =AGGREGATE(9, 6, A1:A10)</t>
+  </si>
+  <si>
+    <t>In this exercise, you have monthly sales data with a Revenue per unit column that uses formulas referencing the units sold column. Two months show #DIV/0! because no units were sold, and one month shows #VALUE! because the data entry is still incomplete. A normal AVERAGE cannot handle these errors.</t>
+  </si>
+  <si>
+    <t>function_num: a number that tells AGGREGATE which calculation to run (1 for AVERAGE, 2 for COUNT, 9 for SUM, and more)</t>
+  </si>
+  <si>
+    <t>options: a number that tells AGGREGATE what to ignore (6 means ignore error values)</t>
+  </si>
+  <si>
+    <t>range: the cells to evaluate</t>
+  </si>
+  <si>
+    <t>Units sold</t>
+  </si>
+  <si>
+    <t>Revenue per unit</t>
+  </si>
+  <si>
+    <t>pending</t>
+  </si>
+  <si>
+    <t>September</t>
+  </si>
+  <si>
+    <t>October</t>
+  </si>
+  <si>
+    <t>November</t>
+  </si>
+  <si>
+    <t>AVERAGE revenue</t>
+  </si>
+  <si>
+    <t>AGGREGATE revenue</t>
+  </si>
+  <si>
+    <t>Count of valid revenue entries</t>
+  </si>
+  <si>
+    <t>Handle #N/A in calculations</t>
+  </si>
+  <si>
+    <t>When you pull data from lookups or external sources, some cells may contain #N/A errors. A regular SUM on these cells will return #N/A, which breaks your reports.</t>
+  </si>
+  <si>
+    <t>There are several ways to sum values while ignoring errors:</t>
+  </si>
+  <si>
+    <t>The AGGREGATE function can perform various calculations (SUM, AVERAGE, COUNT, etc.) while optionally ignoring errors, hidden rows, or nested functions.</t>
+  </si>
+  <si>
+    <t>The syntax is:
+=AGGREGATE(function_num, options, range)
+Where function_num specifies the calculation (9 = SUM) and options controls what to ignore (6 = ignore error values).
+Your task:
+You have quarterly sales data for several products. Some quarters have #N/A errors where data was unavailable.
+In cell C8, calculate the total Q2 Sales (column C) using a method that ignores the #N/A errors and returns the correct sum.</t>
+  </si>
+  <si>
+    <t>Q1 sales</t>
+  </si>
+  <si>
+    <t>Q2 sales</t>
+  </si>
+  <si>
+    <t>Q3 sales</t>
+  </si>
+  <si>
+    <t>Q4 sales</t>
+  </si>
+  <si>
+    <t>Total Q2 sales:</t>
+  </si>
+  <si>
     <r>
       <t>AND returns TRUE only when </t>
     </r>
@@ -2761,9 +2856,9 @@
         <i/>
         <sz val="12"/>
         <color rgb="FF000000"/>
-        <rFont val="Calibri Light"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
-        <scheme val="major"/>
+        <scheme val="minor"/>
       </rPr>
       <t>all</t>
     </r>
@@ -2771,9 +2866,9 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF000000"/>
-        <rFont val="Calibri Light"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
-        <scheme val="major"/>
+        <scheme val="minor"/>
       </rPr>
       <t> tests are TRUE. You’ll typically use it inside IF to create a single decision rule.</t>
     </r>
@@ -2786,9 +2881,9 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF000000"/>
-        <rFont val="Calibri Light"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
-        <scheme val="major"/>
+        <scheme val="minor"/>
       </rPr>
       <t>E (Decision), return "Approve" only when both of these are true:</t>
     </r>
@@ -2801,9 +2896,9 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF000000"/>
-        <rFont val="Calibri Light"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
-        <scheme val="major"/>
+        <scheme val="minor"/>
       </rPr>
       <t>greater than 700</t>
     </r>
@@ -2816,9 +2911,9 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF000000"/>
-        <rFont val="Calibri Light"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
-        <scheme val="major"/>
+        <scheme val="minor"/>
       </rPr>
       <t>greater than 50,000</t>
     </r>
@@ -2831,9 +2926,9 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF000000"/>
-        <rFont val="Calibri Light"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
-        <scheme val="major"/>
+        <scheme val="minor"/>
       </rPr>
       <t>"Decline".</t>
     </r>
@@ -2846,9 +2941,9 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF000000"/>
-        <rFont val="Calibri Light"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
-        <scheme val="major"/>
+        <scheme val="minor"/>
       </rPr>
       <t>E2, then fill it down through E11.</t>
     </r>
@@ -2862,9 +2957,9 @@
         <i/>
         <sz val="12"/>
         <color theme="1"/>
-        <rFont val="Calibri Light"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
-        <scheme val="major"/>
+        <scheme val="minor"/>
       </rPr>
       <t>#DIV/0!</t>
     </r>
@@ -2872,9 +2967,9 @@
       <rPr>
         <sz val="12"/>
         <color theme="1"/>
-        <rFont val="Calibri Light"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
-        <scheme val="major"/>
+        <scheme val="minor"/>
       </rPr>
       <t> error that you get when you divide a number by 0. Since that's not allowed in mathematics, the error is reasonable, yet we still would like to return something other than an error. That's where IFERROR comes in.</t>
     </r>
@@ -2888,9 +2983,9 @@
         <i/>
         <sz val="12"/>
         <color theme="1"/>
-        <rFont val="Calibri Light"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
-        <scheme val="major"/>
+        <scheme val="minor"/>
       </rPr>
       <t>Drinks per guest</t>
     </r>
@@ -2898,9 +2993,9 @@
       <rPr>
         <sz val="12"/>
         <color theme="1"/>
-        <rFont val="Calibri Light"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
-        <scheme val="major"/>
+        <scheme val="minor"/>
       </rPr>
       <t> in cells C2:C4. For each row, divide the number of drinks by the number of guests, and wrap that division in IFERROR so the formula returns the division result when there is no error and 0 otherwise.</t>
     </r>
@@ -2914,9 +3009,9 @@
         <i/>
         <sz val="12"/>
         <color theme="1"/>
-        <rFont val="Calibri Light"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
-        <scheme val="major"/>
+        <scheme val="minor"/>
       </rPr>
       <t>#DIV/0!</t>
     </r>
@@ -2924,12 +3019,21 @@
       <rPr>
         <sz val="12"/>
         <color theme="1"/>
-        <rFont val="Calibri Light"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
-        <scheme val="major"/>
+        <scheme val="minor"/>
       </rPr>
       <t> error.</t>
     </r>
+  </si>
+  <si>
+    <t>1. AGGREGATE function - Has a built-in option to ignore error values</t>
+  </si>
+  <si>
+    <t>2. SUMIF with error checking - Filter out errors before summing</t>
+  </si>
+  <si>
+    <t>3. IFERROR wrapper - Replace each error with 0 before summing</t>
   </si>
 </sst>
 </file>
@@ -2938,7 +3042,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="&quot;₹&quot;\ #,##0.00"/>
-    <numFmt numFmtId="177" formatCode="0.0000000000E+00"/>
+    <numFmt numFmtId="165" formatCode="0.0000000000E+00"/>
   </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
@@ -2951,64 +3055,64 @@
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri Light"/>
+      <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="major"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF1E1E1E"/>
-      <name val="Calibri Light"/>
+      <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="major"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF555555"/>
-      <name val="Calibri Light"/>
+      <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="major"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <i/>
       <sz val="12"/>
       <color rgb="FF000000"/>
-      <name val="Calibri Light"/>
+      <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="major"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
-      <name val="Calibri Light"/>
+      <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="major"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <i/>
       <sz val="12"/>
       <color rgb="FF444444"/>
-      <name val="Calibri Light"/>
+      <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="major"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <i/>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri Light"/>
+      <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="major"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF6B7280"/>
-      <name val="Calibri Light"/>
+      <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="major"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="26">
+  <fills count="28">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3159,6 +3263,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7F2E6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF8EF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -3172,7 +3288,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -3358,10 +3474,16 @@
     <xf numFmtId="0" fontId="1" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3644,7 +3766,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W921"/>
+  <dimension ref="A1:W917"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="149.88671875" style="3" bestFit="1" customWidth="1"/>
@@ -6623,7 +6745,7 @@
         <v>16947</v>
       </c>
     </row>
-    <row r="317" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A317" s="8" t="s">
         <v>338</v>
       </c>
@@ -8131,7 +8253,7 @@
       <c r="G480" s="8"/>
       <c r="H480" s="8"/>
     </row>
-    <row r="481" spans="1:8" ht="140.4" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:8" ht="156" x14ac:dyDescent="0.3">
       <c r="A481" s="8" t="s">
         <v>546</v>
       </c>
@@ -9065,7 +9187,7 @@
       </c>
       <c r="B576" s="46"/>
     </row>
-    <row r="577" spans="1:7" s="5" customFormat="1" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:7" s="5" customFormat="1" ht="78" x14ac:dyDescent="0.3">
       <c r="A577" s="5" t="s">
         <v>625</v>
       </c>
@@ -9105,7 +9227,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="584" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:7" s="5" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
       <c r="C584" s="5" t="str" cm="1">
         <f t="array" ref="C584:E584">_xlfn.XLOOKUP(B582,A588:A594,B588:D594)</f>
         <v>Keira Lewis</v>
@@ -9724,7 +9846,7 @@
     </row>
     <row r="631" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A631" s="5" t="s">
-        <v>827</v>
+        <v>857</v>
       </c>
       <c r="B631" s="5"/>
       <c r="C631" s="5"/>
@@ -9764,7 +9886,7 @@
     </row>
     <row r="635" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A635" s="5" t="s">
-        <v>828</v>
+        <v>858</v>
       </c>
       <c r="B635" s="5"/>
       <c r="C635" s="5"/>
@@ -9775,7 +9897,7 @@
     </row>
     <row r="636" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A636" s="5" t="s">
-        <v>829</v>
+        <v>859</v>
       </c>
       <c r="B636" s="5"/>
       <c r="C636" s="5"/>
@@ -9786,7 +9908,7 @@
     </row>
     <row r="637" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A637" s="5" t="s">
-        <v>830</v>
+        <v>860</v>
       </c>
       <c r="B637" s="5"/>
       <c r="C637" s="5"/>
@@ -9797,7 +9919,7 @@
     </row>
     <row r="638" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A638" s="5" t="s">
-        <v>831</v>
+        <v>861</v>
       </c>
       <c r="B638" s="5"/>
       <c r="C638" s="5"/>
@@ -9808,7 +9930,7 @@
     </row>
     <row r="639" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A639" s="5" t="s">
-        <v>832</v>
+        <v>862</v>
       </c>
       <c r="B639" s="5"/>
       <c r="C639" s="5"/>
@@ -10824,7 +10946,7 @@
       <c r="H720" s="8"/>
       <c r="I720" s="8"/>
     </row>
-    <row r="721" spans="1:9" s="5" customFormat="1" ht="124.8" x14ac:dyDescent="0.3">
+    <row r="721" spans="1:9" s="5" customFormat="1" ht="140.4" x14ac:dyDescent="0.3">
       <c r="A721" s="8" t="s">
         <v>762</v>
       </c>
@@ -11227,17 +11349,17 @@
     </row>
     <row r="747" spans="1:9" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A747" s="8" t="s">
-        <v>833</v>
+        <v>863</v>
       </c>
     </row>
     <row r="748" spans="1:9" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A748" s="8" t="s">
-        <v>834</v>
+        <v>864</v>
       </c>
     </row>
     <row r="749" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A749" s="8" t="s">
-        <v>835</v>
+        <v>865</v>
       </c>
     </row>
     <row r="750" spans="1:9" x14ac:dyDescent="0.3">
@@ -11369,7 +11491,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="768" spans="1:3" ht="171.6" x14ac:dyDescent="0.3">
+    <row r="768" spans="1:3" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A768" s="8" t="s">
         <v>801</v>
       </c>
@@ -11622,159 +11744,429 @@
       <c r="A796" s="8"/>
     </row>
     <row r="797" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A797" s="8"/>
-    </row>
-    <row r="798" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A798" s="8"/>
+      <c r="A797" s="23" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="798" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A798" s="8" t="s">
+        <v>828</v>
+      </c>
     </row>
     <row r="799" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A799" s="8"/>
     </row>
-    <row r="800" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A800" s="8"/>
-    </row>
-    <row r="801" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A801" s="8"/>
-    </row>
-    <row r="802" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A802" s="8"/>
-    </row>
-    <row r="803" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A803" s="8"/>
-    </row>
-    <row r="804" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A804" s="8"/>
-    </row>
-    <row r="805" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A805" s="8"/>
-    </row>
-    <row r="806" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A806" s="8"/>
-    </row>
-    <row r="807" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A807" s="8"/>
-    </row>
-    <row r="808" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A808" s="8"/>
-    </row>
-    <row r="809" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="800" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A800" s="8" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="801" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A801" s="8" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="802" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A802" s="8" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="803" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A803" s="8" t="s">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="804" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A804" s="8" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="805" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A805" s="8" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="806" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A806" s="8" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="807" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A807" s="8" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="808" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A808" s="8" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="809" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A809" s="8"/>
     </row>
-    <row r="810" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A810" s="8"/>
-    </row>
-    <row r="811" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A811" s="8"/>
-    </row>
-    <row r="812" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A812" s="8"/>
-    </row>
-    <row r="813" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A813" s="8"/>
-    </row>
-    <row r="814" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A814" s="8"/>
-    </row>
-    <row r="815" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A815" s="8"/>
-    </row>
-    <row r="816" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A816" s="8"/>
-    </row>
-    <row r="817" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A817" s="8"/>
-    </row>
-    <row r="818" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A818" s="8"/>
-    </row>
-    <row r="819" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A819" s="8"/>
-    </row>
-    <row r="820" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A820" s="8"/>
-    </row>
-    <row r="821" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A821" s="8"/>
-    </row>
-    <row r="822" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="810" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A810" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="B810" s="11" t="s">
+        <v>838</v>
+      </c>
+      <c r="C810" s="11" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="811" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A811" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="B811" s="8">
+        <v>50</v>
+      </c>
+      <c r="C811" s="8">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="812" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A812" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="B812" s="8">
+        <v>60</v>
+      </c>
+      <c r="C812" s="8">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="813" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A813" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="B813" s="8">
+        <v>0</v>
+      </c>
+      <c r="C813" s="8" t="e">
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="814" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A814" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="B814" s="8">
+        <v>40</v>
+      </c>
+      <c r="C814" s="8">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="815" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A815" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="B815" s="8">
+        <v>80</v>
+      </c>
+      <c r="C815" s="8">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="816" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A816" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="B816" s="8">
+        <v>0</v>
+      </c>
+      <c r="C816" s="8" t="e">
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="817" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A817" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="B817" s="8" t="s">
+        <v>840</v>
+      </c>
+      <c r="C817" s="8" t="e">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="818" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A818" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B818" s="8">
+        <v>30</v>
+      </c>
+      <c r="C818" s="8">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="819" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A819" s="8" t="s">
+        <v>841</v>
+      </c>
+      <c r="B819" s="8">
+        <v>100</v>
+      </c>
+      <c r="C819" s="8">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="820" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A820" s="8" t="s">
+        <v>842</v>
+      </c>
+      <c r="B820" s="8">
+        <v>75</v>
+      </c>
+      <c r="C820" s="8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="821" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A821" s="8" t="s">
+        <v>843</v>
+      </c>
+      <c r="B821" s="8">
+        <v>25</v>
+      </c>
+      <c r="C821" s="8">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="822" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A822" s="8"/>
-    </row>
-    <row r="823" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A823" s="8"/>
-    </row>
-    <row r="824" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A824" s="8"/>
-    </row>
-    <row r="825" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A825" s="8"/>
-    </row>
-    <row r="826" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B822" s="8"/>
+      <c r="C822" s="8"/>
+    </row>
+    <row r="823" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A823" s="8" t="s">
+        <v>844</v>
+      </c>
+      <c r="B823" s="9" t="e">
+        <f>AVERAGE(C811:C821)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="C823" s="8" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(B823)</f>
+        <v>=AVERAGE(C811:C821)</v>
+      </c>
+    </row>
+    <row r="824" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A824" s="8" t="s">
+        <v>845</v>
+      </c>
+      <c r="B824" s="9">
+        <f>_xlfn.AGGREGATE(1,6,C811:C821)</f>
+        <v>25.625</v>
+      </c>
+      <c r="C824" s="8" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(B824)</f>
+        <v>=AGGREGATE(1,6,C811:C821)</v>
+      </c>
+    </row>
+    <row r="825" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A825" s="8" t="s">
+        <v>846</v>
+      </c>
+      <c r="B825" s="9">
+        <f>_xlfn.AGGREGATE(2,6,C811:C821)</f>
+        <v>8</v>
+      </c>
+      <c r="C825" s="8" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(B825)</f>
+        <v>=AGGREGATE(2,6,C811:C821)</v>
+      </c>
+    </row>
+    <row r="826" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A826" s="8"/>
     </row>
-    <row r="827" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A827" s="8"/>
-    </row>
-    <row r="828" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A828" s="8"/>
-    </row>
-    <row r="829" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="827" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A827" s="23" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="828" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A828" s="8" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="829" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A829" s="8"/>
     </row>
-    <row r="830" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A830" s="8"/>
-    </row>
-    <row r="831" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="830" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A830" s="8" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="831" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A831" s="8"/>
     </row>
-    <row r="832" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A832" s="8"/>
-    </row>
-    <row r="833" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A833" s="8"/>
-    </row>
-    <row r="834" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A834" s="8"/>
-    </row>
-    <row r="835" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="832" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A832" s="8" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="833" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A833" s="8" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="834" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A834" s="8" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="835" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A835" s="8"/>
     </row>
-    <row r="836" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A836" s="8"/>
-    </row>
-    <row r="837" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A837" s="8"/>
-    </row>
-    <row r="838" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="836" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A836" s="8" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="837" spans="1:5" ht="156" x14ac:dyDescent="0.3">
+      <c r="A837" s="8" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="838" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A838" s="8"/>
     </row>
-    <row r="839" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A839" s="8"/>
-    </row>
-    <row r="840" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A840" s="8"/>
-    </row>
-    <row r="841" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A841" s="8"/>
-    </row>
-    <row r="842" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A842" s="8"/>
-    </row>
-    <row r="843" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A843" s="8"/>
-    </row>
-    <row r="844" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A844" s="8"/>
-    </row>
-    <row r="845" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="839" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A839" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="B839" s="11" t="s">
+        <v>852</v>
+      </c>
+      <c r="C839" s="65" t="s">
+        <v>853</v>
+      </c>
+      <c r="D839" s="11" t="s">
+        <v>854</v>
+      </c>
+      <c r="E839" s="11" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="840" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A840" s="8" t="s">
+        <v>614</v>
+      </c>
+      <c r="B840" s="8">
+        <v>1200</v>
+      </c>
+      <c r="C840" s="66">
+        <v>1450</v>
+      </c>
+      <c r="D840" s="8" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E840" s="8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="841" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A841" s="8" t="s">
+        <v>615</v>
+      </c>
+      <c r="B841" s="8">
+        <v>850</v>
+      </c>
+      <c r="C841" s="66" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D841" s="8">
+        <v>920</v>
+      </c>
+      <c r="E841" s="8">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="842" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A842" s="8" t="s">
+        <v>617</v>
+      </c>
+      <c r="B842" s="8">
+        <v>2100</v>
+      </c>
+      <c r="C842" s="66">
+        <v>2300</v>
+      </c>
+      <c r="D842" s="8">
+        <v>2150</v>
+      </c>
+      <c r="E842" s="8" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="843" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A843" s="8" t="s">
+        <v>618</v>
+      </c>
+      <c r="B843" s="8">
+        <v>1500</v>
+      </c>
+      <c r="C843" s="66">
+        <v>1650</v>
+      </c>
+      <c r="D843" s="8">
+        <v>1800</v>
+      </c>
+      <c r="E843" s="8">
+        <v>1950</v>
+      </c>
+    </row>
+    <row r="844" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A844" s="8" t="s">
+        <v>620</v>
+      </c>
+      <c r="B844" s="8" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C844" s="66">
+        <v>780</v>
+      </c>
+      <c r="D844" s="8">
+        <v>850</v>
+      </c>
+      <c r="E844" s="8">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="845" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A845" s="8"/>
-    </row>
-    <row r="846" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A846" s="8"/>
-    </row>
-    <row r="847" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B845" s="8"/>
+      <c r="C845" s="8"/>
+      <c r="D845" s="8"/>
+      <c r="E845" s="8"/>
+    </row>
+    <row r="846" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A846" s="8" t="s">
+        <v>856</v>
+      </c>
+      <c r="B846" s="8"/>
+      <c r="C846" s="29">
+        <f>_xlfn.AGGREGATE(9,6,C840:C844)</f>
+        <v>6180</v>
+      </c>
+      <c r="D846" s="8"/>
+      <c r="E846" s="8"/>
+    </row>
+    <row r="847" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A847" s="8"/>
-    </row>
-    <row r="848" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B847" s="8"/>
+      <c r="C847" s="8" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(C846)</f>
+        <v>=AGGREGATE(9,6,C840:C844)</v>
+      </c>
+      <c r="D847" s="8"/>
+      <c r="E847" s="8"/>
+    </row>
+    <row r="848" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A848" s="8"/>
     </row>
     <row r="849" spans="1:1" x14ac:dyDescent="0.3">
@@ -11984,20 +12376,17 @@
     <row r="917" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A917" s="8"/>
     </row>
-    <row r="918" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A918" s="8"/>
-    </row>
-    <row r="919" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A919" s="8"/>
-    </row>
-    <row r="920" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A920" s="8"/>
-    </row>
-    <row r="921" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A921" s="8"/>
-    </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="E627:F627"/>
+    <mergeCell ref="B572:B574"/>
+    <mergeCell ref="B550:B552"/>
+    <mergeCell ref="B500:C500"/>
+    <mergeCell ref="C236:C237"/>
+    <mergeCell ref="B256:C256"/>
+    <mergeCell ref="C359:C360"/>
+    <mergeCell ref="C476:E476"/>
+    <mergeCell ref="C477:E477"/>
     <mergeCell ref="B756:C756"/>
     <mergeCell ref="B718:D718"/>
     <mergeCell ref="B742:D742"/>
@@ -12007,15 +12396,6 @@
     <mergeCell ref="B685:C685"/>
     <mergeCell ref="B700:C700"/>
     <mergeCell ref="B702:C702"/>
-    <mergeCell ref="E627:F627"/>
-    <mergeCell ref="B572:B574"/>
-    <mergeCell ref="B550:B552"/>
-    <mergeCell ref="B500:C500"/>
-    <mergeCell ref="C236:C237"/>
-    <mergeCell ref="B256:C256"/>
-    <mergeCell ref="C359:C360"/>
-    <mergeCell ref="C476:E476"/>
-    <mergeCell ref="C477:E477"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Daily Excel/Online Practice Excel.xlsx
+++ b/Daily Excel/Online Practice Excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d58d4d655bee1e81/Desktop/Github/Practice/Daily Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="28" documentId="8_{E0CD9693-A966-48B1-8504-D3B1BCEC178F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ABFEF476-50D9-4F15-A74A-938341DFF525}"/>
+  <xr:revisionPtr revIDLastSave="30" documentId="8_{E0CD9693-A966-48B1-8504-D3B1BCEC178F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C2448820-4AA0-4B7D-AEBF-733C1E04D9BE}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15175,9 +15175,9 @@
         <v>-245.5</v>
       </c>
       <c r="J1097" s="66"/>
-      <c r="K1097" s="28" t="e">
-        <f>VLOOKUP(ISNA(VLOOKUP(B1097,$H$1097:$H$1104,1,FALSE)),"Missing","Match")</f>
-        <v>#VALUE!</v>
+      <c r="K1097" s="28" t="str">
+        <f>IF(ISNA(VLOOKUP(B1097,G1097:G1103,1,FALSE)),"Missing","Match")</f>
+        <v>Match</v>
       </c>
     </row>
     <row r="1098" spans="1:11" x14ac:dyDescent="0.3">
@@ -15207,9 +15207,9 @@
         <v>3500</v>
       </c>
       <c r="J1098" s="66"/>
-      <c r="K1098" s="28" t="e">
-        <f t="shared" ref="K1098:K1104" si="33">VLOOKUP(ISNA(VLOOKUP(B1098,$H$1097:$H$1104,1,FALSE)),"Missing","Match")</f>
-        <v>#VALUE!</v>
+      <c r="K1098" s="28" t="str">
+        <f t="shared" ref="K1098:K1104" si="33">IF(ISNA(VLOOKUP(B1098,G1098:G1104,1,FALSE)),"Missing","Match")</f>
+        <v>Match</v>
       </c>
     </row>
     <row r="1099" spans="1:11" x14ac:dyDescent="0.3">
@@ -15239,9 +15239,9 @@
         <v>-2200</v>
       </c>
       <c r="J1099" s="66"/>
-      <c r="K1099" s="28" t="e">
+      <c r="K1099" s="28" t="str">
         <f t="shared" si="33"/>
-        <v>#VALUE!</v>
+        <v>Match</v>
       </c>
     </row>
     <row r="1100" spans="1:11" x14ac:dyDescent="0.3">
@@ -15271,9 +15271,9 @@
         <v>-4850</v>
       </c>
       <c r="J1100" s="66"/>
-      <c r="K1100" s="28" t="e">
+      <c r="K1100" s="28" t="str">
         <f t="shared" si="33"/>
-        <v>#VALUE!</v>
+        <v>Match</v>
       </c>
     </row>
     <row r="1101" spans="1:11" x14ac:dyDescent="0.3">
@@ -15303,9 +15303,9 @@
         <v>2500</v>
       </c>
       <c r="J1101" s="66"/>
-      <c r="K1101" s="28" t="e">
+      <c r="K1101" s="28" t="str">
         <f t="shared" si="33"/>
-        <v>#VALUE!</v>
+        <v>Missing</v>
       </c>
     </row>
     <row r="1102" spans="1:11" x14ac:dyDescent="0.3">
@@ -15335,9 +15335,9 @@
         <v>-680</v>
       </c>
       <c r="J1102" s="66"/>
-      <c r="K1102" s="28" t="e">
+      <c r="K1102" s="28" t="str">
         <f t="shared" si="33"/>
-        <v>#VALUE!</v>
+        <v>Match</v>
       </c>
     </row>
     <row r="1103" spans="1:11" x14ac:dyDescent="0.3">
@@ -15367,9 +15367,9 @@
         <v>-925</v>
       </c>
       <c r="J1103" s="66"/>
-      <c r="K1103" s="28" t="e">
+      <c r="K1103" s="28" t="str">
         <f t="shared" si="33"/>
-        <v>#VALUE!</v>
+        <v>Missing</v>
       </c>
     </row>
     <row r="1104" spans="1:11" x14ac:dyDescent="0.3">
@@ -15391,9 +15391,9 @@
       <c r="H1104" s="66"/>
       <c r="I1104" s="66"/>
       <c r="J1104" s="66"/>
-      <c r="K1104" s="28" t="e">
+      <c r="K1104" s="28" t="str">
         <f t="shared" si="33"/>
-        <v>#VALUE!</v>
+        <v>Missing</v>
       </c>
     </row>
     <row r="1105" spans="1:11" x14ac:dyDescent="0.3">
@@ -15420,9 +15420,12 @@
       <c r="F1106" s="66"/>
       <c r="G1106" s="66"/>
       <c r="H1106" s="66"/>
-      <c r="I1106" s="66"/>
-      <c r="J1106" s="66"/>
-      <c r="K1106" s="66"/>
+      <c r="I1106" s="68" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(K1097)</f>
+        <v>=IF(ISNA(VLOOKUP(B1097,G1097:G1103,1,FALSE)),"Missing","Match")</v>
+      </c>
+      <c r="J1106" s="68"/>
+      <c r="K1106" s="68"/>
     </row>
     <row r="1107" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1107" s="66" t="s">
@@ -15536,7 +15539,8 @@
       <c r="K1113" s="66"/>
     </row>
   </sheetData>
-  <mergeCells count="24">
+  <mergeCells count="25">
+    <mergeCell ref="I1106:K1106"/>
     <mergeCell ref="B684:C684"/>
     <mergeCell ref="B685:C685"/>
     <mergeCell ref="B700:C700"/>

--- a/Daily Excel/Online Practice Excel.xlsx
+++ b/Daily Excel/Online Practice Excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d58d4d655bee1e81/Desktop/Github/Practice/Daily Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="30" documentId="8_{E0CD9693-A966-48B1-8504-D3B1BCEC178F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C2448820-4AA0-4B7D-AEBF-733C1E04D9BE}"/>
+  <xr:revisionPtr revIDLastSave="34" documentId="8_{E0CD9693-A966-48B1-8504-D3B1BCEC178F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{680AB9DE-5BB3-475A-AB8C-1083CAFCAFFA}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15176,7 +15176,7 @@
       </c>
       <c r="J1097" s="66"/>
       <c r="K1097" s="28" t="str">
-        <f>IF(ISNA(VLOOKUP(B1097,G1097:G1103,1,FALSE)),"Missing","Match")</f>
+        <f>IF(ISNA(VLOOKUP(B1097,$G$1097:$G$1103,1,FALSE)),"Missing","Match")</f>
         <v>Match</v>
       </c>
     </row>
@@ -15208,7 +15208,7 @@
       </c>
       <c r="J1098" s="66"/>
       <c r="K1098" s="28" t="str">
-        <f t="shared" ref="K1098:K1104" si="33">IF(ISNA(VLOOKUP(B1098,G1098:G1104,1,FALSE)),"Missing","Match")</f>
+        <f t="shared" ref="K1098:K1104" si="33">IF(ISNA(VLOOKUP(B1098,$G$1097:$G$1103,1,FALSE)),"Missing","Match")</f>
         <v>Match</v>
       </c>
     </row>
@@ -15393,7 +15393,7 @@
       <c r="J1104" s="66"/>
       <c r="K1104" s="28" t="str">
         <f t="shared" si="33"/>
-        <v>Missing</v>
+        <v>Match</v>
       </c>
     </row>
     <row r="1105" spans="1:11" x14ac:dyDescent="0.3">
@@ -15422,7 +15422,7 @@
       <c r="H1106" s="66"/>
       <c r="I1106" s="68" t="str">
         <f ca="1">_xlfn.FORMULATEXT(K1097)</f>
-        <v>=IF(ISNA(VLOOKUP(B1097,G1097:G1103,1,FALSE)),"Missing","Match")</v>
+        <v>=IF(ISNA(VLOOKUP(B1097,$G$1097:$G$1103,1,FALSE)),"Missing","Match")</v>
       </c>
       <c r="J1106" s="68"/>
       <c r="K1106" s="68"/>
@@ -15487,8 +15487,8 @@
       </c>
       <c r="B1110" s="66"/>
       <c r="C1110" s="28">
-        <f ca="1">SUMIF(D1097:D1104,"Missing",K1098)</f>
-        <v>0</v>
+        <f>SUMIF(K1097:K1104,"Missing",D1097:D1104)</f>
+        <v>1840</v>
       </c>
       <c r="D1110" s="66"/>
       <c r="E1110" s="66"/>

--- a/Daily Excel/Online Practice Excel.xlsx
+++ b/Daily Excel/Online Practice Excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d58d4d655bee1e81/Desktop/Github/Practice/Daily Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="34" documentId="8_{E0CD9693-A966-48B1-8504-D3B1BCEC178F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{680AB9DE-5BB3-475A-AB8C-1083CAFCAFFA}"/>
+  <xr:revisionPtr revIDLastSave="44" documentId="8_{E0CD9693-A966-48B1-8504-D3B1BCEC178F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F6A971C9-1487-481C-9BDD-3B66807D450F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1470" uniqueCount="1090">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1525" uniqueCount="1132">
   <si>
     <t>Double-click on cell A1 in the spreadsheet editor. Replace the placeholder text with:</t>
   </si>
@@ -3720,6 +3720,132 @@
   <si>
     <t>Items in bank not in books:</t>
   </si>
+  <si>
+    <t>Basic SUM</t>
+  </si>
+  <si>
+    <t>When you build a simple report in Excel, one of the most common tasks is adding up a list of numbers to get a total. The SUM function is built for exactly that.</t>
+  </si>
+  <si>
+    <t>What you need to do</t>
+  </si>
+  <si>
+    <t>Total revenue</t>
+  </si>
+  <si>
+    <t>In this sheet, you have monthly revenue figures in column B.</t>
+  </si>
+  <si>
+    <t>1. Click cell B9.</t>
+  </si>
+  <si>
+    <t>2. Type a SUM formula that adds the revenue values in cells B2 through B7.</t>
+  </si>
+  <si>
+    <t>When you’re done, cell B9 should show the total revenue for January through June.</t>
+  </si>
+  <si>
+    <t>Calculate Average Sales</t>
+  </si>
+  <si>
+    <t>In sales analysis, knowing your average order value helps you understand customer spending patterns and set realistic targets.</t>
+  </si>
+  <si>
+    <t>The AVERAGE function calculates the arithmetic mean of a set of numbers. It adds up all the values and divides by how many there are.</t>
+  </si>
+  <si>
+    <t>This will calculate the average of all values in the range B1 through B5.</t>
+  </si>
+  <si>
+    <t>You have a list of recent sales transactions with their order values in cells B2 through B7.</t>
+  </si>
+  <si>
+    <t>Use the AVERAGE function in cell B9 to calculate the average order value across all six transactions.</t>
+  </si>
+  <si>
+    <t>Order Value</t>
+  </si>
+  <si>
+    <t>ORD-101</t>
+  </si>
+  <si>
+    <t>ORD-102</t>
+  </si>
+  <si>
+    <t>ORD-103</t>
+  </si>
+  <si>
+    <t>ORD-104</t>
+  </si>
+  <si>
+    <t>ORD-105</t>
+  </si>
+  <si>
+    <t>ORD-106</t>
+  </si>
+  <si>
+    <t>Average order value:</t>
+  </si>
+  <si>
+    <t>Break-even units</t>
+  </si>
+  <si>
+    <t>Break-even analysis is a cornerstone of financial planning. It tells you exactly how many units you need to sell before your business starts making a profit.</t>
+  </si>
+  <si>
+    <t>At the break-even point, total revenue equals total costs. You're not making money, but you're not losing it either. Every unit sold beyond this point generates profit.</t>
+  </si>
+  <si>
+    <t>Key concepts:</t>
+  </si>
+  <si>
+    <t>The contribution margin represents how much each unit sold contributes toward covering fixed costs. Once you've covered all fixed costs, each additional unit's contribution margin becomes profit.</t>
+  </si>
+  <si>
+    <t>You're analyzing the break-even point for Widget Pro. The spreadsheet shows:</t>
+  </si>
+  <si>
+    <t>Selling price per unit (B5)</t>
+  </si>
+  <si>
+    <t>Variable cost per unit (B6)</t>
+  </si>
+  <si>
+    <t>Monthly fixed costs (B8)</t>
+  </si>
+  <si>
+    <t>Complete the analysis by:</t>
+  </si>
+  <si>
+    <t>Contribution Margin per Unit = Selling Price - Variable Cost per Unit</t>
+  </si>
+  <si>
+    <t>Break-even Units = Fixed Costs ÷ Contribution Margin per Unit</t>
+  </si>
+  <si>
+    <t>1. Calculate the contribution margin per unit in cell B10</t>
+  </si>
+  <si>
+    <t>2. Calculate the break-even units in cell B11</t>
+  </si>
+  <si>
+    <t>Product:</t>
+  </si>
+  <si>
+    <t>Widget Pro</t>
+  </si>
+  <si>
+    <t>Selling price per unit</t>
+  </si>
+  <si>
+    <t>Variable cost per unit</t>
+  </si>
+  <si>
+    <t>Fixed costs (monthly)</t>
+  </si>
+  <si>
+    <t>Contribution margin per unit</t>
+  </si>
 </sst>
 </file>
 
@@ -3729,7 +3855,7 @@
     <numFmt numFmtId="164" formatCode="&quot;₹&quot;\ #,##0.00"/>
     <numFmt numFmtId="165" formatCode="0.0000000000E+00"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3795,6 +3921,12 @@
       <name val="Calibri Light"/>
       <family val="2"/>
       <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="32">
@@ -3997,7 +4129,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -4219,11 +4351,23 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="30" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4509,7 +4653,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W1113"/>
+  <dimension ref="A1:W1184"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="149.88671875" style="3" bestFit="1" customWidth="1"/>
@@ -15099,14 +15243,14 @@
       </c>
     </row>
     <row r="1095" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1095" s="75" t="s">
+      <c r="A1095" s="76" t="s">
         <v>1065</v>
       </c>
       <c r="B1095" s="66"/>
       <c r="C1095" s="66"/>
       <c r="D1095" s="66"/>
       <c r="E1095" s="66"/>
-      <c r="F1095" s="76" t="s">
+      <c r="F1095" s="77" t="s">
         <v>1066</v>
       </c>
       <c r="G1095" s="66"/>
@@ -15513,7 +15657,9 @@
       <c r="K1111" s="66"/>
     </row>
     <row r="1112" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1112" s="66"/>
+      <c r="A1112" s="22" t="s">
+        <v>1090</v>
+      </c>
       <c r="B1112" s="66"/>
       <c r="C1112" s="66"/>
       <c r="D1112" s="66"/>
@@ -15526,7 +15672,9 @@
       <c r="K1112" s="66"/>
     </row>
     <row r="1113" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1113" s="66"/>
+      <c r="A1113" s="66" t="s">
+        <v>1091</v>
+      </c>
       <c r="B1113" s="66"/>
       <c r="C1113" s="66"/>
       <c r="D1113" s="66"/>
@@ -15537,6 +15685,462 @@
       <c r="I1113" s="66"/>
       <c r="J1113" s="66"/>
       <c r="K1113" s="66"/>
+    </row>
+    <row r="1114" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1114" s="66" t="s">
+        <v>1094</v>
+      </c>
+      <c r="B1114" s="66"/>
+      <c r="C1114" s="66"/>
+    </row>
+    <row r="1115" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1115" s="66" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B1115" s="66"/>
+      <c r="C1115" s="66"/>
+    </row>
+    <row r="1116" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1116" s="66" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B1116" s="66"/>
+      <c r="C1116" s="66"/>
+    </row>
+    <row r="1117" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1117" s="66" t="s">
+        <v>1096</v>
+      </c>
+      <c r="B1117" s="66"/>
+      <c r="C1117" s="66"/>
+    </row>
+    <row r="1118" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1118" s="66" t="s">
+        <v>954</v>
+      </c>
+      <c r="B1118" s="66"/>
+      <c r="C1118" s="66"/>
+    </row>
+    <row r="1119" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1119" s="66" t="s">
+        <v>1097</v>
+      </c>
+      <c r="B1119" s="66"/>
+      <c r="C1119" s="66"/>
+    </row>
+    <row r="1120" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1120" s="66"/>
+      <c r="B1120" s="66"/>
+      <c r="C1120" s="66"/>
+    </row>
+    <row r="1121" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1121" s="66" t="s">
+        <v>73</v>
+      </c>
+      <c r="B1121" s="66" t="s">
+        <v>1000</v>
+      </c>
+      <c r="C1121" s="66"/>
+    </row>
+    <row r="1122" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1122" s="66" t="s">
+        <v>75</v>
+      </c>
+      <c r="B1122" s="66">
+        <v>18200</v>
+      </c>
+      <c r="C1122" s="66"/>
+    </row>
+    <row r="1123" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1123" s="66" t="s">
+        <v>76</v>
+      </c>
+      <c r="B1123" s="66">
+        <v>16500</v>
+      </c>
+      <c r="C1123" s="66"/>
+    </row>
+    <row r="1124" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1124" s="66" t="s">
+        <v>77</v>
+      </c>
+      <c r="B1124" s="66">
+        <v>19350</v>
+      </c>
+      <c r="C1124" s="66"/>
+    </row>
+    <row r="1125" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1125" s="66" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1125" s="66">
+        <v>21000</v>
+      </c>
+      <c r="C1125" s="66"/>
+    </row>
+    <row r="1126" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1126" s="66" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1126" s="66">
+        <v>19800</v>
+      </c>
+      <c r="C1126" s="66"/>
+    </row>
+    <row r="1127" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1127" s="66" t="s">
+        <v>80</v>
+      </c>
+      <c r="B1127" s="66">
+        <v>22500</v>
+      </c>
+      <c r="C1127" s="66"/>
+    </row>
+    <row r="1128" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1128" s="66"/>
+      <c r="B1128" s="66"/>
+      <c r="C1128" s="66"/>
+    </row>
+    <row r="1129" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1129" s="66" t="s">
+        <v>1093</v>
+      </c>
+      <c r="B1129" s="8">
+        <f>SUM(B1122:B1127)</f>
+        <v>117350</v>
+      </c>
+      <c r="C1129" s="66"/>
+    </row>
+    <row r="1130" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1130" s="66"/>
+      <c r="B1130" s="66"/>
+      <c r="C1130" s="66"/>
+    </row>
+    <row r="1131" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1131" s="22" t="s">
+        <v>1098</v>
+      </c>
+      <c r="B1131" s="66"/>
+      <c r="C1131" s="66"/>
+    </row>
+    <row r="1132" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1132" s="66" t="s">
+        <v>1099</v>
+      </c>
+      <c r="B1132" s="66"/>
+    </row>
+    <row r="1133" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1133" s="66" t="s">
+        <v>1100</v>
+      </c>
+      <c r="B1133" s="66"/>
+    </row>
+    <row r="1134" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1134" s="66" t="s">
+        <v>1101</v>
+      </c>
+      <c r="B1134" s="66"/>
+    </row>
+    <row r="1135" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1135" s="66" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B1135" s="66"/>
+    </row>
+    <row r="1136" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1136" s="66" t="s">
+        <v>1102</v>
+      </c>
+      <c r="B1136" s="66"/>
+    </row>
+    <row r="1137" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1137" s="66" t="s">
+        <v>1103</v>
+      </c>
+      <c r="B1137" s="66"/>
+    </row>
+    <row r="1138" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1138" s="66"/>
+      <c r="B1138" s="66"/>
+    </row>
+    <row r="1139" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1139" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="B1139" s="10" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="1140" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1140" s="66" t="s">
+        <v>1105</v>
+      </c>
+      <c r="B1140" s="66">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="1141" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1141" s="66" t="s">
+        <v>1106</v>
+      </c>
+      <c r="B1141" s="66">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="1142" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1142" s="66" t="s">
+        <v>1107</v>
+      </c>
+      <c r="B1142" s="66">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="1143" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1143" s="66" t="s">
+        <v>1108</v>
+      </c>
+      <c r="B1143" s="66">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="1144" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1144" s="66" t="s">
+        <v>1109</v>
+      </c>
+      <c r="B1144" s="66">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="1145" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1145" s="66" t="s">
+        <v>1110</v>
+      </c>
+      <c r="B1145" s="66">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="1146" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1146" s="66"/>
+      <c r="B1146" s="66"/>
+    </row>
+    <row r="1147" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1147" s="66" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B1147" s="8">
+        <f>AVERAGE(B1140:B1145)</f>
+        <v>112.5</v>
+      </c>
+    </row>
+    <row r="1149" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1149" s="22" t="s">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="1150" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1150" s="66" t="s">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="1151" spans="1:2" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A1151" s="66" t="s">
+        <v>1114</v>
+      </c>
+    </row>
+    <row r="1152" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1152" s="66" t="s">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="1153" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1153" s="80" t="s">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="1154" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1154" s="80" t="s">
+        <v>1123</v>
+      </c>
+    </row>
+    <row r="1155" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A1155" s="66" t="s">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="1156" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1156" s="66" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="1157" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1157" s="66" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="1158" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1158" s="30" t="s">
+        <v>1118</v>
+      </c>
+    </row>
+    <row r="1159" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1159" s="30" t="s">
+        <v>1119</v>
+      </c>
+    </row>
+    <row r="1160" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1160" s="30" t="s">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="1161" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1161" s="66" t="s">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="1162" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1162" s="30" t="s">
+        <v>1124</v>
+      </c>
+      <c r="B1162" s="30"/>
+      <c r="C1162" s="30"/>
+    </row>
+    <row r="1163" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1163" s="30" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B1163" s="30"/>
+      <c r="C1163" s="30"/>
+    </row>
+    <row r="1164" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1164" s="30"/>
+      <c r="B1164" s="30"/>
+      <c r="C1164" s="30"/>
+    </row>
+    <row r="1165" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1165" s="30" t="s">
+        <v>1126</v>
+      </c>
+      <c r="B1165" s="30" t="s">
+        <v>1127</v>
+      </c>
+      <c r="C1165" s="30"/>
+    </row>
+    <row r="1166" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1166" s="30"/>
+      <c r="B1166" s="30"/>
+      <c r="C1166" s="30"/>
+    </row>
+    <row r="1167" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1167" s="30" t="s">
+        <v>1128</v>
+      </c>
+      <c r="B1167" s="30">
+        <v>75</v>
+      </c>
+      <c r="C1167" s="30"/>
+    </row>
+    <row r="1168" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1168" s="30" t="s">
+        <v>1129</v>
+      </c>
+      <c r="B1168" s="30">
+        <v>45</v>
+      </c>
+      <c r="C1168" s="30"/>
+    </row>
+    <row r="1169" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1169" s="30"/>
+      <c r="B1169" s="30"/>
+      <c r="C1169" s="30"/>
+    </row>
+    <row r="1170" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1170" s="30" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B1170" s="79">
+        <v>24000</v>
+      </c>
+      <c r="C1170" s="30"/>
+    </row>
+    <row r="1171" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1171" s="30"/>
+      <c r="B1171" s="75"/>
+      <c r="C1171" s="30"/>
+    </row>
+    <row r="1172" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1172" s="30" t="s">
+        <v>1131</v>
+      </c>
+      <c r="B1172" s="78">
+        <f>B1167-B1168</f>
+        <v>30</v>
+      </c>
+      <c r="C1172" s="30"/>
+    </row>
+    <row r="1173" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1173" s="30" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B1173" s="78">
+        <f>B1170/B1172</f>
+        <v>800</v>
+      </c>
+      <c r="C1173" s="30"/>
+    </row>
+    <row r="1174" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1174" s="30"/>
+      <c r="B1174" s="30"/>
+      <c r="C1174" s="30"/>
+    </row>
+    <row r="1175" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1175" s="30"/>
+      <c r="B1175" s="30"/>
+      <c r="C1175" s="30"/>
+    </row>
+    <row r="1176" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1176" s="30"/>
+      <c r="B1176" s="30"/>
+      <c r="C1176" s="30"/>
+    </row>
+    <row r="1177" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1177" s="30"/>
+      <c r="B1177" s="30"/>
+      <c r="C1177" s="30"/>
+    </row>
+    <row r="1178" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1178" s="30"/>
+      <c r="B1178" s="30"/>
+      <c r="C1178" s="30"/>
+    </row>
+    <row r="1179" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1179" s="30"/>
+      <c r="B1179" s="30"/>
+      <c r="C1179" s="30"/>
+    </row>
+    <row r="1180" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1180" s="30"/>
+      <c r="B1180" s="30"/>
+      <c r="C1180" s="30"/>
+    </row>
+    <row r="1181" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1181" s="30"/>
+      <c r="B1181" s="30"/>
+      <c r="C1181" s="30"/>
+    </row>
+    <row r="1182" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1182" s="30"/>
+      <c r="B1182" s="30"/>
+      <c r="C1182" s="30"/>
+    </row>
+    <row r="1183" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1183" s="30"/>
+      <c r="B1183" s="30"/>
+      <c r="C1183" s="30"/>
+    </row>
+    <row r="1184" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1184" s="30"/>
+      <c r="B1184" s="30"/>
+      <c r="C1184" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="25">
